--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -5354,13 +5354,13 @@
         <v>31.42</v>
       </c>
       <c r="E58" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0018</v>
       </c>
       <c r="H58" t="n">
         <v>0.28</v>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5434,19 +5434,19 @@
         <v>31.14</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>31.39</v>
+        <v>31.37</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>31.49</v>
+        <v>31.48</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>31.59</v>
+        <v>31.58</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>31.77</v>
+        <v>31.75</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>31.94</v>
+        <v>31.92</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>31.97</v>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -641,144 +641,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.85</v>
+        <v>29.99</v>
       </c>
       <c r="C2" t="n">
-        <v>30.09</v>
+        <v>30.93</v>
       </c>
       <c r="D2" t="n">
-        <v>29.83</v>
+        <v>29.96</v>
       </c>
       <c r="E2" t="n">
-        <v>30.02</v>
+        <v>30.37</v>
       </c>
       <c r="F2" t="n">
-        <v>0.13</v>
+        <v>0.35</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0117</v>
       </c>
       <c r="H2" t="n">
-        <v>0.26</v>
+        <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>29.89</v>
+        <v>29.58</v>
       </c>
       <c r="J2" t="n">
-        <v>29.89</v>
+        <v>29.79</v>
       </c>
       <c r="K2" t="n">
         <v>29.89</v>
       </c>
       <c r="L2" t="n">
-        <v>29.89</v>
+        <v>29.99</v>
       </c>
       <c r="M2" t="n">
-        <v>29.89</v>
+        <v>30.15</v>
       </c>
       <c r="N2" t="n">
-        <v>29.89</v>
+        <v>30.3</v>
       </c>
       <c r="O2" t="n">
-        <v>29.89</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>30.35</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29.99</v>
+        <v>30.37</v>
       </c>
       <c r="C3" t="n">
-        <v>30.93</v>
+        <v>30.65</v>
       </c>
       <c r="D3" t="n">
-        <v>29.96</v>
+        <v>30.37</v>
       </c>
       <c r="E3" t="n">
-        <v>30.37</v>
+        <v>30.56</v>
       </c>
       <c r="F3" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0065</v>
       </c>
       <c r="H3" t="n">
-        <v>0.97</v>
+        <v>0.28</v>
       </c>
       <c r="I3" t="n">
-        <v>29.58</v>
+        <v>28.99</v>
       </c>
       <c r="J3" t="n">
-        <v>29.79</v>
+        <v>29.36</v>
       </c>
       <c r="K3" t="n">
-        <v>29.89</v>
+        <v>29.88</v>
       </c>
       <c r="L3" t="n">
-        <v>29.99</v>
+        <v>30.41</v>
       </c>
       <c r="M3" t="n">
-        <v>30.15</v>
+        <v>30.85</v>
       </c>
       <c r="N3" t="n">
-        <v>30.3</v>
+        <v>31.3</v>
       </c>
       <c r="O3" t="n">
-        <v>30.35</v>
+        <v>31.9</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -791,78 +781,76 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.37</v>
+        <v>30.56</v>
       </c>
       <c r="C4" t="n">
-        <v>30.65</v>
+        <v>30.8</v>
       </c>
       <c r="D4" t="n">
-        <v>30.37</v>
+        <v>30.32</v>
       </c>
       <c r="E4" t="n">
-        <v>30.56</v>
+        <v>30.53</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0012</v>
       </c>
       <c r="H4" t="n">
-        <v>0.28</v>
+        <v>0.47</v>
       </c>
       <c r="I4" t="n">
-        <v>28.99</v>
+        <v>30.09</v>
       </c>
       <c r="J4" t="n">
-        <v>29.36</v>
+        <v>30.31</v>
       </c>
       <c r="K4" t="n">
-        <v>29.88</v>
+        <v>30.42</v>
       </c>
       <c r="L4" t="n">
-        <v>30.41</v>
+        <v>30.54</v>
       </c>
       <c r="M4" t="n">
-        <v>30.85</v>
+        <v>30.7</v>
       </c>
       <c r="N4" t="n">
-        <v>31.3</v>
+        <v>30.87</v>
       </c>
       <c r="O4" t="n">
-        <v>31.9</v>
+        <v>30.93</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -870,16 +858,20 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -894,57 +886,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.56</v>
+        <v>30.48</v>
       </c>
       <c r="C5" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="D5" t="n">
-        <v>30.32</v>
+        <v>30.18</v>
       </c>
       <c r="E5" t="n">
-        <v>30.53</v>
+        <v>30.28</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.04</v>
+        <v>-0.24</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.008</v>
       </c>
       <c r="H5" t="n">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
       <c r="I5" t="n">
-        <v>30.09</v>
+        <v>29.85</v>
       </c>
       <c r="J5" t="n">
-        <v>30.31</v>
+        <v>30.04</v>
       </c>
       <c r="K5" t="n">
-        <v>30.42</v>
+        <v>30.29</v>
       </c>
       <c r="L5" t="n">
         <v>30.54</v>
       </c>
       <c r="M5" t="n">
-        <v>30.7</v>
+        <v>30.77</v>
       </c>
       <c r="N5" t="n">
-        <v>30.87</v>
+        <v>30.99</v>
       </c>
       <c r="O5" t="n">
-        <v>30.93</v>
+        <v>31.27</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -954,18 +946,16 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -980,57 +970,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.48</v>
+        <v>30.28</v>
       </c>
       <c r="C6" t="n">
-        <v>30.5</v>
+        <v>30.33</v>
       </c>
       <c r="D6" t="n">
-        <v>30.18</v>
+        <v>29.94</v>
       </c>
       <c r="E6" t="n">
-        <v>30.28</v>
+        <v>30.11</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0058</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>29.85</v>
+        <v>29.86</v>
       </c>
       <c r="J6" t="n">
-        <v>30.04</v>
+        <v>29.93</v>
       </c>
       <c r="K6" t="n">
-        <v>30.29</v>
+        <v>30.12</v>
       </c>
       <c r="L6" t="n">
-        <v>30.54</v>
+        <v>30.31</v>
       </c>
       <c r="M6" t="n">
-        <v>30.77</v>
+        <v>30.45</v>
       </c>
       <c r="N6" t="n">
-        <v>30.99</v>
+        <v>30.58</v>
       </c>
       <c r="O6" t="n">
-        <v>31.27</v>
+        <v>30.83</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1071,50 +1061,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.28</v>
+        <v>30.22</v>
       </c>
       <c r="C7" t="n">
-        <v>30.33</v>
+        <v>30.59</v>
       </c>
       <c r="D7" t="n">
-        <v>29.94</v>
+        <v>30.15</v>
       </c>
       <c r="E7" t="n">
-        <v>30.11</v>
+        <v>30.44</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.17</v>
+        <v>0.33</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0111</v>
       </c>
       <c r="H7" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="I7" t="n">
-        <v>29.86</v>
+        <v>29.56</v>
       </c>
       <c r="J7" t="n">
-        <v>29.93</v>
+        <v>29.71</v>
       </c>
       <c r="K7" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="L7" t="n">
         <v>30.12</v>
       </c>
-      <c r="L7" t="n">
-        <v>30.31</v>
-      </c>
       <c r="M7" t="n">
-        <v>30.45</v>
+        <v>30.3</v>
       </c>
       <c r="N7" t="n">
-        <v>30.58</v>
+        <v>30.48</v>
       </c>
       <c r="O7" t="n">
-        <v>30.83</v>
+        <v>30.71</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1122,22 +1112,24 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1146,59 +1138,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="C8" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="K8" t="n">
         <v>30.22</v>
       </c>
-      <c r="C8" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="D8" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="E8" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I8" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="J8" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="K8" t="n">
-        <v>29.92</v>
-      </c>
       <c r="L8" t="n">
-        <v>30.12</v>
+        <v>30.41</v>
       </c>
       <c r="M8" t="n">
-        <v>30.3</v>
+        <v>30.66</v>
       </c>
       <c r="N8" t="n">
-        <v>30.48</v>
+        <v>30.92</v>
       </c>
       <c r="O8" t="n">
-        <v>30.71</v>
+        <v>31.03</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1211,18 +1199,14 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1232,55 +1216,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.44</v>
+        <v>30.42</v>
       </c>
       <c r="C9" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="E9" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="K9" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="L9" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="M9" t="n">
         <v>30.53</v>
       </c>
-      <c r="D9" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="E9" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="J9" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="K9" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="L9" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="M9" t="n">
-        <v>30.66</v>
-      </c>
       <c r="N9" t="n">
-        <v>30.92</v>
+        <v>30.63</v>
       </c>
       <c r="O9" t="n">
-        <v>31.03</v>
+        <v>30.73</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1288,22 +1276,30 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1312,57 +1308,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.42</v>
+        <v>30.67</v>
       </c>
       <c r="C10" t="n">
-        <v>30.71</v>
+        <v>30.8</v>
       </c>
       <c r="D10" t="n">
-        <v>30.24</v>
+        <v>30.48</v>
       </c>
       <c r="E10" t="n">
-        <v>30.71</v>
+        <v>30.62</v>
       </c>
       <c r="F10" t="n">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.0027</v>
       </c>
       <c r="H10" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="I10" t="n">
-        <v>30.14</v>
+        <v>29.78</v>
       </c>
       <c r="J10" t="n">
-        <v>30.24</v>
+        <v>30.36</v>
       </c>
       <c r="K10" t="n">
-        <v>30.34</v>
+        <v>30.47</v>
       </c>
       <c r="L10" t="n">
-        <v>30.43</v>
+        <v>30.59</v>
       </c>
       <c r="M10" t="n">
-        <v>30.53</v>
+        <v>30.94</v>
       </c>
       <c r="N10" t="n">
-        <v>30.63</v>
+        <v>31.28</v>
       </c>
       <c r="O10" t="n">
-        <v>30.73</v>
+        <v>31.17</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1370,30 +1366,22 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1409,50 +1397,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="C11" t="n">
-        <v>30.8</v>
+        <v>30.85</v>
       </c>
       <c r="D11" t="n">
-        <v>30.48</v>
+        <v>30.53</v>
       </c>
       <c r="E11" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08</v>
+        <v>0.21</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0069</v>
       </c>
       <c r="H11" t="n">
         <v>0.32</v>
       </c>
       <c r="I11" t="n">
-        <v>29.78</v>
+        <v>30.16</v>
       </c>
       <c r="J11" t="n">
-        <v>30.36</v>
+        <v>30.29</v>
       </c>
       <c r="K11" t="n">
-        <v>30.47</v>
+        <v>30.46</v>
       </c>
       <c r="L11" t="n">
-        <v>30.59</v>
+        <v>30.63</v>
       </c>
       <c r="M11" t="n">
-        <v>30.94</v>
+        <v>30.78</v>
       </c>
       <c r="N11" t="n">
-        <v>31.28</v>
+        <v>30.93</v>
       </c>
       <c r="O11" t="n">
-        <v>31.17</v>
+        <v>31.12</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1465,11 +1453,13 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1482,78 +1472,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="C12" t="n">
-        <v>30.85</v>
+        <v>30.83</v>
       </c>
       <c r="D12" t="n">
-        <v>30.53</v>
+        <v>30.52</v>
       </c>
       <c r="E12" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="F12" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0017</v>
       </c>
       <c r="H12" t="n">
         <v>0.32</v>
       </c>
       <c r="I12" t="n">
-        <v>30.16</v>
+        <v>30.2</v>
       </c>
       <c r="J12" t="n">
-        <v>30.29</v>
+        <v>30.58</v>
       </c>
       <c r="K12" t="n">
-        <v>30.46</v>
+        <v>30.67</v>
       </c>
       <c r="L12" t="n">
-        <v>30.63</v>
+        <v>30.76</v>
       </c>
       <c r="M12" t="n">
-        <v>30.78</v>
+        <v>31</v>
       </c>
       <c r="N12" t="n">
-        <v>30.93</v>
+        <v>31.23</v>
       </c>
       <c r="O12" t="n">
-        <v>31.12</v>
+        <v>31.18</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1566,76 +1554,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="C13" t="n">
-        <v>30.83</v>
+        <v>31.01</v>
       </c>
       <c r="D13" t="n">
-        <v>30.52</v>
+        <v>30.76</v>
       </c>
       <c r="E13" t="n">
-        <v>30.78</v>
+        <v>30.97</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.05</v>
+        <v>0.19</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.006</v>
       </c>
       <c r="H13" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="I13" t="n">
         <v>30.2</v>
       </c>
       <c r="J13" t="n">
-        <v>30.58</v>
+        <v>30.52</v>
       </c>
       <c r="K13" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="L13" t="n">
-        <v>30.76</v>
+        <v>30.73</v>
       </c>
       <c r="M13" t="n">
-        <v>31</v>
+        <v>30.94</v>
       </c>
       <c r="N13" t="n">
-        <v>31.23</v>
+        <v>31.15</v>
       </c>
       <c r="O13" t="n">
-        <v>31.18</v>
+        <v>31.15</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1648,77 +1638,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.78</v>
+        <v>30.96</v>
       </c>
       <c r="C14" t="n">
-        <v>31.01</v>
+        <v>31.18</v>
       </c>
       <c r="D14" t="n">
-        <v>30.76</v>
+        <v>30.36</v>
       </c>
       <c r="E14" t="n">
-        <v>30.97</v>
+        <v>30.55</v>
       </c>
       <c r="F14" t="n">
-        <v>0.19</v>
+        <v>-0.41</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.0133</v>
       </c>
       <c r="H14" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="I14" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="J14" t="n">
-        <v>30.52</v>
+        <v>30.75</v>
       </c>
       <c r="K14" t="n">
-        <v>30.62</v>
+        <v>30.84</v>
       </c>
       <c r="L14" t="n">
-        <v>30.73</v>
+        <v>30.93</v>
       </c>
       <c r="M14" t="n">
-        <v>30.94</v>
+        <v>31.09</v>
       </c>
       <c r="N14" t="n">
-        <v>31.15</v>
+        <v>31.26</v>
       </c>
       <c r="O14" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>31.26</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U14" s="8" t="n">
@@ -1727,174 +1719,170 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30.96</v>
+        <v>30.62</v>
       </c>
       <c r="C15" t="n">
-        <v>31.18</v>
+        <v>31.44</v>
       </c>
       <c r="D15" t="n">
-        <v>30.36</v>
+        <v>30.62</v>
       </c>
       <c r="E15" t="n">
-        <v>30.55</v>
+        <v>31.34</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.41</v>
+        <v>0.78</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0257</v>
       </c>
       <c r="H15" t="n">
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>30.5</v>
+        <v>29.54</v>
       </c>
       <c r="J15" t="n">
-        <v>30.75</v>
+        <v>29.63</v>
       </c>
       <c r="K15" t="n">
-        <v>30.84</v>
+        <v>30.15</v>
       </c>
       <c r="L15" t="n">
-        <v>30.93</v>
+        <v>30.66</v>
       </c>
       <c r="M15" t="n">
-        <v>31.09</v>
+        <v>30.96</v>
       </c>
       <c r="N15" t="n">
-        <v>31.26</v>
+        <v>31.27</v>
       </c>
       <c r="O15" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30.62</v>
+        <v>31.34</v>
       </c>
       <c r="C16" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="D16" t="n">
-        <v>30.62</v>
+        <v>30.65</v>
       </c>
       <c r="E16" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="F16" t="n">
-        <v>0.78</v>
+        <v>0.04</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0012</v>
       </c>
       <c r="H16" t="n">
         <v>0.82</v>
       </c>
       <c r="I16" t="n">
-        <v>29.54</v>
+        <v>29.81</v>
       </c>
       <c r="J16" t="n">
-        <v>29.63</v>
+        <v>30.67</v>
       </c>
       <c r="K16" t="n">
-        <v>30.15</v>
+        <v>30.93</v>
       </c>
       <c r="L16" t="n">
-        <v>30.66</v>
+        <v>31.19</v>
       </c>
       <c r="M16" t="n">
-        <v>30.96</v>
+        <v>31.75</v>
       </c>
       <c r="N16" t="n">
-        <v>31.27</v>
+        <v>32.31</v>
       </c>
       <c r="O16" t="n">
-        <v>32</v>
+        <v>32.26</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1909,63 +1897,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="C17" t="n">
-        <v>31.47</v>
+        <v>31.46</v>
       </c>
       <c r="D17" t="n">
-        <v>30.65</v>
+        <v>31.17</v>
       </c>
       <c r="E17" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0033</v>
       </c>
       <c r="H17" t="n">
-        <v>0.82</v>
+        <v>0.29</v>
       </c>
       <c r="I17" t="n">
-        <v>29.81</v>
+        <v>29.83</v>
       </c>
       <c r="J17" t="n">
-        <v>30.67</v>
+        <v>30.71</v>
       </c>
       <c r="K17" t="n">
-        <v>30.93</v>
+        <v>30.97</v>
       </c>
       <c r="L17" t="n">
-        <v>31.19</v>
+        <v>31.22</v>
       </c>
       <c r="M17" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="N17" t="n">
-        <v>32.31</v>
+        <v>32.36</v>
       </c>
       <c r="O17" t="n">
-        <v>32.26</v>
+        <v>32.3</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
@@ -1986,55 +1970,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="C18" t="n">
-        <v>31.46</v>
+        <v>31.32</v>
       </c>
       <c r="D18" t="n">
-        <v>31.17</v>
+        <v>31.08</v>
       </c>
       <c r="E18" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0015</v>
       </c>
       <c r="H18" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I18" t="n">
-        <v>29.83</v>
+        <v>30.88</v>
       </c>
       <c r="J18" t="n">
-        <v>30.71</v>
+        <v>30.96</v>
       </c>
       <c r="K18" t="n">
-        <v>30.97</v>
+        <v>31.13</v>
       </c>
       <c r="L18" t="n">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="M18" t="n">
-        <v>31.79</v>
+        <v>31.42</v>
       </c>
       <c r="N18" t="n">
-        <v>32.36</v>
+        <v>31.54</v>
       </c>
       <c r="O18" t="n">
-        <v>32.3</v>
+        <v>31.75</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2042,8 +2030,10 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
@@ -2073,50 +2063,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="C19" t="n">
-        <v>31.32</v>
+        <v>31.63</v>
       </c>
       <c r="D19" t="n">
-        <v>31.08</v>
+        <v>31.24</v>
       </c>
       <c r="E19" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0059</v>
       </c>
       <c r="H19" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="I19" t="n">
-        <v>30.88</v>
+        <v>30.83</v>
       </c>
       <c r="J19" t="n">
-        <v>30.96</v>
+        <v>31.14</v>
       </c>
       <c r="K19" t="n">
-        <v>31.13</v>
+        <v>31.2</v>
       </c>
       <c r="L19" t="n">
-        <v>31.3</v>
+        <v>31.26</v>
       </c>
       <c r="M19" t="n">
-        <v>31.42</v>
+        <v>31.44</v>
       </c>
       <c r="N19" t="n">
-        <v>31.54</v>
+        <v>31.62</v>
       </c>
       <c r="O19" t="n">
-        <v>31.75</v>
+        <v>31.56</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2124,83 +2114,83 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="C20" t="n">
-        <v>31.63</v>
+        <v>31.57</v>
       </c>
       <c r="D20" t="n">
-        <v>31.24</v>
+        <v>31.37</v>
       </c>
       <c r="E20" t="n">
-        <v>31.5</v>
+        <v>31.38</v>
       </c>
       <c r="F20" t="n">
-        <v>0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0039</v>
       </c>
       <c r="H20" t="n">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>30.83</v>
+        <v>30.86</v>
       </c>
       <c r="J20" t="n">
-        <v>31.14</v>
+        <v>31.15</v>
       </c>
       <c r="K20" t="n">
-        <v>31.2</v>
+        <v>31.31</v>
       </c>
       <c r="L20" t="n">
-        <v>31.26</v>
+        <v>31.47</v>
       </c>
       <c r="M20" t="n">
-        <v>31.44</v>
+        <v>31.7</v>
       </c>
       <c r="N20" t="n">
-        <v>31.62</v>
+        <v>31.92</v>
       </c>
       <c r="O20" t="n">
-        <v>31.56</v>
+        <v>32.01</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2208,83 +2198,83 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31.5</v>
+        <v>31.39</v>
       </c>
       <c r="C21" t="n">
-        <v>31.57</v>
+        <v>31.46</v>
       </c>
       <c r="D21" t="n">
-        <v>31.37</v>
+        <v>31.25</v>
       </c>
       <c r="E21" t="n">
-        <v>31.38</v>
+        <v>31.36</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0007</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I21" t="n">
-        <v>30.86</v>
+        <v>31.16</v>
       </c>
       <c r="J21" t="n">
-        <v>31.15</v>
+        <v>31.13</v>
       </c>
       <c r="K21" t="n">
-        <v>31.31</v>
+        <v>31.28</v>
       </c>
       <c r="L21" t="n">
-        <v>31.47</v>
+        <v>31.42</v>
       </c>
       <c r="M21" t="n">
-        <v>31.7</v>
+        <v>31.48</v>
       </c>
       <c r="N21" t="n">
-        <v>31.92</v>
+        <v>31.54</v>
       </c>
       <c r="O21" t="n">
-        <v>32.01</v>
+        <v>31.78</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2294,12 +2284,12 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2318,57 +2308,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31.39</v>
+        <v>31.38</v>
       </c>
       <c r="C22" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="D22" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I22" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="J22" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="K22" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="L22" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="M22" t="n">
         <v>31.46</v>
       </c>
-      <c r="D22" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="E22" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-0.0007</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I22" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="J22" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="K22" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="L22" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="M22" t="n">
-        <v>31.48</v>
-      </c>
       <c r="N22" t="n">
-        <v>31.54</v>
+        <v>31.57</v>
       </c>
       <c r="O22" t="n">
-        <v>31.78</v>
+        <v>31.68</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2376,83 +2366,83 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>31.38</v>
+        <v>31.6</v>
       </c>
       <c r="C23" t="n">
-        <v>31.68</v>
+        <v>31.74</v>
       </c>
       <c r="D23" t="n">
-        <v>31.35</v>
+        <v>31.51</v>
       </c>
       <c r="E23" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="F23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H23" t="n">
         <v>0.23</v>
       </c>
-      <c r="G23" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.33</v>
-      </c>
       <c r="I23" t="n">
-        <v>31.04</v>
+        <v>31.02</v>
       </c>
       <c r="J23" t="n">
-        <v>31.15</v>
+        <v>31.31</v>
       </c>
       <c r="K23" t="n">
-        <v>31.25</v>
+        <v>31.43</v>
       </c>
       <c r="L23" t="n">
-        <v>31.36</v>
+        <v>31.55</v>
       </c>
       <c r="M23" t="n">
-        <v>31.46</v>
+        <v>31.76</v>
       </c>
       <c r="N23" t="n">
-        <v>31.57</v>
+        <v>31.96</v>
       </c>
       <c r="O23" t="n">
-        <v>31.68</v>
+        <v>32</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2465,23 +2455,17 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2493,63 +2477,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>31.6</v>
+        <v>31.61</v>
       </c>
       <c r="C24" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="D24" t="n">
-        <v>31.51</v>
+        <v>31.37</v>
       </c>
       <c r="E24" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0005</v>
+        <v>-0.0075</v>
       </c>
       <c r="H24" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="I24" t="n">
-        <v>31.02</v>
+        <v>31.27</v>
       </c>
       <c r="J24" t="n">
-        <v>31.31</v>
+        <v>31.37</v>
       </c>
       <c r="K24" t="n">
-        <v>31.43</v>
+        <v>31.49</v>
       </c>
       <c r="L24" t="n">
-        <v>31.55</v>
+        <v>31.62</v>
       </c>
       <c r="M24" t="n">
-        <v>31.76</v>
+        <v>31.73</v>
       </c>
       <c r="N24" t="n">
-        <v>31.96</v>
+        <v>31.83</v>
       </c>
       <c r="O24" t="n">
-        <v>32</v>
+        <v>31.98</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2566,80 +2554,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="C25" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="D25" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="E25" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I25" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="J25" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="K25" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M25" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N25" t="n">
         <v>31.61</v>
       </c>
-      <c r="C25" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="D25" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="E25" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I25" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="J25" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="K25" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="L25" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="M25" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="N25" t="n">
-        <v>31.83</v>
-      </c>
       <c r="O25" t="n">
-        <v>31.98</v>
+        <v>32</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2650,57 +2644,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.38</v>
+        <v>31.61</v>
       </c>
       <c r="C26" t="n">
-        <v>31.58</v>
+        <v>31.71</v>
       </c>
       <c r="D26" t="n">
-        <v>31.12</v>
+        <v>31.49</v>
       </c>
       <c r="E26" t="n">
         <v>31.58</v>
       </c>
       <c r="F26" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0003</v>
       </c>
       <c r="H26" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="I26" t="n">
-        <v>31.06</v>
+        <v>30.65</v>
       </c>
       <c r="J26" t="n">
-        <v>30.98</v>
+        <v>31.23</v>
       </c>
       <c r="K26" t="n">
-        <v>31.21</v>
+        <v>31.35</v>
       </c>
       <c r="L26" t="n">
-        <v>31.45</v>
+        <v>31.47</v>
       </c>
       <c r="M26" t="n">
-        <v>31.53</v>
+        <v>31.82</v>
       </c>
       <c r="N26" t="n">
-        <v>31.61</v>
+        <v>32.16</v>
       </c>
       <c r="O26" t="n">
-        <v>32</v>
+        <v>32.05</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2708,25 +2702,19 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2738,80 +2726,90 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>31.61</v>
       </c>
       <c r="C27" t="n">
-        <v>31.71</v>
+        <v>32.77</v>
       </c>
       <c r="D27" t="n">
-        <v>31.49</v>
+        <v>31.32</v>
       </c>
       <c r="E27" t="n">
-        <v>31.58</v>
+        <v>31.37</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0065</v>
       </c>
       <c r="H27" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="I27" t="n">
-        <v>30.65</v>
+        <v>31.27</v>
       </c>
       <c r="J27" t="n">
-        <v>31.23</v>
+        <v>31.34</v>
       </c>
       <c r="K27" t="n">
-        <v>31.35</v>
+        <v>31.46</v>
       </c>
       <c r="L27" t="n">
-        <v>31.47</v>
+        <v>31.59</v>
       </c>
       <c r="M27" t="n">
-        <v>31.82</v>
+        <v>31.69</v>
       </c>
       <c r="N27" t="n">
-        <v>32.16</v>
+        <v>31.79</v>
       </c>
       <c r="O27" t="n">
-        <v>32.05</v>
+        <v>31.94</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2820,90 +2818,80 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="C28" t="n">
-        <v>32.77</v>
+        <v>31.65</v>
       </c>
       <c r="D28" t="n">
-        <v>31.32</v>
+        <v>31.26</v>
       </c>
       <c r="E28" t="n">
-        <v>31.37</v>
+        <v>31.51</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.21</v>
+        <v>0.14</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0045</v>
       </c>
       <c r="H28" t="n">
-        <v>1.45</v>
+        <v>0.39</v>
       </c>
       <c r="I28" t="n">
-        <v>31.27</v>
+        <v>29.88</v>
       </c>
       <c r="J28" t="n">
-        <v>31.34</v>
+        <v>29.58</v>
       </c>
       <c r="K28" t="n">
-        <v>31.46</v>
+        <v>30.65</v>
       </c>
       <c r="L28" t="n">
-        <v>31.59</v>
+        <v>31.71</v>
       </c>
       <c r="M28" t="n">
-        <v>31.69</v>
+        <v>32.09</v>
       </c>
       <c r="N28" t="n">
-        <v>31.79</v>
+        <v>32.48</v>
       </c>
       <c r="O28" t="n">
-        <v>31.94</v>
+        <v>34.22</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2919,50 +2907,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.37</v>
+        <v>31.47</v>
       </c>
       <c r="C29" t="n">
-        <v>31.65</v>
+        <v>31.5</v>
       </c>
       <c r="D29" t="n">
-        <v>31.26</v>
+        <v>31.18</v>
       </c>
       <c r="E29" t="n">
-        <v>31.51</v>
+        <v>31.38</v>
       </c>
       <c r="F29" t="n">
-        <v>0.14</v>
+        <v>-0.14</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0043</v>
       </c>
       <c r="H29" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="I29" t="n">
-        <v>29.88</v>
+        <v>30.87</v>
       </c>
       <c r="J29" t="n">
-        <v>29.58</v>
+        <v>31.14</v>
       </c>
       <c r="K29" t="n">
-        <v>30.65</v>
+        <v>31.31</v>
       </c>
       <c r="L29" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="M29" t="n">
         <v>31.71</v>
       </c>
-      <c r="M29" t="n">
-        <v>32.09</v>
-      </c>
       <c r="N29" t="n">
-        <v>32.48</v>
+        <v>31.93</v>
       </c>
       <c r="O29" t="n">
-        <v>34.22</v>
+        <v>32.05</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2970,12 +2958,14 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2994,57 +2984,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C30" t="n">
-        <v>31.5</v>
+        <v>31.96</v>
       </c>
       <c r="D30" t="n">
-        <v>31.18</v>
+        <v>31.39</v>
       </c>
       <c r="E30" t="n">
-        <v>31.38</v>
+        <v>31.8</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0136</v>
       </c>
       <c r="H30" t="n">
-        <v>0.32</v>
+        <v>0.57</v>
       </c>
       <c r="I30" t="n">
-        <v>30.87</v>
+        <v>30.86</v>
       </c>
       <c r="J30" t="n">
-        <v>31.14</v>
+        <v>31.08</v>
       </c>
       <c r="K30" t="n">
-        <v>31.31</v>
+        <v>31.22</v>
       </c>
       <c r="L30" t="n">
-        <v>31.48</v>
+        <v>31.36</v>
       </c>
       <c r="M30" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N30" t="n">
         <v>31.71</v>
       </c>
-      <c r="N30" t="n">
-        <v>31.93</v>
-      </c>
       <c r="O30" t="n">
-        <v>32.05</v>
+        <v>31.81</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3052,83 +3042,83 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.44</v>
+        <v>32.03</v>
       </c>
       <c r="C31" t="n">
-        <v>31.96</v>
+        <v>32.16</v>
       </c>
       <c r="D31" t="n">
-        <v>31.39</v>
+        <v>31.53</v>
       </c>
       <c r="E31" t="n">
-        <v>31.8</v>
+        <v>32.16</v>
       </c>
       <c r="F31" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0113</v>
       </c>
       <c r="H31" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="I31" t="n">
-        <v>30.86</v>
+        <v>30.82</v>
       </c>
       <c r="J31" t="n">
-        <v>31.08</v>
+        <v>31.29</v>
       </c>
       <c r="K31" t="n">
-        <v>31.22</v>
+        <v>31.52</v>
       </c>
       <c r="L31" t="n">
-        <v>31.36</v>
+        <v>31.74</v>
       </c>
       <c r="M31" t="n">
-        <v>31.53</v>
+        <v>32.09</v>
       </c>
       <c r="N31" t="n">
-        <v>31.71</v>
+        <v>32.44</v>
       </c>
       <c r="O31" t="n">
-        <v>31.81</v>
+        <v>32.54</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3146,18 +3136,14 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
@@ -3169,50 +3155,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="C32" t="n">
-        <v>32.16</v>
+        <v>32.12</v>
       </c>
       <c r="D32" t="n">
-        <v>31.53</v>
+        <v>31.8</v>
       </c>
       <c r="E32" t="n">
-        <v>32.16</v>
+        <v>32.02</v>
       </c>
       <c r="F32" t="n">
-        <v>0.36</v>
+        <v>-0.14</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0044</v>
       </c>
       <c r="H32" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="I32" t="n">
-        <v>30.82</v>
+        <v>30.91</v>
       </c>
       <c r="J32" t="n">
-        <v>31.29</v>
+        <v>31.69</v>
       </c>
       <c r="K32" t="n">
-        <v>31.52</v>
+        <v>31.85</v>
       </c>
       <c r="L32" t="n">
-        <v>31.74</v>
+        <v>32.01</v>
       </c>
       <c r="M32" t="n">
-        <v>32.09</v>
+        <v>32.48</v>
       </c>
       <c r="N32" t="n">
-        <v>32.44</v>
+        <v>32.95</v>
       </c>
       <c r="O32" t="n">
-        <v>32.54</v>
+        <v>32.79</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3220,18 +3206,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3244,55 +3230,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.09</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>32.12</v>
+        <v>32.14</v>
       </c>
       <c r="D33" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="E33" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0002</v>
       </c>
       <c r="H33" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I33" t="n">
-        <v>30.91</v>
+        <v>31.47</v>
       </c>
       <c r="J33" t="n">
-        <v>31.69</v>
+        <v>31.73</v>
       </c>
       <c r="K33" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="L33" t="n">
-        <v>32.01</v>
+        <v>31.99</v>
       </c>
       <c r="M33" t="n">
-        <v>32.48</v>
+        <v>32.18</v>
       </c>
       <c r="N33" t="n">
-        <v>32.95</v>
+        <v>32.38</v>
       </c>
       <c r="O33" t="n">
-        <v>32.79</v>
+        <v>32.44</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3326,57 +3316,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="C34" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="D34" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="E34" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I34" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="J34" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="L34" t="n">
         <v>32</v>
       </c>
-      <c r="C34" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="D34" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="E34" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I34" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="J34" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="K34" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="L34" t="n">
-        <v>31.99</v>
-      </c>
       <c r="M34" t="n">
-        <v>32.18</v>
+        <v>32.21</v>
       </c>
       <c r="N34" t="n">
-        <v>32.38</v>
+        <v>32.43</v>
       </c>
       <c r="O34" t="n">
-        <v>32.44</v>
+        <v>32.51</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3389,13 +3379,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3417,50 +3409,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
       <c r="C35" t="n">
-        <v>32.22</v>
+        <v>32.04</v>
       </c>
       <c r="D35" t="n">
-        <v>31.84</v>
+        <v>31.68</v>
       </c>
       <c r="E35" t="n">
-        <v>31.96</v>
+        <v>31.73</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0074</v>
       </c>
       <c r="H35" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I35" t="n">
-        <v>31.42</v>
+        <v>31.47</v>
       </c>
       <c r="J35" t="n">
-        <v>31.7</v>
+        <v>31.55</v>
       </c>
       <c r="K35" t="n">
-        <v>31.85</v>
+        <v>31.78</v>
       </c>
       <c r="L35" t="n">
         <v>32</v>
       </c>
       <c r="M35" t="n">
-        <v>32.21</v>
+        <v>32.15</v>
       </c>
       <c r="N35" t="n">
-        <v>32.43</v>
+        <v>32.3</v>
       </c>
       <c r="O35" t="n">
-        <v>32.51</v>
+        <v>32.59</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3470,18 +3462,16 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3496,57 +3486,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.96</v>
+        <v>31.77</v>
       </c>
       <c r="C36" t="n">
-        <v>32.04</v>
+        <v>31.87</v>
       </c>
       <c r="D36" t="n">
-        <v>31.68</v>
+        <v>31.37</v>
       </c>
       <c r="E36" t="n">
-        <v>31.73</v>
+        <v>31.47</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0083</v>
       </c>
       <c r="H36" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="I36" t="n">
-        <v>31.47</v>
+        <v>31.32</v>
       </c>
       <c r="J36" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K36" t="n">
         <v>31.55</v>
       </c>
-      <c r="K36" t="n">
-        <v>31.78</v>
-      </c>
       <c r="L36" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="M36" t="n">
-        <v>32.15</v>
+        <v>31.91</v>
       </c>
       <c r="N36" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O36" t="n">
-        <v>32.59</v>
+        <v>32.41</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3587,50 +3577,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.77</v>
+        <v>31.47</v>
       </c>
       <c r="C37" t="n">
-        <v>31.87</v>
+        <v>31.59</v>
       </c>
       <c r="D37" t="n">
-        <v>31.37</v>
+        <v>31.18</v>
       </c>
       <c r="E37" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0009</v>
       </c>
       <c r="H37" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="I37" t="n">
-        <v>31.32</v>
+        <v>30.88</v>
       </c>
       <c r="J37" t="n">
-        <v>31.3</v>
+        <v>30.89</v>
       </c>
       <c r="K37" t="n">
-        <v>31.55</v>
+        <v>31.22</v>
       </c>
       <c r="L37" t="n">
-        <v>31.8</v>
+        <v>31.54</v>
       </c>
       <c r="M37" t="n">
-        <v>31.91</v>
+        <v>31.71</v>
       </c>
       <c r="N37" t="n">
-        <v>32.02</v>
+        <v>31.88</v>
       </c>
       <c r="O37" t="n">
-        <v>32.41</v>
+        <v>32.36</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3640,12 +3630,12 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3671,50 +3661,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C38" t="n">
-        <v>31.59</v>
+        <v>31.75</v>
       </c>
       <c r="D38" t="n">
-        <v>31.18</v>
+        <v>31.38</v>
       </c>
       <c r="E38" t="n">
-        <v>31.44</v>
+        <v>31.55</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0037</v>
       </c>
       <c r="H38" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="I38" t="n">
-        <v>30.88</v>
+        <v>30.78</v>
       </c>
       <c r="J38" t="n">
-        <v>30.89</v>
+        <v>31.05</v>
       </c>
       <c r="K38" t="n">
-        <v>31.22</v>
+        <v>31.23</v>
       </c>
       <c r="L38" t="n">
-        <v>31.54</v>
+        <v>31.41</v>
       </c>
       <c r="M38" t="n">
-        <v>31.71</v>
+        <v>31.64</v>
       </c>
       <c r="N38" t="n">
-        <v>31.88</v>
+        <v>31.87</v>
       </c>
       <c r="O38" t="n">
-        <v>32.36</v>
+        <v>32</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3722,18 +3712,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3746,59 +3736,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.44</v>
+        <v>31.64</v>
       </c>
       <c r="C39" t="n">
-        <v>31.75</v>
+        <v>31.69</v>
       </c>
       <c r="D39" t="n">
-        <v>31.38</v>
+        <v>31.3</v>
       </c>
       <c r="E39" t="n">
-        <v>31.55</v>
+        <v>31.3</v>
       </c>
       <c r="F39" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="I39" t="n">
-        <v>30.78</v>
+        <v>31.02</v>
       </c>
       <c r="J39" t="n">
-        <v>31.05</v>
+        <v>31.18</v>
       </c>
       <c r="K39" t="n">
-        <v>31.23</v>
+        <v>31.37</v>
       </c>
       <c r="L39" t="n">
-        <v>31.41</v>
+        <v>31.56</v>
       </c>
       <c r="M39" t="n">
-        <v>31.64</v>
+        <v>31.74</v>
       </c>
       <c r="N39" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="O39" t="n">
-        <v>32</v>
+        <v>32.11</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3806,19 +3792,19 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3830,55 +3816,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.64</v>
+        <v>31.3</v>
       </c>
       <c r="C40" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="D40" t="n">
         <v>31.3</v>
       </c>
       <c r="E40" t="n">
-        <v>31.3</v>
+        <v>31.56</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.26</v>
+        <v>0.27</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="I40" t="n">
-        <v>31.02</v>
+        <v>30.9</v>
       </c>
       <c r="J40" t="n">
-        <v>31.18</v>
+        <v>30.8</v>
       </c>
       <c r="K40" t="n">
-        <v>31.37</v>
+        <v>31.1</v>
       </c>
       <c r="L40" t="n">
-        <v>31.56</v>
+        <v>31.39</v>
       </c>
       <c r="M40" t="n">
-        <v>31.74</v>
+        <v>31.49</v>
       </c>
       <c r="N40" t="n">
-        <v>31.91</v>
+        <v>31.59</v>
       </c>
       <c r="O40" t="n">
-        <v>32.11</v>
+        <v>32.09</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3886,22 +3876,24 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3912,57 +3904,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.3</v>
+        <v>31.59</v>
       </c>
       <c r="C41" t="n">
-        <v>31.62</v>
+        <v>31.78</v>
       </c>
       <c r="D41" t="n">
-        <v>31.3</v>
+        <v>31.36</v>
       </c>
       <c r="E41" t="n">
-        <v>31.56</v>
+        <v>31.36</v>
       </c>
       <c r="F41" t="n">
-        <v>0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0065</v>
       </c>
       <c r="H41" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="I41" t="n">
-        <v>30.9</v>
+        <v>30.98</v>
       </c>
       <c r="J41" t="n">
-        <v>30.8</v>
+        <v>31.29</v>
       </c>
       <c r="K41" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="L41" t="n">
-        <v>31.39</v>
+        <v>31.51</v>
       </c>
       <c r="M41" t="n">
-        <v>31.49</v>
+        <v>31.72</v>
       </c>
       <c r="N41" t="n">
-        <v>31.59</v>
+        <v>31.93</v>
       </c>
       <c r="O41" t="n">
-        <v>32.09</v>
+        <v>31.95</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3970,12 +3962,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -3983,10 +3977,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -4005,50 +3997,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.59</v>
+        <v>31.44</v>
       </c>
       <c r="C42" t="n">
-        <v>31.78</v>
+        <v>31.52</v>
       </c>
       <c r="D42" t="n">
-        <v>31.36</v>
+        <v>31.31</v>
       </c>
       <c r="E42" t="n">
-        <v>31.36</v>
+        <v>31.41</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0018</v>
       </c>
       <c r="H42" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="I42" t="n">
-        <v>30.98</v>
+        <v>30.94</v>
       </c>
       <c r="J42" t="n">
-        <v>31.29</v>
+        <v>30.83</v>
       </c>
       <c r="K42" t="n">
-        <v>31.4</v>
+        <v>31.15</v>
       </c>
       <c r="L42" t="n">
-        <v>31.51</v>
+        <v>31.46</v>
       </c>
       <c r="M42" t="n">
-        <v>31.72</v>
+        <v>31.57</v>
       </c>
       <c r="N42" t="n">
-        <v>31.93</v>
+        <v>31.67</v>
       </c>
       <c r="O42" t="n">
-        <v>31.95</v>
+        <v>32.2</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4056,20 +4048,16 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4084,57 +4072,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.44</v>
+        <v>31.41</v>
       </c>
       <c r="C43" t="n">
-        <v>31.52</v>
+        <v>31.6</v>
       </c>
       <c r="D43" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="E43" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I43" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J43" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="K43" t="n">
         <v>31.31</v>
       </c>
-      <c r="E43" t="n">
+      <c r="L43" t="n">
         <v>31.41</v>
       </c>
-      <c r="F43" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I43" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="J43" t="n">
-        <v>30.83</v>
-      </c>
-      <c r="K43" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="L43" t="n">
-        <v>31.46</v>
-      </c>
       <c r="M43" t="n">
-        <v>31.57</v>
+        <v>31.51</v>
       </c>
       <c r="N43" t="n">
-        <v>31.67</v>
+        <v>31.61</v>
       </c>
       <c r="O43" t="n">
-        <v>32.2</v>
+        <v>31.72</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4142,16 +4130,20 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4166,57 +4158,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.41</v>
+        <v>31.59</v>
       </c>
       <c r="C44" t="n">
-        <v>31.6</v>
+        <v>31.76</v>
       </c>
       <c r="D44" t="n">
-        <v>31.28</v>
+        <v>31.44</v>
       </c>
       <c r="E44" t="n">
         <v>31.56</v>
       </c>
       <c r="F44" t="n">
-        <v>0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0002</v>
       </c>
       <c r="H44" t="n">
         <v>0.33</v>
       </c>
       <c r="I44" t="n">
-        <v>31.11</v>
+        <v>30.95</v>
       </c>
       <c r="J44" t="n">
-        <v>31.21</v>
+        <v>31.3</v>
       </c>
       <c r="K44" t="n">
-        <v>31.31</v>
+        <v>31.4</v>
       </c>
       <c r="L44" t="n">
-        <v>31.41</v>
+        <v>31.5</v>
       </c>
       <c r="M44" t="n">
-        <v>31.51</v>
+        <v>31.73</v>
       </c>
       <c r="N44" t="n">
-        <v>31.61</v>
+        <v>31.95</v>
       </c>
       <c r="O44" t="n">
-        <v>31.72</v>
+        <v>31.93</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4224,19 +4216,17 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U44" s="8" t="n">
@@ -4259,50 +4249,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="C45" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="D45" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="E45" t="n">
-        <v>31.56</v>
+        <v>31.65</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0028</v>
       </c>
       <c r="H45" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="I45" t="n">
-        <v>30.95</v>
+        <v>31.11</v>
       </c>
       <c r="J45" t="n">
-        <v>31.3</v>
+        <v>31.21</v>
       </c>
       <c r="K45" t="n">
-        <v>31.4</v>
+        <v>31.39</v>
       </c>
       <c r="L45" t="n">
-        <v>31.5</v>
+        <v>31.58</v>
       </c>
       <c r="M45" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="N45" t="n">
-        <v>31.95</v>
+        <v>31.86</v>
       </c>
       <c r="O45" t="n">
-        <v>31.93</v>
+        <v>32.09</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4318,10 +4308,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4343,50 +4331,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="C46" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="D46" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E46" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I46" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="J46" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="K46" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="L46" t="n">
         <v>31.61</v>
       </c>
-      <c r="C46" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="D46" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="E46" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I46" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="J46" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="K46" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="L46" t="n">
-        <v>31.58</v>
-      </c>
       <c r="M46" t="n">
-        <v>31.72</v>
+        <v>31.76</v>
       </c>
       <c r="N46" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="O46" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4399,14 +4387,18 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4416,59 +4408,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.7</v>
+        <v>31.85</v>
       </c>
       <c r="C47" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="D47" t="n">
-        <v>31.58</v>
+        <v>31.79</v>
       </c>
       <c r="E47" t="n">
-        <v>31.84</v>
+        <v>31.9</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0016</v>
       </c>
       <c r="H47" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="I47" t="n">
-        <v>31.23</v>
+        <v>31.26</v>
       </c>
       <c r="J47" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="K47" t="n">
-        <v>31.53</v>
+        <v>31.68</v>
       </c>
       <c r="L47" t="n">
-        <v>31.61</v>
+        <v>31.79</v>
       </c>
       <c r="M47" t="n">
-        <v>31.76</v>
+        <v>32.01</v>
       </c>
       <c r="N47" t="n">
-        <v>31.91</v>
+        <v>32.22</v>
       </c>
       <c r="O47" t="n">
-        <v>31.93</v>
+        <v>32.23</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4481,18 +4469,14 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4507,50 +4491,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.85</v>
+        <v>31.93</v>
       </c>
       <c r="C48" t="n">
-        <v>31.96</v>
+        <v>32.23</v>
       </c>
       <c r="D48" t="n">
-        <v>31.79</v>
+        <v>31.92</v>
       </c>
       <c r="E48" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0063</v>
       </c>
       <c r="H48" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="I48" t="n">
-        <v>31.26</v>
+        <v>31.62</v>
       </c>
       <c r="J48" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K48" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="L48" t="n">
-        <v>31.79</v>
+        <v>31.89</v>
       </c>
       <c r="M48" t="n">
-        <v>32.01</v>
+        <v>31.98</v>
       </c>
       <c r="N48" t="n">
-        <v>32.22</v>
+        <v>32.08</v>
       </c>
       <c r="O48" t="n">
-        <v>32.23</v>
+        <v>32.13</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4563,17 +4547,23 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4585,50 +4575,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.93</v>
+        <v>32.1</v>
       </c>
       <c r="C49" t="n">
-        <v>32.23</v>
+        <v>32.42</v>
       </c>
       <c r="D49" t="n">
-        <v>31.92</v>
+        <v>32.03</v>
       </c>
       <c r="E49" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="I49" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="J49" t="n">
-        <v>31.74</v>
+        <v>31.8</v>
       </c>
       <c r="K49" t="n">
-        <v>31.81</v>
+        <v>31.94</v>
       </c>
       <c r="L49" t="n">
-        <v>31.89</v>
+        <v>32.09</v>
       </c>
       <c r="M49" t="n">
-        <v>31.98</v>
+        <v>32.25</v>
       </c>
       <c r="N49" t="n">
-        <v>32.08</v>
+        <v>32.42</v>
       </c>
       <c r="O49" t="n">
-        <v>32.13</v>
+        <v>32.53</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4654,10 +4644,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
@@ -4669,50 +4657,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C50" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D50" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="E50" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I50" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="J50" t="n">
         <v>32.1</v>
       </c>
-      <c r="C50" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D50" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="E50" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I50" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="J50" t="n">
-        <v>31.8</v>
-      </c>
       <c r="K50" t="n">
-        <v>31.94</v>
+        <v>32.2</v>
       </c>
       <c r="L50" t="n">
-        <v>32.09</v>
+        <v>32.31</v>
       </c>
       <c r="M50" t="n">
-        <v>32.25</v>
+        <v>32.59</v>
       </c>
       <c r="N50" t="n">
-        <v>32.42</v>
+        <v>32.87</v>
       </c>
       <c r="O50" t="n">
-        <v>32.53</v>
+        <v>32.81</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4725,18 +4713,14 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4746,55 +4730,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.31</v>
+        <v>32.32</v>
       </c>
       <c r="C51" t="n">
-        <v>32.49</v>
+        <v>32.55</v>
       </c>
       <c r="D51" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="E51" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I51" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="J51" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="K51" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="L51" t="n">
         <v>32.35</v>
       </c>
-      <c r="F51" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I51" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="J51" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="L51" t="n">
-        <v>32.31</v>
-      </c>
       <c r="M51" t="n">
-        <v>32.59</v>
+        <v>32.48</v>
       </c>
       <c r="N51" t="n">
-        <v>32.87</v>
+        <v>32.6</v>
       </c>
       <c r="O51" t="n">
-        <v>32.81</v>
+        <v>32.74</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4802,16 +4790,20 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4826,57 +4818,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>32.32</v>
+        <v>32.29</v>
       </c>
       <c r="C52" t="n">
-        <v>32.55</v>
+        <v>32.49</v>
       </c>
       <c r="D52" t="n">
-        <v>32.21</v>
+        <v>32.12</v>
       </c>
       <c r="E52" t="n">
-        <v>32.29</v>
+        <v>32.24</v>
       </c>
       <c r="F52" t="n">
         <v>-0.06</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="H52" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I52" t="n">
-        <v>31.98</v>
+        <v>31.86</v>
       </c>
       <c r="J52" t="n">
-        <v>32.09</v>
+        <v>31.91</v>
       </c>
       <c r="K52" t="n">
-        <v>32.22</v>
+        <v>32.12</v>
       </c>
       <c r="L52" t="n">
-        <v>32.35</v>
+        <v>32.34</v>
       </c>
       <c r="M52" t="n">
-        <v>32.48</v>
+        <v>32.47</v>
       </c>
       <c r="N52" t="n">
         <v>32.6</v>
       </c>
       <c r="O52" t="n">
-        <v>32.74</v>
+        <v>32.9</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4884,21 +4876,19 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4912,57 +4902,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="C53" t="n">
         <v>32.29</v>
       </c>
-      <c r="C53" t="n">
-        <v>32.49</v>
-      </c>
       <c r="D53" t="n">
-        <v>32.12</v>
+        <v>31.92</v>
       </c>
       <c r="E53" t="n">
-        <v>32.24</v>
+        <v>32.01</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.0071</v>
       </c>
       <c r="H53" t="n">
         <v>0.37</v>
       </c>
       <c r="I53" t="n">
-        <v>31.86</v>
+        <v>31.76</v>
       </c>
       <c r="J53" t="n">
-        <v>31.91</v>
+        <v>31.83</v>
       </c>
       <c r="K53" t="n">
-        <v>32.12</v>
+        <v>32.05</v>
       </c>
       <c r="L53" t="n">
-        <v>32.34</v>
+        <v>32.27</v>
       </c>
       <c r="M53" t="n">
-        <v>32.47</v>
+        <v>32.42</v>
       </c>
       <c r="N53" t="n">
-        <v>32.6</v>
+        <v>32.57</v>
       </c>
       <c r="O53" t="n">
-        <v>32.9</v>
+        <v>32.86</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4970,18 +4960,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -5003,50 +4993,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.24</v>
+        <v>31.99</v>
       </c>
       <c r="C54" t="n">
-        <v>32.29</v>
+        <v>32.01</v>
       </c>
       <c r="D54" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E54" t="n">
-        <v>32.01</v>
+        <v>31.83</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0071</v>
+        <v>-0.0055</v>
       </c>
       <c r="H54" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="I54" t="n">
-        <v>31.76</v>
+        <v>31.55</v>
       </c>
       <c r="J54" t="n">
-        <v>31.83</v>
+        <v>31.59</v>
       </c>
       <c r="K54" t="n">
-        <v>32.05</v>
+        <v>31.82</v>
       </c>
       <c r="L54" t="n">
-        <v>32.27</v>
+        <v>32.06</v>
       </c>
       <c r="M54" t="n">
-        <v>32.42</v>
+        <v>32.19</v>
       </c>
       <c r="N54" t="n">
-        <v>32.57</v>
+        <v>32.33</v>
       </c>
       <c r="O54" t="n">
-        <v>32.86</v>
+        <v>32.66</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5087,60 +5077,62 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.99</v>
+        <v>31.82</v>
       </c>
       <c r="C55" t="n">
-        <v>32.01</v>
+        <v>31.91</v>
       </c>
       <c r="D55" t="n">
-        <v>31.75</v>
+        <v>31.55</v>
       </c>
       <c r="E55" t="n">
-        <v>31.83</v>
+        <v>31.62</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0066</v>
       </c>
       <c r="H55" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="I55" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J55" t="n">
         <v>31.55</v>
       </c>
-      <c r="J55" t="n">
-        <v>31.59</v>
-      </c>
       <c r="K55" t="n">
-        <v>31.82</v>
+        <v>31.7</v>
       </c>
       <c r="L55" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="M55" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="N55" t="n">
         <v>32.06</v>
       </c>
-      <c r="M55" t="n">
-        <v>32.19</v>
-      </c>
-      <c r="N55" t="n">
-        <v>32.33</v>
-      </c>
       <c r="O55" t="n">
-        <v>32.66</v>
+        <v>32.26</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
@@ -5171,72 +5163,70 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.82</v>
+        <v>31.63</v>
       </c>
       <c r="C56" t="n">
-        <v>31.91</v>
+        <v>31.8</v>
       </c>
       <c r="D56" t="n">
-        <v>31.55</v>
+        <v>31.58</v>
       </c>
       <c r="E56" t="n">
-        <v>31.62</v>
+        <v>31.67</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.21</v>
+        <v>0.05</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0066</v>
+        <v>0.0016</v>
       </c>
       <c r="H56" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="I56" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="J56" t="n">
-        <v>31.55</v>
+        <v>31.21</v>
       </c>
       <c r="K56" t="n">
-        <v>31.7</v>
+        <v>31.44</v>
       </c>
       <c r="L56" t="n">
-        <v>31.86</v>
+        <v>31.68</v>
       </c>
       <c r="M56" t="n">
-        <v>31.96</v>
+        <v>31.8</v>
       </c>
       <c r="N56" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="O56" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5250,76 +5240,78 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="C57" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="D57" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="E57" t="n">
         <v>31.63</v>
       </c>
-      <c r="C57" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D57" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="E57" t="n">
-        <v>31.67</v>
-      </c>
       <c r="F57" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0013</v>
       </c>
       <c r="H57" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I57" t="n">
-        <v>31.2</v>
+        <v>31.37</v>
       </c>
       <c r="J57" t="n">
-        <v>31.21</v>
+        <v>31.44</v>
       </c>
       <c r="K57" t="n">
-        <v>31.44</v>
+        <v>31.56</v>
       </c>
       <c r="L57" t="n">
         <v>31.68</v>
       </c>
       <c r="M57" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="N57" t="n">
-        <v>31.92</v>
+        <v>31.88</v>
       </c>
       <c r="O57" t="n">
-        <v>32.27</v>
+        <v>32.02</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5334,79 +5326,77 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.62</v>
+        <v>31.68</v>
       </c>
       <c r="C58" t="n">
-        <v>31.69</v>
+        <v>31.87</v>
       </c>
       <c r="D58" t="n">
-        <v>31.42</v>
+        <v>31.61</v>
       </c>
       <c r="E58" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0015</v>
       </c>
       <c r="H58" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I58" t="n">
-        <v>31.37</v>
+        <v>31.14</v>
       </c>
       <c r="J58" t="n">
-        <v>31.44</v>
+        <v>31.39</v>
       </c>
       <c r="K58" t="n">
-        <v>31.56</v>
+        <v>31.49</v>
       </c>
       <c r="L58" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M58" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="N58" t="n">
-        <v>31.88</v>
+        <v>31.94</v>
       </c>
       <c r="O58" t="n">
-        <v>32.02</v>
+        <v>31.97</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5418,11 +5408,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -5431,25 +5417,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>31.14</v>
+        <v>31.35</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>31.37</v>
+        <v>31.38</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>31.48</v>
+        <v>31.55</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>31.58</v>
+        <v>31.71</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>31.75</v>
+        <v>31.81</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>31.92</v>
+        <v>31.9</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>31.97</v>
+        <v>32.13</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -5340,22 +5340,22 @@
         <v>31.68</v>
       </c>
       <c r="C58" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D58" t="n">
         <v>31.61</v>
       </c>
       <c r="E58" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="F58" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0028</v>
       </c>
       <c r="H58" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="I58" t="n">
         <v>31.14</v>
@@ -5389,12 +5389,12 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5417,25 +5417,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>31.35</v>
+        <v>31.32</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>31.38</v>
+        <v>31.4</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>31.55</v>
+        <v>31.57</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>31.71</v>
+        <v>31.74</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>31.81</v>
+        <v>31.87</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>31.9</v>
+        <v>31.99</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>29.58</v>
+        <v>29.61</v>
       </c>
       <c r="J2" t="n">
-        <v>29.79</v>
+        <v>29.8</v>
       </c>
       <c r="K2" t="n">
-        <v>29.89</v>
+        <v>29.9</v>
       </c>
       <c r="L2" t="n">
         <v>29.99</v>
       </c>
       <c r="M2" t="n">
-        <v>30.15</v>
+        <v>30.14</v>
       </c>
       <c r="N2" t="n">
-        <v>30.3</v>
+        <v>30.28</v>
       </c>
       <c r="O2" t="n">
-        <v>30.35</v>
+        <v>30.34</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -5346,13 +5346,13 @@
         <v>31.61</v>
       </c>
       <c r="E58" t="n">
-        <v>31.72</v>
+        <v>31.77</v>
       </c>
       <c r="F58" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0046</v>
       </c>
       <c r="H58" t="n">
         <v>0.3</v>
@@ -5420,19 +5420,19 @@
         <v>31.32</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>31.4</v>
+        <v>31.48</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>31.74</v>
+        <v>31.77</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>31.87</v>
+        <v>31.92</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>31.99</v>
+        <v>32.08</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>32.21</v>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -5340,22 +5340,22 @@
         <v>31.68</v>
       </c>
       <c r="C58" t="n">
-        <v>31.91</v>
+        <v>31.94</v>
       </c>
       <c r="D58" t="n">
         <v>31.61</v>
       </c>
       <c r="E58" t="n">
-        <v>31.77</v>
+        <v>31.86</v>
       </c>
       <c r="F58" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.0073</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="I58" t="n">
         <v>31.14</v>
@@ -5394,11 +5394,13 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5417,25 +5419,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>31.32</v>
+        <v>31.29</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>31.48</v>
+        <v>31.58</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>31.62</v>
+        <v>31.7</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>31.77</v>
+        <v>31.82</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>31.92</v>
+        <v>32.02</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>32.08</v>
+        <v>32.22</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,25 +659,25 @@
         <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>29.61</v>
+        <v>29.85</v>
       </c>
       <c r="J2" t="n">
-        <v>29.8</v>
+        <v>29.89</v>
       </c>
       <c r="K2" t="n">
-        <v>29.9</v>
+        <v>29.96</v>
       </c>
       <c r="L2" t="n">
-        <v>29.99</v>
+        <v>30.02</v>
       </c>
       <c r="M2" t="n">
-        <v>30.14</v>
+        <v>30.08</v>
       </c>
       <c r="N2" t="n">
-        <v>30.28</v>
+        <v>30.13</v>
       </c>
       <c r="O2" t="n">
-        <v>30.34</v>
+        <v>30.22</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -720,7 +713,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5411,34 +5408,6 @@
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>31.29</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>31.82</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>32.02</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>32.22</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>32.26</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,34 +659,40 @@
         <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>29.85</v>
+        <v>30.02</v>
       </c>
       <c r="J2" t="n">
-        <v>29.89</v>
+        <v>30.02</v>
       </c>
       <c r="K2" t="n">
-        <v>29.96</v>
+        <v>30.02</v>
       </c>
       <c r="L2" t="n">
         <v>30.02</v>
       </c>
       <c r="M2" t="n">
-        <v>30.08</v>
+        <v>30.02</v>
       </c>
       <c r="N2" t="n">
-        <v>30.13</v>
+        <v>30.02</v>
       </c>
       <c r="O2" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>30.02</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -705,7 +711,7 @@
       </c>
       <c r="V2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5343,13 +5349,13 @@
         <v>31.61</v>
       </c>
       <c r="E58" t="n">
-        <v>31.86</v>
+        <v>31.76</v>
       </c>
       <c r="F58" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.0043</v>
       </c>
       <c r="H58" t="n">
         <v>0.32</v>
@@ -5391,13 +5397,11 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -634,85 +634,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.99</v>
+        <v>30.37</v>
       </c>
       <c r="C2" t="n">
-        <v>30.93</v>
+        <v>30.65</v>
       </c>
       <c r="D2" t="n">
-        <v>29.96</v>
+        <v>30.37</v>
       </c>
       <c r="E2" t="n">
-        <v>30.37</v>
+        <v>30.56</v>
       </c>
       <c r="F2" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0065</v>
       </c>
       <c r="H2" t="n">
-        <v>0.97</v>
+        <v>0.28</v>
       </c>
       <c r="I2" t="n">
-        <v>30.02</v>
+        <v>28.99</v>
       </c>
       <c r="J2" t="n">
-        <v>30.02</v>
+        <v>29.36</v>
       </c>
       <c r="K2" t="n">
-        <v>30.02</v>
+        <v>29.88</v>
       </c>
       <c r="L2" t="n">
-        <v>30.02</v>
+        <v>30.41</v>
       </c>
       <c r="M2" t="n">
-        <v>30.02</v>
+        <v>30.85</v>
       </c>
       <c r="N2" t="n">
-        <v>30.02</v>
+        <v>31.3</v>
       </c>
       <c r="O2" t="n">
-        <v>30.02</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31.9</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -728,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.37</v>
+        <v>30.56</v>
       </c>
       <c r="C3" t="n">
-        <v>30.65</v>
+        <v>30.8</v>
       </c>
       <c r="D3" t="n">
-        <v>30.37</v>
+        <v>30.32</v>
       </c>
       <c r="E3" t="n">
-        <v>30.56</v>
+        <v>30.53</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0012</v>
       </c>
       <c r="H3" t="n">
-        <v>0.28</v>
+        <v>0.47</v>
       </c>
       <c r="I3" t="n">
-        <v>28.99</v>
+        <v>30.09</v>
       </c>
       <c r="J3" t="n">
-        <v>29.36</v>
+        <v>30.31</v>
       </c>
       <c r="K3" t="n">
-        <v>29.88</v>
+        <v>30.42</v>
       </c>
       <c r="L3" t="n">
-        <v>30.41</v>
+        <v>30.54</v>
       </c>
       <c r="M3" t="n">
-        <v>30.85</v>
+        <v>30.7</v>
       </c>
       <c r="N3" t="n">
-        <v>31.3</v>
+        <v>30.87</v>
       </c>
       <c r="O3" t="n">
-        <v>31.9</v>
+        <v>30.93</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,16 +767,20 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -803,57 +795,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.56</v>
+        <v>30.48</v>
       </c>
       <c r="C4" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="D4" t="n">
-        <v>30.32</v>
+        <v>30.18</v>
       </c>
       <c r="E4" t="n">
-        <v>30.53</v>
+        <v>30.28</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.04</v>
+        <v>-0.24</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.008</v>
       </c>
       <c r="H4" t="n">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
       <c r="I4" t="n">
-        <v>30.09</v>
+        <v>29.85</v>
       </c>
       <c r="J4" t="n">
-        <v>30.31</v>
+        <v>30.04</v>
       </c>
       <c r="K4" t="n">
-        <v>30.42</v>
+        <v>30.29</v>
       </c>
       <c r="L4" t="n">
         <v>30.54</v>
       </c>
       <c r="M4" t="n">
-        <v>30.7</v>
+        <v>30.77</v>
       </c>
       <c r="N4" t="n">
-        <v>30.87</v>
+        <v>30.99</v>
       </c>
       <c r="O4" t="n">
-        <v>30.93</v>
+        <v>31.27</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -863,18 +855,16 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -889,57 +879,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.48</v>
+        <v>30.28</v>
       </c>
       <c r="C5" t="n">
-        <v>30.5</v>
+        <v>30.33</v>
       </c>
       <c r="D5" t="n">
-        <v>30.18</v>
+        <v>29.94</v>
       </c>
       <c r="E5" t="n">
-        <v>30.28</v>
+        <v>30.11</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0058</v>
       </c>
       <c r="H5" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="I5" t="n">
-        <v>29.85</v>
+        <v>29.86</v>
       </c>
       <c r="J5" t="n">
-        <v>30.04</v>
+        <v>29.93</v>
       </c>
       <c r="K5" t="n">
-        <v>30.29</v>
+        <v>30.12</v>
       </c>
       <c r="L5" t="n">
-        <v>30.54</v>
+        <v>30.31</v>
       </c>
       <c r="M5" t="n">
-        <v>30.77</v>
+        <v>30.45</v>
       </c>
       <c r="N5" t="n">
-        <v>30.99</v>
+        <v>30.58</v>
       </c>
       <c r="O5" t="n">
-        <v>31.27</v>
+        <v>30.83</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -980,50 +970,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.28</v>
+        <v>30.22</v>
       </c>
       <c r="C6" t="n">
-        <v>30.33</v>
+        <v>30.59</v>
       </c>
       <c r="D6" t="n">
-        <v>29.94</v>
+        <v>30.15</v>
       </c>
       <c r="E6" t="n">
-        <v>30.11</v>
+        <v>30.44</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.17</v>
+        <v>0.33</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0111</v>
       </c>
       <c r="H6" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="I6" t="n">
-        <v>29.86</v>
+        <v>29.56</v>
       </c>
       <c r="J6" t="n">
-        <v>29.93</v>
+        <v>29.71</v>
       </c>
       <c r="K6" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="L6" t="n">
         <v>30.12</v>
       </c>
-      <c r="L6" t="n">
-        <v>30.31</v>
-      </c>
       <c r="M6" t="n">
-        <v>30.45</v>
+        <v>30.3</v>
       </c>
       <c r="N6" t="n">
-        <v>30.58</v>
+        <v>30.48</v>
       </c>
       <c r="O6" t="n">
-        <v>30.83</v>
+        <v>30.71</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1031,22 +1021,24 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1055,59 +1047,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="K7" t="n">
         <v>30.22</v>
       </c>
-      <c r="C7" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="D7" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I7" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="J7" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="K7" t="n">
-        <v>29.92</v>
-      </c>
       <c r="L7" t="n">
-        <v>30.12</v>
+        <v>30.41</v>
       </c>
       <c r="M7" t="n">
-        <v>30.3</v>
+        <v>30.66</v>
       </c>
       <c r="N7" t="n">
-        <v>30.48</v>
+        <v>30.92</v>
       </c>
       <c r="O7" t="n">
-        <v>30.71</v>
+        <v>31.03</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1120,18 +1108,14 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1141,55 +1125,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.44</v>
+        <v>30.42</v>
       </c>
       <c r="C8" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="K8" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="M8" t="n">
         <v>30.53</v>
       </c>
-      <c r="D8" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="E8" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="J8" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="K8" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="L8" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="M8" t="n">
-        <v>30.66</v>
-      </c>
       <c r="N8" t="n">
-        <v>30.92</v>
+        <v>30.63</v>
       </c>
       <c r="O8" t="n">
-        <v>31.03</v>
+        <v>30.73</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1197,22 +1185,30 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1221,57 +1217,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.42</v>
+        <v>30.67</v>
       </c>
       <c r="C9" t="n">
-        <v>30.71</v>
+        <v>30.8</v>
       </c>
       <c r="D9" t="n">
-        <v>30.24</v>
+        <v>30.48</v>
       </c>
       <c r="E9" t="n">
-        <v>30.71</v>
+        <v>30.62</v>
       </c>
       <c r="F9" t="n">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.0027</v>
       </c>
       <c r="H9" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="n">
-        <v>30.14</v>
+        <v>29.78</v>
       </c>
       <c r="J9" t="n">
-        <v>30.24</v>
+        <v>30.36</v>
       </c>
       <c r="K9" t="n">
-        <v>30.34</v>
+        <v>30.47</v>
       </c>
       <c r="L9" t="n">
-        <v>30.43</v>
+        <v>30.59</v>
       </c>
       <c r="M9" t="n">
-        <v>30.53</v>
+        <v>30.94</v>
       </c>
       <c r="N9" t="n">
-        <v>30.63</v>
+        <v>31.28</v>
       </c>
       <c r="O9" t="n">
-        <v>30.73</v>
+        <v>31.17</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1279,30 +1275,22 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1318,50 +1306,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="C10" t="n">
-        <v>30.8</v>
+        <v>30.85</v>
       </c>
       <c r="D10" t="n">
-        <v>30.48</v>
+        <v>30.53</v>
       </c>
       <c r="E10" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.08</v>
+        <v>0.21</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0069</v>
       </c>
       <c r="H10" t="n">
         <v>0.32</v>
       </c>
       <c r="I10" t="n">
-        <v>29.78</v>
+        <v>30.16</v>
       </c>
       <c r="J10" t="n">
-        <v>30.36</v>
+        <v>30.29</v>
       </c>
       <c r="K10" t="n">
-        <v>30.47</v>
+        <v>30.46</v>
       </c>
       <c r="L10" t="n">
-        <v>30.59</v>
+        <v>30.63</v>
       </c>
       <c r="M10" t="n">
-        <v>30.94</v>
+        <v>30.78</v>
       </c>
       <c r="N10" t="n">
-        <v>31.28</v>
+        <v>30.93</v>
       </c>
       <c r="O10" t="n">
-        <v>31.17</v>
+        <v>31.12</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1374,11 +1362,13 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1391,78 +1381,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="C11" t="n">
-        <v>30.85</v>
+        <v>30.83</v>
       </c>
       <c r="D11" t="n">
-        <v>30.53</v>
+        <v>30.52</v>
       </c>
       <c r="E11" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="F11" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0017</v>
       </c>
       <c r="H11" t="n">
         <v>0.32</v>
       </c>
       <c r="I11" t="n">
-        <v>30.16</v>
+        <v>30.2</v>
       </c>
       <c r="J11" t="n">
-        <v>30.29</v>
+        <v>30.58</v>
       </c>
       <c r="K11" t="n">
-        <v>30.46</v>
+        <v>30.67</v>
       </c>
       <c r="L11" t="n">
-        <v>30.63</v>
+        <v>30.76</v>
       </c>
       <c r="M11" t="n">
-        <v>30.78</v>
+        <v>31</v>
       </c>
       <c r="N11" t="n">
-        <v>30.93</v>
+        <v>31.23</v>
       </c>
       <c r="O11" t="n">
-        <v>31.12</v>
+        <v>31.18</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1475,76 +1463,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="C12" t="n">
-        <v>30.83</v>
+        <v>31.01</v>
       </c>
       <c r="D12" t="n">
-        <v>30.52</v>
+        <v>30.76</v>
       </c>
       <c r="E12" t="n">
-        <v>30.78</v>
+        <v>30.97</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.05</v>
+        <v>0.19</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.006</v>
       </c>
       <c r="H12" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="I12" t="n">
         <v>30.2</v>
       </c>
       <c r="J12" t="n">
-        <v>30.58</v>
+        <v>30.52</v>
       </c>
       <c r="K12" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="L12" t="n">
-        <v>30.76</v>
+        <v>30.73</v>
       </c>
       <c r="M12" t="n">
-        <v>31</v>
+        <v>30.94</v>
       </c>
       <c r="N12" t="n">
-        <v>31.23</v>
+        <v>31.15</v>
       </c>
       <c r="O12" t="n">
-        <v>31.18</v>
+        <v>31.15</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1557,77 +1547,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.78</v>
+        <v>30.96</v>
       </c>
       <c r="C13" t="n">
-        <v>31.01</v>
+        <v>31.18</v>
       </c>
       <c r="D13" t="n">
-        <v>30.76</v>
+        <v>30.36</v>
       </c>
       <c r="E13" t="n">
-        <v>30.97</v>
+        <v>30.55</v>
       </c>
       <c r="F13" t="n">
-        <v>0.19</v>
+        <v>-0.41</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.0133</v>
       </c>
       <c r="H13" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="I13" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="J13" t="n">
-        <v>30.52</v>
+        <v>30.75</v>
       </c>
       <c r="K13" t="n">
-        <v>30.62</v>
+        <v>30.84</v>
       </c>
       <c r="L13" t="n">
-        <v>30.73</v>
+        <v>30.93</v>
       </c>
       <c r="M13" t="n">
-        <v>30.94</v>
+        <v>31.09</v>
       </c>
       <c r="N13" t="n">
-        <v>31.15</v>
+        <v>31.26</v>
       </c>
       <c r="O13" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>31.26</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1636,174 +1628,170 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.96</v>
+        <v>30.62</v>
       </c>
       <c r="C14" t="n">
-        <v>31.18</v>
+        <v>31.44</v>
       </c>
       <c r="D14" t="n">
-        <v>30.36</v>
+        <v>30.62</v>
       </c>
       <c r="E14" t="n">
-        <v>30.55</v>
+        <v>31.34</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.41</v>
+        <v>0.78</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0257</v>
       </c>
       <c r="H14" t="n">
         <v>0.82</v>
       </c>
       <c r="I14" t="n">
-        <v>30.5</v>
+        <v>29.54</v>
       </c>
       <c r="J14" t="n">
-        <v>30.75</v>
+        <v>29.63</v>
       </c>
       <c r="K14" t="n">
-        <v>30.84</v>
+        <v>30.15</v>
       </c>
       <c r="L14" t="n">
-        <v>30.93</v>
+        <v>30.66</v>
       </c>
       <c r="M14" t="n">
-        <v>31.09</v>
+        <v>30.96</v>
       </c>
       <c r="N14" t="n">
-        <v>31.26</v>
+        <v>31.27</v>
       </c>
       <c r="O14" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30.62</v>
+        <v>31.34</v>
       </c>
       <c r="C15" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="D15" t="n">
-        <v>30.62</v>
+        <v>30.65</v>
       </c>
       <c r="E15" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="F15" t="n">
-        <v>0.78</v>
+        <v>0.04</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0012</v>
       </c>
       <c r="H15" t="n">
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>29.54</v>
+        <v>29.81</v>
       </c>
       <c r="J15" t="n">
-        <v>29.63</v>
+        <v>30.67</v>
       </c>
       <c r="K15" t="n">
-        <v>30.15</v>
+        <v>30.93</v>
       </c>
       <c r="L15" t="n">
-        <v>30.66</v>
+        <v>31.19</v>
       </c>
       <c r="M15" t="n">
-        <v>30.96</v>
+        <v>31.75</v>
       </c>
       <c r="N15" t="n">
-        <v>31.27</v>
+        <v>32.31</v>
       </c>
       <c r="O15" t="n">
-        <v>32</v>
+        <v>32.26</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1818,63 +1806,59 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="C16" t="n">
-        <v>31.47</v>
+        <v>31.46</v>
       </c>
       <c r="D16" t="n">
-        <v>30.65</v>
+        <v>31.17</v>
       </c>
       <c r="E16" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0033</v>
       </c>
       <c r="H16" t="n">
-        <v>0.82</v>
+        <v>0.29</v>
       </c>
       <c r="I16" t="n">
-        <v>29.81</v>
+        <v>29.83</v>
       </c>
       <c r="J16" t="n">
-        <v>30.67</v>
+        <v>30.71</v>
       </c>
       <c r="K16" t="n">
-        <v>30.93</v>
+        <v>30.97</v>
       </c>
       <c r="L16" t="n">
-        <v>31.19</v>
+        <v>31.22</v>
       </c>
       <c r="M16" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="N16" t="n">
-        <v>32.31</v>
+        <v>32.36</v>
       </c>
       <c r="O16" t="n">
-        <v>32.26</v>
+        <v>32.3</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
@@ -1895,55 +1879,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="C17" t="n">
-        <v>31.46</v>
+        <v>31.32</v>
       </c>
       <c r="D17" t="n">
-        <v>31.17</v>
+        <v>31.08</v>
       </c>
       <c r="E17" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0015</v>
       </c>
       <c r="H17" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I17" t="n">
-        <v>29.83</v>
+        <v>30.88</v>
       </c>
       <c r="J17" t="n">
-        <v>30.71</v>
+        <v>30.96</v>
       </c>
       <c r="K17" t="n">
-        <v>30.97</v>
+        <v>31.13</v>
       </c>
       <c r="L17" t="n">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="M17" t="n">
-        <v>31.79</v>
+        <v>31.42</v>
       </c>
       <c r="N17" t="n">
-        <v>32.36</v>
+        <v>31.54</v>
       </c>
       <c r="O17" t="n">
-        <v>32.3</v>
+        <v>31.75</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1951,8 +1939,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
@@ -1982,50 +1972,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="C18" t="n">
-        <v>31.32</v>
+        <v>31.63</v>
       </c>
       <c r="D18" t="n">
-        <v>31.08</v>
+        <v>31.24</v>
       </c>
       <c r="E18" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0059</v>
       </c>
       <c r="H18" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="I18" t="n">
-        <v>30.88</v>
+        <v>30.83</v>
       </c>
       <c r="J18" t="n">
-        <v>30.96</v>
+        <v>31.14</v>
       </c>
       <c r="K18" t="n">
-        <v>31.13</v>
+        <v>31.2</v>
       </c>
       <c r="L18" t="n">
-        <v>31.3</v>
+        <v>31.26</v>
       </c>
       <c r="M18" t="n">
-        <v>31.42</v>
+        <v>31.44</v>
       </c>
       <c r="N18" t="n">
-        <v>31.54</v>
+        <v>31.62</v>
       </c>
       <c r="O18" t="n">
-        <v>31.75</v>
+        <v>31.56</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2033,83 +2023,83 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="C19" t="n">
-        <v>31.63</v>
+        <v>31.57</v>
       </c>
       <c r="D19" t="n">
-        <v>31.24</v>
+        <v>31.37</v>
       </c>
       <c r="E19" t="n">
-        <v>31.5</v>
+        <v>31.38</v>
       </c>
       <c r="F19" t="n">
-        <v>0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0039</v>
       </c>
       <c r="H19" t="n">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="I19" t="n">
-        <v>30.83</v>
+        <v>30.86</v>
       </c>
       <c r="J19" t="n">
-        <v>31.14</v>
+        <v>31.15</v>
       </c>
       <c r="K19" t="n">
-        <v>31.2</v>
+        <v>31.31</v>
       </c>
       <c r="L19" t="n">
-        <v>31.26</v>
+        <v>31.47</v>
       </c>
       <c r="M19" t="n">
-        <v>31.44</v>
+        <v>31.7</v>
       </c>
       <c r="N19" t="n">
-        <v>31.62</v>
+        <v>31.92</v>
       </c>
       <c r="O19" t="n">
-        <v>31.56</v>
+        <v>32.01</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2117,83 +2107,83 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31.5</v>
+        <v>31.39</v>
       </c>
       <c r="C20" t="n">
-        <v>31.57</v>
+        <v>31.46</v>
       </c>
       <c r="D20" t="n">
-        <v>31.37</v>
+        <v>31.25</v>
       </c>
       <c r="E20" t="n">
-        <v>31.38</v>
+        <v>31.36</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0007</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I20" t="n">
-        <v>30.86</v>
+        <v>31.16</v>
       </c>
       <c r="J20" t="n">
-        <v>31.15</v>
+        <v>31.13</v>
       </c>
       <c r="K20" t="n">
-        <v>31.31</v>
+        <v>31.28</v>
       </c>
       <c r="L20" t="n">
-        <v>31.47</v>
+        <v>31.42</v>
       </c>
       <c r="M20" t="n">
-        <v>31.7</v>
+        <v>31.48</v>
       </c>
       <c r="N20" t="n">
-        <v>31.92</v>
+        <v>31.54</v>
       </c>
       <c r="O20" t="n">
-        <v>32.01</v>
+        <v>31.78</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2203,12 +2193,12 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2227,57 +2217,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31.39</v>
+        <v>31.38</v>
       </c>
       <c r="C21" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="D21" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I21" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="J21" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="K21" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="L21" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="M21" t="n">
         <v>31.46</v>
       </c>
-      <c r="D21" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="E21" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-0.0007</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I21" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="J21" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="K21" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="L21" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="M21" t="n">
-        <v>31.48</v>
-      </c>
       <c r="N21" t="n">
-        <v>31.54</v>
+        <v>31.57</v>
       </c>
       <c r="O21" t="n">
-        <v>31.78</v>
+        <v>31.68</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2285,83 +2275,83 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31.38</v>
+        <v>31.6</v>
       </c>
       <c r="C22" t="n">
-        <v>31.68</v>
+        <v>31.74</v>
       </c>
       <c r="D22" t="n">
-        <v>31.35</v>
+        <v>31.51</v>
       </c>
       <c r="E22" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="F22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.23</v>
       </c>
-      <c r="G22" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.33</v>
-      </c>
       <c r="I22" t="n">
-        <v>31.04</v>
+        <v>31.02</v>
       </c>
       <c r="J22" t="n">
-        <v>31.15</v>
+        <v>31.31</v>
       </c>
       <c r="K22" t="n">
-        <v>31.25</v>
+        <v>31.43</v>
       </c>
       <c r="L22" t="n">
-        <v>31.36</v>
+        <v>31.55</v>
       </c>
       <c r="M22" t="n">
-        <v>31.46</v>
+        <v>31.76</v>
       </c>
       <c r="N22" t="n">
-        <v>31.57</v>
+        <v>31.96</v>
       </c>
       <c r="O22" t="n">
-        <v>31.68</v>
+        <v>32</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2374,23 +2364,17 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2402,63 +2386,67 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>31.6</v>
+        <v>31.61</v>
       </c>
       <c r="C23" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="D23" t="n">
-        <v>31.51</v>
+        <v>31.37</v>
       </c>
       <c r="E23" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0005</v>
+        <v>-0.0075</v>
       </c>
       <c r="H23" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="I23" t="n">
-        <v>31.02</v>
+        <v>31.27</v>
       </c>
       <c r="J23" t="n">
-        <v>31.31</v>
+        <v>31.37</v>
       </c>
       <c r="K23" t="n">
-        <v>31.43</v>
+        <v>31.49</v>
       </c>
       <c r="L23" t="n">
-        <v>31.55</v>
+        <v>31.62</v>
       </c>
       <c r="M23" t="n">
-        <v>31.76</v>
+        <v>31.73</v>
       </c>
       <c r="N23" t="n">
-        <v>31.96</v>
+        <v>31.83</v>
       </c>
       <c r="O23" t="n">
-        <v>32</v>
+        <v>31.98</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2475,80 +2463,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="C24" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="D24" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="E24" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I24" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="J24" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="K24" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="L24" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M24" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N24" t="n">
         <v>31.61</v>
       </c>
-      <c r="C24" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="D24" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="E24" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I24" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="J24" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="K24" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="L24" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="M24" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="N24" t="n">
-        <v>31.83</v>
-      </c>
       <c r="O24" t="n">
-        <v>31.98</v>
+        <v>32</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2559,57 +2553,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31.38</v>
+        <v>31.61</v>
       </c>
       <c r="C25" t="n">
-        <v>31.58</v>
+        <v>31.71</v>
       </c>
       <c r="D25" t="n">
-        <v>31.12</v>
+        <v>31.49</v>
       </c>
       <c r="E25" t="n">
         <v>31.58</v>
       </c>
       <c r="F25" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0003</v>
       </c>
       <c r="H25" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="I25" t="n">
-        <v>31.06</v>
+        <v>30.65</v>
       </c>
       <c r="J25" t="n">
-        <v>30.98</v>
+        <v>31.23</v>
       </c>
       <c r="K25" t="n">
-        <v>31.21</v>
+        <v>31.35</v>
       </c>
       <c r="L25" t="n">
-        <v>31.45</v>
+        <v>31.47</v>
       </c>
       <c r="M25" t="n">
-        <v>31.53</v>
+        <v>31.82</v>
       </c>
       <c r="N25" t="n">
-        <v>31.61</v>
+        <v>32.16</v>
       </c>
       <c r="O25" t="n">
-        <v>32</v>
+        <v>32.05</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2617,25 +2611,19 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2647,80 +2635,90 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>31.61</v>
       </c>
       <c r="C26" t="n">
-        <v>31.71</v>
+        <v>32.77</v>
       </c>
       <c r="D26" t="n">
-        <v>31.49</v>
+        <v>31.32</v>
       </c>
       <c r="E26" t="n">
-        <v>31.58</v>
+        <v>31.37</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0065</v>
       </c>
       <c r="H26" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="I26" t="n">
-        <v>30.65</v>
+        <v>31.27</v>
       </c>
       <c r="J26" t="n">
-        <v>31.23</v>
+        <v>31.34</v>
       </c>
       <c r="K26" t="n">
-        <v>31.35</v>
+        <v>31.46</v>
       </c>
       <c r="L26" t="n">
-        <v>31.47</v>
+        <v>31.59</v>
       </c>
       <c r="M26" t="n">
-        <v>31.82</v>
+        <v>31.69</v>
       </c>
       <c r="N26" t="n">
-        <v>32.16</v>
+        <v>31.79</v>
       </c>
       <c r="O26" t="n">
-        <v>32.05</v>
+        <v>31.94</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2729,90 +2727,80 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="C27" t="n">
-        <v>32.77</v>
+        <v>31.65</v>
       </c>
       <c r="D27" t="n">
-        <v>31.32</v>
+        <v>31.26</v>
       </c>
       <c r="E27" t="n">
-        <v>31.37</v>
+        <v>31.51</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.21</v>
+        <v>0.14</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0045</v>
       </c>
       <c r="H27" t="n">
-        <v>1.45</v>
+        <v>0.39</v>
       </c>
       <c r="I27" t="n">
-        <v>31.27</v>
+        <v>29.88</v>
       </c>
       <c r="J27" t="n">
-        <v>31.34</v>
+        <v>29.58</v>
       </c>
       <c r="K27" t="n">
-        <v>31.46</v>
+        <v>30.65</v>
       </c>
       <c r="L27" t="n">
-        <v>31.59</v>
+        <v>31.71</v>
       </c>
       <c r="M27" t="n">
-        <v>31.69</v>
+        <v>32.09</v>
       </c>
       <c r="N27" t="n">
-        <v>31.79</v>
+        <v>32.48</v>
       </c>
       <c r="O27" t="n">
-        <v>31.94</v>
+        <v>34.22</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2828,50 +2816,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31.37</v>
+        <v>31.47</v>
       </c>
       <c r="C28" t="n">
-        <v>31.65</v>
+        <v>31.5</v>
       </c>
       <c r="D28" t="n">
-        <v>31.26</v>
+        <v>31.18</v>
       </c>
       <c r="E28" t="n">
-        <v>31.51</v>
+        <v>31.38</v>
       </c>
       <c r="F28" t="n">
-        <v>0.14</v>
+        <v>-0.14</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0043</v>
       </c>
       <c r="H28" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="I28" t="n">
-        <v>29.88</v>
+        <v>30.87</v>
       </c>
       <c r="J28" t="n">
-        <v>29.58</v>
+        <v>31.14</v>
       </c>
       <c r="K28" t="n">
-        <v>30.65</v>
+        <v>31.31</v>
       </c>
       <c r="L28" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="M28" t="n">
         <v>31.71</v>
       </c>
-      <c r="M28" t="n">
-        <v>32.09</v>
-      </c>
       <c r="N28" t="n">
-        <v>32.48</v>
+        <v>31.93</v>
       </c>
       <c r="O28" t="n">
-        <v>34.22</v>
+        <v>32.05</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2879,12 +2867,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2903,57 +2893,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C29" t="n">
-        <v>31.5</v>
+        <v>31.96</v>
       </c>
       <c r="D29" t="n">
-        <v>31.18</v>
+        <v>31.39</v>
       </c>
       <c r="E29" t="n">
-        <v>31.38</v>
+        <v>31.8</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0136</v>
       </c>
       <c r="H29" t="n">
-        <v>0.32</v>
+        <v>0.57</v>
       </c>
       <c r="I29" t="n">
-        <v>30.87</v>
+        <v>30.86</v>
       </c>
       <c r="J29" t="n">
-        <v>31.14</v>
+        <v>31.08</v>
       </c>
       <c r="K29" t="n">
-        <v>31.31</v>
+        <v>31.22</v>
       </c>
       <c r="L29" t="n">
-        <v>31.48</v>
+        <v>31.36</v>
       </c>
       <c r="M29" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N29" t="n">
         <v>31.71</v>
       </c>
-      <c r="N29" t="n">
-        <v>31.93</v>
-      </c>
       <c r="O29" t="n">
-        <v>32.05</v>
+        <v>31.81</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2961,83 +2951,83 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>31.44</v>
+        <v>32.03</v>
       </c>
       <c r="C30" t="n">
-        <v>31.96</v>
+        <v>32.16</v>
       </c>
       <c r="D30" t="n">
-        <v>31.39</v>
+        <v>31.53</v>
       </c>
       <c r="E30" t="n">
-        <v>31.8</v>
+        <v>32.16</v>
       </c>
       <c r="F30" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0113</v>
       </c>
       <c r="H30" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="I30" t="n">
-        <v>30.86</v>
+        <v>30.82</v>
       </c>
       <c r="J30" t="n">
-        <v>31.08</v>
+        <v>31.29</v>
       </c>
       <c r="K30" t="n">
-        <v>31.22</v>
+        <v>31.52</v>
       </c>
       <c r="L30" t="n">
-        <v>31.36</v>
+        <v>31.74</v>
       </c>
       <c r="M30" t="n">
-        <v>31.53</v>
+        <v>32.09</v>
       </c>
       <c r="N30" t="n">
-        <v>31.71</v>
+        <v>32.44</v>
       </c>
       <c r="O30" t="n">
-        <v>31.81</v>
+        <v>32.54</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3055,18 +3045,14 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
@@ -3078,50 +3064,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="C31" t="n">
-        <v>32.16</v>
+        <v>32.12</v>
       </c>
       <c r="D31" t="n">
-        <v>31.53</v>
+        <v>31.8</v>
       </c>
       <c r="E31" t="n">
-        <v>32.16</v>
+        <v>32.02</v>
       </c>
       <c r="F31" t="n">
-        <v>0.36</v>
+        <v>-0.14</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0044</v>
       </c>
       <c r="H31" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="I31" t="n">
-        <v>30.82</v>
+        <v>30.91</v>
       </c>
       <c r="J31" t="n">
-        <v>31.29</v>
+        <v>31.69</v>
       </c>
       <c r="K31" t="n">
-        <v>31.52</v>
+        <v>31.85</v>
       </c>
       <c r="L31" t="n">
-        <v>31.74</v>
+        <v>32.01</v>
       </c>
       <c r="M31" t="n">
-        <v>32.09</v>
+        <v>32.48</v>
       </c>
       <c r="N31" t="n">
-        <v>32.44</v>
+        <v>32.95</v>
       </c>
       <c r="O31" t="n">
-        <v>32.54</v>
+        <v>32.79</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3129,18 +3115,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3153,55 +3139,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.09</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>32.12</v>
+        <v>32.14</v>
       </c>
       <c r="D32" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="E32" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0002</v>
       </c>
       <c r="H32" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I32" t="n">
-        <v>30.91</v>
+        <v>31.47</v>
       </c>
       <c r="J32" t="n">
-        <v>31.69</v>
+        <v>31.73</v>
       </c>
       <c r="K32" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="L32" t="n">
-        <v>32.01</v>
+        <v>31.99</v>
       </c>
       <c r="M32" t="n">
-        <v>32.48</v>
+        <v>32.18</v>
       </c>
       <c r="N32" t="n">
-        <v>32.95</v>
+        <v>32.38</v>
       </c>
       <c r="O32" t="n">
-        <v>32.79</v>
+        <v>32.44</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3235,57 +3225,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="C33" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="D33" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="E33" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I33" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="J33" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="L33" t="n">
         <v>32</v>
       </c>
-      <c r="C33" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="D33" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="E33" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I33" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="J33" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="K33" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="L33" t="n">
-        <v>31.99</v>
-      </c>
       <c r="M33" t="n">
-        <v>32.18</v>
+        <v>32.21</v>
       </c>
       <c r="N33" t="n">
-        <v>32.38</v>
+        <v>32.43</v>
       </c>
       <c r="O33" t="n">
-        <v>32.44</v>
+        <v>32.51</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3298,13 +3288,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3326,50 +3318,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
       <c r="C34" t="n">
-        <v>32.22</v>
+        <v>32.04</v>
       </c>
       <c r="D34" t="n">
-        <v>31.84</v>
+        <v>31.68</v>
       </c>
       <c r="E34" t="n">
-        <v>31.96</v>
+        <v>31.73</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0074</v>
       </c>
       <c r="H34" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I34" t="n">
-        <v>31.42</v>
+        <v>31.47</v>
       </c>
       <c r="J34" t="n">
-        <v>31.7</v>
+        <v>31.55</v>
       </c>
       <c r="K34" t="n">
-        <v>31.85</v>
+        <v>31.78</v>
       </c>
       <c r="L34" t="n">
         <v>32</v>
       </c>
       <c r="M34" t="n">
-        <v>32.21</v>
+        <v>32.15</v>
       </c>
       <c r="N34" t="n">
-        <v>32.43</v>
+        <v>32.3</v>
       </c>
       <c r="O34" t="n">
-        <v>32.51</v>
+        <v>32.59</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3379,18 +3371,16 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3405,57 +3395,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.96</v>
+        <v>31.77</v>
       </c>
       <c r="C35" t="n">
-        <v>32.04</v>
+        <v>31.87</v>
       </c>
       <c r="D35" t="n">
-        <v>31.68</v>
+        <v>31.37</v>
       </c>
       <c r="E35" t="n">
-        <v>31.73</v>
+        <v>31.47</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0083</v>
       </c>
       <c r="H35" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="I35" t="n">
-        <v>31.47</v>
+        <v>31.32</v>
       </c>
       <c r="J35" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K35" t="n">
         <v>31.55</v>
       </c>
-      <c r="K35" t="n">
-        <v>31.78</v>
-      </c>
       <c r="L35" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="M35" t="n">
-        <v>32.15</v>
+        <v>31.91</v>
       </c>
       <c r="N35" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O35" t="n">
-        <v>32.59</v>
+        <v>32.41</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3496,50 +3486,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.77</v>
+        <v>31.47</v>
       </c>
       <c r="C36" t="n">
-        <v>31.87</v>
+        <v>31.59</v>
       </c>
       <c r="D36" t="n">
-        <v>31.37</v>
+        <v>31.18</v>
       </c>
       <c r="E36" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0009</v>
       </c>
       <c r="H36" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="I36" t="n">
-        <v>31.32</v>
+        <v>30.88</v>
       </c>
       <c r="J36" t="n">
-        <v>31.3</v>
+        <v>30.89</v>
       </c>
       <c r="K36" t="n">
-        <v>31.55</v>
+        <v>31.22</v>
       </c>
       <c r="L36" t="n">
-        <v>31.8</v>
+        <v>31.54</v>
       </c>
       <c r="M36" t="n">
-        <v>31.91</v>
+        <v>31.71</v>
       </c>
       <c r="N36" t="n">
-        <v>32.02</v>
+        <v>31.88</v>
       </c>
       <c r="O36" t="n">
-        <v>32.41</v>
+        <v>32.36</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3549,12 +3539,12 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3580,50 +3570,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C37" t="n">
-        <v>31.59</v>
+        <v>31.75</v>
       </c>
       <c r="D37" t="n">
-        <v>31.18</v>
+        <v>31.38</v>
       </c>
       <c r="E37" t="n">
-        <v>31.44</v>
+        <v>31.55</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0037</v>
       </c>
       <c r="H37" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="I37" t="n">
-        <v>30.88</v>
+        <v>30.78</v>
       </c>
       <c r="J37" t="n">
-        <v>30.89</v>
+        <v>31.05</v>
       </c>
       <c r="K37" t="n">
-        <v>31.22</v>
+        <v>31.23</v>
       </c>
       <c r="L37" t="n">
-        <v>31.54</v>
+        <v>31.41</v>
       </c>
       <c r="M37" t="n">
-        <v>31.71</v>
+        <v>31.64</v>
       </c>
       <c r="N37" t="n">
-        <v>31.88</v>
+        <v>31.87</v>
       </c>
       <c r="O37" t="n">
-        <v>32.36</v>
+        <v>32</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3631,18 +3621,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3655,59 +3645,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.44</v>
+        <v>31.64</v>
       </c>
       <c r="C38" t="n">
-        <v>31.75</v>
+        <v>31.69</v>
       </c>
       <c r="D38" t="n">
-        <v>31.38</v>
+        <v>31.3</v>
       </c>
       <c r="E38" t="n">
-        <v>31.55</v>
+        <v>31.3</v>
       </c>
       <c r="F38" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="I38" t="n">
-        <v>30.78</v>
+        <v>31.02</v>
       </c>
       <c r="J38" t="n">
-        <v>31.05</v>
+        <v>31.18</v>
       </c>
       <c r="K38" t="n">
-        <v>31.23</v>
+        <v>31.37</v>
       </c>
       <c r="L38" t="n">
-        <v>31.41</v>
+        <v>31.56</v>
       </c>
       <c r="M38" t="n">
-        <v>31.64</v>
+        <v>31.74</v>
       </c>
       <c r="N38" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="O38" t="n">
-        <v>32</v>
+        <v>32.11</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3715,19 +3701,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3739,55 +3725,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.64</v>
+        <v>31.3</v>
       </c>
       <c r="C39" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="D39" t="n">
         <v>31.3</v>
       </c>
       <c r="E39" t="n">
-        <v>31.3</v>
+        <v>31.56</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.26</v>
+        <v>0.27</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="I39" t="n">
-        <v>31.02</v>
+        <v>30.9</v>
       </c>
       <c r="J39" t="n">
-        <v>31.18</v>
+        <v>30.8</v>
       </c>
       <c r="K39" t="n">
-        <v>31.37</v>
+        <v>31.1</v>
       </c>
       <c r="L39" t="n">
-        <v>31.56</v>
+        <v>31.39</v>
       </c>
       <c r="M39" t="n">
-        <v>31.74</v>
+        <v>31.49</v>
       </c>
       <c r="N39" t="n">
-        <v>31.91</v>
+        <v>31.59</v>
       </c>
       <c r="O39" t="n">
-        <v>32.11</v>
+        <v>32.09</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3795,22 +3785,24 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3821,57 +3813,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.3</v>
+        <v>31.59</v>
       </c>
       <c r="C40" t="n">
-        <v>31.62</v>
+        <v>31.78</v>
       </c>
       <c r="D40" t="n">
-        <v>31.3</v>
+        <v>31.36</v>
       </c>
       <c r="E40" t="n">
-        <v>31.56</v>
+        <v>31.36</v>
       </c>
       <c r="F40" t="n">
-        <v>0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0065</v>
       </c>
       <c r="H40" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="I40" t="n">
-        <v>30.9</v>
+        <v>30.98</v>
       </c>
       <c r="J40" t="n">
-        <v>30.8</v>
+        <v>31.29</v>
       </c>
       <c r="K40" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="L40" t="n">
-        <v>31.39</v>
+        <v>31.51</v>
       </c>
       <c r="M40" t="n">
-        <v>31.49</v>
+        <v>31.72</v>
       </c>
       <c r="N40" t="n">
-        <v>31.59</v>
+        <v>31.93</v>
       </c>
       <c r="O40" t="n">
-        <v>32.09</v>
+        <v>31.95</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3879,12 +3871,14 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3892,10 +3886,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3914,50 +3906,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.59</v>
+        <v>31.44</v>
       </c>
       <c r="C41" t="n">
-        <v>31.78</v>
+        <v>31.52</v>
       </c>
       <c r="D41" t="n">
-        <v>31.36</v>
+        <v>31.31</v>
       </c>
       <c r="E41" t="n">
-        <v>31.36</v>
+        <v>31.41</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0018</v>
       </c>
       <c r="H41" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="I41" t="n">
-        <v>30.98</v>
+        <v>30.94</v>
       </c>
       <c r="J41" t="n">
-        <v>31.29</v>
+        <v>30.83</v>
       </c>
       <c r="K41" t="n">
-        <v>31.4</v>
+        <v>31.15</v>
       </c>
       <c r="L41" t="n">
-        <v>31.51</v>
+        <v>31.46</v>
       </c>
       <c r="M41" t="n">
-        <v>31.72</v>
+        <v>31.57</v>
       </c>
       <c r="N41" t="n">
-        <v>31.93</v>
+        <v>31.67</v>
       </c>
       <c r="O41" t="n">
-        <v>31.95</v>
+        <v>32.2</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3965,20 +3957,16 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3993,57 +3981,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.44</v>
+        <v>31.41</v>
       </c>
       <c r="C42" t="n">
-        <v>31.52</v>
+        <v>31.6</v>
       </c>
       <c r="D42" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="E42" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I42" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J42" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="K42" t="n">
         <v>31.31</v>
       </c>
-      <c r="E42" t="n">
+      <c r="L42" t="n">
         <v>31.41</v>
       </c>
-      <c r="F42" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I42" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="J42" t="n">
-        <v>30.83</v>
-      </c>
-      <c r="K42" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="L42" t="n">
-        <v>31.46</v>
-      </c>
       <c r="M42" t="n">
-        <v>31.57</v>
+        <v>31.51</v>
       </c>
       <c r="N42" t="n">
-        <v>31.67</v>
+        <v>31.61</v>
       </c>
       <c r="O42" t="n">
-        <v>32.2</v>
+        <v>31.72</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4051,16 +4039,20 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4075,57 +4067,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.41</v>
+        <v>31.59</v>
       </c>
       <c r="C43" t="n">
-        <v>31.6</v>
+        <v>31.76</v>
       </c>
       <c r="D43" t="n">
-        <v>31.28</v>
+        <v>31.44</v>
       </c>
       <c r="E43" t="n">
         <v>31.56</v>
       </c>
       <c r="F43" t="n">
-        <v>0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0002</v>
       </c>
       <c r="H43" t="n">
         <v>0.33</v>
       </c>
       <c r="I43" t="n">
-        <v>31.11</v>
+        <v>30.95</v>
       </c>
       <c r="J43" t="n">
-        <v>31.21</v>
+        <v>31.3</v>
       </c>
       <c r="K43" t="n">
-        <v>31.31</v>
+        <v>31.4</v>
       </c>
       <c r="L43" t="n">
-        <v>31.41</v>
+        <v>31.5</v>
       </c>
       <c r="M43" t="n">
-        <v>31.51</v>
+        <v>31.73</v>
       </c>
       <c r="N43" t="n">
-        <v>31.61</v>
+        <v>31.95</v>
       </c>
       <c r="O43" t="n">
-        <v>31.72</v>
+        <v>31.93</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4133,19 +4125,17 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U43" s="8" t="n">
@@ -4168,50 +4158,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="C44" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="D44" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="E44" t="n">
-        <v>31.56</v>
+        <v>31.65</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0028</v>
       </c>
       <c r="H44" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="I44" t="n">
-        <v>30.95</v>
+        <v>31.11</v>
       </c>
       <c r="J44" t="n">
-        <v>31.3</v>
+        <v>31.21</v>
       </c>
       <c r="K44" t="n">
-        <v>31.4</v>
+        <v>31.39</v>
       </c>
       <c r="L44" t="n">
-        <v>31.5</v>
+        <v>31.58</v>
       </c>
       <c r="M44" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="N44" t="n">
-        <v>31.95</v>
+        <v>31.86</v>
       </c>
       <c r="O44" t="n">
-        <v>31.93</v>
+        <v>32.09</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4227,10 +4217,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4252,50 +4240,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="C45" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="D45" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E45" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I45" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="J45" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="K45" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="L45" t="n">
         <v>31.61</v>
       </c>
-      <c r="C45" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="D45" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="E45" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I45" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="J45" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="K45" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="L45" t="n">
-        <v>31.58</v>
-      </c>
       <c r="M45" t="n">
-        <v>31.72</v>
+        <v>31.76</v>
       </c>
       <c r="N45" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="O45" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4308,14 +4296,18 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4325,59 +4317,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.7</v>
+        <v>31.85</v>
       </c>
       <c r="C46" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="D46" t="n">
-        <v>31.58</v>
+        <v>31.79</v>
       </c>
       <c r="E46" t="n">
-        <v>31.84</v>
+        <v>31.9</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0016</v>
       </c>
       <c r="H46" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="I46" t="n">
-        <v>31.23</v>
+        <v>31.26</v>
       </c>
       <c r="J46" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="K46" t="n">
-        <v>31.53</v>
+        <v>31.68</v>
       </c>
       <c r="L46" t="n">
-        <v>31.61</v>
+        <v>31.79</v>
       </c>
       <c r="M46" t="n">
-        <v>31.76</v>
+        <v>32.01</v>
       </c>
       <c r="N46" t="n">
-        <v>31.91</v>
+        <v>32.22</v>
       </c>
       <c r="O46" t="n">
-        <v>31.93</v>
+        <v>32.23</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4390,18 +4378,14 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4416,50 +4400,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.85</v>
+        <v>31.93</v>
       </c>
       <c r="C47" t="n">
-        <v>31.96</v>
+        <v>32.23</v>
       </c>
       <c r="D47" t="n">
-        <v>31.79</v>
+        <v>31.92</v>
       </c>
       <c r="E47" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0063</v>
       </c>
       <c r="H47" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="I47" t="n">
-        <v>31.26</v>
+        <v>31.62</v>
       </c>
       <c r="J47" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K47" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="L47" t="n">
-        <v>31.79</v>
+        <v>31.89</v>
       </c>
       <c r="M47" t="n">
-        <v>32.01</v>
+        <v>31.98</v>
       </c>
       <c r="N47" t="n">
-        <v>32.22</v>
+        <v>32.08</v>
       </c>
       <c r="O47" t="n">
-        <v>32.23</v>
+        <v>32.13</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4472,17 +4456,23 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4494,50 +4484,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.93</v>
+        <v>32.1</v>
       </c>
       <c r="C48" t="n">
-        <v>32.23</v>
+        <v>32.42</v>
       </c>
       <c r="D48" t="n">
-        <v>31.92</v>
+        <v>32.03</v>
       </c>
       <c r="E48" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="I48" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="J48" t="n">
-        <v>31.74</v>
+        <v>31.8</v>
       </c>
       <c r="K48" t="n">
-        <v>31.81</v>
+        <v>31.94</v>
       </c>
       <c r="L48" t="n">
-        <v>31.89</v>
+        <v>32.09</v>
       </c>
       <c r="M48" t="n">
-        <v>31.98</v>
+        <v>32.25</v>
       </c>
       <c r="N48" t="n">
-        <v>32.08</v>
+        <v>32.42</v>
       </c>
       <c r="O48" t="n">
-        <v>32.13</v>
+        <v>32.53</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4563,10 +4553,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4578,50 +4566,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C49" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D49" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="E49" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I49" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="J49" t="n">
         <v>32.1</v>
       </c>
-      <c r="C49" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D49" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="E49" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I49" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="J49" t="n">
-        <v>31.8</v>
-      </c>
       <c r="K49" t="n">
-        <v>31.94</v>
+        <v>32.2</v>
       </c>
       <c r="L49" t="n">
-        <v>32.09</v>
+        <v>32.31</v>
       </c>
       <c r="M49" t="n">
-        <v>32.25</v>
+        <v>32.59</v>
       </c>
       <c r="N49" t="n">
-        <v>32.42</v>
+        <v>32.87</v>
       </c>
       <c r="O49" t="n">
-        <v>32.53</v>
+        <v>32.81</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4634,18 +4622,14 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4655,55 +4639,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32.31</v>
+        <v>32.32</v>
       </c>
       <c r="C50" t="n">
-        <v>32.49</v>
+        <v>32.55</v>
       </c>
       <c r="D50" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="E50" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I50" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="J50" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="K50" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="L50" t="n">
         <v>32.35</v>
       </c>
-      <c r="F50" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I50" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="J50" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="L50" t="n">
-        <v>32.31</v>
-      </c>
       <c r="M50" t="n">
-        <v>32.59</v>
+        <v>32.48</v>
       </c>
       <c r="N50" t="n">
-        <v>32.87</v>
+        <v>32.6</v>
       </c>
       <c r="O50" t="n">
-        <v>32.81</v>
+        <v>32.74</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4711,16 +4699,20 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4735,57 +4727,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.32</v>
+        <v>32.29</v>
       </c>
       <c r="C51" t="n">
-        <v>32.55</v>
+        <v>32.49</v>
       </c>
       <c r="D51" t="n">
-        <v>32.21</v>
+        <v>32.12</v>
       </c>
       <c r="E51" t="n">
-        <v>32.29</v>
+        <v>32.24</v>
       </c>
       <c r="F51" t="n">
         <v>-0.06</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="H51" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I51" t="n">
-        <v>31.98</v>
+        <v>31.86</v>
       </c>
       <c r="J51" t="n">
-        <v>32.09</v>
+        <v>31.91</v>
       </c>
       <c r="K51" t="n">
-        <v>32.22</v>
+        <v>32.12</v>
       </c>
       <c r="L51" t="n">
-        <v>32.35</v>
+        <v>32.34</v>
       </c>
       <c r="M51" t="n">
-        <v>32.48</v>
+        <v>32.47</v>
       </c>
       <c r="N51" t="n">
         <v>32.6</v>
       </c>
       <c r="O51" t="n">
-        <v>32.74</v>
+        <v>32.9</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4793,21 +4785,19 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4821,57 +4811,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="C52" t="n">
         <v>32.29</v>
       </c>
-      <c r="C52" t="n">
-        <v>32.49</v>
-      </c>
       <c r="D52" t="n">
-        <v>32.12</v>
+        <v>31.92</v>
       </c>
       <c r="E52" t="n">
-        <v>32.24</v>
+        <v>32.01</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.0071</v>
       </c>
       <c r="H52" t="n">
         <v>0.37</v>
       </c>
       <c r="I52" t="n">
-        <v>31.86</v>
+        <v>31.76</v>
       </c>
       <c r="J52" t="n">
-        <v>31.91</v>
+        <v>31.83</v>
       </c>
       <c r="K52" t="n">
-        <v>32.12</v>
+        <v>32.05</v>
       </c>
       <c r="L52" t="n">
-        <v>32.34</v>
+        <v>32.27</v>
       </c>
       <c r="M52" t="n">
-        <v>32.47</v>
+        <v>32.42</v>
       </c>
       <c r="N52" t="n">
-        <v>32.6</v>
+        <v>32.57</v>
       </c>
       <c r="O52" t="n">
-        <v>32.9</v>
+        <v>32.86</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4879,18 +4869,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4912,50 +4902,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>32.24</v>
+        <v>31.99</v>
       </c>
       <c r="C53" t="n">
-        <v>32.29</v>
+        <v>32.01</v>
       </c>
       <c r="D53" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E53" t="n">
-        <v>32.01</v>
+        <v>31.83</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0071</v>
+        <v>-0.0055</v>
       </c>
       <c r="H53" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="I53" t="n">
-        <v>31.76</v>
+        <v>31.55</v>
       </c>
       <c r="J53" t="n">
-        <v>31.83</v>
+        <v>31.59</v>
       </c>
       <c r="K53" t="n">
-        <v>32.05</v>
+        <v>31.82</v>
       </c>
       <c r="L53" t="n">
-        <v>32.27</v>
+        <v>32.06</v>
       </c>
       <c r="M53" t="n">
-        <v>32.42</v>
+        <v>32.19</v>
       </c>
       <c r="N53" t="n">
-        <v>32.57</v>
+        <v>32.33</v>
       </c>
       <c r="O53" t="n">
-        <v>32.86</v>
+        <v>32.66</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4996,60 +4986,62 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.99</v>
+        <v>31.82</v>
       </c>
       <c r="C54" t="n">
-        <v>32.01</v>
+        <v>31.91</v>
       </c>
       <c r="D54" t="n">
-        <v>31.75</v>
+        <v>31.55</v>
       </c>
       <c r="E54" t="n">
-        <v>31.83</v>
+        <v>31.62</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0066</v>
       </c>
       <c r="H54" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="I54" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J54" t="n">
         <v>31.55</v>
       </c>
-      <c r="J54" t="n">
-        <v>31.59</v>
-      </c>
       <c r="K54" t="n">
-        <v>31.82</v>
+        <v>31.7</v>
       </c>
       <c r="L54" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="M54" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="N54" t="n">
         <v>32.06</v>
       </c>
-      <c r="M54" t="n">
-        <v>32.19</v>
-      </c>
-      <c r="N54" t="n">
-        <v>32.33</v>
-      </c>
       <c r="O54" t="n">
-        <v>32.66</v>
+        <v>32.26</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5080,72 +5072,70 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.82</v>
+        <v>31.63</v>
       </c>
       <c r="C55" t="n">
-        <v>31.91</v>
+        <v>31.8</v>
       </c>
       <c r="D55" t="n">
-        <v>31.55</v>
+        <v>31.58</v>
       </c>
       <c r="E55" t="n">
-        <v>31.62</v>
+        <v>31.67</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.21</v>
+        <v>0.05</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0066</v>
+        <v>0.0016</v>
       </c>
       <c r="H55" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="I55" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="J55" t="n">
-        <v>31.55</v>
+        <v>31.21</v>
       </c>
       <c r="K55" t="n">
-        <v>31.7</v>
+        <v>31.44</v>
       </c>
       <c r="L55" t="n">
-        <v>31.86</v>
+        <v>31.68</v>
       </c>
       <c r="M55" t="n">
-        <v>31.96</v>
+        <v>31.8</v>
       </c>
       <c r="N55" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="O55" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5159,76 +5149,78 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="C56" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="D56" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="E56" t="n">
         <v>31.63</v>
       </c>
-      <c r="C56" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D56" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="E56" t="n">
-        <v>31.67</v>
-      </c>
       <c r="F56" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0013</v>
       </c>
       <c r="H56" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I56" t="n">
-        <v>31.2</v>
+        <v>31.37</v>
       </c>
       <c r="J56" t="n">
-        <v>31.21</v>
+        <v>31.44</v>
       </c>
       <c r="K56" t="n">
-        <v>31.44</v>
+        <v>31.56</v>
       </c>
       <c r="L56" t="n">
         <v>31.68</v>
       </c>
       <c r="M56" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="N56" t="n">
-        <v>31.92</v>
+        <v>31.88</v>
       </c>
       <c r="O56" t="n">
-        <v>32.27</v>
+        <v>32.02</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5243,78 +5235,76 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.62</v>
+        <v>31.68</v>
       </c>
       <c r="C57" t="n">
-        <v>31.69</v>
+        <v>31.94</v>
       </c>
       <c r="D57" t="n">
-        <v>31.42</v>
+        <v>31.61</v>
       </c>
       <c r="E57" t="n">
-        <v>31.63</v>
+        <v>31.76</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0043</v>
       </c>
       <c r="H57" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="I57" t="n">
-        <v>31.37</v>
+        <v>31.14</v>
       </c>
       <c r="J57" t="n">
-        <v>31.44</v>
+        <v>31.39</v>
       </c>
       <c r="K57" t="n">
-        <v>31.56</v>
+        <v>31.49</v>
       </c>
       <c r="L57" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M57" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="N57" t="n">
-        <v>31.88</v>
+        <v>31.94</v>
       </c>
       <c r="O57" t="n">
-        <v>32.02</v>
+        <v>31.97</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5327,59 +5317,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="C58" t="n">
-        <v>31.94</v>
+        <v>31.86</v>
       </c>
       <c r="D58" t="n">
-        <v>31.61</v>
+        <v>31.7</v>
       </c>
       <c r="E58" t="n">
-        <v>31.76</v>
+        <v>31.81</v>
       </c>
       <c r="F58" t="n">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0014</v>
       </c>
       <c r="H58" t="n">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="I58" t="n">
-        <v>31.14</v>
+        <v>31.29</v>
       </c>
       <c r="J58" t="n">
-        <v>31.39</v>
+        <v>31.44</v>
       </c>
       <c r="K58" t="n">
-        <v>31.49</v>
+        <v>31.6</v>
       </c>
       <c r="L58" t="n">
-        <v>31.59</v>
+        <v>31.77</v>
       </c>
       <c r="M58" t="n">
-        <v>31.77</v>
+        <v>31.93</v>
       </c>
       <c r="N58" t="n">
-        <v>31.94</v>
+        <v>32.08</v>
       </c>
       <c r="O58" t="n">
-        <v>31.97</v>
+        <v>32.26</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5392,13 +5378,11 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5411,7 +5395,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.28</v>
       </c>
       <c r="I2" t="n">
-        <v>28.99</v>
+        <v>29.12</v>
       </c>
       <c r="J2" t="n">
-        <v>29.36</v>
+        <v>29.41</v>
       </c>
       <c r="K2" t="n">
-        <v>29.88</v>
+        <v>29.92</v>
       </c>
       <c r="L2" t="n">
-        <v>30.41</v>
+        <v>30.42</v>
       </c>
       <c r="M2" t="n">
-        <v>30.85</v>
+        <v>30.82</v>
       </c>
       <c r="N2" t="n">
-        <v>31.3</v>
+        <v>31.22</v>
       </c>
       <c r="O2" t="n">
-        <v>31.9</v>
+        <v>31.83</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -5332,19 +5332,19 @@
         <v>31.86</v>
       </c>
       <c r="D58" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="E58" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="F58" t="n">
-        <v>0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0008</v>
       </c>
       <c r="H58" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="I58" t="n">
         <v>31.29</v>
@@ -5373,12 +5373,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5397,7 +5399,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.28</v>
       </c>
       <c r="I2" t="n">
-        <v>29.12</v>
+        <v>29.28</v>
       </c>
       <c r="J2" t="n">
-        <v>29.41</v>
+        <v>29.47</v>
       </c>
       <c r="K2" t="n">
-        <v>29.92</v>
+        <v>29.95</v>
       </c>
       <c r="L2" t="n">
-        <v>30.42</v>
+        <v>30.44</v>
       </c>
       <c r="M2" t="n">
-        <v>30.82</v>
+        <v>30.78</v>
       </c>
       <c r="N2" t="n">
-        <v>31.22</v>
+        <v>31.12</v>
       </c>
       <c r="O2" t="n">
-        <v>31.83</v>
+        <v>31.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -5335,13 +5335,13 @@
         <v>31.6</v>
       </c>
       <c r="E58" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0027</v>
       </c>
       <c r="H58" t="n">
         <v>0.26</v>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.28</v>
       </c>
       <c r="I2" t="n">
-        <v>29.28</v>
+        <v>29.58</v>
       </c>
       <c r="J2" t="n">
-        <v>29.47</v>
+        <v>29.58</v>
       </c>
       <c r="K2" t="n">
-        <v>29.95</v>
+        <v>30.03</v>
       </c>
       <c r="L2" t="n">
-        <v>30.44</v>
+        <v>30.48</v>
       </c>
       <c r="M2" t="n">
-        <v>30.78</v>
+        <v>30.7</v>
       </c>
       <c r="N2" t="n">
-        <v>31.12</v>
+        <v>30.93</v>
       </c>
       <c r="O2" t="n">
-        <v>31.75</v>
+        <v>31.6</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5335,16 +5335,16 @@
         <v>31.6</v>
       </c>
       <c r="E58" t="n">
-        <v>31.68</v>
+        <v>31.79</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0008</v>
       </c>
       <c r="H58" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="I58" t="n">
         <v>31.29</v>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,59 +659,67 @@
         <v>0.28</v>
       </c>
       <c r="I2" t="n">
-        <v>29.58</v>
+        <v>30.37</v>
       </c>
       <c r="J2" t="n">
-        <v>29.58</v>
+        <v>30.37</v>
       </c>
       <c r="K2" t="n">
-        <v>30.03</v>
+        <v>30.37</v>
       </c>
       <c r="L2" t="n">
-        <v>30.48</v>
+        <v>30.37</v>
       </c>
       <c r="M2" t="n">
-        <v>30.7</v>
+        <v>30.37</v>
       </c>
       <c r="N2" t="n">
-        <v>30.93</v>
+        <v>30.37</v>
       </c>
       <c r="O2" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>30.37</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5335,13 +5343,13 @@
         <v>31.6</v>
       </c>
       <c r="E58" t="n">
-        <v>31.79</v>
+        <v>31.71</v>
       </c>
       <c r="F58" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0016</v>
       </c>
       <c r="H58" t="n">
         <v>0.27</v>
@@ -5378,9 +5386,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5399,7 +5407,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,140 +634,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.37</v>
+        <v>30.56</v>
       </c>
       <c r="C2" t="n">
-        <v>30.65</v>
+        <v>30.8</v>
       </c>
       <c r="D2" t="n">
-        <v>30.37</v>
+        <v>30.32</v>
       </c>
       <c r="E2" t="n">
-        <v>30.56</v>
+        <v>30.53</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0012</v>
       </c>
       <c r="H2" t="n">
-        <v>0.28</v>
+        <v>0.47</v>
       </c>
       <c r="I2" t="n">
-        <v>30.37</v>
+        <v>30.09</v>
       </c>
       <c r="J2" t="n">
-        <v>30.37</v>
+        <v>30.31</v>
       </c>
       <c r="K2" t="n">
-        <v>30.37</v>
+        <v>30.42</v>
       </c>
       <c r="L2" t="n">
-        <v>30.37</v>
+        <v>30.54</v>
       </c>
       <c r="M2" t="n">
-        <v>30.37</v>
+        <v>30.7</v>
       </c>
       <c r="N2" t="n">
-        <v>30.37</v>
+        <v>30.87</v>
       </c>
       <c r="O2" t="n">
-        <v>30.37</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
+        <v>30.93</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.56</v>
+        <v>30.48</v>
       </c>
       <c r="C3" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.32</v>
+        <v>30.18</v>
       </c>
       <c r="E3" t="n">
-        <v>30.53</v>
+        <v>30.28</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.04</v>
+        <v>-0.24</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.008</v>
       </c>
       <c r="H3" t="n">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
       <c r="I3" t="n">
-        <v>30.09</v>
+        <v>29.85</v>
       </c>
       <c r="J3" t="n">
-        <v>30.31</v>
+        <v>30.04</v>
       </c>
       <c r="K3" t="n">
-        <v>30.42</v>
+        <v>30.29</v>
       </c>
       <c r="L3" t="n">
         <v>30.54</v>
       </c>
       <c r="M3" t="n">
-        <v>30.7</v>
+        <v>30.77</v>
       </c>
       <c r="N3" t="n">
-        <v>30.87</v>
+        <v>30.99</v>
       </c>
       <c r="O3" t="n">
-        <v>30.93</v>
+        <v>31.27</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -777,18 +773,16 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -803,57 +797,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.48</v>
+        <v>30.28</v>
       </c>
       <c r="C4" t="n">
-        <v>30.5</v>
+        <v>30.33</v>
       </c>
       <c r="D4" t="n">
-        <v>30.18</v>
+        <v>29.94</v>
       </c>
       <c r="E4" t="n">
-        <v>30.28</v>
+        <v>30.11</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="I4" t="n">
-        <v>29.85</v>
+        <v>29.86</v>
       </c>
       <c r="J4" t="n">
-        <v>30.04</v>
+        <v>29.93</v>
       </c>
       <c r="K4" t="n">
-        <v>30.29</v>
+        <v>30.12</v>
       </c>
       <c r="L4" t="n">
-        <v>30.54</v>
+        <v>30.31</v>
       </c>
       <c r="M4" t="n">
-        <v>30.77</v>
+        <v>30.45</v>
       </c>
       <c r="N4" t="n">
-        <v>30.99</v>
+        <v>30.58</v>
       </c>
       <c r="O4" t="n">
-        <v>31.27</v>
+        <v>30.83</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -866,7 +860,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -894,50 +888,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.28</v>
+        <v>30.22</v>
       </c>
       <c r="C5" t="n">
-        <v>30.33</v>
+        <v>30.59</v>
       </c>
       <c r="D5" t="n">
-        <v>29.94</v>
+        <v>30.15</v>
       </c>
       <c r="E5" t="n">
-        <v>30.11</v>
+        <v>30.44</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.17</v>
+        <v>0.33</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0111</v>
       </c>
       <c r="H5" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="I5" t="n">
-        <v>29.86</v>
+        <v>29.56</v>
       </c>
       <c r="J5" t="n">
-        <v>29.93</v>
+        <v>29.71</v>
       </c>
       <c r="K5" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="L5" t="n">
         <v>30.12</v>
       </c>
-      <c r="L5" t="n">
-        <v>30.31</v>
-      </c>
       <c r="M5" t="n">
-        <v>30.45</v>
+        <v>30.3</v>
       </c>
       <c r="N5" t="n">
-        <v>30.58</v>
+        <v>30.48</v>
       </c>
       <c r="O5" t="n">
-        <v>30.83</v>
+        <v>30.71</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -945,22 +939,24 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
@@ -969,59 +965,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="K6" t="n">
         <v>30.22</v>
       </c>
-      <c r="C6" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="D6" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="E6" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I6" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="J6" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="K6" t="n">
-        <v>29.92</v>
-      </c>
       <c r="L6" t="n">
-        <v>30.12</v>
+        <v>30.41</v>
       </c>
       <c r="M6" t="n">
-        <v>30.3</v>
+        <v>30.66</v>
       </c>
       <c r="N6" t="n">
-        <v>30.48</v>
+        <v>30.92</v>
       </c>
       <c r="O6" t="n">
-        <v>30.71</v>
+        <v>31.03</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1032,20 +1024,16 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1055,55 +1043,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.44</v>
+        <v>30.42</v>
       </c>
       <c r="C7" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I7" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="K7" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="L7" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="M7" t="n">
         <v>30.53</v>
       </c>
-      <c r="D7" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="J7" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="K7" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="L7" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="M7" t="n">
-        <v>30.66</v>
-      </c>
       <c r="N7" t="n">
-        <v>30.92</v>
+        <v>30.63</v>
       </c>
       <c r="O7" t="n">
-        <v>31.03</v>
+        <v>30.73</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,22 +1103,30 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1135,57 +1135,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.42</v>
+        <v>30.67</v>
       </c>
       <c r="C8" t="n">
-        <v>30.71</v>
+        <v>30.8</v>
       </c>
       <c r="D8" t="n">
-        <v>30.24</v>
+        <v>30.48</v>
       </c>
       <c r="E8" t="n">
-        <v>30.71</v>
+        <v>30.62</v>
       </c>
       <c r="F8" t="n">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.0027</v>
       </c>
       <c r="H8" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="I8" t="n">
-        <v>30.14</v>
+        <v>29.78</v>
       </c>
       <c r="J8" t="n">
-        <v>30.24</v>
+        <v>30.36</v>
       </c>
       <c r="K8" t="n">
-        <v>30.34</v>
+        <v>30.47</v>
       </c>
       <c r="L8" t="n">
-        <v>30.43</v>
+        <v>30.59</v>
       </c>
       <c r="M8" t="n">
-        <v>30.53</v>
+        <v>30.94</v>
       </c>
       <c r="N8" t="n">
-        <v>30.63</v>
+        <v>31.28</v>
       </c>
       <c r="O8" t="n">
-        <v>30.73</v>
+        <v>31.17</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1193,30 +1193,22 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1232,50 +1224,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="C9" t="n">
-        <v>30.8</v>
+        <v>30.85</v>
       </c>
       <c r="D9" t="n">
-        <v>30.48</v>
+        <v>30.53</v>
       </c>
       <c r="E9" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08</v>
+        <v>0.21</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0069</v>
       </c>
       <c r="H9" t="n">
         <v>0.32</v>
       </c>
       <c r="I9" t="n">
-        <v>29.78</v>
+        <v>30.16</v>
       </c>
       <c r="J9" t="n">
-        <v>30.36</v>
+        <v>30.29</v>
       </c>
       <c r="K9" t="n">
-        <v>30.47</v>
+        <v>30.46</v>
       </c>
       <c r="L9" t="n">
-        <v>30.59</v>
+        <v>30.63</v>
       </c>
       <c r="M9" t="n">
-        <v>30.94</v>
+        <v>30.78</v>
       </c>
       <c r="N9" t="n">
-        <v>31.28</v>
+        <v>30.93</v>
       </c>
       <c r="O9" t="n">
-        <v>31.17</v>
+        <v>31.12</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1286,13 +1278,15 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1305,78 +1299,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="C10" t="n">
-        <v>30.85</v>
+        <v>30.83</v>
       </c>
       <c r="D10" t="n">
-        <v>30.53</v>
+        <v>30.52</v>
       </c>
       <c r="E10" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="F10" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0017</v>
       </c>
       <c r="H10" t="n">
         <v>0.32</v>
       </c>
       <c r="I10" t="n">
-        <v>30.16</v>
+        <v>30.2</v>
       </c>
       <c r="J10" t="n">
-        <v>30.29</v>
+        <v>30.58</v>
       </c>
       <c r="K10" t="n">
-        <v>30.46</v>
+        <v>30.67</v>
       </c>
       <c r="L10" t="n">
-        <v>30.63</v>
+        <v>30.76</v>
       </c>
       <c r="M10" t="n">
-        <v>30.78</v>
+        <v>31</v>
       </c>
       <c r="N10" t="n">
-        <v>30.93</v>
+        <v>31.23</v>
       </c>
       <c r="O10" t="n">
-        <v>31.12</v>
+        <v>31.18</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1389,76 +1381,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="C11" t="n">
-        <v>30.83</v>
+        <v>31.01</v>
       </c>
       <c r="D11" t="n">
-        <v>30.52</v>
+        <v>30.76</v>
       </c>
       <c r="E11" t="n">
-        <v>30.78</v>
+        <v>30.97</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05</v>
+        <v>0.19</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.006</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="I11" t="n">
         <v>30.2</v>
       </c>
       <c r="J11" t="n">
-        <v>30.58</v>
+        <v>30.52</v>
       </c>
       <c r="K11" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="L11" t="n">
-        <v>30.76</v>
+        <v>30.73</v>
       </c>
       <c r="M11" t="n">
-        <v>31</v>
+        <v>30.94</v>
       </c>
       <c r="N11" t="n">
-        <v>31.23</v>
+        <v>31.15</v>
       </c>
       <c r="O11" t="n">
-        <v>31.18</v>
+        <v>31.15</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1471,77 +1465,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.78</v>
+        <v>30.96</v>
       </c>
       <c r="C12" t="n">
-        <v>31.01</v>
+        <v>31.18</v>
       </c>
       <c r="D12" t="n">
-        <v>30.76</v>
+        <v>30.36</v>
       </c>
       <c r="E12" t="n">
-        <v>30.97</v>
+        <v>30.55</v>
       </c>
       <c r="F12" t="n">
-        <v>0.19</v>
+        <v>-0.41</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.0133</v>
       </c>
       <c r="H12" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="J12" t="n">
-        <v>30.52</v>
+        <v>30.75</v>
       </c>
       <c r="K12" t="n">
-        <v>30.62</v>
+        <v>30.84</v>
       </c>
       <c r="L12" t="n">
-        <v>30.73</v>
+        <v>30.93</v>
       </c>
       <c r="M12" t="n">
-        <v>30.94</v>
+        <v>31.09</v>
       </c>
       <c r="N12" t="n">
-        <v>31.15</v>
+        <v>31.26</v>
       </c>
       <c r="O12" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+        <v>31.26</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1550,174 +1546,170 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.96</v>
+        <v>30.62</v>
       </c>
       <c r="C13" t="n">
-        <v>31.18</v>
+        <v>31.44</v>
       </c>
       <c r="D13" t="n">
-        <v>30.36</v>
+        <v>30.62</v>
       </c>
       <c r="E13" t="n">
-        <v>30.55</v>
+        <v>31.34</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.41</v>
+        <v>0.78</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0257</v>
       </c>
       <c r="H13" t="n">
         <v>0.82</v>
       </c>
       <c r="I13" t="n">
-        <v>30.5</v>
+        <v>29.54</v>
       </c>
       <c r="J13" t="n">
-        <v>30.75</v>
+        <v>29.63</v>
       </c>
       <c r="K13" t="n">
-        <v>30.84</v>
+        <v>30.15</v>
       </c>
       <c r="L13" t="n">
-        <v>30.93</v>
+        <v>30.66</v>
       </c>
       <c r="M13" t="n">
-        <v>31.09</v>
+        <v>30.96</v>
       </c>
       <c r="N13" t="n">
-        <v>31.26</v>
+        <v>31.27</v>
       </c>
       <c r="O13" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.62</v>
+        <v>31.34</v>
       </c>
       <c r="C14" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="D14" t="n">
-        <v>30.62</v>
+        <v>30.65</v>
       </c>
       <c r="E14" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="F14" t="n">
-        <v>0.78</v>
+        <v>0.04</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0012</v>
       </c>
       <c r="H14" t="n">
         <v>0.82</v>
       </c>
       <c r="I14" t="n">
-        <v>29.54</v>
+        <v>29.81</v>
       </c>
       <c r="J14" t="n">
-        <v>29.63</v>
+        <v>30.67</v>
       </c>
       <c r="K14" t="n">
-        <v>30.15</v>
+        <v>30.93</v>
       </c>
       <c r="L14" t="n">
-        <v>30.66</v>
+        <v>31.19</v>
       </c>
       <c r="M14" t="n">
-        <v>30.96</v>
+        <v>31.75</v>
       </c>
       <c r="N14" t="n">
-        <v>31.27</v>
+        <v>32.31</v>
       </c>
       <c r="O14" t="n">
-        <v>32</v>
+        <v>32.26</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1732,65 +1724,61 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="C15" t="n">
-        <v>31.47</v>
+        <v>31.46</v>
       </c>
       <c r="D15" t="n">
-        <v>30.65</v>
+        <v>31.17</v>
       </c>
       <c r="E15" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0033</v>
       </c>
       <c r="H15" t="n">
-        <v>0.82</v>
+        <v>0.29</v>
       </c>
       <c r="I15" t="n">
-        <v>29.81</v>
+        <v>29.83</v>
       </c>
       <c r="J15" t="n">
-        <v>30.67</v>
+        <v>30.71</v>
       </c>
       <c r="K15" t="n">
-        <v>30.93</v>
+        <v>30.97</v>
       </c>
       <c r="L15" t="n">
-        <v>31.19</v>
+        <v>31.22</v>
       </c>
       <c r="M15" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="N15" t="n">
-        <v>32.31</v>
+        <v>32.36</v>
       </c>
       <c r="O15" t="n">
-        <v>32.26</v>
+        <v>32.3</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1809,55 +1797,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="C16" t="n">
-        <v>31.46</v>
+        <v>31.32</v>
       </c>
       <c r="D16" t="n">
-        <v>31.17</v>
+        <v>31.08</v>
       </c>
       <c r="E16" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0015</v>
       </c>
       <c r="H16" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I16" t="n">
-        <v>29.83</v>
+        <v>30.88</v>
       </c>
       <c r="J16" t="n">
-        <v>30.71</v>
+        <v>30.96</v>
       </c>
       <c r="K16" t="n">
-        <v>30.97</v>
+        <v>31.13</v>
       </c>
       <c r="L16" t="n">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="M16" t="n">
-        <v>31.79</v>
+        <v>31.42</v>
       </c>
       <c r="N16" t="n">
-        <v>32.36</v>
+        <v>31.54</v>
       </c>
       <c r="O16" t="n">
-        <v>32.3</v>
+        <v>31.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1865,10 +1857,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1896,50 +1890,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="C17" t="n">
-        <v>31.32</v>
+        <v>31.63</v>
       </c>
       <c r="D17" t="n">
-        <v>31.08</v>
+        <v>31.24</v>
       </c>
       <c r="E17" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0059</v>
       </c>
       <c r="H17" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="I17" t="n">
-        <v>30.88</v>
+        <v>30.83</v>
       </c>
       <c r="J17" t="n">
-        <v>30.96</v>
+        <v>31.14</v>
       </c>
       <c r="K17" t="n">
-        <v>31.13</v>
+        <v>31.2</v>
       </c>
       <c r="L17" t="n">
-        <v>31.3</v>
+        <v>31.26</v>
       </c>
       <c r="M17" t="n">
-        <v>31.42</v>
+        <v>31.44</v>
       </c>
       <c r="N17" t="n">
-        <v>31.54</v>
+        <v>31.62</v>
       </c>
       <c r="O17" t="n">
-        <v>31.75</v>
+        <v>31.56</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1947,83 +1941,83 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="C18" t="n">
-        <v>31.63</v>
+        <v>31.57</v>
       </c>
       <c r="D18" t="n">
-        <v>31.24</v>
+        <v>31.37</v>
       </c>
       <c r="E18" t="n">
-        <v>31.5</v>
+        <v>31.38</v>
       </c>
       <c r="F18" t="n">
-        <v>0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0039</v>
       </c>
       <c r="H18" t="n">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>30.83</v>
+        <v>30.86</v>
       </c>
       <c r="J18" t="n">
-        <v>31.14</v>
+        <v>31.15</v>
       </c>
       <c r="K18" t="n">
-        <v>31.2</v>
+        <v>31.31</v>
       </c>
       <c r="L18" t="n">
-        <v>31.26</v>
+        <v>31.47</v>
       </c>
       <c r="M18" t="n">
-        <v>31.44</v>
+        <v>31.7</v>
       </c>
       <c r="N18" t="n">
-        <v>31.62</v>
+        <v>31.92</v>
       </c>
       <c r="O18" t="n">
-        <v>31.56</v>
+        <v>32.01</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2031,83 +2025,83 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31.5</v>
+        <v>31.39</v>
       </c>
       <c r="C19" t="n">
-        <v>31.57</v>
+        <v>31.46</v>
       </c>
       <c r="D19" t="n">
-        <v>31.37</v>
+        <v>31.25</v>
       </c>
       <c r="E19" t="n">
-        <v>31.38</v>
+        <v>31.36</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0007</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I19" t="n">
-        <v>30.86</v>
+        <v>31.16</v>
       </c>
       <c r="J19" t="n">
-        <v>31.15</v>
+        <v>31.13</v>
       </c>
       <c r="K19" t="n">
-        <v>31.31</v>
+        <v>31.28</v>
       </c>
       <c r="L19" t="n">
-        <v>31.47</v>
+        <v>31.42</v>
       </c>
       <c r="M19" t="n">
-        <v>31.7</v>
+        <v>31.48</v>
       </c>
       <c r="N19" t="n">
-        <v>31.92</v>
+        <v>31.54</v>
       </c>
       <c r="O19" t="n">
-        <v>32.01</v>
+        <v>31.78</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2117,12 +2111,12 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2141,57 +2135,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31.39</v>
+        <v>31.38</v>
       </c>
       <c r="C20" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="D20" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="E20" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I20" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="J20" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="K20" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="L20" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="M20" t="n">
         <v>31.46</v>
       </c>
-      <c r="D20" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="E20" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-0.0007</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I20" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="J20" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="K20" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="L20" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="M20" t="n">
-        <v>31.48</v>
-      </c>
       <c r="N20" t="n">
-        <v>31.54</v>
+        <v>31.57</v>
       </c>
       <c r="O20" t="n">
-        <v>31.78</v>
+        <v>31.68</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2199,83 +2193,83 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31.38</v>
+        <v>31.6</v>
       </c>
       <c r="C21" t="n">
-        <v>31.68</v>
+        <v>31.74</v>
       </c>
       <c r="D21" t="n">
-        <v>31.35</v>
+        <v>31.51</v>
       </c>
       <c r="E21" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="F21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.23</v>
       </c>
-      <c r="G21" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.33</v>
-      </c>
       <c r="I21" t="n">
-        <v>31.04</v>
+        <v>31.02</v>
       </c>
       <c r="J21" t="n">
-        <v>31.15</v>
+        <v>31.31</v>
       </c>
       <c r="K21" t="n">
-        <v>31.25</v>
+        <v>31.43</v>
       </c>
       <c r="L21" t="n">
-        <v>31.36</v>
+        <v>31.55</v>
       </c>
       <c r="M21" t="n">
-        <v>31.46</v>
+        <v>31.76</v>
       </c>
       <c r="N21" t="n">
-        <v>31.57</v>
+        <v>31.96</v>
       </c>
       <c r="O21" t="n">
-        <v>31.68</v>
+        <v>32</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2286,25 +2280,19 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2316,63 +2304,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31.6</v>
+        <v>31.61</v>
       </c>
       <c r="C22" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="D22" t="n">
-        <v>31.51</v>
+        <v>31.37</v>
       </c>
       <c r="E22" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0005</v>
+        <v>-0.0075</v>
       </c>
       <c r="H22" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="I22" t="n">
-        <v>31.02</v>
+        <v>31.27</v>
       </c>
       <c r="J22" t="n">
-        <v>31.31</v>
+        <v>31.37</v>
       </c>
       <c r="K22" t="n">
-        <v>31.43</v>
+        <v>31.49</v>
       </c>
       <c r="L22" t="n">
-        <v>31.55</v>
+        <v>31.62</v>
       </c>
       <c r="M22" t="n">
-        <v>31.76</v>
+        <v>31.73</v>
       </c>
       <c r="N22" t="n">
-        <v>31.96</v>
+        <v>31.83</v>
       </c>
       <c r="O22" t="n">
-        <v>32</v>
+        <v>31.98</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2389,80 +2381,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="C23" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="D23" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="E23" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I23" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="J23" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="K23" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="L23" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M23" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N23" t="n">
         <v>31.61</v>
       </c>
-      <c r="C23" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="D23" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="E23" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I23" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="J23" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="K23" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="L23" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="M23" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="N23" t="n">
-        <v>31.83</v>
-      </c>
       <c r="O23" t="n">
-        <v>31.98</v>
+        <v>32</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2473,57 +2471,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>31.38</v>
+        <v>31.61</v>
       </c>
       <c r="C24" t="n">
-        <v>31.58</v>
+        <v>31.71</v>
       </c>
       <c r="D24" t="n">
-        <v>31.12</v>
+        <v>31.49</v>
       </c>
       <c r="E24" t="n">
         <v>31.58</v>
       </c>
       <c r="F24" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0003</v>
       </c>
       <c r="H24" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="I24" t="n">
-        <v>31.06</v>
+        <v>30.65</v>
       </c>
       <c r="J24" t="n">
-        <v>30.98</v>
+        <v>31.23</v>
       </c>
       <c r="K24" t="n">
-        <v>31.21</v>
+        <v>31.35</v>
       </c>
       <c r="L24" t="n">
-        <v>31.45</v>
+        <v>31.47</v>
       </c>
       <c r="M24" t="n">
-        <v>31.53</v>
+        <v>31.82</v>
       </c>
       <c r="N24" t="n">
-        <v>31.61</v>
+        <v>32.16</v>
       </c>
       <c r="O24" t="n">
-        <v>32</v>
+        <v>32.05</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2531,25 +2529,19 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2561,80 +2553,90 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>31.61</v>
       </c>
       <c r="C25" t="n">
-        <v>31.71</v>
+        <v>32.77</v>
       </c>
       <c r="D25" t="n">
-        <v>31.49</v>
+        <v>31.32</v>
       </c>
       <c r="E25" t="n">
-        <v>31.58</v>
+        <v>31.37</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0065</v>
       </c>
       <c r="H25" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="I25" t="n">
-        <v>30.65</v>
+        <v>31.27</v>
       </c>
       <c r="J25" t="n">
-        <v>31.23</v>
+        <v>31.34</v>
       </c>
       <c r="K25" t="n">
-        <v>31.35</v>
+        <v>31.46</v>
       </c>
       <c r="L25" t="n">
-        <v>31.47</v>
+        <v>31.59</v>
       </c>
       <c r="M25" t="n">
-        <v>31.82</v>
+        <v>31.69</v>
       </c>
       <c r="N25" t="n">
-        <v>32.16</v>
+        <v>31.79</v>
       </c>
       <c r="O25" t="n">
-        <v>32.05</v>
+        <v>31.94</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2643,90 +2645,80 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="C26" t="n">
-        <v>32.77</v>
+        <v>31.65</v>
       </c>
       <c r="D26" t="n">
-        <v>31.32</v>
+        <v>31.26</v>
       </c>
       <c r="E26" t="n">
-        <v>31.37</v>
+        <v>31.51</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.21</v>
+        <v>0.14</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0045</v>
       </c>
       <c r="H26" t="n">
-        <v>1.45</v>
+        <v>0.39</v>
       </c>
       <c r="I26" t="n">
-        <v>31.27</v>
+        <v>29.88</v>
       </c>
       <c r="J26" t="n">
-        <v>31.34</v>
+        <v>29.58</v>
       </c>
       <c r="K26" t="n">
-        <v>31.46</v>
+        <v>30.65</v>
       </c>
       <c r="L26" t="n">
-        <v>31.59</v>
+        <v>31.71</v>
       </c>
       <c r="M26" t="n">
-        <v>31.69</v>
+        <v>32.09</v>
       </c>
       <c r="N26" t="n">
-        <v>31.79</v>
+        <v>32.48</v>
       </c>
       <c r="O26" t="n">
-        <v>31.94</v>
+        <v>34.22</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2742,50 +2734,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.37</v>
+        <v>31.47</v>
       </c>
       <c r="C27" t="n">
-        <v>31.65</v>
+        <v>31.5</v>
       </c>
       <c r="D27" t="n">
-        <v>31.26</v>
+        <v>31.18</v>
       </c>
       <c r="E27" t="n">
-        <v>31.51</v>
+        <v>31.38</v>
       </c>
       <c r="F27" t="n">
-        <v>0.14</v>
+        <v>-0.14</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0043</v>
       </c>
       <c r="H27" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="I27" t="n">
-        <v>29.88</v>
+        <v>30.87</v>
       </c>
       <c r="J27" t="n">
-        <v>29.58</v>
+        <v>31.14</v>
       </c>
       <c r="K27" t="n">
-        <v>30.65</v>
+        <v>31.31</v>
       </c>
       <c r="L27" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="M27" t="n">
         <v>31.71</v>
       </c>
-      <c r="M27" t="n">
-        <v>32.09</v>
-      </c>
       <c r="N27" t="n">
-        <v>32.48</v>
+        <v>31.93</v>
       </c>
       <c r="O27" t="n">
-        <v>34.22</v>
+        <v>32.05</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2793,12 +2785,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2817,57 +2811,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C28" t="n">
-        <v>31.5</v>
+        <v>31.96</v>
       </c>
       <c r="D28" t="n">
-        <v>31.18</v>
+        <v>31.39</v>
       </c>
       <c r="E28" t="n">
-        <v>31.38</v>
+        <v>31.8</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0136</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32</v>
+        <v>0.57</v>
       </c>
       <c r="I28" t="n">
-        <v>30.87</v>
+        <v>30.86</v>
       </c>
       <c r="J28" t="n">
-        <v>31.14</v>
+        <v>31.08</v>
       </c>
       <c r="K28" t="n">
-        <v>31.31</v>
+        <v>31.22</v>
       </c>
       <c r="L28" t="n">
-        <v>31.48</v>
+        <v>31.36</v>
       </c>
       <c r="M28" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N28" t="n">
         <v>31.71</v>
       </c>
-      <c r="N28" t="n">
-        <v>31.93</v>
-      </c>
       <c r="O28" t="n">
-        <v>32.05</v>
+        <v>31.81</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2875,83 +2869,83 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.44</v>
+        <v>32.03</v>
       </c>
       <c r="C29" t="n">
-        <v>31.96</v>
+        <v>32.16</v>
       </c>
       <c r="D29" t="n">
-        <v>31.39</v>
+        <v>31.53</v>
       </c>
       <c r="E29" t="n">
-        <v>31.8</v>
+        <v>32.16</v>
       </c>
       <c r="F29" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0113</v>
       </c>
       <c r="H29" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="I29" t="n">
-        <v>30.86</v>
+        <v>30.82</v>
       </c>
       <c r="J29" t="n">
-        <v>31.08</v>
+        <v>31.29</v>
       </c>
       <c r="K29" t="n">
-        <v>31.22</v>
+        <v>31.52</v>
       </c>
       <c r="L29" t="n">
-        <v>31.36</v>
+        <v>31.74</v>
       </c>
       <c r="M29" t="n">
-        <v>31.53</v>
+        <v>32.09</v>
       </c>
       <c r="N29" t="n">
-        <v>31.71</v>
+        <v>32.44</v>
       </c>
       <c r="O29" t="n">
-        <v>31.81</v>
+        <v>32.54</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2962,25 +2956,21 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2992,50 +2982,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="C30" t="n">
-        <v>32.16</v>
+        <v>32.12</v>
       </c>
       <c r="D30" t="n">
-        <v>31.53</v>
+        <v>31.8</v>
       </c>
       <c r="E30" t="n">
-        <v>32.16</v>
+        <v>32.02</v>
       </c>
       <c r="F30" t="n">
-        <v>0.36</v>
+        <v>-0.14</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0044</v>
       </c>
       <c r="H30" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="I30" t="n">
-        <v>30.82</v>
+        <v>30.91</v>
       </c>
       <c r="J30" t="n">
-        <v>31.29</v>
+        <v>31.69</v>
       </c>
       <c r="K30" t="n">
-        <v>31.52</v>
+        <v>31.85</v>
       </c>
       <c r="L30" t="n">
-        <v>31.74</v>
+        <v>32.01</v>
       </c>
       <c r="M30" t="n">
-        <v>32.09</v>
+        <v>32.48</v>
       </c>
       <c r="N30" t="n">
-        <v>32.44</v>
+        <v>32.95</v>
       </c>
       <c r="O30" t="n">
-        <v>32.54</v>
+        <v>32.79</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3043,18 +3033,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3067,55 +3057,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.09</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>32.12</v>
+        <v>32.14</v>
       </c>
       <c r="D31" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="E31" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0002</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I31" t="n">
-        <v>30.91</v>
+        <v>31.47</v>
       </c>
       <c r="J31" t="n">
-        <v>31.69</v>
+        <v>31.73</v>
       </c>
       <c r="K31" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="L31" t="n">
-        <v>32.01</v>
+        <v>31.99</v>
       </c>
       <c r="M31" t="n">
-        <v>32.48</v>
+        <v>32.18</v>
       </c>
       <c r="N31" t="n">
-        <v>32.95</v>
+        <v>32.38</v>
       </c>
       <c r="O31" t="n">
-        <v>32.79</v>
+        <v>32.44</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3128,7 +3122,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3149,57 +3143,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="C32" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="D32" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="E32" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I32" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="J32" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="L32" t="n">
         <v>32</v>
       </c>
-      <c r="C32" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="D32" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="E32" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I32" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="J32" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="K32" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="L32" t="n">
-        <v>31.99</v>
-      </c>
       <c r="M32" t="n">
-        <v>32.18</v>
+        <v>32.21</v>
       </c>
       <c r="N32" t="n">
-        <v>32.38</v>
+        <v>32.43</v>
       </c>
       <c r="O32" t="n">
-        <v>32.44</v>
+        <v>32.51</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3214,11 +3208,13 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3240,50 +3236,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
       <c r="C33" t="n">
-        <v>32.22</v>
+        <v>32.04</v>
       </c>
       <c r="D33" t="n">
-        <v>31.84</v>
+        <v>31.68</v>
       </c>
       <c r="E33" t="n">
-        <v>31.96</v>
+        <v>31.73</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0074</v>
       </c>
       <c r="H33" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I33" t="n">
-        <v>31.42</v>
+        <v>31.47</v>
       </c>
       <c r="J33" t="n">
-        <v>31.7</v>
+        <v>31.55</v>
       </c>
       <c r="K33" t="n">
-        <v>31.85</v>
+        <v>31.78</v>
       </c>
       <c r="L33" t="n">
         <v>32</v>
       </c>
       <c r="M33" t="n">
-        <v>32.21</v>
+        <v>32.15</v>
       </c>
       <c r="N33" t="n">
-        <v>32.43</v>
+        <v>32.3</v>
       </c>
       <c r="O33" t="n">
-        <v>32.51</v>
+        <v>32.59</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3293,18 +3289,16 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3319,57 +3313,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.96</v>
+        <v>31.77</v>
       </c>
       <c r="C34" t="n">
-        <v>32.04</v>
+        <v>31.87</v>
       </c>
       <c r="D34" t="n">
-        <v>31.68</v>
+        <v>31.37</v>
       </c>
       <c r="E34" t="n">
-        <v>31.73</v>
+        <v>31.47</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0083</v>
       </c>
       <c r="H34" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="I34" t="n">
-        <v>31.47</v>
+        <v>31.32</v>
       </c>
       <c r="J34" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K34" t="n">
         <v>31.55</v>
       </c>
-      <c r="K34" t="n">
-        <v>31.78</v>
-      </c>
       <c r="L34" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="M34" t="n">
-        <v>32.15</v>
+        <v>31.91</v>
       </c>
       <c r="N34" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O34" t="n">
-        <v>32.59</v>
+        <v>32.41</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3382,7 +3376,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3410,50 +3404,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.77</v>
+        <v>31.47</v>
       </c>
       <c r="C35" t="n">
-        <v>31.87</v>
+        <v>31.59</v>
       </c>
       <c r="D35" t="n">
-        <v>31.37</v>
+        <v>31.18</v>
       </c>
       <c r="E35" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0009</v>
       </c>
       <c r="H35" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="I35" t="n">
-        <v>31.32</v>
+        <v>30.88</v>
       </c>
       <c r="J35" t="n">
-        <v>31.3</v>
+        <v>30.89</v>
       </c>
       <c r="K35" t="n">
-        <v>31.55</v>
+        <v>31.22</v>
       </c>
       <c r="L35" t="n">
-        <v>31.8</v>
+        <v>31.54</v>
       </c>
       <c r="M35" t="n">
-        <v>31.91</v>
+        <v>31.71</v>
       </c>
       <c r="N35" t="n">
-        <v>32.02</v>
+        <v>31.88</v>
       </c>
       <c r="O35" t="n">
-        <v>32.41</v>
+        <v>32.36</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3463,12 +3457,12 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3494,50 +3488,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C36" t="n">
-        <v>31.59</v>
+        <v>31.75</v>
       </c>
       <c r="D36" t="n">
-        <v>31.18</v>
+        <v>31.38</v>
       </c>
       <c r="E36" t="n">
-        <v>31.44</v>
+        <v>31.55</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0037</v>
       </c>
       <c r="H36" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="I36" t="n">
-        <v>30.88</v>
+        <v>30.78</v>
       </c>
       <c r="J36" t="n">
-        <v>30.89</v>
+        <v>31.05</v>
       </c>
       <c r="K36" t="n">
-        <v>31.22</v>
+        <v>31.23</v>
       </c>
       <c r="L36" t="n">
-        <v>31.54</v>
+        <v>31.41</v>
       </c>
       <c r="M36" t="n">
-        <v>31.71</v>
+        <v>31.64</v>
       </c>
       <c r="N36" t="n">
-        <v>31.88</v>
+        <v>31.87</v>
       </c>
       <c r="O36" t="n">
-        <v>32.36</v>
+        <v>32</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3545,18 +3539,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3569,59 +3563,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.44</v>
+        <v>31.64</v>
       </c>
       <c r="C37" t="n">
-        <v>31.75</v>
+        <v>31.69</v>
       </c>
       <c r="D37" t="n">
-        <v>31.38</v>
+        <v>31.3</v>
       </c>
       <c r="E37" t="n">
-        <v>31.55</v>
+        <v>31.3</v>
       </c>
       <c r="F37" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="I37" t="n">
-        <v>30.78</v>
+        <v>31.02</v>
       </c>
       <c r="J37" t="n">
-        <v>31.05</v>
+        <v>31.18</v>
       </c>
       <c r="K37" t="n">
-        <v>31.23</v>
+        <v>31.37</v>
       </c>
       <c r="L37" t="n">
-        <v>31.41</v>
+        <v>31.56</v>
       </c>
       <c r="M37" t="n">
-        <v>31.64</v>
+        <v>31.74</v>
       </c>
       <c r="N37" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="O37" t="n">
-        <v>32</v>
+        <v>32.11</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3629,18 +3619,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3653,55 +3643,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.64</v>
+        <v>31.3</v>
       </c>
       <c r="C38" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="D38" t="n">
         <v>31.3</v>
       </c>
       <c r="E38" t="n">
-        <v>31.3</v>
+        <v>31.56</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.26</v>
+        <v>0.27</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="I38" t="n">
-        <v>31.02</v>
+        <v>30.9</v>
       </c>
       <c r="J38" t="n">
-        <v>31.18</v>
+        <v>30.8</v>
       </c>
       <c r="K38" t="n">
-        <v>31.37</v>
+        <v>31.1</v>
       </c>
       <c r="L38" t="n">
-        <v>31.56</v>
+        <v>31.39</v>
       </c>
       <c r="M38" t="n">
-        <v>31.74</v>
+        <v>31.49</v>
       </c>
       <c r="N38" t="n">
-        <v>31.91</v>
+        <v>31.59</v>
       </c>
       <c r="O38" t="n">
-        <v>32.11</v>
+        <v>32.09</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3709,22 +3703,24 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3735,57 +3731,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.3</v>
+        <v>31.59</v>
       </c>
       <c r="C39" t="n">
-        <v>31.62</v>
+        <v>31.78</v>
       </c>
       <c r="D39" t="n">
-        <v>31.3</v>
+        <v>31.36</v>
       </c>
       <c r="E39" t="n">
-        <v>31.56</v>
+        <v>31.36</v>
       </c>
       <c r="F39" t="n">
-        <v>0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0065</v>
       </c>
       <c r="H39" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="I39" t="n">
-        <v>30.9</v>
+        <v>30.98</v>
       </c>
       <c r="J39" t="n">
-        <v>30.8</v>
+        <v>31.29</v>
       </c>
       <c r="K39" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="L39" t="n">
-        <v>31.39</v>
+        <v>31.51</v>
       </c>
       <c r="M39" t="n">
-        <v>31.49</v>
+        <v>31.72</v>
       </c>
       <c r="N39" t="n">
-        <v>31.59</v>
+        <v>31.93</v>
       </c>
       <c r="O39" t="n">
-        <v>32.09</v>
+        <v>31.95</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3793,12 +3789,14 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3806,10 +3804,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3828,50 +3824,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.59</v>
+        <v>31.44</v>
       </c>
       <c r="C40" t="n">
-        <v>31.78</v>
+        <v>31.52</v>
       </c>
       <c r="D40" t="n">
-        <v>31.36</v>
+        <v>31.31</v>
       </c>
       <c r="E40" t="n">
-        <v>31.36</v>
+        <v>31.41</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0018</v>
       </c>
       <c r="H40" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="I40" t="n">
-        <v>30.98</v>
+        <v>30.94</v>
       </c>
       <c r="J40" t="n">
-        <v>31.29</v>
+        <v>30.83</v>
       </c>
       <c r="K40" t="n">
-        <v>31.4</v>
+        <v>31.15</v>
       </c>
       <c r="L40" t="n">
-        <v>31.51</v>
+        <v>31.46</v>
       </c>
       <c r="M40" t="n">
-        <v>31.72</v>
+        <v>31.57</v>
       </c>
       <c r="N40" t="n">
-        <v>31.93</v>
+        <v>31.67</v>
       </c>
       <c r="O40" t="n">
-        <v>31.95</v>
+        <v>32.2</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3879,20 +3875,16 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3907,57 +3899,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.44</v>
+        <v>31.41</v>
       </c>
       <c r="C41" t="n">
-        <v>31.52</v>
+        <v>31.6</v>
       </c>
       <c r="D41" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="E41" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I41" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J41" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="K41" t="n">
         <v>31.31</v>
       </c>
-      <c r="E41" t="n">
+      <c r="L41" t="n">
         <v>31.41</v>
       </c>
-      <c r="F41" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I41" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="J41" t="n">
-        <v>30.83</v>
-      </c>
-      <c r="K41" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="L41" t="n">
-        <v>31.46</v>
-      </c>
       <c r="M41" t="n">
-        <v>31.57</v>
+        <v>31.51</v>
       </c>
       <c r="N41" t="n">
-        <v>31.67</v>
+        <v>31.61</v>
       </c>
       <c r="O41" t="n">
-        <v>32.2</v>
+        <v>31.72</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3965,16 +3957,20 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3989,57 +3985,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.41</v>
+        <v>31.59</v>
       </c>
       <c r="C42" t="n">
-        <v>31.6</v>
+        <v>31.76</v>
       </c>
       <c r="D42" t="n">
-        <v>31.28</v>
+        <v>31.44</v>
       </c>
       <c r="E42" t="n">
         <v>31.56</v>
       </c>
       <c r="F42" t="n">
-        <v>0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0002</v>
       </c>
       <c r="H42" t="n">
         <v>0.33</v>
       </c>
       <c r="I42" t="n">
-        <v>31.11</v>
+        <v>30.95</v>
       </c>
       <c r="J42" t="n">
-        <v>31.21</v>
+        <v>31.3</v>
       </c>
       <c r="K42" t="n">
-        <v>31.31</v>
+        <v>31.4</v>
       </c>
       <c r="L42" t="n">
-        <v>31.41</v>
+        <v>31.5</v>
       </c>
       <c r="M42" t="n">
-        <v>31.51</v>
+        <v>31.73</v>
       </c>
       <c r="N42" t="n">
-        <v>31.61</v>
+        <v>31.95</v>
       </c>
       <c r="O42" t="n">
-        <v>31.72</v>
+        <v>31.93</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4047,19 +4043,17 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4082,50 +4076,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="C43" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="D43" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="E43" t="n">
-        <v>31.56</v>
+        <v>31.65</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0028</v>
       </c>
       <c r="H43" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="I43" t="n">
-        <v>30.95</v>
+        <v>31.11</v>
       </c>
       <c r="J43" t="n">
-        <v>31.3</v>
+        <v>31.21</v>
       </c>
       <c r="K43" t="n">
-        <v>31.4</v>
+        <v>31.39</v>
       </c>
       <c r="L43" t="n">
-        <v>31.5</v>
+        <v>31.58</v>
       </c>
       <c r="M43" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="N43" t="n">
-        <v>31.95</v>
+        <v>31.86</v>
       </c>
       <c r="O43" t="n">
-        <v>31.93</v>
+        <v>32.09</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4136,15 +4130,13 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4166,50 +4158,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="C44" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="D44" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E44" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I44" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="J44" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="K44" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="L44" t="n">
         <v>31.61</v>
       </c>
-      <c r="C44" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="D44" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="E44" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I44" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="J44" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="K44" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="L44" t="n">
-        <v>31.58</v>
-      </c>
       <c r="M44" t="n">
-        <v>31.72</v>
+        <v>31.76</v>
       </c>
       <c r="N44" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="O44" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4220,16 +4212,20 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4239,59 +4235,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.7</v>
+        <v>31.85</v>
       </c>
       <c r="C45" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="D45" t="n">
-        <v>31.58</v>
+        <v>31.79</v>
       </c>
       <c r="E45" t="n">
-        <v>31.84</v>
+        <v>31.9</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0016</v>
       </c>
       <c r="H45" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="I45" t="n">
-        <v>31.23</v>
+        <v>31.26</v>
       </c>
       <c r="J45" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="K45" t="n">
-        <v>31.53</v>
+        <v>31.68</v>
       </c>
       <c r="L45" t="n">
-        <v>31.61</v>
+        <v>31.79</v>
       </c>
       <c r="M45" t="n">
-        <v>31.76</v>
+        <v>32.01</v>
       </c>
       <c r="N45" t="n">
-        <v>31.91</v>
+        <v>32.22</v>
       </c>
       <c r="O45" t="n">
-        <v>31.93</v>
+        <v>32.23</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4302,20 +4294,16 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4330,50 +4318,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.85</v>
+        <v>31.93</v>
       </c>
       <c r="C46" t="n">
-        <v>31.96</v>
+        <v>32.23</v>
       </c>
       <c r="D46" t="n">
-        <v>31.79</v>
+        <v>31.92</v>
       </c>
       <c r="E46" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="F46" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0063</v>
       </c>
       <c r="H46" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="I46" t="n">
-        <v>31.26</v>
+        <v>31.62</v>
       </c>
       <c r="J46" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K46" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="L46" t="n">
-        <v>31.79</v>
+        <v>31.89</v>
       </c>
       <c r="M46" t="n">
-        <v>32.01</v>
+        <v>31.98</v>
       </c>
       <c r="N46" t="n">
-        <v>32.22</v>
+        <v>32.08</v>
       </c>
       <c r="O46" t="n">
-        <v>32.23</v>
+        <v>32.13</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4384,19 +4372,25 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
@@ -4408,50 +4402,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31.93</v>
+        <v>32.1</v>
       </c>
       <c r="C47" t="n">
-        <v>32.23</v>
+        <v>32.42</v>
       </c>
       <c r="D47" t="n">
-        <v>31.92</v>
+        <v>32.03</v>
       </c>
       <c r="E47" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="I47" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="J47" t="n">
-        <v>31.74</v>
+        <v>31.8</v>
       </c>
       <c r="K47" t="n">
-        <v>31.81</v>
+        <v>31.94</v>
       </c>
       <c r="L47" t="n">
-        <v>31.89</v>
+        <v>32.09</v>
       </c>
       <c r="M47" t="n">
-        <v>31.98</v>
+        <v>32.25</v>
       </c>
       <c r="N47" t="n">
-        <v>32.08</v>
+        <v>32.42</v>
       </c>
       <c r="O47" t="n">
-        <v>32.13</v>
+        <v>32.53</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4462,7 +4456,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4477,10 +4471,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4492,50 +4484,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C48" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D48" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="E48" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I48" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="J48" t="n">
         <v>32.1</v>
       </c>
-      <c r="C48" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D48" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="E48" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I48" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="J48" t="n">
-        <v>31.8</v>
-      </c>
       <c r="K48" t="n">
-        <v>31.94</v>
+        <v>32.2</v>
       </c>
       <c r="L48" t="n">
-        <v>32.09</v>
+        <v>32.31</v>
       </c>
       <c r="M48" t="n">
-        <v>32.25</v>
+        <v>32.59</v>
       </c>
       <c r="N48" t="n">
-        <v>32.42</v>
+        <v>32.87</v>
       </c>
       <c r="O48" t="n">
-        <v>32.53</v>
+        <v>32.81</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4546,20 +4538,16 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4569,55 +4557,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>32.31</v>
+        <v>32.32</v>
       </c>
       <c r="C49" t="n">
-        <v>32.49</v>
+        <v>32.55</v>
       </c>
       <c r="D49" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="E49" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I49" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="J49" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="K49" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="L49" t="n">
         <v>32.35</v>
       </c>
-      <c r="F49" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I49" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="J49" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="L49" t="n">
-        <v>32.31</v>
-      </c>
       <c r="M49" t="n">
-        <v>32.59</v>
+        <v>32.48</v>
       </c>
       <c r="N49" t="n">
-        <v>32.87</v>
+        <v>32.6</v>
       </c>
       <c r="O49" t="n">
-        <v>32.81</v>
+        <v>32.74</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4625,16 +4617,20 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4649,57 +4645,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32.32</v>
+        <v>32.29</v>
       </c>
       <c r="C50" t="n">
-        <v>32.55</v>
+        <v>32.49</v>
       </c>
       <c r="D50" t="n">
-        <v>32.21</v>
+        <v>32.12</v>
       </c>
       <c r="E50" t="n">
-        <v>32.29</v>
+        <v>32.24</v>
       </c>
       <c r="F50" t="n">
         <v>-0.06</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="H50" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I50" t="n">
-        <v>31.98</v>
+        <v>31.86</v>
       </c>
       <c r="J50" t="n">
-        <v>32.09</v>
+        <v>31.91</v>
       </c>
       <c r="K50" t="n">
-        <v>32.22</v>
+        <v>32.12</v>
       </c>
       <c r="L50" t="n">
-        <v>32.35</v>
+        <v>32.34</v>
       </c>
       <c r="M50" t="n">
-        <v>32.48</v>
+        <v>32.47</v>
       </c>
       <c r="N50" t="n">
         <v>32.6</v>
       </c>
       <c r="O50" t="n">
-        <v>32.74</v>
+        <v>32.9</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4707,21 +4703,19 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4735,57 +4729,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="C51" t="n">
         <v>32.29</v>
       </c>
-      <c r="C51" t="n">
-        <v>32.49</v>
-      </c>
       <c r="D51" t="n">
-        <v>32.12</v>
+        <v>31.92</v>
       </c>
       <c r="E51" t="n">
-        <v>32.24</v>
+        <v>32.01</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.0071</v>
       </c>
       <c r="H51" t="n">
         <v>0.37</v>
       </c>
       <c r="I51" t="n">
-        <v>31.86</v>
+        <v>31.76</v>
       </c>
       <c r="J51" t="n">
-        <v>31.91</v>
+        <v>31.83</v>
       </c>
       <c r="K51" t="n">
-        <v>32.12</v>
+        <v>32.05</v>
       </c>
       <c r="L51" t="n">
-        <v>32.34</v>
+        <v>32.27</v>
       </c>
       <c r="M51" t="n">
-        <v>32.47</v>
+        <v>32.42</v>
       </c>
       <c r="N51" t="n">
-        <v>32.6</v>
+        <v>32.57</v>
       </c>
       <c r="O51" t="n">
-        <v>32.9</v>
+        <v>32.86</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4793,18 +4787,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4826,50 +4820,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>32.24</v>
+        <v>31.99</v>
       </c>
       <c r="C52" t="n">
-        <v>32.29</v>
+        <v>32.01</v>
       </c>
       <c r="D52" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E52" t="n">
-        <v>32.01</v>
+        <v>31.83</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0071</v>
+        <v>-0.0055</v>
       </c>
       <c r="H52" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="I52" t="n">
-        <v>31.76</v>
+        <v>31.55</v>
       </c>
       <c r="J52" t="n">
-        <v>31.83</v>
+        <v>31.59</v>
       </c>
       <c r="K52" t="n">
-        <v>32.05</v>
+        <v>31.82</v>
       </c>
       <c r="L52" t="n">
-        <v>32.27</v>
+        <v>32.06</v>
       </c>
       <c r="M52" t="n">
-        <v>32.42</v>
+        <v>32.19</v>
       </c>
       <c r="N52" t="n">
-        <v>32.57</v>
+        <v>32.33</v>
       </c>
       <c r="O52" t="n">
-        <v>32.86</v>
+        <v>32.66</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4882,7 +4876,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4910,63 +4904,65 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.99</v>
+        <v>31.82</v>
       </c>
       <c r="C53" t="n">
-        <v>32.01</v>
+        <v>31.91</v>
       </c>
       <c r="D53" t="n">
-        <v>31.75</v>
+        <v>31.55</v>
       </c>
       <c r="E53" t="n">
-        <v>31.83</v>
+        <v>31.62</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0066</v>
       </c>
       <c r="H53" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="I53" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J53" t="n">
         <v>31.55</v>
       </c>
-      <c r="J53" t="n">
-        <v>31.59</v>
-      </c>
       <c r="K53" t="n">
-        <v>31.82</v>
+        <v>31.7</v>
       </c>
       <c r="L53" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="M53" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="N53" t="n">
         <v>32.06</v>
       </c>
-      <c r="M53" t="n">
-        <v>32.19</v>
-      </c>
-      <c r="N53" t="n">
-        <v>32.33</v>
-      </c>
       <c r="O53" t="n">
-        <v>32.66</v>
+        <v>32.26</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4994,72 +4990,70 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.82</v>
+        <v>31.63</v>
       </c>
       <c r="C54" t="n">
-        <v>31.91</v>
+        <v>31.8</v>
       </c>
       <c r="D54" t="n">
-        <v>31.55</v>
+        <v>31.58</v>
       </c>
       <c r="E54" t="n">
-        <v>31.62</v>
+        <v>31.67</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.21</v>
+        <v>0.05</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0066</v>
+        <v>0.0016</v>
       </c>
       <c r="H54" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="I54" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="J54" t="n">
-        <v>31.55</v>
+        <v>31.21</v>
       </c>
       <c r="K54" t="n">
-        <v>31.7</v>
+        <v>31.44</v>
       </c>
       <c r="L54" t="n">
-        <v>31.86</v>
+        <v>31.68</v>
       </c>
       <c r="M54" t="n">
-        <v>31.96</v>
+        <v>31.8</v>
       </c>
       <c r="N54" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="O54" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5073,76 +5067,78 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="C55" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="D55" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="E55" t="n">
         <v>31.63</v>
       </c>
-      <c r="C55" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D55" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="E55" t="n">
-        <v>31.67</v>
-      </c>
       <c r="F55" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0013</v>
       </c>
       <c r="H55" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I55" t="n">
-        <v>31.2</v>
+        <v>31.37</v>
       </c>
       <c r="J55" t="n">
-        <v>31.21</v>
+        <v>31.44</v>
       </c>
       <c r="K55" t="n">
-        <v>31.44</v>
+        <v>31.56</v>
       </c>
       <c r="L55" t="n">
         <v>31.68</v>
       </c>
       <c r="M55" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="N55" t="n">
-        <v>31.92</v>
+        <v>31.88</v>
       </c>
       <c r="O55" t="n">
-        <v>32.27</v>
+        <v>32.02</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5157,78 +5153,76 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.62</v>
+        <v>31.68</v>
       </c>
       <c r="C56" t="n">
-        <v>31.69</v>
+        <v>31.94</v>
       </c>
       <c r="D56" t="n">
-        <v>31.42</v>
+        <v>31.61</v>
       </c>
       <c r="E56" t="n">
-        <v>31.63</v>
+        <v>31.76</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0043</v>
       </c>
       <c r="H56" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="I56" t="n">
-        <v>31.37</v>
+        <v>31.14</v>
       </c>
       <c r="J56" t="n">
-        <v>31.44</v>
+        <v>31.39</v>
       </c>
       <c r="K56" t="n">
-        <v>31.56</v>
+        <v>31.49</v>
       </c>
       <c r="L56" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M56" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="N56" t="n">
-        <v>31.88</v>
+        <v>31.94</v>
       </c>
       <c r="O56" t="n">
-        <v>32.02</v>
+        <v>31.97</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5241,59 +5235,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="C57" t="n">
-        <v>31.94</v>
+        <v>31.86</v>
       </c>
       <c r="D57" t="n">
-        <v>31.61</v>
+        <v>31.6</v>
       </c>
       <c r="E57" t="n">
-        <v>31.76</v>
+        <v>31.71</v>
       </c>
       <c r="F57" t="n">
-        <v>0.14</v>
+        <v>-0.05</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0016</v>
       </c>
       <c r="H57" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="I57" t="n">
-        <v>31.14</v>
+        <v>31.29</v>
       </c>
       <c r="J57" t="n">
-        <v>31.39</v>
+        <v>31.44</v>
       </c>
       <c r="K57" t="n">
-        <v>31.49</v>
+        <v>31.6</v>
       </c>
       <c r="L57" t="n">
-        <v>31.59</v>
+        <v>31.77</v>
       </c>
       <c r="M57" t="n">
-        <v>31.77</v>
+        <v>31.93</v>
       </c>
       <c r="N57" t="n">
-        <v>31.94</v>
+        <v>32.08</v>
       </c>
       <c r="O57" t="n">
-        <v>31.97</v>
+        <v>32.26</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5301,18 +5291,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5325,55 +5315,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.81</v>
+        <v>31.78</v>
       </c>
       <c r="C58" t="n">
-        <v>31.86</v>
+        <v>31.82</v>
       </c>
       <c r="D58" t="n">
-        <v>31.6</v>
+        <v>31.73</v>
       </c>
       <c r="E58" t="n">
-        <v>31.71</v>
+        <v>31.78</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.002</v>
       </c>
       <c r="H58" t="n">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="I58" t="n">
-        <v>31.29</v>
+        <v>31.33</v>
       </c>
       <c r="J58" t="n">
         <v>31.44</v>
       </c>
       <c r="K58" t="n">
-        <v>31.6</v>
+        <v>31.58</v>
       </c>
       <c r="L58" t="n">
-        <v>31.77</v>
+        <v>31.72</v>
       </c>
       <c r="M58" t="n">
-        <v>31.93</v>
+        <v>31.85</v>
       </c>
       <c r="N58" t="n">
-        <v>32.08</v>
+        <v>31.97</v>
       </c>
       <c r="O58" t="n">
-        <v>32.26</v>
+        <v>32.13</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5381,14 +5375,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5407,7 +5399,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,31 +659,33 @@
         <v>0.47</v>
       </c>
       <c r="I2" t="n">
-        <v>30.09</v>
+        <v>30.17</v>
       </c>
       <c r="J2" t="n">
-        <v>30.31</v>
+        <v>30.34</v>
       </c>
       <c r="K2" t="n">
-        <v>30.42</v>
+        <v>30.44</v>
       </c>
       <c r="L2" t="n">
-        <v>30.54</v>
+        <v>30.55</v>
       </c>
       <c r="M2" t="n">
-        <v>30.7</v>
+        <v>30.68</v>
       </c>
       <c r="N2" t="n">
-        <v>30.87</v>
+        <v>30.82</v>
       </c>
       <c r="O2" t="n">
-        <v>30.93</v>
+        <v>30.89</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -5331,7 +5333,7 @@
         <v>31.78</v>
       </c>
       <c r="C58" t="n">
-        <v>31.82</v>
+        <v>31.9</v>
       </c>
       <c r="D58" t="n">
         <v>31.73</v>
@@ -5343,10 +5345,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0022</v>
       </c>
       <c r="H58" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="I58" t="n">
         <v>31.33</v>
@@ -5383,8 +5385,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5397,11 +5401,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.47</v>
       </c>
       <c r="I2" t="n">
-        <v>30.17</v>
+        <v>30.25</v>
       </c>
       <c r="J2" t="n">
-        <v>30.34</v>
+        <v>30.37</v>
       </c>
       <c r="K2" t="n">
-        <v>30.44</v>
+        <v>30.46</v>
       </c>
       <c r="L2" t="n">
-        <v>30.55</v>
+        <v>30.56</v>
       </c>
       <c r="M2" t="n">
-        <v>30.68</v>
+        <v>30.66</v>
       </c>
       <c r="N2" t="n">
-        <v>30.82</v>
+        <v>30.77</v>
       </c>
       <c r="O2" t="n">
-        <v>30.89</v>
+        <v>30.85</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -702,8 +702,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5339,13 +5341,13 @@
         <v>31.73</v>
       </c>
       <c r="E58" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="F58" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.0043</v>
       </c>
       <c r="H58" t="n">
         <v>0.18</v>
@@ -5382,12 +5384,12 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.47</v>
       </c>
       <c r="I2" t="n">
-        <v>30.25</v>
+        <v>30.28</v>
       </c>
       <c r="J2" t="n">
-        <v>30.37</v>
+        <v>30.41</v>
       </c>
       <c r="K2" t="n">
-        <v>30.46</v>
+        <v>30.48</v>
       </c>
       <c r="L2" t="n">
-        <v>30.56</v>
+        <v>30.55</v>
       </c>
       <c r="M2" t="n">
-        <v>30.66</v>
+        <v>30.65</v>
       </c>
       <c r="N2" t="n">
-        <v>30.77</v>
+        <v>30.75</v>
       </c>
       <c r="O2" t="n">
-        <v>30.85</v>
+        <v>30.79</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -707,8 +707,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5335,22 +5337,22 @@
         <v>31.78</v>
       </c>
       <c r="C58" t="n">
-        <v>31.9</v>
+        <v>32.07</v>
       </c>
       <c r="D58" t="n">
         <v>31.73</v>
       </c>
       <c r="E58" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="F58" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0049</v>
       </c>
       <c r="H58" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="I58" t="n">
         <v>31.33</v>
@@ -5392,8 +5394,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,28 +659,30 @@
         <v>0.47</v>
       </c>
       <c r="I2" t="n">
-        <v>30.28</v>
+        <v>30.56</v>
       </c>
       <c r="J2" t="n">
-        <v>30.41</v>
+        <v>30.56</v>
       </c>
       <c r="K2" t="n">
-        <v>30.48</v>
+        <v>30.56</v>
       </c>
       <c r="L2" t="n">
-        <v>30.55</v>
+        <v>30.56</v>
       </c>
       <c r="M2" t="n">
-        <v>30.65</v>
+        <v>30.56</v>
       </c>
       <c r="N2" t="n">
-        <v>30.75</v>
+        <v>30.56</v>
       </c>
       <c r="O2" t="n">
-        <v>30.79</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>30.56</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
@@ -694,7 +696,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -714,12 +716,12 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -798,14 +800,10 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -882,14 +880,10 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -968,10 +962,14 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1046,12 +1044,12 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1132,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1216,7 +1214,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1300,7 +1298,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1382,7 +1380,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1466,7 +1464,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1552,7 +1550,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1638,7 +1636,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1720,7 +1718,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1798,7 +1796,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1882,7 +1880,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1970,7 +1968,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2050,7 +2048,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2134,7 +2132,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2222,7 +2220,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2300,7 +2298,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2382,7 +2380,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2470,7 +2468,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2552,7 +2550,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2644,7 +2642,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2726,7 +2724,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2810,7 +2808,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2898,7 +2896,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2978,7 +2976,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3058,7 +3056,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3142,7 +3140,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3228,7 +3226,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3312,7 +3310,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3396,7 +3394,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3480,7 +3478,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3564,7 +3562,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3644,7 +3642,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3730,7 +3728,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3816,7 +3814,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3898,7 +3896,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3984,7 +3982,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4068,7 +4066,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4150,7 +4148,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4236,7 +4234,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4314,7 +4312,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4398,7 +4396,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4480,7 +4478,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4558,7 +4556,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4644,7 +4642,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4728,7 +4726,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4812,7 +4810,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4896,7 +4894,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4982,7 +4980,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5066,7 +5064,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5152,7 +5150,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5236,7 +5234,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5316,7 +5314,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5343,13 +5341,13 @@
         <v>31.73</v>
       </c>
       <c r="E58" t="n">
-        <v>31.87</v>
+        <v>31.81</v>
       </c>
       <c r="F58" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0029</v>
       </c>
       <c r="H58" t="n">
         <v>0.34</v>
@@ -5402,7 +5400,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,144 +634,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.56</v>
+        <v>30.48</v>
       </c>
       <c r="C2" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="D2" t="n">
-        <v>30.32</v>
+        <v>30.18</v>
       </c>
       <c r="E2" t="n">
-        <v>30.53</v>
+        <v>30.28</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.04</v>
+        <v>-0.24</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.008</v>
       </c>
       <c r="H2" t="n">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
       <c r="I2" t="n">
-        <v>30.56</v>
+        <v>29.85</v>
       </c>
       <c r="J2" t="n">
-        <v>30.56</v>
+        <v>30.04</v>
       </c>
       <c r="K2" t="n">
-        <v>30.56</v>
+        <v>30.29</v>
       </c>
       <c r="L2" t="n">
-        <v>30.56</v>
+        <v>30.54</v>
       </c>
       <c r="M2" t="n">
-        <v>30.56</v>
+        <v>30.77</v>
       </c>
       <c r="N2" t="n">
-        <v>30.56</v>
+        <v>30.99</v>
       </c>
       <c r="O2" t="n">
-        <v>30.56</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>31.27</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.48</v>
+        <v>30.28</v>
       </c>
       <c r="C3" t="n">
-        <v>30.5</v>
+        <v>30.33</v>
       </c>
       <c r="D3" t="n">
-        <v>30.18</v>
+        <v>29.94</v>
       </c>
       <c r="E3" t="n">
-        <v>30.28</v>
+        <v>30.11</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0058</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="I3" t="n">
-        <v>29.85</v>
+        <v>29.86</v>
       </c>
       <c r="J3" t="n">
-        <v>30.04</v>
+        <v>29.93</v>
       </c>
       <c r="K3" t="n">
-        <v>30.29</v>
+        <v>30.12</v>
       </c>
       <c r="L3" t="n">
-        <v>30.54</v>
+        <v>30.31</v>
       </c>
       <c r="M3" t="n">
-        <v>30.77</v>
+        <v>30.45</v>
       </c>
       <c r="N3" t="n">
-        <v>30.99</v>
+        <v>30.58</v>
       </c>
       <c r="O3" t="n">
-        <v>31.27</v>
+        <v>30.83</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -800,58 +790,62 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.28</v>
+        <v>30.22</v>
       </c>
       <c r="C4" t="n">
-        <v>30.33</v>
+        <v>30.59</v>
       </c>
       <c r="D4" t="n">
-        <v>29.94</v>
+        <v>30.15</v>
       </c>
       <c r="E4" t="n">
-        <v>30.11</v>
+        <v>30.44</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.17</v>
+        <v>0.33</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0111</v>
       </c>
       <c r="H4" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="I4" t="n">
-        <v>29.86</v>
+        <v>29.56</v>
       </c>
       <c r="J4" t="n">
-        <v>29.93</v>
+        <v>29.71</v>
       </c>
       <c r="K4" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="L4" t="n">
         <v>30.12</v>
       </c>
-      <c r="L4" t="n">
-        <v>30.31</v>
-      </c>
       <c r="M4" t="n">
-        <v>30.45</v>
+        <v>30.3</v>
       </c>
       <c r="N4" t="n">
-        <v>30.58</v>
+        <v>30.48</v>
       </c>
       <c r="O4" t="n">
-        <v>30.83</v>
+        <v>30.71</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,28 +853,30 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -888,50 +884,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="C5" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="K5" t="n">
         <v>30.22</v>
       </c>
-      <c r="C5" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="D5" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="E5" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I5" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="J5" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="K5" t="n">
-        <v>29.92</v>
-      </c>
       <c r="L5" t="n">
-        <v>30.12</v>
+        <v>30.41</v>
       </c>
       <c r="M5" t="n">
-        <v>30.3</v>
+        <v>30.66</v>
       </c>
       <c r="N5" t="n">
-        <v>30.48</v>
+        <v>30.92</v>
       </c>
       <c r="O5" t="n">
-        <v>30.71</v>
+        <v>31.03</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -944,80 +940,76 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.44</v>
+        <v>30.42</v>
       </c>
       <c r="C6" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="M6" t="n">
         <v>30.53</v>
       </c>
-      <c r="D6" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="E6" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="J6" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="K6" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="L6" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="M6" t="n">
-        <v>30.66</v>
-      </c>
       <c r="N6" t="n">
-        <v>30.92</v>
+        <v>30.63</v>
       </c>
       <c r="O6" t="n">
-        <v>31.03</v>
+        <v>30.73</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,26 +1017,34 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1056,50 +1056,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.42</v>
+        <v>30.67</v>
       </c>
       <c r="C7" t="n">
-        <v>30.71</v>
+        <v>30.8</v>
       </c>
       <c r="D7" t="n">
-        <v>30.24</v>
+        <v>30.48</v>
       </c>
       <c r="E7" t="n">
-        <v>30.71</v>
+        <v>30.62</v>
       </c>
       <c r="F7" t="n">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.0027</v>
       </c>
       <c r="H7" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="I7" t="n">
-        <v>30.14</v>
+        <v>29.78</v>
       </c>
       <c r="J7" t="n">
-        <v>30.24</v>
+        <v>30.36</v>
       </c>
       <c r="K7" t="n">
-        <v>30.34</v>
+        <v>30.47</v>
       </c>
       <c r="L7" t="n">
-        <v>30.43</v>
+        <v>30.59</v>
       </c>
       <c r="M7" t="n">
-        <v>30.53</v>
+        <v>30.94</v>
       </c>
       <c r="N7" t="n">
-        <v>30.63</v>
+        <v>31.28</v>
       </c>
       <c r="O7" t="n">
-        <v>30.73</v>
+        <v>31.17</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,32 +1107,24 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1146,50 +1138,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="C8" t="n">
-        <v>30.8</v>
+        <v>30.85</v>
       </c>
       <c r="D8" t="n">
-        <v>30.48</v>
+        <v>30.53</v>
       </c>
       <c r="E8" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08</v>
+        <v>0.21</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0069</v>
       </c>
       <c r="H8" t="n">
         <v>0.32</v>
       </c>
       <c r="I8" t="n">
-        <v>29.78</v>
+        <v>30.16</v>
       </c>
       <c r="J8" t="n">
-        <v>30.36</v>
+        <v>30.29</v>
       </c>
       <c r="K8" t="n">
-        <v>30.47</v>
+        <v>30.46</v>
       </c>
       <c r="L8" t="n">
-        <v>30.59</v>
+        <v>30.63</v>
       </c>
       <c r="M8" t="n">
-        <v>30.94</v>
+        <v>30.78</v>
       </c>
       <c r="N8" t="n">
-        <v>31.28</v>
+        <v>30.93</v>
       </c>
       <c r="O8" t="n">
-        <v>31.17</v>
+        <v>31.12</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1202,11 +1194,13 @@
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1214,83 +1208,81 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="C9" t="n">
-        <v>30.85</v>
+        <v>30.83</v>
       </c>
       <c r="D9" t="n">
-        <v>30.53</v>
+        <v>30.52</v>
       </c>
       <c r="E9" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="F9" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0017</v>
       </c>
       <c r="H9" t="n">
         <v>0.32</v>
       </c>
       <c r="I9" t="n">
-        <v>30.16</v>
+        <v>30.2</v>
       </c>
       <c r="J9" t="n">
-        <v>30.29</v>
+        <v>30.58</v>
       </c>
       <c r="K9" t="n">
-        <v>30.46</v>
+        <v>30.67</v>
       </c>
       <c r="L9" t="n">
-        <v>30.63</v>
+        <v>30.76</v>
       </c>
       <c r="M9" t="n">
-        <v>30.78</v>
+        <v>31</v>
       </c>
       <c r="N9" t="n">
-        <v>30.93</v>
+        <v>31.23</v>
       </c>
       <c r="O9" t="n">
-        <v>31.12</v>
+        <v>31.18</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1298,81 +1290,83 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="C10" t="n">
-        <v>30.83</v>
+        <v>31.01</v>
       </c>
       <c r="D10" t="n">
-        <v>30.52</v>
+        <v>30.76</v>
       </c>
       <c r="E10" t="n">
-        <v>30.78</v>
+        <v>30.97</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.05</v>
+        <v>0.19</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.006</v>
       </c>
       <c r="H10" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="I10" t="n">
         <v>30.2</v>
       </c>
       <c r="J10" t="n">
-        <v>30.58</v>
+        <v>30.52</v>
       </c>
       <c r="K10" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="L10" t="n">
-        <v>30.76</v>
+        <v>30.73</v>
       </c>
       <c r="M10" t="n">
-        <v>31</v>
+        <v>30.94</v>
       </c>
       <c r="N10" t="n">
-        <v>31.23</v>
+        <v>31.15</v>
       </c>
       <c r="O10" t="n">
-        <v>31.18</v>
+        <v>31.15</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1380,82 +1374,84 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30.78</v>
+        <v>30.96</v>
       </c>
       <c r="C11" t="n">
-        <v>31.01</v>
+        <v>31.18</v>
       </c>
       <c r="D11" t="n">
-        <v>30.76</v>
+        <v>30.36</v>
       </c>
       <c r="E11" t="n">
-        <v>30.97</v>
+        <v>30.55</v>
       </c>
       <c r="F11" t="n">
-        <v>0.19</v>
+        <v>-0.41</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.0133</v>
       </c>
       <c r="H11" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="I11" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="J11" t="n">
-        <v>30.52</v>
+        <v>30.75</v>
       </c>
       <c r="K11" t="n">
-        <v>30.62</v>
+        <v>30.84</v>
       </c>
       <c r="L11" t="n">
-        <v>30.73</v>
+        <v>30.93</v>
       </c>
       <c r="M11" t="n">
-        <v>30.94</v>
+        <v>31.09</v>
       </c>
       <c r="N11" t="n">
-        <v>31.15</v>
+        <v>31.26</v>
       </c>
       <c r="O11" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>31.26</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U11" s="8" t="n">
@@ -1466,177 +1462,173 @@
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.96</v>
+        <v>30.62</v>
       </c>
       <c r="C12" t="n">
-        <v>31.18</v>
+        <v>31.44</v>
       </c>
       <c r="D12" t="n">
-        <v>30.36</v>
+        <v>30.62</v>
       </c>
       <c r="E12" t="n">
-        <v>30.55</v>
+        <v>31.34</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.41</v>
+        <v>0.78</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0257</v>
       </c>
       <c r="H12" t="n">
         <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>30.5</v>
+        <v>29.54</v>
       </c>
       <c r="J12" t="n">
-        <v>30.75</v>
+        <v>29.63</v>
       </c>
       <c r="K12" t="n">
-        <v>30.84</v>
+        <v>30.15</v>
       </c>
       <c r="L12" t="n">
-        <v>30.93</v>
+        <v>30.66</v>
       </c>
       <c r="M12" t="n">
-        <v>31.09</v>
+        <v>30.96</v>
       </c>
       <c r="N12" t="n">
-        <v>31.26</v>
+        <v>31.27</v>
       </c>
       <c r="O12" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.62</v>
+        <v>31.34</v>
       </c>
       <c r="C13" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="D13" t="n">
-        <v>30.62</v>
+        <v>30.65</v>
       </c>
       <c r="E13" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="F13" t="n">
-        <v>0.78</v>
+        <v>0.04</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0012</v>
       </c>
       <c r="H13" t="n">
         <v>0.82</v>
       </c>
       <c r="I13" t="n">
-        <v>29.54</v>
+        <v>29.81</v>
       </c>
       <c r="J13" t="n">
-        <v>29.63</v>
+        <v>30.67</v>
       </c>
       <c r="K13" t="n">
-        <v>30.15</v>
+        <v>30.93</v>
       </c>
       <c r="L13" t="n">
-        <v>30.66</v>
+        <v>31.19</v>
       </c>
       <c r="M13" t="n">
-        <v>30.96</v>
+        <v>31.75</v>
       </c>
       <c r="N13" t="n">
-        <v>31.27</v>
+        <v>32.31</v>
       </c>
       <c r="O13" t="n">
-        <v>32</v>
+        <v>32.26</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1646,63 +1638,59 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="C14" t="n">
-        <v>31.47</v>
+        <v>31.46</v>
       </c>
       <c r="D14" t="n">
-        <v>30.65</v>
+        <v>31.17</v>
       </c>
       <c r="E14" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0033</v>
       </c>
       <c r="H14" t="n">
-        <v>0.82</v>
+        <v>0.29</v>
       </c>
       <c r="I14" t="n">
-        <v>29.81</v>
+        <v>29.83</v>
       </c>
       <c r="J14" t="n">
-        <v>30.67</v>
+        <v>30.71</v>
       </c>
       <c r="K14" t="n">
-        <v>30.93</v>
+        <v>30.97</v>
       </c>
       <c r="L14" t="n">
-        <v>31.19</v>
+        <v>31.22</v>
       </c>
       <c r="M14" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="N14" t="n">
-        <v>32.31</v>
+        <v>32.36</v>
       </c>
       <c r="O14" t="n">
-        <v>32.26</v>
+        <v>32.3</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
@@ -1718,60 +1706,64 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="C15" t="n">
-        <v>31.46</v>
+        <v>31.32</v>
       </c>
       <c r="D15" t="n">
-        <v>31.17</v>
+        <v>31.08</v>
       </c>
       <c r="E15" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0015</v>
       </c>
       <c r="H15" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I15" t="n">
-        <v>29.83</v>
+        <v>30.88</v>
       </c>
       <c r="J15" t="n">
-        <v>30.71</v>
+        <v>30.96</v>
       </c>
       <c r="K15" t="n">
-        <v>30.97</v>
+        <v>31.13</v>
       </c>
       <c r="L15" t="n">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="M15" t="n">
-        <v>31.79</v>
+        <v>31.42</v>
       </c>
       <c r="N15" t="n">
-        <v>32.36</v>
+        <v>31.54</v>
       </c>
       <c r="O15" t="n">
-        <v>32.3</v>
+        <v>31.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1779,8 +1771,10 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
@@ -1796,7 +1790,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1810,50 +1804,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="C16" t="n">
-        <v>31.32</v>
+        <v>31.63</v>
       </c>
       <c r="D16" t="n">
-        <v>31.08</v>
+        <v>31.24</v>
       </c>
       <c r="E16" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0059</v>
       </c>
       <c r="H16" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="I16" t="n">
-        <v>30.88</v>
+        <v>30.83</v>
       </c>
       <c r="J16" t="n">
-        <v>30.96</v>
+        <v>31.14</v>
       </c>
       <c r="K16" t="n">
-        <v>31.13</v>
+        <v>31.2</v>
       </c>
       <c r="L16" t="n">
-        <v>31.3</v>
+        <v>31.26</v>
       </c>
       <c r="M16" t="n">
-        <v>31.42</v>
+        <v>31.44</v>
       </c>
       <c r="N16" t="n">
-        <v>31.54</v>
+        <v>31.62</v>
       </c>
       <c r="O16" t="n">
-        <v>31.75</v>
+        <v>31.56</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1861,83 +1855,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63</v>
+        <v>31.57</v>
       </c>
       <c r="D17" t="n">
-        <v>31.24</v>
+        <v>31.37</v>
       </c>
       <c r="E17" t="n">
-        <v>31.5</v>
+        <v>31.38</v>
       </c>
       <c r="F17" t="n">
-        <v>0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0039</v>
       </c>
       <c r="H17" t="n">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>30.83</v>
+        <v>30.86</v>
       </c>
       <c r="J17" t="n">
-        <v>31.14</v>
+        <v>31.15</v>
       </c>
       <c r="K17" t="n">
-        <v>31.2</v>
+        <v>31.31</v>
       </c>
       <c r="L17" t="n">
-        <v>31.26</v>
+        <v>31.47</v>
       </c>
       <c r="M17" t="n">
-        <v>31.44</v>
+        <v>31.7</v>
       </c>
       <c r="N17" t="n">
-        <v>31.62</v>
+        <v>31.92</v>
       </c>
       <c r="O17" t="n">
-        <v>31.56</v>
+        <v>32.01</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,83 +1939,83 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.5</v>
+        <v>31.39</v>
       </c>
       <c r="C18" t="n">
-        <v>31.57</v>
+        <v>31.46</v>
       </c>
       <c r="D18" t="n">
-        <v>31.37</v>
+        <v>31.25</v>
       </c>
       <c r="E18" t="n">
-        <v>31.38</v>
+        <v>31.36</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I18" t="n">
-        <v>30.86</v>
+        <v>31.16</v>
       </c>
       <c r="J18" t="n">
-        <v>31.15</v>
+        <v>31.13</v>
       </c>
       <c r="K18" t="n">
-        <v>31.31</v>
+        <v>31.28</v>
       </c>
       <c r="L18" t="n">
-        <v>31.47</v>
+        <v>31.42</v>
       </c>
       <c r="M18" t="n">
-        <v>31.7</v>
+        <v>31.48</v>
       </c>
       <c r="N18" t="n">
-        <v>31.92</v>
+        <v>31.54</v>
       </c>
       <c r="O18" t="n">
-        <v>32.01</v>
+        <v>31.78</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2031,12 +2025,12 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2048,64 +2042,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31.39</v>
+        <v>31.38</v>
       </c>
       <c r="C19" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="D19" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="E19" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I19" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="J19" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="K19" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="L19" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="M19" t="n">
         <v>31.46</v>
       </c>
-      <c r="D19" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="E19" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>-0.0007</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I19" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="J19" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="K19" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="L19" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="M19" t="n">
-        <v>31.48</v>
-      </c>
       <c r="N19" t="n">
-        <v>31.54</v>
+        <v>31.57</v>
       </c>
       <c r="O19" t="n">
-        <v>31.78</v>
+        <v>31.68</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2113,83 +2107,83 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31.38</v>
+        <v>31.6</v>
       </c>
       <c r="C20" t="n">
-        <v>31.68</v>
+        <v>31.74</v>
       </c>
       <c r="D20" t="n">
-        <v>31.35</v>
+        <v>31.51</v>
       </c>
       <c r="E20" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="F20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H20" t="n">
         <v>0.23</v>
       </c>
-      <c r="G20" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.33</v>
-      </c>
       <c r="I20" t="n">
-        <v>31.04</v>
+        <v>31.02</v>
       </c>
       <c r="J20" t="n">
-        <v>31.15</v>
+        <v>31.31</v>
       </c>
       <c r="K20" t="n">
-        <v>31.25</v>
+        <v>31.43</v>
       </c>
       <c r="L20" t="n">
-        <v>31.36</v>
+        <v>31.55</v>
       </c>
       <c r="M20" t="n">
-        <v>31.46</v>
+        <v>31.76</v>
       </c>
       <c r="N20" t="n">
-        <v>31.57</v>
+        <v>31.96</v>
       </c>
       <c r="O20" t="n">
-        <v>31.68</v>
+        <v>32</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2202,25 +2196,19 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2230,63 +2218,67 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31.6</v>
+        <v>31.61</v>
       </c>
       <c r="C21" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="D21" t="n">
-        <v>31.51</v>
+        <v>31.37</v>
       </c>
       <c r="E21" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0005</v>
+        <v>-0.0075</v>
       </c>
       <c r="H21" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="I21" t="n">
-        <v>31.02</v>
+        <v>31.27</v>
       </c>
       <c r="J21" t="n">
-        <v>31.31</v>
+        <v>31.37</v>
       </c>
       <c r="K21" t="n">
-        <v>31.43</v>
+        <v>31.49</v>
       </c>
       <c r="L21" t="n">
-        <v>31.55</v>
+        <v>31.62</v>
       </c>
       <c r="M21" t="n">
-        <v>31.76</v>
+        <v>31.73</v>
       </c>
       <c r="N21" t="n">
-        <v>31.96</v>
+        <v>31.83</v>
       </c>
       <c r="O21" t="n">
-        <v>32</v>
+        <v>31.98</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2298,146 +2290,152 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="C22" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="D22" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="E22" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I22" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="J22" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="K22" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="L22" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M22" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N22" t="n">
         <v>31.61</v>
       </c>
-      <c r="C22" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="D22" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="E22" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I22" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="J22" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="K22" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="L22" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="M22" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="N22" t="n">
-        <v>31.83</v>
-      </c>
       <c r="O22" t="n">
-        <v>31.98</v>
+        <v>32</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>31.38</v>
+        <v>31.61</v>
       </c>
       <c r="C23" t="n">
-        <v>31.58</v>
+        <v>31.71</v>
       </c>
       <c r="D23" t="n">
-        <v>31.12</v>
+        <v>31.49</v>
       </c>
       <c r="E23" t="n">
         <v>31.58</v>
       </c>
       <c r="F23" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0003</v>
       </c>
       <c r="H23" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="I23" t="n">
-        <v>31.06</v>
+        <v>30.65</v>
       </c>
       <c r="J23" t="n">
-        <v>30.98</v>
+        <v>31.23</v>
       </c>
       <c r="K23" t="n">
-        <v>31.21</v>
+        <v>31.35</v>
       </c>
       <c r="L23" t="n">
-        <v>31.45</v>
+        <v>31.47</v>
       </c>
       <c r="M23" t="n">
-        <v>31.53</v>
+        <v>31.82</v>
       </c>
       <c r="N23" t="n">
-        <v>31.61</v>
+        <v>32.16</v>
       </c>
       <c r="O23" t="n">
-        <v>32</v>
+        <v>32.05</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2445,204 +2443,198 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>31.61</v>
       </c>
       <c r="C24" t="n">
-        <v>31.71</v>
+        <v>32.77</v>
       </c>
       <c r="D24" t="n">
-        <v>31.49</v>
+        <v>31.32</v>
       </c>
       <c r="E24" t="n">
-        <v>31.58</v>
+        <v>31.37</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0065</v>
       </c>
       <c r="H24" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="I24" t="n">
-        <v>30.65</v>
+        <v>31.27</v>
       </c>
       <c r="J24" t="n">
-        <v>31.23</v>
+        <v>31.34</v>
       </c>
       <c r="K24" t="n">
-        <v>31.35</v>
+        <v>31.46</v>
       </c>
       <c r="L24" t="n">
-        <v>31.47</v>
+        <v>31.59</v>
       </c>
       <c r="M24" t="n">
-        <v>31.82</v>
+        <v>31.69</v>
       </c>
       <c r="N24" t="n">
-        <v>32.16</v>
+        <v>31.79</v>
       </c>
       <c r="O24" t="n">
-        <v>32.05</v>
+        <v>31.94</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="C25" t="n">
-        <v>32.77</v>
+        <v>31.65</v>
       </c>
       <c r="D25" t="n">
-        <v>31.32</v>
+        <v>31.26</v>
       </c>
       <c r="E25" t="n">
-        <v>31.37</v>
+        <v>31.51</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.21</v>
+        <v>0.14</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0045</v>
       </c>
       <c r="H25" t="n">
-        <v>1.45</v>
+        <v>0.39</v>
       </c>
       <c r="I25" t="n">
-        <v>31.27</v>
+        <v>29.88</v>
       </c>
       <c r="J25" t="n">
-        <v>31.34</v>
+        <v>29.58</v>
       </c>
       <c r="K25" t="n">
-        <v>31.46</v>
+        <v>30.65</v>
       </c>
       <c r="L25" t="n">
-        <v>31.59</v>
+        <v>31.71</v>
       </c>
       <c r="M25" t="n">
-        <v>31.69</v>
+        <v>32.09</v>
       </c>
       <c r="N25" t="n">
-        <v>31.79</v>
+        <v>32.48</v>
       </c>
       <c r="O25" t="n">
-        <v>31.94</v>
+        <v>34.22</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2656,50 +2648,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.37</v>
+        <v>31.47</v>
       </c>
       <c r="C26" t="n">
-        <v>31.65</v>
+        <v>31.5</v>
       </c>
       <c r="D26" t="n">
-        <v>31.26</v>
+        <v>31.18</v>
       </c>
       <c r="E26" t="n">
-        <v>31.51</v>
+        <v>31.38</v>
       </c>
       <c r="F26" t="n">
-        <v>0.14</v>
+        <v>-0.14</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0043</v>
       </c>
       <c r="H26" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="I26" t="n">
-        <v>29.88</v>
+        <v>30.87</v>
       </c>
       <c r="J26" t="n">
-        <v>29.58</v>
+        <v>31.14</v>
       </c>
       <c r="K26" t="n">
-        <v>30.65</v>
+        <v>31.31</v>
       </c>
       <c r="L26" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="M26" t="n">
         <v>31.71</v>
       </c>
-      <c r="M26" t="n">
-        <v>32.09</v>
-      </c>
       <c r="N26" t="n">
-        <v>32.48</v>
+        <v>31.93</v>
       </c>
       <c r="O26" t="n">
-        <v>34.22</v>
+        <v>32.05</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2707,12 +2699,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2724,64 +2718,64 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C27" t="n">
-        <v>31.5</v>
+        <v>31.96</v>
       </c>
       <c r="D27" t="n">
-        <v>31.18</v>
+        <v>31.39</v>
       </c>
       <c r="E27" t="n">
-        <v>31.38</v>
+        <v>31.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0136</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32</v>
+        <v>0.57</v>
       </c>
       <c r="I27" t="n">
-        <v>30.87</v>
+        <v>30.86</v>
       </c>
       <c r="J27" t="n">
-        <v>31.14</v>
+        <v>31.08</v>
       </c>
       <c r="K27" t="n">
-        <v>31.31</v>
+        <v>31.22</v>
       </c>
       <c r="L27" t="n">
-        <v>31.48</v>
+        <v>31.36</v>
       </c>
       <c r="M27" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N27" t="n">
         <v>31.71</v>
       </c>
-      <c r="N27" t="n">
-        <v>31.93</v>
-      </c>
       <c r="O27" t="n">
-        <v>32.05</v>
+        <v>31.81</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2789,83 +2783,83 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31.44</v>
+        <v>32.03</v>
       </c>
       <c r="C28" t="n">
-        <v>31.96</v>
+        <v>32.16</v>
       </c>
       <c r="D28" t="n">
-        <v>31.39</v>
+        <v>31.53</v>
       </c>
       <c r="E28" t="n">
-        <v>31.8</v>
+        <v>32.16</v>
       </c>
       <c r="F28" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0113</v>
       </c>
       <c r="H28" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="I28" t="n">
-        <v>30.86</v>
+        <v>30.82</v>
       </c>
       <c r="J28" t="n">
-        <v>31.08</v>
+        <v>31.29</v>
       </c>
       <c r="K28" t="n">
-        <v>31.22</v>
+        <v>31.52</v>
       </c>
       <c r="L28" t="n">
-        <v>31.36</v>
+        <v>31.74</v>
       </c>
       <c r="M28" t="n">
-        <v>31.53</v>
+        <v>32.09</v>
       </c>
       <c r="N28" t="n">
-        <v>31.71</v>
+        <v>32.44</v>
       </c>
       <c r="O28" t="n">
-        <v>31.81</v>
+        <v>32.54</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2883,20 +2877,16 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2906,50 +2896,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="C29" t="n">
-        <v>32.16</v>
+        <v>32.12</v>
       </c>
       <c r="D29" t="n">
-        <v>31.53</v>
+        <v>31.8</v>
       </c>
       <c r="E29" t="n">
-        <v>32.16</v>
+        <v>32.02</v>
       </c>
       <c r="F29" t="n">
-        <v>0.36</v>
+        <v>-0.14</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0044</v>
       </c>
       <c r="H29" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="I29" t="n">
-        <v>30.82</v>
+        <v>30.91</v>
       </c>
       <c r="J29" t="n">
-        <v>31.29</v>
+        <v>31.69</v>
       </c>
       <c r="K29" t="n">
-        <v>31.52</v>
+        <v>31.85</v>
       </c>
       <c r="L29" t="n">
-        <v>31.74</v>
+        <v>32.01</v>
       </c>
       <c r="M29" t="n">
-        <v>32.09</v>
+        <v>32.48</v>
       </c>
       <c r="N29" t="n">
-        <v>32.44</v>
+        <v>32.95</v>
       </c>
       <c r="O29" t="n">
-        <v>32.54</v>
+        <v>32.79</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2957,18 +2947,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2976,60 +2966,64 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.09</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>32.12</v>
+        <v>32.14</v>
       </c>
       <c r="D30" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="E30" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0002</v>
       </c>
       <c r="H30" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I30" t="n">
-        <v>30.91</v>
+        <v>31.47</v>
       </c>
       <c r="J30" t="n">
-        <v>31.69</v>
+        <v>31.73</v>
       </c>
       <c r="K30" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="L30" t="n">
-        <v>32.01</v>
+        <v>31.99</v>
       </c>
       <c r="M30" t="n">
-        <v>32.48</v>
+        <v>32.18</v>
       </c>
       <c r="N30" t="n">
-        <v>32.95</v>
+        <v>32.38</v>
       </c>
       <c r="O30" t="n">
-        <v>32.79</v>
+        <v>32.44</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3056,64 +3050,64 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="C31" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="D31" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="E31" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I31" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="J31" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="L31" t="n">
         <v>32</v>
       </c>
-      <c r="C31" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="D31" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="E31" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I31" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="J31" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="K31" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="L31" t="n">
-        <v>31.99</v>
-      </c>
       <c r="M31" t="n">
-        <v>32.18</v>
+        <v>32.21</v>
       </c>
       <c r="N31" t="n">
-        <v>32.38</v>
+        <v>32.43</v>
       </c>
       <c r="O31" t="n">
-        <v>32.44</v>
+        <v>32.51</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3126,13 +3120,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3140,7 +3136,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3154,50 +3150,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
       <c r="C32" t="n">
-        <v>32.22</v>
+        <v>32.04</v>
       </c>
       <c r="D32" t="n">
-        <v>31.84</v>
+        <v>31.68</v>
       </c>
       <c r="E32" t="n">
-        <v>31.96</v>
+        <v>31.73</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0074</v>
       </c>
       <c r="H32" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I32" t="n">
-        <v>31.42</v>
+        <v>31.47</v>
       </c>
       <c r="J32" t="n">
-        <v>31.7</v>
+        <v>31.55</v>
       </c>
       <c r="K32" t="n">
-        <v>31.85</v>
+        <v>31.78</v>
       </c>
       <c r="L32" t="n">
         <v>32</v>
       </c>
       <c r="M32" t="n">
-        <v>32.21</v>
+        <v>32.15</v>
       </c>
       <c r="N32" t="n">
-        <v>32.43</v>
+        <v>32.3</v>
       </c>
       <c r="O32" t="n">
-        <v>32.51</v>
+        <v>32.59</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3207,18 +3203,16 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3226,64 +3220,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31.96</v>
+        <v>31.77</v>
       </c>
       <c r="C33" t="n">
-        <v>32.04</v>
+        <v>31.87</v>
       </c>
       <c r="D33" t="n">
-        <v>31.68</v>
+        <v>31.37</v>
       </c>
       <c r="E33" t="n">
-        <v>31.73</v>
+        <v>31.47</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0083</v>
       </c>
       <c r="H33" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="I33" t="n">
-        <v>31.47</v>
+        <v>31.32</v>
       </c>
       <c r="J33" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K33" t="n">
         <v>31.55</v>
       </c>
-      <c r="K33" t="n">
-        <v>31.78</v>
-      </c>
       <c r="L33" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="M33" t="n">
-        <v>32.15</v>
+        <v>31.91</v>
       </c>
       <c r="N33" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O33" t="n">
-        <v>32.59</v>
+        <v>32.41</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3310,7 +3304,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3324,50 +3318,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.77</v>
+        <v>31.47</v>
       </c>
       <c r="C34" t="n">
-        <v>31.87</v>
+        <v>31.59</v>
       </c>
       <c r="D34" t="n">
-        <v>31.37</v>
+        <v>31.18</v>
       </c>
       <c r="E34" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0009</v>
       </c>
       <c r="H34" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="I34" t="n">
-        <v>31.32</v>
+        <v>30.88</v>
       </c>
       <c r="J34" t="n">
-        <v>31.3</v>
+        <v>30.89</v>
       </c>
       <c r="K34" t="n">
-        <v>31.55</v>
+        <v>31.22</v>
       </c>
       <c r="L34" t="n">
-        <v>31.8</v>
+        <v>31.54</v>
       </c>
       <c r="M34" t="n">
-        <v>31.91</v>
+        <v>31.71</v>
       </c>
       <c r="N34" t="n">
-        <v>32.02</v>
+        <v>31.88</v>
       </c>
       <c r="O34" t="n">
-        <v>32.41</v>
+        <v>32.36</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3377,12 +3371,12 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3394,7 +3388,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3408,50 +3402,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C35" t="n">
-        <v>31.59</v>
+        <v>31.75</v>
       </c>
       <c r="D35" t="n">
-        <v>31.18</v>
+        <v>31.38</v>
       </c>
       <c r="E35" t="n">
-        <v>31.44</v>
+        <v>31.55</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0037</v>
       </c>
       <c r="H35" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="I35" t="n">
-        <v>30.88</v>
+        <v>30.78</v>
       </c>
       <c r="J35" t="n">
-        <v>30.89</v>
+        <v>31.05</v>
       </c>
       <c r="K35" t="n">
-        <v>31.22</v>
+        <v>31.23</v>
       </c>
       <c r="L35" t="n">
-        <v>31.54</v>
+        <v>31.41</v>
       </c>
       <c r="M35" t="n">
-        <v>31.71</v>
+        <v>31.64</v>
       </c>
       <c r="N35" t="n">
-        <v>31.88</v>
+        <v>31.87</v>
       </c>
       <c r="O35" t="n">
-        <v>32.36</v>
+        <v>32</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3459,18 +3453,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3478,64 +3472,60 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.44</v>
+        <v>31.64</v>
       </c>
       <c r="C36" t="n">
-        <v>31.75</v>
+        <v>31.69</v>
       </c>
       <c r="D36" t="n">
-        <v>31.38</v>
+        <v>31.3</v>
       </c>
       <c r="E36" t="n">
-        <v>31.55</v>
+        <v>31.3</v>
       </c>
       <c r="F36" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>30.78</v>
+        <v>31.02</v>
       </c>
       <c r="J36" t="n">
-        <v>31.05</v>
+        <v>31.18</v>
       </c>
       <c r="K36" t="n">
-        <v>31.23</v>
+        <v>31.37</v>
       </c>
       <c r="L36" t="n">
-        <v>31.41</v>
+        <v>31.56</v>
       </c>
       <c r="M36" t="n">
-        <v>31.64</v>
+        <v>31.74</v>
       </c>
       <c r="N36" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="O36" t="n">
-        <v>32</v>
+        <v>32.11</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3543,79 +3533,83 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.64</v>
+        <v>31.3</v>
       </c>
       <c r="C37" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="D37" t="n">
         <v>31.3</v>
       </c>
       <c r="E37" t="n">
-        <v>31.3</v>
+        <v>31.56</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.26</v>
+        <v>0.27</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="I37" t="n">
-        <v>31.02</v>
+        <v>30.9</v>
       </c>
       <c r="J37" t="n">
-        <v>31.18</v>
+        <v>30.8</v>
       </c>
       <c r="K37" t="n">
-        <v>31.37</v>
+        <v>31.1</v>
       </c>
       <c r="L37" t="n">
-        <v>31.56</v>
+        <v>31.39</v>
       </c>
       <c r="M37" t="n">
-        <v>31.74</v>
+        <v>31.49</v>
       </c>
       <c r="N37" t="n">
-        <v>31.91</v>
+        <v>31.59</v>
       </c>
       <c r="O37" t="n">
-        <v>32.11</v>
+        <v>32.09</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3623,83 +3617,85 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.3</v>
+        <v>31.59</v>
       </c>
       <c r="C38" t="n">
-        <v>31.62</v>
+        <v>31.78</v>
       </c>
       <c r="D38" t="n">
-        <v>31.3</v>
+        <v>31.36</v>
       </c>
       <c r="E38" t="n">
-        <v>31.56</v>
+        <v>31.36</v>
       </c>
       <c r="F38" t="n">
-        <v>0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0065</v>
       </c>
       <c r="H38" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="I38" t="n">
-        <v>30.9</v>
+        <v>30.98</v>
       </c>
       <c r="J38" t="n">
-        <v>30.8</v>
+        <v>31.29</v>
       </c>
       <c r="K38" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="L38" t="n">
-        <v>31.39</v>
+        <v>31.51</v>
       </c>
       <c r="M38" t="n">
-        <v>31.49</v>
+        <v>31.72</v>
       </c>
       <c r="N38" t="n">
-        <v>31.59</v>
+        <v>31.93</v>
       </c>
       <c r="O38" t="n">
-        <v>32.09</v>
+        <v>31.95</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3707,12 +3703,14 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3720,15 +3718,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3742,50 +3738,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.59</v>
+        <v>31.44</v>
       </c>
       <c r="C39" t="n">
-        <v>31.78</v>
+        <v>31.52</v>
       </c>
       <c r="D39" t="n">
-        <v>31.36</v>
+        <v>31.31</v>
       </c>
       <c r="E39" t="n">
-        <v>31.36</v>
+        <v>31.41</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0018</v>
       </c>
       <c r="H39" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="I39" t="n">
-        <v>30.98</v>
+        <v>30.94</v>
       </c>
       <c r="J39" t="n">
-        <v>31.29</v>
+        <v>30.83</v>
       </c>
       <c r="K39" t="n">
-        <v>31.4</v>
+        <v>31.15</v>
       </c>
       <c r="L39" t="n">
-        <v>31.51</v>
+        <v>31.46</v>
       </c>
       <c r="M39" t="n">
-        <v>31.72</v>
+        <v>31.57</v>
       </c>
       <c r="N39" t="n">
-        <v>31.93</v>
+        <v>31.67</v>
       </c>
       <c r="O39" t="n">
-        <v>31.95</v>
+        <v>32.2</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3793,20 +3789,16 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3814,64 +3806,64 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.44</v>
+        <v>31.41</v>
       </c>
       <c r="C40" t="n">
-        <v>31.52</v>
+        <v>31.6</v>
       </c>
       <c r="D40" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="E40" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I40" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J40" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="K40" t="n">
         <v>31.31</v>
       </c>
-      <c r="E40" t="n">
+      <c r="L40" t="n">
         <v>31.41</v>
       </c>
-      <c r="F40" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I40" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="J40" t="n">
-        <v>30.83</v>
-      </c>
-      <c r="K40" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="L40" t="n">
-        <v>31.46</v>
-      </c>
       <c r="M40" t="n">
-        <v>31.57</v>
+        <v>31.51</v>
       </c>
       <c r="N40" t="n">
-        <v>31.67</v>
+        <v>31.61</v>
       </c>
       <c r="O40" t="n">
-        <v>32.2</v>
+        <v>31.72</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3879,16 +3871,20 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3896,64 +3892,64 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.41</v>
+        <v>31.59</v>
       </c>
       <c r="C41" t="n">
-        <v>31.6</v>
+        <v>31.76</v>
       </c>
       <c r="D41" t="n">
-        <v>31.28</v>
+        <v>31.44</v>
       </c>
       <c r="E41" t="n">
         <v>31.56</v>
       </c>
       <c r="F41" t="n">
-        <v>0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0002</v>
       </c>
       <c r="H41" t="n">
         <v>0.33</v>
       </c>
       <c r="I41" t="n">
-        <v>31.11</v>
+        <v>30.95</v>
       </c>
       <c r="J41" t="n">
-        <v>31.21</v>
+        <v>31.3</v>
       </c>
       <c r="K41" t="n">
-        <v>31.31</v>
+        <v>31.4</v>
       </c>
       <c r="L41" t="n">
-        <v>31.41</v>
+        <v>31.5</v>
       </c>
       <c r="M41" t="n">
-        <v>31.51</v>
+        <v>31.73</v>
       </c>
       <c r="N41" t="n">
-        <v>31.61</v>
+        <v>31.95</v>
       </c>
       <c r="O41" t="n">
-        <v>31.72</v>
+        <v>31.93</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3961,28 +3957,26 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3996,50 +3990,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="C42" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="D42" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="E42" t="n">
-        <v>31.56</v>
+        <v>31.65</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0028</v>
       </c>
       <c r="H42" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="I42" t="n">
-        <v>30.95</v>
+        <v>31.11</v>
       </c>
       <c r="J42" t="n">
-        <v>31.3</v>
+        <v>31.21</v>
       </c>
       <c r="K42" t="n">
-        <v>31.4</v>
+        <v>31.39</v>
       </c>
       <c r="L42" t="n">
-        <v>31.5</v>
+        <v>31.58</v>
       </c>
       <c r="M42" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="N42" t="n">
-        <v>31.95</v>
+        <v>31.86</v>
       </c>
       <c r="O42" t="n">
-        <v>31.93</v>
+        <v>32.09</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4055,10 +4049,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4066,7 +4058,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4080,50 +4072,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="C43" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="D43" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E43" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I43" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="J43" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="K43" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="L43" t="n">
         <v>31.61</v>
       </c>
-      <c r="C43" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="D43" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="E43" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I43" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="J43" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="K43" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="L43" t="n">
-        <v>31.58</v>
-      </c>
       <c r="M43" t="n">
-        <v>31.72</v>
+        <v>31.76</v>
       </c>
       <c r="N43" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="O43" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4136,76 +4128,76 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.7</v>
+        <v>31.85</v>
       </c>
       <c r="C44" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="D44" t="n">
-        <v>31.58</v>
+        <v>31.79</v>
       </c>
       <c r="E44" t="n">
-        <v>31.84</v>
+        <v>31.9</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0016</v>
       </c>
       <c r="H44" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="I44" t="n">
-        <v>31.23</v>
+        <v>31.26</v>
       </c>
       <c r="J44" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="K44" t="n">
-        <v>31.53</v>
+        <v>31.68</v>
       </c>
       <c r="L44" t="n">
-        <v>31.61</v>
+        <v>31.79</v>
       </c>
       <c r="M44" t="n">
-        <v>31.76</v>
+        <v>32.01</v>
       </c>
       <c r="N44" t="n">
-        <v>31.91</v>
+        <v>32.22</v>
       </c>
       <c r="O44" t="n">
-        <v>31.93</v>
+        <v>32.23</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4218,23 +4210,19 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4244,50 +4232,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.85</v>
+        <v>31.93</v>
       </c>
       <c r="C45" t="n">
-        <v>31.96</v>
+        <v>32.23</v>
       </c>
       <c r="D45" t="n">
-        <v>31.79</v>
+        <v>31.92</v>
       </c>
       <c r="E45" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="F45" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0063</v>
       </c>
       <c r="H45" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="I45" t="n">
-        <v>31.26</v>
+        <v>31.62</v>
       </c>
       <c r="J45" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K45" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="L45" t="n">
-        <v>31.79</v>
+        <v>31.89</v>
       </c>
       <c r="M45" t="n">
-        <v>32.01</v>
+        <v>31.98</v>
       </c>
       <c r="N45" t="n">
-        <v>32.22</v>
+        <v>32.08</v>
       </c>
       <c r="O45" t="n">
-        <v>32.23</v>
+        <v>32.13</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4300,19 +4288,25 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4322,50 +4316,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.93</v>
+        <v>32.1</v>
       </c>
       <c r="C46" t="n">
-        <v>32.23</v>
+        <v>32.42</v>
       </c>
       <c r="D46" t="n">
-        <v>31.92</v>
+        <v>32.03</v>
       </c>
       <c r="E46" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="I46" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="J46" t="n">
-        <v>31.74</v>
+        <v>31.8</v>
       </c>
       <c r="K46" t="n">
-        <v>31.81</v>
+        <v>31.94</v>
       </c>
       <c r="L46" t="n">
-        <v>31.89</v>
+        <v>32.09</v>
       </c>
       <c r="M46" t="n">
-        <v>31.98</v>
+        <v>32.25</v>
       </c>
       <c r="N46" t="n">
-        <v>32.08</v>
+        <v>32.42</v>
       </c>
       <c r="O46" t="n">
-        <v>32.13</v>
+        <v>32.53</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4391,12 +4385,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4406,50 +4398,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C47" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D47" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="E47" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I47" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="J47" t="n">
         <v>32.1</v>
       </c>
-      <c r="C47" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D47" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="E47" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I47" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="J47" t="n">
-        <v>31.8</v>
-      </c>
       <c r="K47" t="n">
-        <v>31.94</v>
+        <v>32.2</v>
       </c>
       <c r="L47" t="n">
-        <v>32.09</v>
+        <v>32.31</v>
       </c>
       <c r="M47" t="n">
-        <v>32.25</v>
+        <v>32.59</v>
       </c>
       <c r="N47" t="n">
-        <v>32.42</v>
+        <v>32.87</v>
       </c>
       <c r="O47" t="n">
-        <v>32.53</v>
+        <v>32.81</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4462,76 +4454,76 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32.31</v>
+        <v>32.32</v>
       </c>
       <c r="C48" t="n">
-        <v>32.49</v>
+        <v>32.55</v>
       </c>
       <c r="D48" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="E48" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I48" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="J48" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="K48" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="L48" t="n">
         <v>32.35</v>
       </c>
-      <c r="F48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I48" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="J48" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="L48" t="n">
-        <v>32.31</v>
-      </c>
       <c r="M48" t="n">
-        <v>32.59</v>
+        <v>32.48</v>
       </c>
       <c r="N48" t="n">
-        <v>32.87</v>
+        <v>32.6</v>
       </c>
       <c r="O48" t="n">
-        <v>32.81</v>
+        <v>32.74</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4539,16 +4531,20 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4556,64 +4552,64 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>32.32</v>
+        <v>32.29</v>
       </c>
       <c r="C49" t="n">
-        <v>32.55</v>
+        <v>32.49</v>
       </c>
       <c r="D49" t="n">
-        <v>32.21</v>
+        <v>32.12</v>
       </c>
       <c r="E49" t="n">
-        <v>32.29</v>
+        <v>32.24</v>
       </c>
       <c r="F49" t="n">
         <v>-0.06</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="H49" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I49" t="n">
-        <v>31.98</v>
+        <v>31.86</v>
       </c>
       <c r="J49" t="n">
-        <v>32.09</v>
+        <v>31.91</v>
       </c>
       <c r="K49" t="n">
-        <v>32.22</v>
+        <v>32.12</v>
       </c>
       <c r="L49" t="n">
-        <v>32.35</v>
+        <v>32.34</v>
       </c>
       <c r="M49" t="n">
-        <v>32.48</v>
+        <v>32.47</v>
       </c>
       <c r="N49" t="n">
         <v>32.6</v>
       </c>
       <c r="O49" t="n">
-        <v>32.74</v>
+        <v>32.9</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4621,85 +4617,83 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="C50" t="n">
         <v>32.29</v>
       </c>
-      <c r="C50" t="n">
-        <v>32.49</v>
-      </c>
       <c r="D50" t="n">
-        <v>32.12</v>
+        <v>31.92</v>
       </c>
       <c r="E50" t="n">
-        <v>32.24</v>
+        <v>32.01</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.0071</v>
       </c>
       <c r="H50" t="n">
         <v>0.37</v>
       </c>
       <c r="I50" t="n">
-        <v>31.86</v>
+        <v>31.76</v>
       </c>
       <c r="J50" t="n">
-        <v>31.91</v>
+        <v>31.83</v>
       </c>
       <c r="K50" t="n">
-        <v>32.12</v>
+        <v>32.05</v>
       </c>
       <c r="L50" t="n">
-        <v>32.34</v>
+        <v>32.27</v>
       </c>
       <c r="M50" t="n">
-        <v>32.47</v>
+        <v>32.42</v>
       </c>
       <c r="N50" t="n">
-        <v>32.6</v>
+        <v>32.57</v>
       </c>
       <c r="O50" t="n">
-        <v>32.9</v>
+        <v>32.86</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4707,18 +4701,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4726,7 +4720,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4740,50 +4734,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.24</v>
+        <v>31.99</v>
       </c>
       <c r="C51" t="n">
-        <v>32.29</v>
+        <v>32.01</v>
       </c>
       <c r="D51" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E51" t="n">
-        <v>32.01</v>
+        <v>31.83</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0071</v>
+        <v>-0.0055</v>
       </c>
       <c r="H51" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="I51" t="n">
-        <v>31.76</v>
+        <v>31.55</v>
       </c>
       <c r="J51" t="n">
-        <v>31.83</v>
+        <v>31.59</v>
       </c>
       <c r="K51" t="n">
-        <v>32.05</v>
+        <v>31.82</v>
       </c>
       <c r="L51" t="n">
-        <v>32.27</v>
+        <v>32.06</v>
       </c>
       <c r="M51" t="n">
-        <v>32.42</v>
+        <v>32.19</v>
       </c>
       <c r="N51" t="n">
-        <v>32.57</v>
+        <v>32.33</v>
       </c>
       <c r="O51" t="n">
-        <v>32.86</v>
+        <v>32.66</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4810,7 +4804,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4824,60 +4818,62 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.99</v>
+        <v>31.82</v>
       </c>
       <c r="C52" t="n">
-        <v>32.01</v>
+        <v>31.91</v>
       </c>
       <c r="D52" t="n">
-        <v>31.75</v>
+        <v>31.55</v>
       </c>
       <c r="E52" t="n">
-        <v>31.83</v>
+        <v>31.62</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0066</v>
       </c>
       <c r="H52" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="I52" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J52" t="n">
         <v>31.55</v>
       </c>
-      <c r="J52" t="n">
-        <v>31.59</v>
-      </c>
       <c r="K52" t="n">
-        <v>31.82</v>
+        <v>31.7</v>
       </c>
       <c r="L52" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="M52" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="N52" t="n">
         <v>32.06</v>
       </c>
-      <c r="M52" t="n">
-        <v>32.19</v>
-      </c>
-      <c r="N52" t="n">
-        <v>32.33</v>
-      </c>
       <c r="O52" t="n">
-        <v>32.66</v>
+        <v>32.26</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
@@ -4894,7 +4890,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4908,155 +4904,155 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.82</v>
+        <v>31.63</v>
       </c>
       <c r="C53" t="n">
-        <v>31.91</v>
+        <v>31.8</v>
       </c>
       <c r="D53" t="n">
-        <v>31.55</v>
+        <v>31.58</v>
       </c>
       <c r="E53" t="n">
-        <v>31.62</v>
+        <v>31.67</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.21</v>
+        <v>0.05</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0066</v>
+        <v>0.0016</v>
       </c>
       <c r="H53" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="I53" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="J53" t="n">
-        <v>31.55</v>
+        <v>31.21</v>
       </c>
       <c r="K53" t="n">
-        <v>31.7</v>
+        <v>31.44</v>
       </c>
       <c r="L53" t="n">
-        <v>31.86</v>
+        <v>31.68</v>
       </c>
       <c r="M53" t="n">
-        <v>31.96</v>
+        <v>31.8</v>
       </c>
       <c r="N53" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="O53" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="C54" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="D54" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="E54" t="n">
         <v>31.63</v>
       </c>
-      <c r="C54" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D54" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="E54" t="n">
-        <v>31.67</v>
-      </c>
       <c r="F54" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0013</v>
       </c>
       <c r="H54" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I54" t="n">
-        <v>31.2</v>
+        <v>31.37</v>
       </c>
       <c r="J54" t="n">
-        <v>31.21</v>
+        <v>31.44</v>
       </c>
       <c r="K54" t="n">
-        <v>31.44</v>
+        <v>31.56</v>
       </c>
       <c r="L54" t="n">
         <v>31.68</v>
       </c>
       <c r="M54" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="N54" t="n">
-        <v>31.92</v>
+        <v>31.88</v>
       </c>
       <c r="O54" t="n">
-        <v>32.27</v>
+        <v>32.02</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5064,85 +5060,83 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.62</v>
+        <v>31.68</v>
       </c>
       <c r="C55" t="n">
-        <v>31.69</v>
+        <v>31.94</v>
       </c>
       <c r="D55" t="n">
-        <v>31.42</v>
+        <v>31.61</v>
       </c>
       <c r="E55" t="n">
-        <v>31.63</v>
+        <v>31.76</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0043</v>
       </c>
       <c r="H55" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="I55" t="n">
-        <v>31.37</v>
+        <v>31.14</v>
       </c>
       <c r="J55" t="n">
-        <v>31.44</v>
+        <v>31.39</v>
       </c>
       <c r="K55" t="n">
-        <v>31.56</v>
+        <v>31.49</v>
       </c>
       <c r="L55" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M55" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="N55" t="n">
-        <v>31.88</v>
+        <v>31.94</v>
       </c>
       <c r="O55" t="n">
-        <v>32.02</v>
+        <v>31.97</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5150,64 +5144,60 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="C56" t="n">
-        <v>31.94</v>
+        <v>31.86</v>
       </c>
       <c r="D56" t="n">
-        <v>31.61</v>
+        <v>31.6</v>
       </c>
       <c r="E56" t="n">
-        <v>31.76</v>
+        <v>31.71</v>
       </c>
       <c r="F56" t="n">
-        <v>0.14</v>
+        <v>-0.05</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0016</v>
       </c>
       <c r="H56" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="I56" t="n">
-        <v>31.14</v>
+        <v>31.29</v>
       </c>
       <c r="J56" t="n">
-        <v>31.39</v>
+        <v>31.44</v>
       </c>
       <c r="K56" t="n">
-        <v>31.49</v>
+        <v>31.6</v>
       </c>
       <c r="L56" t="n">
-        <v>31.59</v>
+        <v>31.77</v>
       </c>
       <c r="M56" t="n">
-        <v>31.77</v>
+        <v>31.93</v>
       </c>
       <c r="N56" t="n">
-        <v>31.94</v>
+        <v>32.08</v>
       </c>
       <c r="O56" t="n">
-        <v>31.97</v>
+        <v>32.26</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5215,18 +5205,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5234,60 +5224,64 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="C57" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="D57" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E57" t="n">
         <v>31.81</v>
       </c>
-      <c r="C57" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="D57" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E57" t="n">
-        <v>31.71</v>
-      </c>
       <c r="F57" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0029</v>
       </c>
       <c r="H57" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I57" t="n">
-        <v>31.29</v>
+        <v>31.33</v>
       </c>
       <c r="J57" t="n">
         <v>31.44</v>
       </c>
       <c r="K57" t="n">
-        <v>31.6</v>
+        <v>31.58</v>
       </c>
       <c r="L57" t="n">
-        <v>31.77</v>
+        <v>31.72</v>
       </c>
       <c r="M57" t="n">
-        <v>31.93</v>
+        <v>31.85</v>
       </c>
       <c r="N57" t="n">
-        <v>32.08</v>
+        <v>31.97</v>
       </c>
       <c r="O57" t="n">
-        <v>32.26</v>
+        <v>32.13</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5295,83 +5289,81 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.78</v>
+        <v>31.83</v>
       </c>
       <c r="C58" t="n">
-        <v>32.07</v>
+        <v>31.85</v>
       </c>
       <c r="D58" t="n">
-        <v>31.73</v>
+        <v>31.71</v>
       </c>
       <c r="E58" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="F58" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0009</v>
       </c>
       <c r="H58" t="n">
-        <v>0.34</v>
+        <v>0.14</v>
       </c>
       <c r="I58" t="n">
-        <v>31.33</v>
+        <v>31.38</v>
       </c>
       <c r="J58" t="n">
-        <v>31.44</v>
+        <v>31.42</v>
       </c>
       <c r="K58" t="n">
-        <v>31.58</v>
+        <v>31.63</v>
       </c>
       <c r="L58" t="n">
-        <v>31.72</v>
+        <v>31.85</v>
       </c>
       <c r="M58" t="n">
-        <v>31.85</v>
+        <v>31.98</v>
       </c>
       <c r="N58" t="n">
-        <v>31.97</v>
+        <v>32.1</v>
       </c>
       <c r="O58" t="n">
-        <v>32.13</v>
+        <v>32.42</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5382,30 +5374,30 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.32</v>
       </c>
       <c r="I2" t="n">
-        <v>29.85</v>
+        <v>29.87</v>
       </c>
       <c r="J2" t="n">
-        <v>30.04</v>
+        <v>30.07</v>
       </c>
       <c r="K2" t="n">
-        <v>30.29</v>
+        <v>30.3</v>
       </c>
       <c r="L2" t="n">
         <v>30.54</v>
       </c>
       <c r="M2" t="n">
-        <v>30.77</v>
+        <v>30.75</v>
       </c>
       <c r="N2" t="n">
-        <v>30.99</v>
+        <v>30.97</v>
       </c>
       <c r="O2" t="n">
-        <v>31.27</v>
+        <v>31.22</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5330,19 +5330,19 @@
         <v>31.85</v>
       </c>
       <c r="D58" t="n">
-        <v>31.71</v>
+        <v>31.7</v>
       </c>
       <c r="E58" t="n">
-        <v>31.83</v>
+        <v>31.75</v>
       </c>
       <c r="F58" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0017</v>
       </c>
       <c r="H58" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="I58" t="n">
         <v>31.38</v>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.32</v>
       </c>
       <c r="I2" t="n">
-        <v>29.87</v>
+        <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="K2" t="n">
-        <v>30.3</v>
+        <v>30.33</v>
       </c>
       <c r="L2" t="n">
-        <v>30.54</v>
+        <v>30.53</v>
       </c>
       <c r="M2" t="n">
-        <v>30.75</v>
+        <v>30.73</v>
       </c>
       <c r="N2" t="n">
-        <v>30.97</v>
+        <v>30.93</v>
       </c>
       <c r="O2" t="n">
-        <v>31.22</v>
+        <v>31.12</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5327,22 +5327,22 @@
         <v>31.83</v>
       </c>
       <c r="C58" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="D58" t="n">
         <v>31.7</v>
       </c>
       <c r="E58" t="n">
-        <v>31.75</v>
+        <v>31.78</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0009</v>
       </c>
       <c r="H58" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="I58" t="n">
         <v>31.38</v>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.32</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.95</v>
       </c>
       <c r="J2" t="n">
-        <v>30.13</v>
+        <v>30.17</v>
       </c>
       <c r="K2" t="n">
-        <v>30.33</v>
+        <v>30.34</v>
       </c>
       <c r="L2" t="n">
-        <v>30.53</v>
+        <v>30.52</v>
       </c>
       <c r="M2" t="n">
-        <v>30.73</v>
+        <v>30.71</v>
       </c>
       <c r="N2" t="n">
-        <v>30.93</v>
+        <v>30.91</v>
       </c>
       <c r="O2" t="n">
-        <v>31.12</v>
+        <v>31.07</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5327,22 +5327,22 @@
         <v>31.83</v>
       </c>
       <c r="C58" t="n">
-        <v>31.89</v>
+        <v>32.01</v>
       </c>
       <c r="D58" t="n">
         <v>31.7</v>
       </c>
       <c r="E58" t="n">
-        <v>31.78</v>
+        <v>31.85</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0013</v>
       </c>
       <c r="H58" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="I58" t="n">
         <v>31.38</v>
@@ -5379,8 +5379,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5395,7 +5397,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,35 +659,39 @@
         <v>0.32</v>
       </c>
       <c r="I2" t="n">
-        <v>29.95</v>
+        <v>30.53</v>
       </c>
       <c r="J2" t="n">
-        <v>30.17</v>
+        <v>30.53</v>
       </c>
       <c r="K2" t="n">
-        <v>30.34</v>
+        <v>30.53</v>
       </c>
       <c r="L2" t="n">
-        <v>30.52</v>
+        <v>30.53</v>
       </c>
       <c r="M2" t="n">
-        <v>30.71</v>
+        <v>30.53</v>
       </c>
       <c r="N2" t="n">
-        <v>30.91</v>
+        <v>30.53</v>
       </c>
       <c r="O2" t="n">
-        <v>31.07</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>30.53</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -706,14 +710,10 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -790,14 +790,10 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -876,10 +872,14 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1124,7 +1124,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1208,7 +1208,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1290,7 +1290,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1374,7 +1374,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1460,7 +1460,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1546,7 +1546,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1628,7 +1628,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1706,7 +1706,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1790,7 +1790,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1878,7 +1878,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1958,7 +1958,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2042,7 +2042,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2130,7 +2130,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2208,7 +2208,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2290,7 +2290,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2378,7 +2378,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2460,7 +2460,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2552,7 +2552,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2634,7 +2634,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2718,7 +2718,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2806,7 +2806,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2886,7 +2886,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2966,7 +2966,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3050,7 +3050,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3136,7 +3136,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3220,7 +3220,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3304,7 +3304,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3388,7 +3388,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3472,7 +3472,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3552,7 +3552,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3638,7 +3638,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3724,7 +3724,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3806,7 +3806,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3892,7 +3892,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3976,7 +3976,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4058,7 +4058,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4144,7 +4144,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4222,7 +4222,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4306,7 +4306,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4388,7 +4388,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4466,7 +4466,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4552,7 +4552,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4636,7 +4636,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4720,7 +4720,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4804,7 +4804,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4890,7 +4890,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4974,7 +4974,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5060,7 +5060,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5144,7 +5144,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5224,7 +5224,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5310,7 +5310,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5333,13 +5333,13 @@
         <v>31.7</v>
       </c>
       <c r="E58" t="n">
-        <v>31.85</v>
+        <v>31.92</v>
       </c>
       <c r="F58" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0034</v>
       </c>
       <c r="H58" t="n">
         <v>0.3</v>
@@ -5374,9 +5374,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5390,7 +5390,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,11 +110,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,66 +637,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.48</v>
+        <v>30.28</v>
       </c>
       <c r="C2" t="n">
-        <v>30.5</v>
+        <v>30.33</v>
       </c>
       <c r="D2" t="n">
-        <v>30.18</v>
+        <v>29.94</v>
       </c>
       <c r="E2" t="n">
-        <v>30.28</v>
+        <v>30.11</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0058</v>
       </c>
       <c r="H2" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="I2" t="n">
-        <v>30.53</v>
+        <v>29.86</v>
       </c>
       <c r="J2" t="n">
-        <v>30.53</v>
+        <v>29.93</v>
       </c>
       <c r="K2" t="n">
-        <v>30.53</v>
+        <v>30.12</v>
       </c>
       <c r="L2" t="n">
-        <v>30.53</v>
+        <v>30.31</v>
       </c>
       <c r="M2" t="n">
-        <v>30.53</v>
+        <v>30.45</v>
       </c>
       <c r="N2" t="n">
-        <v>30.53</v>
+        <v>30.58</v>
       </c>
       <c r="O2" t="n">
-        <v>30.53</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>30.83</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -710,58 +709,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.28</v>
+        <v>30.22</v>
       </c>
       <c r="C3" t="n">
-        <v>30.33</v>
+        <v>30.59</v>
       </c>
       <c r="D3" t="n">
-        <v>29.94</v>
+        <v>30.15</v>
       </c>
       <c r="E3" t="n">
-        <v>30.11</v>
+        <v>30.44</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.17</v>
+        <v>0.33</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0111</v>
       </c>
       <c r="H3" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="I3" t="n">
-        <v>29.86</v>
+        <v>29.56</v>
       </c>
       <c r="J3" t="n">
-        <v>29.93</v>
+        <v>29.71</v>
       </c>
       <c r="K3" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="L3" t="n">
         <v>30.12</v>
       </c>
-      <c r="L3" t="n">
-        <v>30.31</v>
-      </c>
       <c r="M3" t="n">
-        <v>30.45</v>
+        <v>30.3</v>
       </c>
       <c r="N3" t="n">
-        <v>30.58</v>
+        <v>30.48</v>
       </c>
       <c r="O3" t="n">
-        <v>30.83</v>
+        <v>30.71</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,28 +772,30 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -798,50 +803,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="C4" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="K4" t="n">
         <v>30.22</v>
       </c>
-      <c r="C4" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="D4" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="E4" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I4" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="J4" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="K4" t="n">
-        <v>29.92</v>
-      </c>
       <c r="L4" t="n">
-        <v>30.12</v>
+        <v>30.41</v>
       </c>
       <c r="M4" t="n">
-        <v>30.3</v>
+        <v>30.66</v>
       </c>
       <c r="N4" t="n">
-        <v>30.48</v>
+        <v>30.92</v>
       </c>
       <c r="O4" t="n">
-        <v>30.71</v>
+        <v>31.03</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,80 +859,76 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.44</v>
+        <v>30.42</v>
       </c>
       <c r="C5" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="K5" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="M5" t="n">
         <v>30.53</v>
       </c>
-      <c r="D5" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="E5" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="J5" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="K5" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="L5" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="M5" t="n">
-        <v>30.66</v>
-      </c>
       <c r="N5" t="n">
-        <v>30.92</v>
+        <v>30.63</v>
       </c>
       <c r="O5" t="n">
-        <v>31.03</v>
+        <v>30.73</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,26 +936,34 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -966,50 +975,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.42</v>
+        <v>30.67</v>
       </c>
       <c r="C6" t="n">
-        <v>30.71</v>
+        <v>30.8</v>
       </c>
       <c r="D6" t="n">
-        <v>30.24</v>
+        <v>30.48</v>
       </c>
       <c r="E6" t="n">
-        <v>30.71</v>
+        <v>30.62</v>
       </c>
       <c r="F6" t="n">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.0027</v>
       </c>
       <c r="H6" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="I6" t="n">
-        <v>30.14</v>
+        <v>29.78</v>
       </c>
       <c r="J6" t="n">
-        <v>30.24</v>
+        <v>30.36</v>
       </c>
       <c r="K6" t="n">
-        <v>30.34</v>
+        <v>30.47</v>
       </c>
       <c r="L6" t="n">
-        <v>30.43</v>
+        <v>30.59</v>
       </c>
       <c r="M6" t="n">
-        <v>30.53</v>
+        <v>30.94</v>
       </c>
       <c r="N6" t="n">
-        <v>30.63</v>
+        <v>31.28</v>
       </c>
       <c r="O6" t="n">
-        <v>30.73</v>
+        <v>31.17</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,32 +1026,24 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W6" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1056,50 +1057,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="C7" t="n">
-        <v>30.8</v>
+        <v>30.85</v>
       </c>
       <c r="D7" t="n">
-        <v>30.48</v>
+        <v>30.53</v>
       </c>
       <c r="E7" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.08</v>
+        <v>0.21</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0069</v>
       </c>
       <c r="H7" t="n">
         <v>0.32</v>
       </c>
       <c r="I7" t="n">
-        <v>29.78</v>
+        <v>30.16</v>
       </c>
       <c r="J7" t="n">
-        <v>30.36</v>
+        <v>30.29</v>
       </c>
       <c r="K7" t="n">
-        <v>30.47</v>
+        <v>30.46</v>
       </c>
       <c r="L7" t="n">
-        <v>30.59</v>
+        <v>30.63</v>
       </c>
       <c r="M7" t="n">
-        <v>30.94</v>
+        <v>30.78</v>
       </c>
       <c r="N7" t="n">
-        <v>31.28</v>
+        <v>30.93</v>
       </c>
       <c r="O7" t="n">
-        <v>31.17</v>
+        <v>31.12</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,11 +1113,13 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1124,83 +1127,81 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="C8" t="n">
-        <v>30.85</v>
+        <v>30.83</v>
       </c>
       <c r="D8" t="n">
-        <v>30.53</v>
+        <v>30.52</v>
       </c>
       <c r="E8" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="F8" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0017</v>
       </c>
       <c r="H8" t="n">
         <v>0.32</v>
       </c>
       <c r="I8" t="n">
-        <v>30.16</v>
+        <v>30.2</v>
       </c>
       <c r="J8" t="n">
-        <v>30.29</v>
+        <v>30.58</v>
       </c>
       <c r="K8" t="n">
-        <v>30.46</v>
+        <v>30.67</v>
       </c>
       <c r="L8" t="n">
-        <v>30.63</v>
+        <v>30.76</v>
       </c>
       <c r="M8" t="n">
-        <v>30.78</v>
+        <v>31</v>
       </c>
       <c r="N8" t="n">
-        <v>30.93</v>
+        <v>31.23</v>
       </c>
       <c r="O8" t="n">
-        <v>31.12</v>
+        <v>31.18</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1208,81 +1209,83 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="C9" t="n">
-        <v>30.83</v>
+        <v>31.01</v>
       </c>
       <c r="D9" t="n">
-        <v>30.52</v>
+        <v>30.76</v>
       </c>
       <c r="E9" t="n">
-        <v>30.78</v>
+        <v>30.97</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.05</v>
+        <v>0.19</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="I9" t="n">
         <v>30.2</v>
       </c>
       <c r="J9" t="n">
-        <v>30.58</v>
+        <v>30.52</v>
       </c>
       <c r="K9" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="L9" t="n">
-        <v>30.76</v>
+        <v>30.73</v>
       </c>
       <c r="M9" t="n">
-        <v>31</v>
+        <v>30.94</v>
       </c>
       <c r="N9" t="n">
-        <v>31.23</v>
+        <v>31.15</v>
       </c>
       <c r="O9" t="n">
-        <v>31.18</v>
+        <v>31.15</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1290,82 +1293,84 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.78</v>
+        <v>30.96</v>
       </c>
       <c r="C10" t="n">
-        <v>31.01</v>
+        <v>31.18</v>
       </c>
       <c r="D10" t="n">
-        <v>30.76</v>
+        <v>30.36</v>
       </c>
       <c r="E10" t="n">
-        <v>30.97</v>
+        <v>30.55</v>
       </c>
       <c r="F10" t="n">
-        <v>0.19</v>
+        <v>-0.41</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.0133</v>
       </c>
       <c r="H10" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="J10" t="n">
-        <v>30.52</v>
+        <v>30.75</v>
       </c>
       <c r="K10" t="n">
-        <v>30.62</v>
+        <v>30.84</v>
       </c>
       <c r="L10" t="n">
-        <v>30.73</v>
+        <v>30.93</v>
       </c>
       <c r="M10" t="n">
-        <v>30.94</v>
+        <v>31.09</v>
       </c>
       <c r="N10" t="n">
-        <v>31.15</v>
+        <v>31.26</v>
       </c>
       <c r="O10" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>31.26</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U10" s="8" t="n">
@@ -1376,177 +1381,173 @@
       </c>
       <c r="W10" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30.96</v>
+        <v>30.62</v>
       </c>
       <c r="C11" t="n">
-        <v>31.18</v>
+        <v>31.44</v>
       </c>
       <c r="D11" t="n">
-        <v>30.36</v>
+        <v>30.62</v>
       </c>
       <c r="E11" t="n">
-        <v>30.55</v>
+        <v>31.34</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.41</v>
+        <v>0.78</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0257</v>
       </c>
       <c r="H11" t="n">
         <v>0.82</v>
       </c>
       <c r="I11" t="n">
-        <v>30.5</v>
+        <v>29.54</v>
       </c>
       <c r="J11" t="n">
-        <v>30.75</v>
+        <v>29.63</v>
       </c>
       <c r="K11" t="n">
-        <v>30.84</v>
+        <v>30.15</v>
       </c>
       <c r="L11" t="n">
-        <v>30.93</v>
+        <v>30.66</v>
       </c>
       <c r="M11" t="n">
-        <v>31.09</v>
+        <v>30.96</v>
       </c>
       <c r="N11" t="n">
-        <v>31.26</v>
+        <v>31.27</v>
       </c>
       <c r="O11" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.62</v>
+        <v>31.34</v>
       </c>
       <c r="C12" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="D12" t="n">
-        <v>30.62</v>
+        <v>30.65</v>
       </c>
       <c r="E12" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="F12" t="n">
-        <v>0.78</v>
+        <v>0.04</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0012</v>
       </c>
       <c r="H12" t="n">
         <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>29.54</v>
+        <v>29.81</v>
       </c>
       <c r="J12" t="n">
-        <v>29.63</v>
+        <v>30.67</v>
       </c>
       <c r="K12" t="n">
-        <v>30.15</v>
+        <v>30.93</v>
       </c>
       <c r="L12" t="n">
-        <v>30.66</v>
+        <v>31.19</v>
       </c>
       <c r="M12" t="n">
-        <v>30.96</v>
+        <v>31.75</v>
       </c>
       <c r="N12" t="n">
-        <v>31.27</v>
+        <v>32.31</v>
       </c>
       <c r="O12" t="n">
-        <v>32</v>
+        <v>32.26</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1556,63 +1557,59 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47</v>
+        <v>31.46</v>
       </c>
       <c r="D13" t="n">
-        <v>30.65</v>
+        <v>31.17</v>
       </c>
       <c r="E13" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0033</v>
       </c>
       <c r="H13" t="n">
-        <v>0.82</v>
+        <v>0.29</v>
       </c>
       <c r="I13" t="n">
-        <v>29.81</v>
+        <v>29.83</v>
       </c>
       <c r="J13" t="n">
-        <v>30.67</v>
+        <v>30.71</v>
       </c>
       <c r="K13" t="n">
-        <v>30.93</v>
+        <v>30.97</v>
       </c>
       <c r="L13" t="n">
-        <v>31.19</v>
+        <v>31.22</v>
       </c>
       <c r="M13" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="N13" t="n">
-        <v>32.31</v>
+        <v>32.36</v>
       </c>
       <c r="O13" t="n">
-        <v>32.26</v>
+        <v>32.3</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
@@ -1628,60 +1625,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="C14" t="n">
-        <v>31.46</v>
+        <v>31.32</v>
       </c>
       <c r="D14" t="n">
-        <v>31.17</v>
+        <v>31.08</v>
       </c>
       <c r="E14" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0015</v>
       </c>
       <c r="H14" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I14" t="n">
-        <v>29.83</v>
+        <v>30.88</v>
       </c>
       <c r="J14" t="n">
-        <v>30.71</v>
+        <v>30.96</v>
       </c>
       <c r="K14" t="n">
-        <v>30.97</v>
+        <v>31.13</v>
       </c>
       <c r="L14" t="n">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="M14" t="n">
-        <v>31.79</v>
+        <v>31.42</v>
       </c>
       <c r="N14" t="n">
-        <v>32.36</v>
+        <v>31.54</v>
       </c>
       <c r="O14" t="n">
-        <v>32.3</v>
+        <v>31.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,8 +1690,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
@@ -1706,7 +1709,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1720,50 +1723,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="C15" t="n">
-        <v>31.32</v>
+        <v>31.63</v>
       </c>
       <c r="D15" t="n">
-        <v>31.08</v>
+        <v>31.24</v>
       </c>
       <c r="E15" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0059</v>
       </c>
       <c r="H15" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="I15" t="n">
-        <v>30.88</v>
+        <v>30.83</v>
       </c>
       <c r="J15" t="n">
-        <v>30.96</v>
+        <v>31.14</v>
       </c>
       <c r="K15" t="n">
-        <v>31.13</v>
+        <v>31.2</v>
       </c>
       <c r="L15" t="n">
-        <v>31.3</v>
+        <v>31.26</v>
       </c>
       <c r="M15" t="n">
-        <v>31.42</v>
+        <v>31.44</v>
       </c>
       <c r="N15" t="n">
-        <v>31.54</v>
+        <v>31.62</v>
       </c>
       <c r="O15" t="n">
-        <v>31.75</v>
+        <v>31.56</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,83 +1774,83 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="C16" t="n">
-        <v>31.63</v>
+        <v>31.57</v>
       </c>
       <c r="D16" t="n">
-        <v>31.24</v>
+        <v>31.37</v>
       </c>
       <c r="E16" t="n">
-        <v>31.5</v>
+        <v>31.38</v>
       </c>
       <c r="F16" t="n">
-        <v>0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0039</v>
       </c>
       <c r="H16" t="n">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>30.83</v>
+        <v>30.86</v>
       </c>
       <c r="J16" t="n">
-        <v>31.14</v>
+        <v>31.15</v>
       </c>
       <c r="K16" t="n">
-        <v>31.2</v>
+        <v>31.31</v>
       </c>
       <c r="L16" t="n">
-        <v>31.26</v>
+        <v>31.47</v>
       </c>
       <c r="M16" t="n">
-        <v>31.44</v>
+        <v>31.7</v>
       </c>
       <c r="N16" t="n">
-        <v>31.62</v>
+        <v>31.92</v>
       </c>
       <c r="O16" t="n">
-        <v>31.56</v>
+        <v>32.01</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1855,83 +1858,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.5</v>
+        <v>31.39</v>
       </c>
       <c r="C17" t="n">
-        <v>31.57</v>
+        <v>31.46</v>
       </c>
       <c r="D17" t="n">
-        <v>31.37</v>
+        <v>31.25</v>
       </c>
       <c r="E17" t="n">
-        <v>31.38</v>
+        <v>31.36</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0007</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I17" t="n">
-        <v>30.86</v>
+        <v>31.16</v>
       </c>
       <c r="J17" t="n">
-        <v>31.15</v>
+        <v>31.13</v>
       </c>
       <c r="K17" t="n">
-        <v>31.31</v>
+        <v>31.28</v>
       </c>
       <c r="L17" t="n">
-        <v>31.47</v>
+        <v>31.42</v>
       </c>
       <c r="M17" t="n">
-        <v>31.7</v>
+        <v>31.48</v>
       </c>
       <c r="N17" t="n">
-        <v>31.92</v>
+        <v>31.54</v>
       </c>
       <c r="O17" t="n">
-        <v>32.01</v>
+        <v>31.78</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1941,12 +1944,12 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1958,64 +1961,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.39</v>
+        <v>31.38</v>
       </c>
       <c r="C18" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="D18" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="E18" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I18" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="J18" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="K18" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="L18" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="M18" t="n">
         <v>31.46</v>
       </c>
-      <c r="D18" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="E18" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>-0.0007</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I18" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="J18" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="K18" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="L18" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="M18" t="n">
-        <v>31.48</v>
-      </c>
       <c r="N18" t="n">
-        <v>31.54</v>
+        <v>31.57</v>
       </c>
       <c r="O18" t="n">
-        <v>31.78</v>
+        <v>31.68</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2023,83 +2026,83 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31.38</v>
+        <v>31.6</v>
       </c>
       <c r="C19" t="n">
-        <v>31.68</v>
+        <v>31.74</v>
       </c>
       <c r="D19" t="n">
-        <v>31.35</v>
+        <v>31.51</v>
       </c>
       <c r="E19" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="F19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H19" t="n">
         <v>0.23</v>
       </c>
-      <c r="G19" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.33</v>
-      </c>
       <c r="I19" t="n">
-        <v>31.04</v>
+        <v>31.02</v>
       </c>
       <c r="J19" t="n">
-        <v>31.15</v>
+        <v>31.31</v>
       </c>
       <c r="K19" t="n">
-        <v>31.25</v>
+        <v>31.43</v>
       </c>
       <c r="L19" t="n">
-        <v>31.36</v>
+        <v>31.55</v>
       </c>
       <c r="M19" t="n">
-        <v>31.46</v>
+        <v>31.76</v>
       </c>
       <c r="N19" t="n">
-        <v>31.57</v>
+        <v>31.96</v>
       </c>
       <c r="O19" t="n">
-        <v>31.68</v>
+        <v>32</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2112,25 +2115,19 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2140,63 +2137,67 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31.6</v>
+        <v>31.61</v>
       </c>
       <c r="C20" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="D20" t="n">
-        <v>31.51</v>
+        <v>31.37</v>
       </c>
       <c r="E20" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0005</v>
+        <v>-0.0075</v>
       </c>
       <c r="H20" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="I20" t="n">
-        <v>31.02</v>
+        <v>31.27</v>
       </c>
       <c r="J20" t="n">
-        <v>31.31</v>
+        <v>31.37</v>
       </c>
       <c r="K20" t="n">
-        <v>31.43</v>
+        <v>31.49</v>
       </c>
       <c r="L20" t="n">
-        <v>31.55</v>
+        <v>31.62</v>
       </c>
       <c r="M20" t="n">
-        <v>31.76</v>
+        <v>31.73</v>
       </c>
       <c r="N20" t="n">
-        <v>31.96</v>
+        <v>31.83</v>
       </c>
       <c r="O20" t="n">
-        <v>32</v>
+        <v>31.98</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2208,146 +2209,152 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="C21" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="D21" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="E21" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I21" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="J21" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="K21" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="L21" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M21" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N21" t="n">
         <v>31.61</v>
       </c>
-      <c r="C21" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="D21" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="E21" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I21" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="J21" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="K21" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="L21" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="M21" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="N21" t="n">
-        <v>31.83</v>
-      </c>
       <c r="O21" t="n">
-        <v>31.98</v>
+        <v>32</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31.38</v>
+        <v>31.61</v>
       </c>
       <c r="C22" t="n">
-        <v>31.58</v>
+        <v>31.71</v>
       </c>
       <c r="D22" t="n">
-        <v>31.12</v>
+        <v>31.49</v>
       </c>
       <c r="E22" t="n">
         <v>31.58</v>
       </c>
       <c r="F22" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0003</v>
       </c>
       <c r="H22" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="I22" t="n">
-        <v>31.06</v>
+        <v>30.65</v>
       </c>
       <c r="J22" t="n">
-        <v>30.98</v>
+        <v>31.23</v>
       </c>
       <c r="K22" t="n">
-        <v>31.21</v>
+        <v>31.35</v>
       </c>
       <c r="L22" t="n">
-        <v>31.45</v>
+        <v>31.47</v>
       </c>
       <c r="M22" t="n">
-        <v>31.53</v>
+        <v>31.82</v>
       </c>
       <c r="N22" t="n">
-        <v>31.61</v>
+        <v>32.16</v>
       </c>
       <c r="O22" t="n">
-        <v>32</v>
+        <v>32.05</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,204 +2362,198 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>31.61</v>
       </c>
       <c r="C23" t="n">
-        <v>31.71</v>
+        <v>32.77</v>
       </c>
       <c r="D23" t="n">
-        <v>31.49</v>
+        <v>31.32</v>
       </c>
       <c r="E23" t="n">
-        <v>31.58</v>
+        <v>31.37</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0065</v>
       </c>
       <c r="H23" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="I23" t="n">
-        <v>30.65</v>
+        <v>31.27</v>
       </c>
       <c r="J23" t="n">
-        <v>31.23</v>
+        <v>31.34</v>
       </c>
       <c r="K23" t="n">
-        <v>31.35</v>
+        <v>31.46</v>
       </c>
       <c r="L23" t="n">
-        <v>31.47</v>
+        <v>31.59</v>
       </c>
       <c r="M23" t="n">
-        <v>31.82</v>
+        <v>31.69</v>
       </c>
       <c r="N23" t="n">
-        <v>32.16</v>
+        <v>31.79</v>
       </c>
       <c r="O23" t="n">
-        <v>32.05</v>
+        <v>31.94</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="C24" t="n">
-        <v>32.77</v>
+        <v>31.65</v>
       </c>
       <c r="D24" t="n">
-        <v>31.32</v>
+        <v>31.26</v>
       </c>
       <c r="E24" t="n">
-        <v>31.37</v>
+        <v>31.51</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.21</v>
+        <v>0.14</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0045</v>
       </c>
       <c r="H24" t="n">
-        <v>1.45</v>
+        <v>0.39</v>
       </c>
       <c r="I24" t="n">
-        <v>31.27</v>
+        <v>29.88</v>
       </c>
       <c r="J24" t="n">
-        <v>31.34</v>
+        <v>29.58</v>
       </c>
       <c r="K24" t="n">
-        <v>31.46</v>
+        <v>30.65</v>
       </c>
       <c r="L24" t="n">
-        <v>31.59</v>
+        <v>31.71</v>
       </c>
       <c r="M24" t="n">
-        <v>31.69</v>
+        <v>32.09</v>
       </c>
       <c r="N24" t="n">
-        <v>31.79</v>
+        <v>32.48</v>
       </c>
       <c r="O24" t="n">
-        <v>31.94</v>
+        <v>34.22</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2566,50 +2567,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31.37</v>
+        <v>31.47</v>
       </c>
       <c r="C25" t="n">
-        <v>31.65</v>
+        <v>31.5</v>
       </c>
       <c r="D25" t="n">
-        <v>31.26</v>
+        <v>31.18</v>
       </c>
       <c r="E25" t="n">
-        <v>31.51</v>
+        <v>31.38</v>
       </c>
       <c r="F25" t="n">
-        <v>0.14</v>
+        <v>-0.14</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0043</v>
       </c>
       <c r="H25" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="I25" t="n">
-        <v>29.88</v>
+        <v>30.87</v>
       </c>
       <c r="J25" t="n">
-        <v>29.58</v>
+        <v>31.14</v>
       </c>
       <c r="K25" t="n">
-        <v>30.65</v>
+        <v>31.31</v>
       </c>
       <c r="L25" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="M25" t="n">
         <v>31.71</v>
       </c>
-      <c r="M25" t="n">
-        <v>32.09</v>
-      </c>
       <c r="N25" t="n">
-        <v>32.48</v>
+        <v>31.93</v>
       </c>
       <c r="O25" t="n">
-        <v>34.22</v>
+        <v>32.05</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2617,12 +2618,14 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2634,64 +2637,64 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C26" t="n">
-        <v>31.5</v>
+        <v>31.96</v>
       </c>
       <c r="D26" t="n">
-        <v>31.18</v>
+        <v>31.39</v>
       </c>
       <c r="E26" t="n">
-        <v>31.38</v>
+        <v>31.8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0136</v>
       </c>
       <c r="H26" t="n">
-        <v>0.32</v>
+        <v>0.57</v>
       </c>
       <c r="I26" t="n">
-        <v>30.87</v>
+        <v>30.86</v>
       </c>
       <c r="J26" t="n">
-        <v>31.14</v>
+        <v>31.08</v>
       </c>
       <c r="K26" t="n">
-        <v>31.31</v>
+        <v>31.22</v>
       </c>
       <c r="L26" t="n">
-        <v>31.48</v>
+        <v>31.36</v>
       </c>
       <c r="M26" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N26" t="n">
         <v>31.71</v>
       </c>
-      <c r="N26" t="n">
-        <v>31.93</v>
-      </c>
       <c r="O26" t="n">
-        <v>32.05</v>
+        <v>31.81</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2699,83 +2702,83 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.44</v>
+        <v>32.03</v>
       </c>
       <c r="C27" t="n">
-        <v>31.96</v>
+        <v>32.16</v>
       </c>
       <c r="D27" t="n">
-        <v>31.39</v>
+        <v>31.53</v>
       </c>
       <c r="E27" t="n">
-        <v>31.8</v>
+        <v>32.16</v>
       </c>
       <c r="F27" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0113</v>
       </c>
       <c r="H27" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="I27" t="n">
-        <v>30.86</v>
+        <v>30.82</v>
       </c>
       <c r="J27" t="n">
-        <v>31.08</v>
+        <v>31.29</v>
       </c>
       <c r="K27" t="n">
-        <v>31.22</v>
+        <v>31.52</v>
       </c>
       <c r="L27" t="n">
-        <v>31.36</v>
+        <v>31.74</v>
       </c>
       <c r="M27" t="n">
-        <v>31.53</v>
+        <v>32.09</v>
       </c>
       <c r="N27" t="n">
-        <v>31.71</v>
+        <v>32.44</v>
       </c>
       <c r="O27" t="n">
-        <v>31.81</v>
+        <v>32.54</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2793,20 +2796,16 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2816,50 +2815,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="C28" t="n">
-        <v>32.16</v>
+        <v>32.12</v>
       </c>
       <c r="D28" t="n">
-        <v>31.53</v>
+        <v>31.8</v>
       </c>
       <c r="E28" t="n">
-        <v>32.16</v>
+        <v>32.02</v>
       </c>
       <c r="F28" t="n">
-        <v>0.36</v>
+        <v>-0.14</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0044</v>
       </c>
       <c r="H28" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="I28" t="n">
-        <v>30.82</v>
+        <v>30.91</v>
       </c>
       <c r="J28" t="n">
-        <v>31.29</v>
+        <v>31.69</v>
       </c>
       <c r="K28" t="n">
-        <v>31.52</v>
+        <v>31.85</v>
       </c>
       <c r="L28" t="n">
-        <v>31.74</v>
+        <v>32.01</v>
       </c>
       <c r="M28" t="n">
-        <v>32.09</v>
+        <v>32.48</v>
       </c>
       <c r="N28" t="n">
-        <v>32.44</v>
+        <v>32.95</v>
       </c>
       <c r="O28" t="n">
-        <v>32.54</v>
+        <v>32.79</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2867,18 +2866,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2886,60 +2885,64 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32.09</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>32.12</v>
+        <v>32.14</v>
       </c>
       <c r="D29" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="E29" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0002</v>
       </c>
       <c r="H29" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I29" t="n">
-        <v>30.91</v>
+        <v>31.47</v>
       </c>
       <c r="J29" t="n">
-        <v>31.69</v>
+        <v>31.73</v>
       </c>
       <c r="K29" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="L29" t="n">
-        <v>32.01</v>
+        <v>31.99</v>
       </c>
       <c r="M29" t="n">
-        <v>32.48</v>
+        <v>32.18</v>
       </c>
       <c r="N29" t="n">
-        <v>32.95</v>
+        <v>32.38</v>
       </c>
       <c r="O29" t="n">
-        <v>32.79</v>
+        <v>32.44</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2966,64 +2969,64 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="C30" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="D30" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="E30" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I30" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="J30" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K30" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="L30" t="n">
         <v>32</v>
       </c>
-      <c r="C30" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="D30" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="E30" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I30" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="J30" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="K30" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="L30" t="n">
-        <v>31.99</v>
-      </c>
       <c r="M30" t="n">
-        <v>32.18</v>
+        <v>32.21</v>
       </c>
       <c r="N30" t="n">
-        <v>32.38</v>
+        <v>32.43</v>
       </c>
       <c r="O30" t="n">
-        <v>32.44</v>
+        <v>32.51</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3036,13 +3039,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3050,7 +3055,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3064,50 +3069,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
       <c r="C31" t="n">
-        <v>32.22</v>
+        <v>32.04</v>
       </c>
       <c r="D31" t="n">
-        <v>31.84</v>
+        <v>31.68</v>
       </c>
       <c r="E31" t="n">
-        <v>31.96</v>
+        <v>31.73</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0074</v>
       </c>
       <c r="H31" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I31" t="n">
-        <v>31.42</v>
+        <v>31.47</v>
       </c>
       <c r="J31" t="n">
-        <v>31.7</v>
+        <v>31.55</v>
       </c>
       <c r="K31" t="n">
-        <v>31.85</v>
+        <v>31.78</v>
       </c>
       <c r="L31" t="n">
         <v>32</v>
       </c>
       <c r="M31" t="n">
-        <v>32.21</v>
+        <v>32.15</v>
       </c>
       <c r="N31" t="n">
-        <v>32.43</v>
+        <v>32.3</v>
       </c>
       <c r="O31" t="n">
-        <v>32.51</v>
+        <v>32.59</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3117,18 +3122,16 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3136,64 +3139,64 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31.96</v>
+        <v>31.77</v>
       </c>
       <c r="C32" t="n">
-        <v>32.04</v>
+        <v>31.87</v>
       </c>
       <c r="D32" t="n">
-        <v>31.68</v>
+        <v>31.37</v>
       </c>
       <c r="E32" t="n">
-        <v>31.73</v>
+        <v>31.47</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0083</v>
       </c>
       <c r="H32" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="I32" t="n">
-        <v>31.47</v>
+        <v>31.32</v>
       </c>
       <c r="J32" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K32" t="n">
         <v>31.55</v>
       </c>
-      <c r="K32" t="n">
-        <v>31.78</v>
-      </c>
       <c r="L32" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="M32" t="n">
-        <v>32.15</v>
+        <v>31.91</v>
       </c>
       <c r="N32" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O32" t="n">
-        <v>32.59</v>
+        <v>32.41</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3220,7 +3223,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3234,50 +3237,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31.77</v>
+        <v>31.47</v>
       </c>
       <c r="C33" t="n">
-        <v>31.87</v>
+        <v>31.59</v>
       </c>
       <c r="D33" t="n">
-        <v>31.37</v>
+        <v>31.18</v>
       </c>
       <c r="E33" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0009</v>
       </c>
       <c r="H33" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="I33" t="n">
-        <v>31.32</v>
+        <v>30.88</v>
       </c>
       <c r="J33" t="n">
-        <v>31.3</v>
+        <v>30.89</v>
       </c>
       <c r="K33" t="n">
-        <v>31.55</v>
+        <v>31.22</v>
       </c>
       <c r="L33" t="n">
-        <v>31.8</v>
+        <v>31.54</v>
       </c>
       <c r="M33" t="n">
-        <v>31.91</v>
+        <v>31.71</v>
       </c>
       <c r="N33" t="n">
-        <v>32.02</v>
+        <v>31.88</v>
       </c>
       <c r="O33" t="n">
-        <v>32.41</v>
+        <v>32.36</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3287,12 +3290,12 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3304,7 +3307,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3318,50 +3321,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C34" t="n">
-        <v>31.59</v>
+        <v>31.75</v>
       </c>
       <c r="D34" t="n">
-        <v>31.18</v>
+        <v>31.38</v>
       </c>
       <c r="E34" t="n">
-        <v>31.44</v>
+        <v>31.55</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0037</v>
       </c>
       <c r="H34" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="I34" t="n">
-        <v>30.88</v>
+        <v>30.78</v>
       </c>
       <c r="J34" t="n">
-        <v>30.89</v>
+        <v>31.05</v>
       </c>
       <c r="K34" t="n">
-        <v>31.22</v>
+        <v>31.23</v>
       </c>
       <c r="L34" t="n">
-        <v>31.54</v>
+        <v>31.41</v>
       </c>
       <c r="M34" t="n">
-        <v>31.71</v>
+        <v>31.64</v>
       </c>
       <c r="N34" t="n">
-        <v>31.88</v>
+        <v>31.87</v>
       </c>
       <c r="O34" t="n">
-        <v>32.36</v>
+        <v>32</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3369,18 +3372,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3388,64 +3391,60 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.44</v>
+        <v>31.64</v>
       </c>
       <c r="C35" t="n">
-        <v>31.75</v>
+        <v>31.69</v>
       </c>
       <c r="D35" t="n">
-        <v>31.38</v>
+        <v>31.3</v>
       </c>
       <c r="E35" t="n">
-        <v>31.55</v>
+        <v>31.3</v>
       </c>
       <c r="F35" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="I35" t="n">
-        <v>30.78</v>
+        <v>31.02</v>
       </c>
       <c r="J35" t="n">
-        <v>31.05</v>
+        <v>31.18</v>
       </c>
       <c r="K35" t="n">
-        <v>31.23</v>
+        <v>31.37</v>
       </c>
       <c r="L35" t="n">
-        <v>31.41</v>
+        <v>31.56</v>
       </c>
       <c r="M35" t="n">
-        <v>31.64</v>
+        <v>31.74</v>
       </c>
       <c r="N35" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="O35" t="n">
-        <v>32</v>
+        <v>32.11</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3453,79 +3452,83 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.64</v>
+        <v>31.3</v>
       </c>
       <c r="C36" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="D36" t="n">
         <v>31.3</v>
       </c>
       <c r="E36" t="n">
-        <v>31.3</v>
+        <v>31.56</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.26</v>
+        <v>0.27</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="I36" t="n">
-        <v>31.02</v>
+        <v>30.9</v>
       </c>
       <c r="J36" t="n">
-        <v>31.18</v>
+        <v>30.8</v>
       </c>
       <c r="K36" t="n">
-        <v>31.37</v>
+        <v>31.1</v>
       </c>
       <c r="L36" t="n">
-        <v>31.56</v>
+        <v>31.39</v>
       </c>
       <c r="M36" t="n">
-        <v>31.74</v>
+        <v>31.49</v>
       </c>
       <c r="N36" t="n">
-        <v>31.91</v>
+        <v>31.59</v>
       </c>
       <c r="O36" t="n">
-        <v>32.11</v>
+        <v>32.09</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3533,83 +3536,85 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.3</v>
+        <v>31.59</v>
       </c>
       <c r="C37" t="n">
-        <v>31.62</v>
+        <v>31.78</v>
       </c>
       <c r="D37" t="n">
-        <v>31.3</v>
+        <v>31.36</v>
       </c>
       <c r="E37" t="n">
-        <v>31.56</v>
+        <v>31.36</v>
       </c>
       <c r="F37" t="n">
-        <v>0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0065</v>
       </c>
       <c r="H37" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="I37" t="n">
-        <v>30.9</v>
+        <v>30.98</v>
       </c>
       <c r="J37" t="n">
-        <v>30.8</v>
+        <v>31.29</v>
       </c>
       <c r="K37" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="L37" t="n">
-        <v>31.39</v>
+        <v>31.51</v>
       </c>
       <c r="M37" t="n">
-        <v>31.49</v>
+        <v>31.72</v>
       </c>
       <c r="N37" t="n">
-        <v>31.59</v>
+        <v>31.93</v>
       </c>
       <c r="O37" t="n">
-        <v>32.09</v>
+        <v>31.95</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3617,12 +3622,14 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3630,15 +3637,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3652,50 +3657,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.59</v>
+        <v>31.44</v>
       </c>
       <c r="C38" t="n">
-        <v>31.78</v>
+        <v>31.52</v>
       </c>
       <c r="D38" t="n">
-        <v>31.36</v>
+        <v>31.31</v>
       </c>
       <c r="E38" t="n">
-        <v>31.36</v>
+        <v>31.41</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0018</v>
       </c>
       <c r="H38" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="I38" t="n">
-        <v>30.98</v>
+        <v>30.94</v>
       </c>
       <c r="J38" t="n">
-        <v>31.29</v>
+        <v>30.83</v>
       </c>
       <c r="K38" t="n">
-        <v>31.4</v>
+        <v>31.15</v>
       </c>
       <c r="L38" t="n">
-        <v>31.51</v>
+        <v>31.46</v>
       </c>
       <c r="M38" t="n">
-        <v>31.72</v>
+        <v>31.57</v>
       </c>
       <c r="N38" t="n">
-        <v>31.93</v>
+        <v>31.67</v>
       </c>
       <c r="O38" t="n">
-        <v>31.95</v>
+        <v>32.2</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3703,20 +3708,16 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3724,64 +3725,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.44</v>
+        <v>31.41</v>
       </c>
       <c r="C39" t="n">
-        <v>31.52</v>
+        <v>31.6</v>
       </c>
       <c r="D39" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="E39" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I39" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J39" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="K39" t="n">
         <v>31.31</v>
       </c>
-      <c r="E39" t="n">
+      <c r="L39" t="n">
         <v>31.41</v>
       </c>
-      <c r="F39" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="J39" t="n">
-        <v>30.83</v>
-      </c>
-      <c r="K39" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="L39" t="n">
-        <v>31.46</v>
-      </c>
       <c r="M39" t="n">
-        <v>31.57</v>
+        <v>31.51</v>
       </c>
       <c r="N39" t="n">
-        <v>31.67</v>
+        <v>31.61</v>
       </c>
       <c r="O39" t="n">
-        <v>32.2</v>
+        <v>31.72</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3789,16 +3790,20 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3806,64 +3811,64 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.41</v>
+        <v>31.59</v>
       </c>
       <c r="C40" t="n">
-        <v>31.6</v>
+        <v>31.76</v>
       </c>
       <c r="D40" t="n">
-        <v>31.28</v>
+        <v>31.44</v>
       </c>
       <c r="E40" t="n">
         <v>31.56</v>
       </c>
       <c r="F40" t="n">
-        <v>0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0002</v>
       </c>
       <c r="H40" t="n">
         <v>0.33</v>
       </c>
       <c r="I40" t="n">
-        <v>31.11</v>
+        <v>30.95</v>
       </c>
       <c r="J40" t="n">
-        <v>31.21</v>
+        <v>31.3</v>
       </c>
       <c r="K40" t="n">
-        <v>31.31</v>
+        <v>31.4</v>
       </c>
       <c r="L40" t="n">
-        <v>31.41</v>
+        <v>31.5</v>
       </c>
       <c r="M40" t="n">
-        <v>31.51</v>
+        <v>31.73</v>
       </c>
       <c r="N40" t="n">
-        <v>31.61</v>
+        <v>31.95</v>
       </c>
       <c r="O40" t="n">
-        <v>31.72</v>
+        <v>31.93</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3871,28 +3876,26 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3906,50 +3909,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="C41" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="D41" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="E41" t="n">
-        <v>31.56</v>
+        <v>31.65</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0028</v>
       </c>
       <c r="H41" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="I41" t="n">
-        <v>30.95</v>
+        <v>31.11</v>
       </c>
       <c r="J41" t="n">
-        <v>31.3</v>
+        <v>31.21</v>
       </c>
       <c r="K41" t="n">
-        <v>31.4</v>
+        <v>31.39</v>
       </c>
       <c r="L41" t="n">
-        <v>31.5</v>
+        <v>31.58</v>
       </c>
       <c r="M41" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="N41" t="n">
-        <v>31.95</v>
+        <v>31.86</v>
       </c>
       <c r="O41" t="n">
-        <v>31.93</v>
+        <v>32.09</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3965,10 +3968,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3976,7 +3977,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3990,50 +3991,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="C42" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="D42" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E42" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I42" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="J42" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="K42" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="L42" t="n">
         <v>31.61</v>
       </c>
-      <c r="C42" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="D42" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="E42" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I42" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="J42" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="K42" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="L42" t="n">
-        <v>31.58</v>
-      </c>
       <c r="M42" t="n">
-        <v>31.72</v>
+        <v>31.76</v>
       </c>
       <c r="N42" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="O42" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4046,76 +4047,76 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.7</v>
+        <v>31.85</v>
       </c>
       <c r="C43" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="D43" t="n">
-        <v>31.58</v>
+        <v>31.79</v>
       </c>
       <c r="E43" t="n">
-        <v>31.84</v>
+        <v>31.9</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0016</v>
       </c>
       <c r="H43" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="I43" t="n">
-        <v>31.23</v>
+        <v>31.26</v>
       </c>
       <c r="J43" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="K43" t="n">
-        <v>31.53</v>
+        <v>31.68</v>
       </c>
       <c r="L43" t="n">
-        <v>31.61</v>
+        <v>31.79</v>
       </c>
       <c r="M43" t="n">
-        <v>31.76</v>
+        <v>32.01</v>
       </c>
       <c r="N43" t="n">
-        <v>31.91</v>
+        <v>32.22</v>
       </c>
       <c r="O43" t="n">
-        <v>31.93</v>
+        <v>32.23</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4128,23 +4129,19 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4154,50 +4151,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.85</v>
+        <v>31.93</v>
       </c>
       <c r="C44" t="n">
-        <v>31.96</v>
+        <v>32.23</v>
       </c>
       <c r="D44" t="n">
-        <v>31.79</v>
+        <v>31.92</v>
       </c>
       <c r="E44" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0063</v>
       </c>
       <c r="H44" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="I44" t="n">
-        <v>31.26</v>
+        <v>31.62</v>
       </c>
       <c r="J44" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K44" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="L44" t="n">
-        <v>31.79</v>
+        <v>31.89</v>
       </c>
       <c r="M44" t="n">
-        <v>32.01</v>
+        <v>31.98</v>
       </c>
       <c r="N44" t="n">
-        <v>32.22</v>
+        <v>32.08</v>
       </c>
       <c r="O44" t="n">
-        <v>32.23</v>
+        <v>32.13</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4210,19 +4207,25 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4232,50 +4235,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.93</v>
+        <v>32.1</v>
       </c>
       <c r="C45" t="n">
-        <v>32.23</v>
+        <v>32.42</v>
       </c>
       <c r="D45" t="n">
-        <v>31.92</v>
+        <v>32.03</v>
       </c>
       <c r="E45" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="I45" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="J45" t="n">
-        <v>31.74</v>
+        <v>31.8</v>
       </c>
       <c r="K45" t="n">
-        <v>31.81</v>
+        <v>31.94</v>
       </c>
       <c r="L45" t="n">
-        <v>31.89</v>
+        <v>32.09</v>
       </c>
       <c r="M45" t="n">
-        <v>31.98</v>
+        <v>32.25</v>
       </c>
       <c r="N45" t="n">
-        <v>32.08</v>
+        <v>32.42</v>
       </c>
       <c r="O45" t="n">
-        <v>32.13</v>
+        <v>32.53</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4301,12 +4304,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4316,50 +4317,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C46" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D46" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="E46" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I46" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="J46" t="n">
         <v>32.1</v>
       </c>
-      <c r="C46" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D46" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="E46" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I46" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="J46" t="n">
-        <v>31.8</v>
-      </c>
       <c r="K46" t="n">
-        <v>31.94</v>
+        <v>32.2</v>
       </c>
       <c r="L46" t="n">
-        <v>32.09</v>
+        <v>32.31</v>
       </c>
       <c r="M46" t="n">
-        <v>32.25</v>
+        <v>32.59</v>
       </c>
       <c r="N46" t="n">
-        <v>32.42</v>
+        <v>32.87</v>
       </c>
       <c r="O46" t="n">
-        <v>32.53</v>
+        <v>32.81</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4372,76 +4373,76 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32.31</v>
+        <v>32.32</v>
       </c>
       <c r="C47" t="n">
-        <v>32.49</v>
+        <v>32.55</v>
       </c>
       <c r="D47" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="E47" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I47" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="J47" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="K47" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="L47" t="n">
         <v>32.35</v>
       </c>
-      <c r="F47" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I47" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="J47" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>32.31</v>
-      </c>
       <c r="M47" t="n">
-        <v>32.59</v>
+        <v>32.48</v>
       </c>
       <c r="N47" t="n">
-        <v>32.87</v>
+        <v>32.6</v>
       </c>
       <c r="O47" t="n">
-        <v>32.81</v>
+        <v>32.74</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4449,16 +4450,20 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4466,64 +4471,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32.32</v>
+        <v>32.29</v>
       </c>
       <c r="C48" t="n">
-        <v>32.55</v>
+        <v>32.49</v>
       </c>
       <c r="D48" t="n">
-        <v>32.21</v>
+        <v>32.12</v>
       </c>
       <c r="E48" t="n">
-        <v>32.29</v>
+        <v>32.24</v>
       </c>
       <c r="F48" t="n">
         <v>-0.06</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="H48" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I48" t="n">
-        <v>31.98</v>
+        <v>31.86</v>
       </c>
       <c r="J48" t="n">
-        <v>32.09</v>
+        <v>31.91</v>
       </c>
       <c r="K48" t="n">
-        <v>32.22</v>
+        <v>32.12</v>
       </c>
       <c r="L48" t="n">
-        <v>32.35</v>
+        <v>32.34</v>
       </c>
       <c r="M48" t="n">
-        <v>32.48</v>
+        <v>32.47</v>
       </c>
       <c r="N48" t="n">
         <v>32.6</v>
       </c>
       <c r="O48" t="n">
-        <v>32.74</v>
+        <v>32.9</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4531,85 +4536,83 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="C49" t="n">
         <v>32.29</v>
       </c>
-      <c r="C49" t="n">
-        <v>32.49</v>
-      </c>
       <c r="D49" t="n">
-        <v>32.12</v>
+        <v>31.92</v>
       </c>
       <c r="E49" t="n">
-        <v>32.24</v>
+        <v>32.01</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.0071</v>
       </c>
       <c r="H49" t="n">
         <v>0.37</v>
       </c>
       <c r="I49" t="n">
-        <v>31.86</v>
+        <v>31.76</v>
       </c>
       <c r="J49" t="n">
-        <v>31.91</v>
+        <v>31.83</v>
       </c>
       <c r="K49" t="n">
-        <v>32.12</v>
+        <v>32.05</v>
       </c>
       <c r="L49" t="n">
-        <v>32.34</v>
+        <v>32.27</v>
       </c>
       <c r="M49" t="n">
-        <v>32.47</v>
+        <v>32.42</v>
       </c>
       <c r="N49" t="n">
-        <v>32.6</v>
+        <v>32.57</v>
       </c>
       <c r="O49" t="n">
-        <v>32.9</v>
+        <v>32.86</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4617,18 +4620,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4636,7 +4639,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4650,50 +4653,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32.24</v>
+        <v>31.99</v>
       </c>
       <c r="C50" t="n">
-        <v>32.29</v>
+        <v>32.01</v>
       </c>
       <c r="D50" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E50" t="n">
-        <v>32.01</v>
+        <v>31.83</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0071</v>
+        <v>-0.0055</v>
       </c>
       <c r="H50" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="I50" t="n">
-        <v>31.76</v>
+        <v>31.55</v>
       </c>
       <c r="J50" t="n">
-        <v>31.83</v>
+        <v>31.59</v>
       </c>
       <c r="K50" t="n">
-        <v>32.05</v>
+        <v>31.82</v>
       </c>
       <c r="L50" t="n">
-        <v>32.27</v>
+        <v>32.06</v>
       </c>
       <c r="M50" t="n">
-        <v>32.42</v>
+        <v>32.19</v>
       </c>
       <c r="N50" t="n">
-        <v>32.57</v>
+        <v>32.33</v>
       </c>
       <c r="O50" t="n">
-        <v>32.86</v>
+        <v>32.66</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4720,7 +4723,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4734,60 +4737,62 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.99</v>
+        <v>31.82</v>
       </c>
       <c r="C51" t="n">
-        <v>32.01</v>
+        <v>31.91</v>
       </c>
       <c r="D51" t="n">
-        <v>31.75</v>
+        <v>31.55</v>
       </c>
       <c r="E51" t="n">
-        <v>31.83</v>
+        <v>31.62</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0066</v>
       </c>
       <c r="H51" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="I51" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J51" t="n">
         <v>31.55</v>
       </c>
-      <c r="J51" t="n">
-        <v>31.59</v>
-      </c>
       <c r="K51" t="n">
-        <v>31.82</v>
+        <v>31.7</v>
       </c>
       <c r="L51" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="M51" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="N51" t="n">
         <v>32.06</v>
       </c>
-      <c r="M51" t="n">
-        <v>32.19</v>
-      </c>
-      <c r="N51" t="n">
-        <v>32.33</v>
-      </c>
       <c r="O51" t="n">
-        <v>32.66</v>
+        <v>32.26</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
@@ -4804,7 +4809,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4818,155 +4823,155 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.82</v>
+        <v>31.63</v>
       </c>
       <c r="C52" t="n">
-        <v>31.91</v>
+        <v>31.8</v>
       </c>
       <c r="D52" t="n">
-        <v>31.55</v>
+        <v>31.58</v>
       </c>
       <c r="E52" t="n">
-        <v>31.62</v>
+        <v>31.67</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.21</v>
+        <v>0.05</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0066</v>
+        <v>0.0016</v>
       </c>
       <c r="H52" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="I52" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="J52" t="n">
-        <v>31.55</v>
+        <v>31.21</v>
       </c>
       <c r="K52" t="n">
-        <v>31.7</v>
+        <v>31.44</v>
       </c>
       <c r="L52" t="n">
-        <v>31.86</v>
+        <v>31.68</v>
       </c>
       <c r="M52" t="n">
-        <v>31.96</v>
+        <v>31.8</v>
       </c>
       <c r="N52" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="O52" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="C53" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="D53" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="E53" t="n">
         <v>31.63</v>
       </c>
-      <c r="C53" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D53" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="E53" t="n">
-        <v>31.67</v>
-      </c>
       <c r="F53" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0013</v>
       </c>
       <c r="H53" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I53" t="n">
-        <v>31.2</v>
+        <v>31.37</v>
       </c>
       <c r="J53" t="n">
-        <v>31.21</v>
+        <v>31.44</v>
       </c>
       <c r="K53" t="n">
-        <v>31.44</v>
+        <v>31.56</v>
       </c>
       <c r="L53" t="n">
         <v>31.68</v>
       </c>
       <c r="M53" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="N53" t="n">
-        <v>31.92</v>
+        <v>31.88</v>
       </c>
       <c r="O53" t="n">
-        <v>32.27</v>
+        <v>32.02</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4974,85 +4979,83 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.62</v>
+        <v>31.68</v>
       </c>
       <c r="C54" t="n">
-        <v>31.69</v>
+        <v>31.94</v>
       </c>
       <c r="D54" t="n">
-        <v>31.42</v>
+        <v>31.61</v>
       </c>
       <c r="E54" t="n">
-        <v>31.63</v>
+        <v>31.76</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0043</v>
       </c>
       <c r="H54" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="I54" t="n">
-        <v>31.37</v>
+        <v>31.14</v>
       </c>
       <c r="J54" t="n">
-        <v>31.44</v>
+        <v>31.39</v>
       </c>
       <c r="K54" t="n">
-        <v>31.56</v>
+        <v>31.49</v>
       </c>
       <c r="L54" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M54" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="N54" t="n">
-        <v>31.88</v>
+        <v>31.94</v>
       </c>
       <c r="O54" t="n">
-        <v>32.02</v>
+        <v>31.97</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5060,64 +5063,60 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="C55" t="n">
-        <v>31.94</v>
+        <v>31.86</v>
       </c>
       <c r="D55" t="n">
-        <v>31.61</v>
+        <v>31.6</v>
       </c>
       <c r="E55" t="n">
-        <v>31.76</v>
+        <v>31.71</v>
       </c>
       <c r="F55" t="n">
-        <v>0.14</v>
+        <v>-0.05</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0016</v>
       </c>
       <c r="H55" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="I55" t="n">
-        <v>31.14</v>
+        <v>31.29</v>
       </c>
       <c r="J55" t="n">
-        <v>31.39</v>
+        <v>31.44</v>
       </c>
       <c r="K55" t="n">
-        <v>31.49</v>
+        <v>31.6</v>
       </c>
       <c r="L55" t="n">
-        <v>31.59</v>
+        <v>31.77</v>
       </c>
       <c r="M55" t="n">
-        <v>31.77</v>
+        <v>31.93</v>
       </c>
       <c r="N55" t="n">
-        <v>31.94</v>
+        <v>32.08</v>
       </c>
       <c r="O55" t="n">
-        <v>31.97</v>
+        <v>32.26</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5125,18 +5124,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5144,60 +5143,64 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="C56" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="D56" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E56" t="n">
         <v>31.81</v>
       </c>
-      <c r="C56" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="D56" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E56" t="n">
-        <v>31.71</v>
-      </c>
       <c r="F56" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0029</v>
       </c>
       <c r="H56" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I56" t="n">
-        <v>31.29</v>
+        <v>31.33</v>
       </c>
       <c r="J56" t="n">
         <v>31.44</v>
       </c>
       <c r="K56" t="n">
-        <v>31.6</v>
+        <v>31.58</v>
       </c>
       <c r="L56" t="n">
-        <v>31.77</v>
+        <v>31.72</v>
       </c>
       <c r="M56" t="n">
-        <v>31.93</v>
+        <v>31.85</v>
       </c>
       <c r="N56" t="n">
-        <v>32.08</v>
+        <v>31.97</v>
       </c>
       <c r="O56" t="n">
-        <v>32.26</v>
+        <v>32.13</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5205,83 +5208,81 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.78</v>
+        <v>31.83</v>
       </c>
       <c r="C57" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="D57" t="n">
-        <v>31.73</v>
+        <v>31.7</v>
       </c>
       <c r="E57" t="n">
-        <v>31.81</v>
+        <v>31.95</v>
       </c>
       <c r="F57" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0044</v>
       </c>
       <c r="H57" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="I57" t="n">
-        <v>31.33</v>
+        <v>31.38</v>
       </c>
       <c r="J57" t="n">
-        <v>31.44</v>
+        <v>31.42</v>
       </c>
       <c r="K57" t="n">
-        <v>31.58</v>
+        <v>31.63</v>
       </c>
       <c r="L57" t="n">
-        <v>31.72</v>
+        <v>31.85</v>
       </c>
       <c r="M57" t="n">
-        <v>31.85</v>
+        <v>31.98</v>
       </c>
       <c r="N57" t="n">
-        <v>31.97</v>
+        <v>32.1</v>
       </c>
       <c r="O57" t="n">
-        <v>32.13</v>
+        <v>32.42</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5302,71 +5303,75 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.83</v>
+        <v>31.92</v>
       </c>
       <c r="C58" t="n">
-        <v>32.01</v>
+        <v>31.94</v>
       </c>
       <c r="D58" t="n">
-        <v>31.7</v>
+        <v>31.85</v>
       </c>
       <c r="E58" t="n">
-        <v>31.92</v>
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>0.11</v>
+        <v/>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0034</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
       <c r="I58" t="n">
-        <v>31.38</v>
+        <v>31.4</v>
       </c>
       <c r="J58" t="n">
-        <v>31.42</v>
+        <v>31.69</v>
       </c>
       <c r="K58" t="n">
-        <v>31.63</v>
+        <v>31.8</v>
       </c>
       <c r="L58" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="M58" t="n">
-        <v>31.98</v>
+        <v>32.1</v>
       </c>
       <c r="N58" t="n">
-        <v>32.1</v>
+        <v>32.29</v>
       </c>
       <c r="O58" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+        <v>32.31</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5374,15 +5379,13 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5390,14 +5393,14 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -5330,7 +5330,7 @@
         <v>31.92</v>
       </c>
       <c r="C58" t="n">
-        <v>31.94</v>
+        <v>31.95</v>
       </c>
       <c r="D58" t="n">
         <v>31.85</v>
@@ -5345,7 +5345,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I58" t="n">
         <v>31.4</v>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -662,35 +662,39 @@
         <v>0.39</v>
       </c>
       <c r="I2" t="n">
-        <v>29.86</v>
+        <v>29.96</v>
       </c>
       <c r="J2" t="n">
-        <v>29.93</v>
+        <v>30.07</v>
       </c>
       <c r="K2" t="n">
-        <v>30.12</v>
+        <v>30.18</v>
       </c>
       <c r="L2" t="n">
-        <v>30.31</v>
+        <v>30.29</v>
       </c>
       <c r="M2" t="n">
-        <v>30.45</v>
+        <v>30.39</v>
       </c>
       <c r="N2" t="n">
-        <v>30.58</v>
+        <v>30.5</v>
       </c>
       <c r="O2" t="n">
-        <v>30.83</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>30.62</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -5327,13 +5331,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.92</v>
+        <v>31.93</v>
       </c>
       <c r="C58" t="n">
-        <v>31.95</v>
+        <v>32.12</v>
       </c>
       <c r="D58" t="n">
-        <v>31.85</v>
+        <v>31.89</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5345,7 +5349,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="I58" t="n">
         <v>31.4</v>
@@ -5384,8 +5388,10 @@
           <t>=</t>
         </is>
       </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5398,11 +5404,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5331,25 +5328,25 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="C58" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="E58" t="n">
         <v>31.93</v>
       </c>
-      <c r="C58" t="n">
-        <v>32.12</v>
-      </c>
-      <c r="D58" t="n">
-        <v>31.89</v>
-      </c>
-      <c r="E58" t="n">
-        <v/>
-      </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-0.02</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="I58" t="n">
         <v>31.4</v>
@@ -5372,10 +5369,8 @@
       <c r="O58" t="n">
         <v>32.31</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5383,9 +5378,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5404,7 +5399,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.39</v>
       </c>
       <c r="I2" t="n">
-        <v>29.96</v>
+        <v>30.01</v>
       </c>
       <c r="J2" t="n">
-        <v>30.07</v>
+        <v>30.1</v>
       </c>
       <c r="K2" t="n">
-        <v>30.18</v>
+        <v>30.19</v>
       </c>
       <c r="L2" t="n">
         <v>30.29</v>
       </c>
       <c r="M2" t="n">
-        <v>30.39</v>
+        <v>30.38</v>
       </c>
       <c r="N2" t="n">
-        <v>30.5</v>
+        <v>30.47</v>
       </c>
       <c r="O2" t="n">
-        <v>30.62</v>
+        <v>30.57</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5331,22 +5331,22 @@
         <v>31.92</v>
       </c>
       <c r="C58" t="n">
-        <v>32.2</v>
+        <v>32.23</v>
       </c>
       <c r="D58" t="n">
         <v>31.83</v>
       </c>
       <c r="E58" t="n">
-        <v>31.93</v>
+        <v>32.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.02</v>
+        <v>0.16</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="H58" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="I58" t="n">
         <v>31.4</v>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5399,11 +5399,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,25 +659,25 @@
         <v>0.39</v>
       </c>
       <c r="I2" t="n">
-        <v>30.01</v>
+        <v>30.03</v>
       </c>
       <c r="J2" t="n">
-        <v>30.1</v>
+        <v>30.12</v>
       </c>
       <c r="K2" t="n">
-        <v>30.19</v>
+        <v>30.2</v>
       </c>
       <c r="L2" t="n">
-        <v>30.29</v>
+        <v>30.28</v>
       </c>
       <c r="M2" t="n">
-        <v>30.38</v>
+        <v>30.37</v>
       </c>
       <c r="N2" t="n">
-        <v>30.47</v>
+        <v>30.45</v>
       </c>
       <c r="O2" t="n">
-        <v>30.57</v>
+        <v>30.53</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -710,14 +710,10 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -796,10 +792,14 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1044,7 +1044,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1128,7 +1128,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1210,7 +1210,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1294,7 +1294,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1380,7 +1380,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1466,7 +1466,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1548,7 +1548,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1626,7 +1626,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1710,7 +1710,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1798,7 +1798,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1878,7 +1878,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1962,7 +1962,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2050,7 +2050,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2128,7 +2128,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2210,7 +2210,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2298,7 +2298,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2380,7 +2380,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2472,7 +2472,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2554,7 +2554,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2638,7 +2638,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2726,7 +2726,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2806,7 +2806,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2886,7 +2886,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2970,7 +2970,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3056,7 +3056,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3140,7 +3140,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3224,7 +3224,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3308,7 +3308,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3392,7 +3392,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3472,7 +3472,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3558,7 +3558,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3644,7 +3644,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3726,7 +3726,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3812,7 +3812,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3896,7 +3896,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3978,7 +3978,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4064,7 +4064,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4142,7 +4142,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4226,7 +4226,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4308,7 +4308,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4386,7 +4386,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4472,7 +4472,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4556,7 +4556,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4640,7 +4640,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4724,7 +4724,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4810,7 +4810,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4894,7 +4894,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4980,7 +4980,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5064,7 +5064,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5144,7 +5144,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5230,7 +5230,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5310,7 +5310,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5331,22 +5331,22 @@
         <v>31.92</v>
       </c>
       <c r="C58" t="n">
-        <v>32.23</v>
+        <v>32.45</v>
       </c>
       <c r="D58" t="n">
         <v>31.83</v>
       </c>
       <c r="E58" t="n">
-        <v>32.1</v>
+        <v>32.19</v>
       </c>
       <c r="F58" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0076</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="I58" t="n">
         <v>31.4</v>
@@ -5388,13 +5388,17 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,34 +659,34 @@
         <v>0.39</v>
       </c>
       <c r="I2" t="n">
-        <v>30.03</v>
+        <v>30.28</v>
       </c>
       <c r="J2" t="n">
-        <v>30.12</v>
+        <v>30.28</v>
       </c>
       <c r="K2" t="n">
-        <v>30.2</v>
+        <v>30.28</v>
       </c>
       <c r="L2" t="n">
         <v>30.28</v>
       </c>
       <c r="M2" t="n">
-        <v>30.37</v>
+        <v>30.28</v>
       </c>
       <c r="N2" t="n">
-        <v>30.45</v>
+        <v>30.28</v>
       </c>
       <c r="O2" t="n">
-        <v>30.53</v>
+        <v>30.28</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -699,21 +699,31 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5331,22 +5341,22 @@
         <v>31.92</v>
       </c>
       <c r="C58" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="D58" t="n">
         <v>31.83</v>
       </c>
       <c r="E58" t="n">
-        <v>32.19</v>
+        <v>32.43</v>
       </c>
       <c r="F58" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0151</v>
       </c>
       <c r="H58" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="I58" t="n">
         <v>31.4</v>
@@ -5385,17 +5395,17 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W58" s="11" t="inlineStr">

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -5347,16 +5347,16 @@
         <v>31.83</v>
       </c>
       <c r="E58" t="n">
-        <v>32.43</v>
+        <v>32.44</v>
       </c>
       <c r="F58" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0154</v>
       </c>
       <c r="H58" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="I58" t="n">
         <v>31.4</v>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,17 +104,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,144 +637,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.28</v>
+        <v>30.22</v>
       </c>
       <c r="C2" t="n">
-        <v>30.33</v>
+        <v>30.59</v>
       </c>
       <c r="D2" t="n">
-        <v>29.94</v>
+        <v>30.15</v>
       </c>
       <c r="E2" t="n">
-        <v>30.11</v>
+        <v>30.44</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.17</v>
+        <v>0.33</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0111</v>
       </c>
       <c r="H2" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="I2" t="n">
-        <v>30.28</v>
+        <v>29.56</v>
       </c>
       <c r="J2" t="n">
-        <v>30.28</v>
+        <v>29.71</v>
       </c>
       <c r="K2" t="n">
-        <v>30.28</v>
+        <v>29.92</v>
       </c>
       <c r="L2" t="n">
-        <v>30.28</v>
+        <v>30.12</v>
       </c>
       <c r="M2" t="n">
-        <v>30.28</v>
+        <v>30.3</v>
       </c>
       <c r="N2" t="n">
-        <v>30.28</v>
+        <v>30.48</v>
       </c>
       <c r="O2" t="n">
-        <v>30.28</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>30.71</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="C3" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="K3" t="n">
         <v>30.22</v>
       </c>
-      <c r="C3" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="D3" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="E3" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I3" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="J3" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="K3" t="n">
-        <v>29.92</v>
-      </c>
       <c r="L3" t="n">
-        <v>30.12</v>
+        <v>30.41</v>
       </c>
       <c r="M3" t="n">
-        <v>30.3</v>
+        <v>30.66</v>
       </c>
       <c r="N3" t="n">
-        <v>30.48</v>
+        <v>30.92</v>
       </c>
       <c r="O3" t="n">
-        <v>30.71</v>
+        <v>31.03</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -782,82 +773,78 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.44</v>
+        <v>30.42</v>
       </c>
       <c r="C4" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I4" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="K4" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="L4" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="M4" t="n">
         <v>30.53</v>
       </c>
-      <c r="D4" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="E4" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="J4" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="K4" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="L4" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="M4" t="n">
-        <v>30.66</v>
-      </c>
       <c r="N4" t="n">
-        <v>30.92</v>
+        <v>30.63</v>
       </c>
       <c r="O4" t="n">
-        <v>31.03</v>
+        <v>30.73</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -865,26 +852,34 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -896,50 +891,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.42</v>
+        <v>30.67</v>
       </c>
       <c r="C5" t="n">
-        <v>30.71</v>
+        <v>30.8</v>
       </c>
       <c r="D5" t="n">
-        <v>30.24</v>
+        <v>30.48</v>
       </c>
       <c r="E5" t="n">
-        <v>30.71</v>
+        <v>30.62</v>
       </c>
       <c r="F5" t="n">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.0027</v>
       </c>
       <c r="H5" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="I5" t="n">
-        <v>30.14</v>
+        <v>29.78</v>
       </c>
       <c r="J5" t="n">
-        <v>30.24</v>
+        <v>30.36</v>
       </c>
       <c r="K5" t="n">
-        <v>30.34</v>
+        <v>30.47</v>
       </c>
       <c r="L5" t="n">
-        <v>30.43</v>
+        <v>30.59</v>
       </c>
       <c r="M5" t="n">
-        <v>30.53</v>
+        <v>30.94</v>
       </c>
       <c r="N5" t="n">
-        <v>30.63</v>
+        <v>31.28</v>
       </c>
       <c r="O5" t="n">
-        <v>30.73</v>
+        <v>31.17</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -947,32 +942,24 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -986,50 +973,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>30.85</v>
       </c>
       <c r="D6" t="n">
-        <v>30.48</v>
+        <v>30.53</v>
       </c>
       <c r="E6" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.08</v>
+        <v>0.21</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0069</v>
       </c>
       <c r="H6" t="n">
         <v>0.32</v>
       </c>
       <c r="I6" t="n">
-        <v>29.78</v>
+        <v>30.16</v>
       </c>
       <c r="J6" t="n">
-        <v>30.36</v>
+        <v>30.29</v>
       </c>
       <c r="K6" t="n">
-        <v>30.47</v>
+        <v>30.46</v>
       </c>
       <c r="L6" t="n">
-        <v>30.59</v>
+        <v>30.63</v>
       </c>
       <c r="M6" t="n">
-        <v>30.94</v>
+        <v>30.78</v>
       </c>
       <c r="N6" t="n">
-        <v>31.28</v>
+        <v>30.93</v>
       </c>
       <c r="O6" t="n">
-        <v>31.17</v>
+        <v>31.12</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1040,13 +1027,15 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1054,83 +1043,81 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W6" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="C7" t="n">
-        <v>30.85</v>
+        <v>30.83</v>
       </c>
       <c r="D7" t="n">
-        <v>30.53</v>
+        <v>30.52</v>
       </c>
       <c r="E7" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="F7" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0017</v>
       </c>
       <c r="H7" t="n">
         <v>0.32</v>
       </c>
       <c r="I7" t="n">
-        <v>30.16</v>
+        <v>30.2</v>
       </c>
       <c r="J7" t="n">
-        <v>30.29</v>
+        <v>30.58</v>
       </c>
       <c r="K7" t="n">
-        <v>30.46</v>
+        <v>30.67</v>
       </c>
       <c r="L7" t="n">
-        <v>30.63</v>
+        <v>30.76</v>
       </c>
       <c r="M7" t="n">
-        <v>30.78</v>
+        <v>31</v>
       </c>
       <c r="N7" t="n">
-        <v>30.93</v>
+        <v>31.23</v>
       </c>
       <c r="O7" t="n">
-        <v>31.12</v>
+        <v>31.18</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1138,81 +1125,83 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="C8" t="n">
-        <v>30.83</v>
+        <v>31.01</v>
       </c>
       <c r="D8" t="n">
-        <v>30.52</v>
+        <v>30.76</v>
       </c>
       <c r="E8" t="n">
-        <v>30.78</v>
+        <v>30.97</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.05</v>
+        <v>0.19</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.006</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="I8" t="n">
         <v>30.2</v>
       </c>
       <c r="J8" t="n">
-        <v>30.58</v>
+        <v>30.52</v>
       </c>
       <c r="K8" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="L8" t="n">
-        <v>30.76</v>
+        <v>30.73</v>
       </c>
       <c r="M8" t="n">
-        <v>31</v>
+        <v>30.94</v>
       </c>
       <c r="N8" t="n">
-        <v>31.23</v>
+        <v>31.15</v>
       </c>
       <c r="O8" t="n">
-        <v>31.18</v>
+        <v>31.15</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1220,82 +1209,84 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.78</v>
+        <v>30.96</v>
       </c>
       <c r="C9" t="n">
-        <v>31.01</v>
+        <v>31.18</v>
       </c>
       <c r="D9" t="n">
-        <v>30.76</v>
+        <v>30.36</v>
       </c>
       <c r="E9" t="n">
-        <v>30.97</v>
+        <v>30.55</v>
       </c>
       <c r="F9" t="n">
-        <v>0.19</v>
+        <v>-0.41</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.0133</v>
       </c>
       <c r="H9" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="I9" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="J9" t="n">
-        <v>30.52</v>
+        <v>30.75</v>
       </c>
       <c r="K9" t="n">
-        <v>30.62</v>
+        <v>30.84</v>
       </c>
       <c r="L9" t="n">
-        <v>30.73</v>
+        <v>30.93</v>
       </c>
       <c r="M9" t="n">
-        <v>30.94</v>
+        <v>31.09</v>
       </c>
       <c r="N9" t="n">
-        <v>31.15</v>
+        <v>31.26</v>
       </c>
       <c r="O9" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>31.26</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U9" s="8" t="n">
@@ -1306,177 +1297,173 @@
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.96</v>
+        <v>30.62</v>
       </c>
       <c r="C10" t="n">
-        <v>31.18</v>
+        <v>31.44</v>
       </c>
       <c r="D10" t="n">
-        <v>30.36</v>
+        <v>30.62</v>
       </c>
       <c r="E10" t="n">
-        <v>30.55</v>
+        <v>31.34</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.41</v>
+        <v>0.78</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0257</v>
       </c>
       <c r="H10" t="n">
         <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>30.5</v>
+        <v>29.54</v>
       </c>
       <c r="J10" t="n">
-        <v>30.75</v>
+        <v>29.63</v>
       </c>
       <c r="K10" t="n">
-        <v>30.84</v>
+        <v>30.15</v>
       </c>
       <c r="L10" t="n">
-        <v>30.93</v>
+        <v>30.66</v>
       </c>
       <c r="M10" t="n">
-        <v>31.09</v>
+        <v>30.96</v>
       </c>
       <c r="N10" t="n">
-        <v>31.26</v>
+        <v>31.27</v>
       </c>
       <c r="O10" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30.62</v>
+        <v>31.34</v>
       </c>
       <c r="C11" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="D11" t="n">
-        <v>30.62</v>
+        <v>30.65</v>
       </c>
       <c r="E11" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="F11" t="n">
-        <v>0.78</v>
+        <v>0.04</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0012</v>
       </c>
       <c r="H11" t="n">
         <v>0.82</v>
       </c>
       <c r="I11" t="n">
-        <v>29.54</v>
+        <v>29.81</v>
       </c>
       <c r="J11" t="n">
-        <v>29.63</v>
+        <v>30.67</v>
       </c>
       <c r="K11" t="n">
-        <v>30.15</v>
+        <v>30.93</v>
       </c>
       <c r="L11" t="n">
-        <v>30.66</v>
+        <v>31.19</v>
       </c>
       <c r="M11" t="n">
-        <v>30.96</v>
+        <v>31.75</v>
       </c>
       <c r="N11" t="n">
-        <v>31.27</v>
+        <v>32.31</v>
       </c>
       <c r="O11" t="n">
-        <v>32</v>
+        <v>32.26</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1486,65 +1473,61 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="C12" t="n">
-        <v>31.47</v>
+        <v>31.46</v>
       </c>
       <c r="D12" t="n">
-        <v>30.65</v>
+        <v>31.17</v>
       </c>
       <c r="E12" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0033</v>
       </c>
       <c r="H12" t="n">
-        <v>0.82</v>
+        <v>0.29</v>
       </c>
       <c r="I12" t="n">
-        <v>29.81</v>
+        <v>29.83</v>
       </c>
       <c r="J12" t="n">
-        <v>30.67</v>
+        <v>30.71</v>
       </c>
       <c r="K12" t="n">
-        <v>30.93</v>
+        <v>30.97</v>
       </c>
       <c r="L12" t="n">
-        <v>31.19</v>
+        <v>31.22</v>
       </c>
       <c r="M12" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="N12" t="n">
-        <v>32.31</v>
+        <v>32.36</v>
       </c>
       <c r="O12" t="n">
-        <v>32.26</v>
+        <v>32.3</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1558,60 +1541,64 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="C13" t="n">
-        <v>31.46</v>
+        <v>31.32</v>
       </c>
       <c r="D13" t="n">
-        <v>31.17</v>
+        <v>31.08</v>
       </c>
       <c r="E13" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0015</v>
       </c>
       <c r="H13" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I13" t="n">
-        <v>29.83</v>
+        <v>30.88</v>
       </c>
       <c r="J13" t="n">
-        <v>30.71</v>
+        <v>30.96</v>
       </c>
       <c r="K13" t="n">
-        <v>30.97</v>
+        <v>31.13</v>
       </c>
       <c r="L13" t="n">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="M13" t="n">
-        <v>31.79</v>
+        <v>31.42</v>
       </c>
       <c r="N13" t="n">
-        <v>32.36</v>
+        <v>31.54</v>
       </c>
       <c r="O13" t="n">
-        <v>32.3</v>
+        <v>31.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1619,10 +1606,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1636,7 +1625,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1650,50 +1639,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="C14" t="n">
-        <v>31.32</v>
+        <v>31.63</v>
       </c>
       <c r="D14" t="n">
-        <v>31.08</v>
+        <v>31.24</v>
       </c>
       <c r="E14" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0059</v>
       </c>
       <c r="H14" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="I14" t="n">
-        <v>30.88</v>
+        <v>30.83</v>
       </c>
       <c r="J14" t="n">
-        <v>30.96</v>
+        <v>31.14</v>
       </c>
       <c r="K14" t="n">
-        <v>31.13</v>
+        <v>31.2</v>
       </c>
       <c r="L14" t="n">
-        <v>31.3</v>
+        <v>31.26</v>
       </c>
       <c r="M14" t="n">
-        <v>31.42</v>
+        <v>31.44</v>
       </c>
       <c r="N14" t="n">
-        <v>31.54</v>
+        <v>31.62</v>
       </c>
       <c r="O14" t="n">
-        <v>31.75</v>
+        <v>31.56</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1701,83 +1690,83 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="C15" t="n">
-        <v>31.63</v>
+        <v>31.57</v>
       </c>
       <c r="D15" t="n">
-        <v>31.24</v>
+        <v>31.37</v>
       </c>
       <c r="E15" t="n">
-        <v>31.5</v>
+        <v>31.38</v>
       </c>
       <c r="F15" t="n">
-        <v>0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0039</v>
       </c>
       <c r="H15" t="n">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>30.83</v>
+        <v>30.86</v>
       </c>
       <c r="J15" t="n">
-        <v>31.14</v>
+        <v>31.15</v>
       </c>
       <c r="K15" t="n">
-        <v>31.2</v>
+        <v>31.31</v>
       </c>
       <c r="L15" t="n">
-        <v>31.26</v>
+        <v>31.47</v>
       </c>
       <c r="M15" t="n">
-        <v>31.44</v>
+        <v>31.7</v>
       </c>
       <c r="N15" t="n">
-        <v>31.62</v>
+        <v>31.92</v>
       </c>
       <c r="O15" t="n">
-        <v>31.56</v>
+        <v>32.01</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1785,83 +1774,83 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr"/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31.5</v>
+        <v>31.39</v>
       </c>
       <c r="C16" t="n">
-        <v>31.57</v>
+        <v>31.46</v>
       </c>
       <c r="D16" t="n">
-        <v>31.37</v>
+        <v>31.25</v>
       </c>
       <c r="E16" t="n">
-        <v>31.38</v>
+        <v>31.36</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0007</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I16" t="n">
-        <v>30.86</v>
+        <v>31.16</v>
       </c>
       <c r="J16" t="n">
-        <v>31.15</v>
+        <v>31.13</v>
       </c>
       <c r="K16" t="n">
-        <v>31.31</v>
+        <v>31.28</v>
       </c>
       <c r="L16" t="n">
-        <v>31.47</v>
+        <v>31.42</v>
       </c>
       <c r="M16" t="n">
-        <v>31.7</v>
+        <v>31.48</v>
       </c>
       <c r="N16" t="n">
-        <v>31.92</v>
+        <v>31.54</v>
       </c>
       <c r="O16" t="n">
-        <v>32.01</v>
+        <v>31.78</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1871,12 +1860,12 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1888,64 +1877,64 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.39</v>
+        <v>31.38</v>
       </c>
       <c r="C17" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="D17" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I17" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="J17" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="M17" t="n">
         <v>31.46</v>
       </c>
-      <c r="D17" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="E17" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>-0.0007</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I17" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="J17" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="K17" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="L17" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="M17" t="n">
-        <v>31.48</v>
-      </c>
       <c r="N17" t="n">
-        <v>31.54</v>
+        <v>31.57</v>
       </c>
       <c r="O17" t="n">
-        <v>31.78</v>
+        <v>31.68</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1953,83 +1942,83 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.38</v>
+        <v>31.6</v>
       </c>
       <c r="C18" t="n">
-        <v>31.68</v>
+        <v>31.74</v>
       </c>
       <c r="D18" t="n">
-        <v>31.35</v>
+        <v>31.51</v>
       </c>
       <c r="E18" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="F18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.23</v>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.33</v>
-      </c>
       <c r="I18" t="n">
-        <v>31.04</v>
+        <v>31.02</v>
       </c>
       <c r="J18" t="n">
-        <v>31.15</v>
+        <v>31.31</v>
       </c>
       <c r="K18" t="n">
-        <v>31.25</v>
+        <v>31.43</v>
       </c>
       <c r="L18" t="n">
-        <v>31.36</v>
+        <v>31.55</v>
       </c>
       <c r="M18" t="n">
-        <v>31.46</v>
+        <v>31.76</v>
       </c>
       <c r="N18" t="n">
-        <v>31.57</v>
+        <v>31.96</v>
       </c>
       <c r="O18" t="n">
-        <v>31.68</v>
+        <v>32</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2040,27 +2029,21 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2070,63 +2053,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31.6</v>
+        <v>31.61</v>
       </c>
       <c r="C19" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="D19" t="n">
-        <v>31.51</v>
+        <v>31.37</v>
       </c>
       <c r="E19" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0005</v>
+        <v>-0.0075</v>
       </c>
       <c r="H19" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="I19" t="n">
-        <v>31.02</v>
+        <v>31.27</v>
       </c>
       <c r="J19" t="n">
-        <v>31.31</v>
+        <v>31.37</v>
       </c>
       <c r="K19" t="n">
-        <v>31.43</v>
+        <v>31.49</v>
       </c>
       <c r="L19" t="n">
-        <v>31.55</v>
+        <v>31.62</v>
       </c>
       <c r="M19" t="n">
-        <v>31.76</v>
+        <v>31.73</v>
       </c>
       <c r="N19" t="n">
-        <v>31.96</v>
+        <v>31.83</v>
       </c>
       <c r="O19" t="n">
-        <v>32</v>
+        <v>31.98</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2138,146 +2125,152 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="C20" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="D20" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="E20" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I20" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="J20" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="K20" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="L20" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M20" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N20" t="n">
         <v>31.61</v>
       </c>
-      <c r="C20" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="D20" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="E20" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I20" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="J20" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="K20" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="L20" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="M20" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="N20" t="n">
-        <v>31.83</v>
-      </c>
       <c r="O20" t="n">
-        <v>31.98</v>
+        <v>32</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31.38</v>
+        <v>31.61</v>
       </c>
       <c r="C21" t="n">
-        <v>31.58</v>
+        <v>31.71</v>
       </c>
       <c r="D21" t="n">
-        <v>31.12</v>
+        <v>31.49</v>
       </c>
       <c r="E21" t="n">
         <v>31.58</v>
       </c>
       <c r="F21" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0003</v>
       </c>
       <c r="H21" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="I21" t="n">
-        <v>31.06</v>
+        <v>30.65</v>
       </c>
       <c r="J21" t="n">
-        <v>30.98</v>
+        <v>31.23</v>
       </c>
       <c r="K21" t="n">
-        <v>31.21</v>
+        <v>31.35</v>
       </c>
       <c r="L21" t="n">
-        <v>31.45</v>
+        <v>31.47</v>
       </c>
       <c r="M21" t="n">
-        <v>31.53</v>
+        <v>31.82</v>
       </c>
       <c r="N21" t="n">
-        <v>31.61</v>
+        <v>32.16</v>
       </c>
       <c r="O21" t="n">
-        <v>32</v>
+        <v>32.05</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2285,204 +2278,198 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>31.61</v>
       </c>
       <c r="C22" t="n">
-        <v>31.71</v>
+        <v>32.77</v>
       </c>
       <c r="D22" t="n">
-        <v>31.49</v>
+        <v>31.32</v>
       </c>
       <c r="E22" t="n">
-        <v>31.58</v>
+        <v>31.37</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0065</v>
       </c>
       <c r="H22" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="I22" t="n">
-        <v>30.65</v>
+        <v>31.27</v>
       </c>
       <c r="J22" t="n">
-        <v>31.23</v>
+        <v>31.34</v>
       </c>
       <c r="K22" t="n">
-        <v>31.35</v>
+        <v>31.46</v>
       </c>
       <c r="L22" t="n">
-        <v>31.47</v>
+        <v>31.59</v>
       </c>
       <c r="M22" t="n">
-        <v>31.82</v>
+        <v>31.69</v>
       </c>
       <c r="N22" t="n">
-        <v>32.16</v>
+        <v>31.79</v>
       </c>
       <c r="O22" t="n">
-        <v>32.05</v>
+        <v>31.94</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="C23" t="n">
-        <v>32.77</v>
+        <v>31.65</v>
       </c>
       <c r="D23" t="n">
-        <v>31.32</v>
+        <v>31.26</v>
       </c>
       <c r="E23" t="n">
-        <v>31.37</v>
+        <v>31.51</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.21</v>
+        <v>0.14</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0045</v>
       </c>
       <c r="H23" t="n">
-        <v>1.45</v>
+        <v>0.39</v>
       </c>
       <c r="I23" t="n">
-        <v>31.27</v>
+        <v>29.88</v>
       </c>
       <c r="J23" t="n">
-        <v>31.34</v>
+        <v>29.58</v>
       </c>
       <c r="K23" t="n">
-        <v>31.46</v>
+        <v>30.65</v>
       </c>
       <c r="L23" t="n">
-        <v>31.59</v>
+        <v>31.71</v>
       </c>
       <c r="M23" t="n">
-        <v>31.69</v>
+        <v>32.09</v>
       </c>
       <c r="N23" t="n">
-        <v>31.79</v>
+        <v>32.48</v>
       </c>
       <c r="O23" t="n">
-        <v>31.94</v>
+        <v>34.22</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2496,50 +2483,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>31.37</v>
+        <v>31.47</v>
       </c>
       <c r="C24" t="n">
-        <v>31.65</v>
+        <v>31.5</v>
       </c>
       <c r="D24" t="n">
-        <v>31.26</v>
+        <v>31.18</v>
       </c>
       <c r="E24" t="n">
-        <v>31.51</v>
+        <v>31.38</v>
       </c>
       <c r="F24" t="n">
-        <v>0.14</v>
+        <v>-0.14</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0043</v>
       </c>
       <c r="H24" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="I24" t="n">
-        <v>29.88</v>
+        <v>30.87</v>
       </c>
       <c r="J24" t="n">
-        <v>29.58</v>
+        <v>31.14</v>
       </c>
       <c r="K24" t="n">
-        <v>30.65</v>
+        <v>31.31</v>
       </c>
       <c r="L24" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="M24" t="n">
         <v>31.71</v>
       </c>
-      <c r="M24" t="n">
-        <v>32.09</v>
-      </c>
       <c r="N24" t="n">
-        <v>32.48</v>
+        <v>31.93</v>
       </c>
       <c r="O24" t="n">
-        <v>34.22</v>
+        <v>32.05</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2547,12 +2534,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2564,64 +2553,64 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C25" t="n">
-        <v>31.5</v>
+        <v>31.96</v>
       </c>
       <c r="D25" t="n">
-        <v>31.18</v>
+        <v>31.39</v>
       </c>
       <c r="E25" t="n">
-        <v>31.38</v>
+        <v>31.8</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0136</v>
       </c>
       <c r="H25" t="n">
-        <v>0.32</v>
+        <v>0.57</v>
       </c>
       <c r="I25" t="n">
-        <v>30.87</v>
+        <v>30.86</v>
       </c>
       <c r="J25" t="n">
-        <v>31.14</v>
+        <v>31.08</v>
       </c>
       <c r="K25" t="n">
-        <v>31.31</v>
+        <v>31.22</v>
       </c>
       <c r="L25" t="n">
-        <v>31.48</v>
+        <v>31.36</v>
       </c>
       <c r="M25" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N25" t="n">
         <v>31.71</v>
       </c>
-      <c r="N25" t="n">
-        <v>31.93</v>
-      </c>
       <c r="O25" t="n">
-        <v>32.05</v>
+        <v>31.81</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2629,83 +2618,83 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.44</v>
+        <v>32.03</v>
       </c>
       <c r="C26" t="n">
-        <v>31.96</v>
+        <v>32.16</v>
       </c>
       <c r="D26" t="n">
-        <v>31.39</v>
+        <v>31.53</v>
       </c>
       <c r="E26" t="n">
-        <v>31.8</v>
+        <v>32.16</v>
       </c>
       <c r="F26" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0113</v>
       </c>
       <c r="H26" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="I26" t="n">
-        <v>30.86</v>
+        <v>30.82</v>
       </c>
       <c r="J26" t="n">
-        <v>31.08</v>
+        <v>31.29</v>
       </c>
       <c r="K26" t="n">
-        <v>31.22</v>
+        <v>31.52</v>
       </c>
       <c r="L26" t="n">
-        <v>31.36</v>
+        <v>31.74</v>
       </c>
       <c r="M26" t="n">
-        <v>31.53</v>
+        <v>32.09</v>
       </c>
       <c r="N26" t="n">
-        <v>31.71</v>
+        <v>32.44</v>
       </c>
       <c r="O26" t="n">
-        <v>31.81</v>
+        <v>32.54</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2716,27 +2705,23 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2746,50 +2731,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="C27" t="n">
-        <v>32.16</v>
+        <v>32.12</v>
       </c>
       <c r="D27" t="n">
-        <v>31.53</v>
+        <v>31.8</v>
       </c>
       <c r="E27" t="n">
-        <v>32.16</v>
+        <v>32.02</v>
       </c>
       <c r="F27" t="n">
-        <v>0.36</v>
+        <v>-0.14</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0044</v>
       </c>
       <c r="H27" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="I27" t="n">
-        <v>30.82</v>
+        <v>30.91</v>
       </c>
       <c r="J27" t="n">
-        <v>31.29</v>
+        <v>31.69</v>
       </c>
       <c r="K27" t="n">
-        <v>31.52</v>
+        <v>31.85</v>
       </c>
       <c r="L27" t="n">
-        <v>31.74</v>
+        <v>32.01</v>
       </c>
       <c r="M27" t="n">
-        <v>32.09</v>
+        <v>32.48</v>
       </c>
       <c r="N27" t="n">
-        <v>32.44</v>
+        <v>32.95</v>
       </c>
       <c r="O27" t="n">
-        <v>32.54</v>
+        <v>32.79</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2797,18 +2782,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2816,60 +2801,64 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.09</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
-        <v>32.12</v>
+        <v>32.14</v>
       </c>
       <c r="D28" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="E28" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0002</v>
       </c>
       <c r="H28" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I28" t="n">
-        <v>30.91</v>
+        <v>31.47</v>
       </c>
       <c r="J28" t="n">
-        <v>31.69</v>
+        <v>31.73</v>
       </c>
       <c r="K28" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="L28" t="n">
-        <v>32.01</v>
+        <v>31.99</v>
       </c>
       <c r="M28" t="n">
-        <v>32.48</v>
+        <v>32.18</v>
       </c>
       <c r="N28" t="n">
-        <v>32.95</v>
+        <v>32.38</v>
       </c>
       <c r="O28" t="n">
-        <v>32.79</v>
+        <v>32.44</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2882,7 +2871,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2896,64 +2885,64 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="C29" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="D29" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="E29" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I29" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="J29" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="L29" t="n">
         <v>32</v>
       </c>
-      <c r="C29" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="D29" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="E29" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I29" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="J29" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="K29" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="L29" t="n">
-        <v>31.99</v>
-      </c>
       <c r="M29" t="n">
-        <v>32.18</v>
+        <v>32.21</v>
       </c>
       <c r="N29" t="n">
-        <v>32.38</v>
+        <v>32.43</v>
       </c>
       <c r="O29" t="n">
-        <v>32.44</v>
+        <v>32.51</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2968,11 +2957,13 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2980,7 +2971,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2994,50 +2985,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
       <c r="C30" t="n">
-        <v>32.22</v>
+        <v>32.04</v>
       </c>
       <c r="D30" t="n">
-        <v>31.84</v>
+        <v>31.68</v>
       </c>
       <c r="E30" t="n">
-        <v>31.96</v>
+        <v>31.73</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0074</v>
       </c>
       <c r="H30" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I30" t="n">
-        <v>31.42</v>
+        <v>31.47</v>
       </c>
       <c r="J30" t="n">
-        <v>31.7</v>
+        <v>31.55</v>
       </c>
       <c r="K30" t="n">
-        <v>31.85</v>
+        <v>31.78</v>
       </c>
       <c r="L30" t="n">
         <v>32</v>
       </c>
       <c r="M30" t="n">
-        <v>32.21</v>
+        <v>32.15</v>
       </c>
       <c r="N30" t="n">
-        <v>32.43</v>
+        <v>32.3</v>
       </c>
       <c r="O30" t="n">
-        <v>32.51</v>
+        <v>32.59</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3047,18 +3038,16 @@
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3066,64 +3055,64 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.96</v>
+        <v>31.77</v>
       </c>
       <c r="C31" t="n">
-        <v>32.04</v>
+        <v>31.87</v>
       </c>
       <c r="D31" t="n">
-        <v>31.68</v>
+        <v>31.37</v>
       </c>
       <c r="E31" t="n">
-        <v>31.73</v>
+        <v>31.47</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0083</v>
       </c>
       <c r="H31" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="I31" t="n">
-        <v>31.47</v>
+        <v>31.32</v>
       </c>
       <c r="J31" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K31" t="n">
         <v>31.55</v>
       </c>
-      <c r="K31" t="n">
-        <v>31.78</v>
-      </c>
       <c r="L31" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="M31" t="n">
-        <v>32.15</v>
+        <v>31.91</v>
       </c>
       <c r="N31" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O31" t="n">
-        <v>32.59</v>
+        <v>32.41</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3136,7 +3125,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3150,7 +3139,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3164,50 +3153,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31.77</v>
+        <v>31.47</v>
       </c>
       <c r="C32" t="n">
-        <v>31.87</v>
+        <v>31.59</v>
       </c>
       <c r="D32" t="n">
-        <v>31.37</v>
+        <v>31.18</v>
       </c>
       <c r="E32" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0009</v>
       </c>
       <c r="H32" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="I32" t="n">
-        <v>31.32</v>
+        <v>30.88</v>
       </c>
       <c r="J32" t="n">
-        <v>31.3</v>
+        <v>30.89</v>
       </c>
       <c r="K32" t="n">
-        <v>31.55</v>
+        <v>31.22</v>
       </c>
       <c r="L32" t="n">
-        <v>31.8</v>
+        <v>31.54</v>
       </c>
       <c r="M32" t="n">
-        <v>31.91</v>
+        <v>31.71</v>
       </c>
       <c r="N32" t="n">
-        <v>32.02</v>
+        <v>31.88</v>
       </c>
       <c r="O32" t="n">
-        <v>32.41</v>
+        <v>32.36</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3217,12 +3206,12 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3234,7 +3223,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3248,50 +3237,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C33" t="n">
-        <v>31.59</v>
+        <v>31.75</v>
       </c>
       <c r="D33" t="n">
-        <v>31.18</v>
+        <v>31.38</v>
       </c>
       <c r="E33" t="n">
-        <v>31.44</v>
+        <v>31.55</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0037</v>
       </c>
       <c r="H33" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="I33" t="n">
-        <v>30.88</v>
+        <v>30.78</v>
       </c>
       <c r="J33" t="n">
-        <v>30.89</v>
+        <v>31.05</v>
       </c>
       <c r="K33" t="n">
-        <v>31.22</v>
+        <v>31.23</v>
       </c>
       <c r="L33" t="n">
-        <v>31.54</v>
+        <v>31.41</v>
       </c>
       <c r="M33" t="n">
-        <v>31.71</v>
+        <v>31.64</v>
       </c>
       <c r="N33" t="n">
-        <v>31.88</v>
+        <v>31.87</v>
       </c>
       <c r="O33" t="n">
-        <v>32.36</v>
+        <v>32</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3299,18 +3288,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3318,64 +3307,60 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.44</v>
+        <v>31.64</v>
       </c>
       <c r="C34" t="n">
-        <v>31.75</v>
+        <v>31.69</v>
       </c>
       <c r="D34" t="n">
-        <v>31.38</v>
+        <v>31.3</v>
       </c>
       <c r="E34" t="n">
-        <v>31.55</v>
+        <v>31.3</v>
       </c>
       <c r="F34" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="I34" t="n">
-        <v>30.78</v>
+        <v>31.02</v>
       </c>
       <c r="J34" t="n">
-        <v>31.05</v>
+        <v>31.18</v>
       </c>
       <c r="K34" t="n">
-        <v>31.23</v>
+        <v>31.37</v>
       </c>
       <c r="L34" t="n">
-        <v>31.41</v>
+        <v>31.56</v>
       </c>
       <c r="M34" t="n">
-        <v>31.64</v>
+        <v>31.74</v>
       </c>
       <c r="N34" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="O34" t="n">
-        <v>32</v>
+        <v>32.11</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3383,18 +3368,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3402,60 +3387,64 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.64</v>
+        <v>31.3</v>
       </c>
       <c r="C35" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="D35" t="n">
         <v>31.3</v>
       </c>
       <c r="E35" t="n">
-        <v>31.3</v>
+        <v>31.56</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.26</v>
+        <v>0.27</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="I35" t="n">
-        <v>31.02</v>
+        <v>30.9</v>
       </c>
       <c r="J35" t="n">
-        <v>31.18</v>
+        <v>30.8</v>
       </c>
       <c r="K35" t="n">
-        <v>31.37</v>
+        <v>31.1</v>
       </c>
       <c r="L35" t="n">
-        <v>31.56</v>
+        <v>31.39</v>
       </c>
       <c r="M35" t="n">
-        <v>31.74</v>
+        <v>31.49</v>
       </c>
       <c r="N35" t="n">
-        <v>31.91</v>
+        <v>31.59</v>
       </c>
       <c r="O35" t="n">
-        <v>32.11</v>
+        <v>32.09</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3463,83 +3452,85 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.3</v>
+        <v>31.59</v>
       </c>
       <c r="C36" t="n">
-        <v>31.62</v>
+        <v>31.78</v>
       </c>
       <c r="D36" t="n">
-        <v>31.3</v>
+        <v>31.36</v>
       </c>
       <c r="E36" t="n">
-        <v>31.56</v>
+        <v>31.36</v>
       </c>
       <c r="F36" t="n">
-        <v>0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0065</v>
       </c>
       <c r="H36" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="I36" t="n">
-        <v>30.9</v>
+        <v>30.98</v>
       </c>
       <c r="J36" t="n">
-        <v>30.8</v>
+        <v>31.29</v>
       </c>
       <c r="K36" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="L36" t="n">
-        <v>31.39</v>
+        <v>31.51</v>
       </c>
       <c r="M36" t="n">
-        <v>31.49</v>
+        <v>31.72</v>
       </c>
       <c r="N36" t="n">
-        <v>31.59</v>
+        <v>31.93</v>
       </c>
       <c r="O36" t="n">
-        <v>32.09</v>
+        <v>31.95</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3547,12 +3538,14 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3560,15 +3553,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3582,50 +3573,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.59</v>
+        <v>31.44</v>
       </c>
       <c r="C37" t="n">
-        <v>31.78</v>
+        <v>31.52</v>
       </c>
       <c r="D37" t="n">
-        <v>31.36</v>
+        <v>31.31</v>
       </c>
       <c r="E37" t="n">
-        <v>31.36</v>
+        <v>31.41</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0018</v>
       </c>
       <c r="H37" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="I37" t="n">
-        <v>30.98</v>
+        <v>30.94</v>
       </c>
       <c r="J37" t="n">
-        <v>31.29</v>
+        <v>30.83</v>
       </c>
       <c r="K37" t="n">
-        <v>31.4</v>
+        <v>31.15</v>
       </c>
       <c r="L37" t="n">
-        <v>31.51</v>
+        <v>31.46</v>
       </c>
       <c r="M37" t="n">
-        <v>31.72</v>
+        <v>31.57</v>
       </c>
       <c r="N37" t="n">
-        <v>31.93</v>
+        <v>31.67</v>
       </c>
       <c r="O37" t="n">
-        <v>31.95</v>
+        <v>32.2</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3633,20 +3624,16 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3654,64 +3641,64 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.44</v>
+        <v>31.41</v>
       </c>
       <c r="C38" t="n">
-        <v>31.52</v>
+        <v>31.6</v>
       </c>
       <c r="D38" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="E38" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I38" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J38" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="K38" t="n">
         <v>31.31</v>
       </c>
-      <c r="E38" t="n">
+      <c r="L38" t="n">
         <v>31.41</v>
       </c>
-      <c r="F38" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="J38" t="n">
-        <v>30.83</v>
-      </c>
-      <c r="K38" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="L38" t="n">
-        <v>31.46</v>
-      </c>
       <c r="M38" t="n">
-        <v>31.57</v>
+        <v>31.51</v>
       </c>
       <c r="N38" t="n">
-        <v>31.67</v>
+        <v>31.61</v>
       </c>
       <c r="O38" t="n">
-        <v>32.2</v>
+        <v>31.72</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3719,16 +3706,20 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3736,64 +3727,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.41</v>
+        <v>31.59</v>
       </c>
       <c r="C39" t="n">
-        <v>31.6</v>
+        <v>31.76</v>
       </c>
       <c r="D39" t="n">
-        <v>31.28</v>
+        <v>31.44</v>
       </c>
       <c r="E39" t="n">
         <v>31.56</v>
       </c>
       <c r="F39" t="n">
-        <v>0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0002</v>
       </c>
       <c r="H39" t="n">
         <v>0.33</v>
       </c>
       <c r="I39" t="n">
-        <v>31.11</v>
+        <v>30.95</v>
       </c>
       <c r="J39" t="n">
-        <v>31.21</v>
+        <v>31.3</v>
       </c>
       <c r="K39" t="n">
-        <v>31.31</v>
+        <v>31.4</v>
       </c>
       <c r="L39" t="n">
-        <v>31.41</v>
+        <v>31.5</v>
       </c>
       <c r="M39" t="n">
-        <v>31.51</v>
+        <v>31.73</v>
       </c>
       <c r="N39" t="n">
-        <v>31.61</v>
+        <v>31.95</v>
       </c>
       <c r="O39" t="n">
-        <v>31.72</v>
+        <v>31.93</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3801,28 +3792,26 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3836,50 +3825,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="C40" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="D40" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="E40" t="n">
-        <v>31.56</v>
+        <v>31.65</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0028</v>
       </c>
       <c r="H40" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="I40" t="n">
-        <v>30.95</v>
+        <v>31.11</v>
       </c>
       <c r="J40" t="n">
-        <v>31.3</v>
+        <v>31.21</v>
       </c>
       <c r="K40" t="n">
-        <v>31.4</v>
+        <v>31.39</v>
       </c>
       <c r="L40" t="n">
-        <v>31.5</v>
+        <v>31.58</v>
       </c>
       <c r="M40" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="N40" t="n">
-        <v>31.95</v>
+        <v>31.86</v>
       </c>
       <c r="O40" t="n">
-        <v>31.93</v>
+        <v>32.09</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3890,15 +3879,13 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3906,7 +3893,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3920,50 +3907,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="C41" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="D41" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E41" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I41" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="J41" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="K41" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="L41" t="n">
         <v>31.61</v>
       </c>
-      <c r="C41" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="D41" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="E41" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I41" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="J41" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="K41" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="L41" t="n">
-        <v>31.58</v>
-      </c>
       <c r="M41" t="n">
-        <v>31.72</v>
+        <v>31.76</v>
       </c>
       <c r="N41" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="O41" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3974,78 +3961,78 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W41" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.7</v>
+        <v>31.85</v>
       </c>
       <c r="C42" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="D42" t="n">
-        <v>31.58</v>
+        <v>31.79</v>
       </c>
       <c r="E42" t="n">
-        <v>31.84</v>
+        <v>31.9</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0016</v>
       </c>
       <c r="H42" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="I42" t="n">
-        <v>31.23</v>
+        <v>31.26</v>
       </c>
       <c r="J42" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="K42" t="n">
-        <v>31.53</v>
+        <v>31.68</v>
       </c>
       <c r="L42" t="n">
-        <v>31.61</v>
+        <v>31.79</v>
       </c>
       <c r="M42" t="n">
-        <v>31.76</v>
+        <v>32.01</v>
       </c>
       <c r="N42" t="n">
-        <v>31.91</v>
+        <v>32.22</v>
       </c>
       <c r="O42" t="n">
-        <v>31.93</v>
+        <v>32.23</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4056,25 +4043,21 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4084,50 +4067,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.85</v>
+        <v>31.93</v>
       </c>
       <c r="C43" t="n">
-        <v>31.96</v>
+        <v>32.23</v>
       </c>
       <c r="D43" t="n">
-        <v>31.79</v>
+        <v>31.92</v>
       </c>
       <c r="E43" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0063</v>
       </c>
       <c r="H43" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="I43" t="n">
-        <v>31.26</v>
+        <v>31.62</v>
       </c>
       <c r="J43" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K43" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="L43" t="n">
-        <v>31.79</v>
+        <v>31.89</v>
       </c>
       <c r="M43" t="n">
-        <v>32.01</v>
+        <v>31.98</v>
       </c>
       <c r="N43" t="n">
-        <v>32.22</v>
+        <v>32.08</v>
       </c>
       <c r="O43" t="n">
-        <v>32.23</v>
+        <v>32.13</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4138,21 +4121,27 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4162,50 +4151,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.93</v>
+        <v>32.1</v>
       </c>
       <c r="C44" t="n">
-        <v>32.23</v>
+        <v>32.42</v>
       </c>
       <c r="D44" t="n">
-        <v>31.92</v>
+        <v>32.03</v>
       </c>
       <c r="E44" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="I44" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="J44" t="n">
-        <v>31.74</v>
+        <v>31.8</v>
       </c>
       <c r="K44" t="n">
-        <v>31.81</v>
+        <v>31.94</v>
       </c>
       <c r="L44" t="n">
-        <v>31.89</v>
+        <v>32.09</v>
       </c>
       <c r="M44" t="n">
-        <v>31.98</v>
+        <v>32.25</v>
       </c>
       <c r="N44" t="n">
-        <v>32.08</v>
+        <v>32.42</v>
       </c>
       <c r="O44" t="n">
-        <v>32.13</v>
+        <v>32.53</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4216,7 +4205,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4231,12 +4220,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4246,50 +4233,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C45" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D45" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="E45" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I45" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="J45" t="n">
         <v>32.1</v>
       </c>
-      <c r="C45" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D45" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="E45" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I45" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="J45" t="n">
-        <v>31.8</v>
-      </c>
       <c r="K45" t="n">
-        <v>31.94</v>
+        <v>32.2</v>
       </c>
       <c r="L45" t="n">
-        <v>32.09</v>
+        <v>32.31</v>
       </c>
       <c r="M45" t="n">
-        <v>32.25</v>
+        <v>32.59</v>
       </c>
       <c r="N45" t="n">
-        <v>32.42</v>
+        <v>32.87</v>
       </c>
       <c r="O45" t="n">
-        <v>32.53</v>
+        <v>32.81</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4300,78 +4287,78 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32.31</v>
+        <v>32.32</v>
       </c>
       <c r="C46" t="n">
-        <v>32.49</v>
+        <v>32.55</v>
       </c>
       <c r="D46" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="E46" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I46" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="J46" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="K46" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="L46" t="n">
         <v>32.35</v>
       </c>
-      <c r="F46" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I46" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="J46" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="L46" t="n">
-        <v>32.31</v>
-      </c>
       <c r="M46" t="n">
-        <v>32.59</v>
+        <v>32.48</v>
       </c>
       <c r="N46" t="n">
-        <v>32.87</v>
+        <v>32.6</v>
       </c>
       <c r="O46" t="n">
-        <v>32.81</v>
+        <v>32.74</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4379,16 +4366,20 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4396,64 +4387,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32.32</v>
+        <v>32.29</v>
       </c>
       <c r="C47" t="n">
-        <v>32.55</v>
+        <v>32.49</v>
       </c>
       <c r="D47" t="n">
-        <v>32.21</v>
+        <v>32.12</v>
       </c>
       <c r="E47" t="n">
-        <v>32.29</v>
+        <v>32.24</v>
       </c>
       <c r="F47" t="n">
         <v>-0.06</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="H47" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I47" t="n">
-        <v>31.98</v>
+        <v>31.86</v>
       </c>
       <c r="J47" t="n">
-        <v>32.09</v>
+        <v>31.91</v>
       </c>
       <c r="K47" t="n">
-        <v>32.22</v>
+        <v>32.12</v>
       </c>
       <c r="L47" t="n">
-        <v>32.35</v>
+        <v>32.34</v>
       </c>
       <c r="M47" t="n">
-        <v>32.48</v>
+        <v>32.47</v>
       </c>
       <c r="N47" t="n">
         <v>32.6</v>
       </c>
       <c r="O47" t="n">
-        <v>32.74</v>
+        <v>32.9</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4461,85 +4452,83 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="C48" t="n">
         <v>32.29</v>
       </c>
-      <c r="C48" t="n">
-        <v>32.49</v>
-      </c>
       <c r="D48" t="n">
-        <v>32.12</v>
+        <v>31.92</v>
       </c>
       <c r="E48" t="n">
-        <v>32.24</v>
+        <v>32.01</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.0071</v>
       </c>
       <c r="H48" t="n">
         <v>0.37</v>
       </c>
       <c r="I48" t="n">
-        <v>31.86</v>
+        <v>31.76</v>
       </c>
       <c r="J48" t="n">
-        <v>31.91</v>
+        <v>31.83</v>
       </c>
       <c r="K48" t="n">
-        <v>32.12</v>
+        <v>32.05</v>
       </c>
       <c r="L48" t="n">
-        <v>32.34</v>
+        <v>32.27</v>
       </c>
       <c r="M48" t="n">
-        <v>32.47</v>
+        <v>32.42</v>
       </c>
       <c r="N48" t="n">
-        <v>32.6</v>
+        <v>32.57</v>
       </c>
       <c r="O48" t="n">
-        <v>32.9</v>
+        <v>32.86</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4547,18 +4536,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4566,7 +4555,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4580,50 +4569,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>32.24</v>
+        <v>31.99</v>
       </c>
       <c r="C49" t="n">
-        <v>32.29</v>
+        <v>32.01</v>
       </c>
       <c r="D49" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E49" t="n">
-        <v>32.01</v>
+        <v>31.83</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0071</v>
+        <v>-0.0055</v>
       </c>
       <c r="H49" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="I49" t="n">
-        <v>31.76</v>
+        <v>31.55</v>
       </c>
       <c r="J49" t="n">
-        <v>31.83</v>
+        <v>31.59</v>
       </c>
       <c r="K49" t="n">
-        <v>32.05</v>
+        <v>31.82</v>
       </c>
       <c r="L49" t="n">
-        <v>32.27</v>
+        <v>32.06</v>
       </c>
       <c r="M49" t="n">
-        <v>32.42</v>
+        <v>32.19</v>
       </c>
       <c r="N49" t="n">
-        <v>32.57</v>
+        <v>32.33</v>
       </c>
       <c r="O49" t="n">
-        <v>32.86</v>
+        <v>32.66</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4636,7 +4625,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4650,7 +4639,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4664,63 +4653,65 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.99</v>
+        <v>31.82</v>
       </c>
       <c r="C50" t="n">
-        <v>32.01</v>
+        <v>31.91</v>
       </c>
       <c r="D50" t="n">
-        <v>31.75</v>
+        <v>31.55</v>
       </c>
       <c r="E50" t="n">
-        <v>31.83</v>
+        <v>31.62</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0066</v>
       </c>
       <c r="H50" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="I50" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J50" t="n">
         <v>31.55</v>
       </c>
-      <c r="J50" t="n">
-        <v>31.59</v>
-      </c>
       <c r="K50" t="n">
-        <v>31.82</v>
+        <v>31.7</v>
       </c>
       <c r="L50" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="M50" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="N50" t="n">
         <v>32.06</v>
       </c>
-      <c r="M50" t="n">
-        <v>32.19</v>
-      </c>
-      <c r="N50" t="n">
-        <v>32.33</v>
-      </c>
       <c r="O50" t="n">
-        <v>32.66</v>
+        <v>32.26</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4734,7 +4725,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4748,155 +4739,155 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.82</v>
+        <v>31.63</v>
       </c>
       <c r="C51" t="n">
-        <v>31.91</v>
+        <v>31.8</v>
       </c>
       <c r="D51" t="n">
-        <v>31.55</v>
+        <v>31.58</v>
       </c>
       <c r="E51" t="n">
-        <v>31.62</v>
+        <v>31.67</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.21</v>
+        <v>0.05</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0066</v>
+        <v>0.0016</v>
       </c>
       <c r="H51" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="I51" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="J51" t="n">
-        <v>31.55</v>
+        <v>31.21</v>
       </c>
       <c r="K51" t="n">
-        <v>31.7</v>
+        <v>31.44</v>
       </c>
       <c r="L51" t="n">
-        <v>31.86</v>
+        <v>31.68</v>
       </c>
       <c r="M51" t="n">
-        <v>31.96</v>
+        <v>31.8</v>
       </c>
       <c r="N51" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="O51" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="C52" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="D52" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="E52" t="n">
         <v>31.63</v>
       </c>
-      <c r="C52" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D52" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="E52" t="n">
-        <v>31.67</v>
-      </c>
       <c r="F52" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0013</v>
       </c>
       <c r="H52" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I52" t="n">
-        <v>31.2</v>
+        <v>31.37</v>
       </c>
       <c r="J52" t="n">
-        <v>31.21</v>
+        <v>31.44</v>
       </c>
       <c r="K52" t="n">
-        <v>31.44</v>
+        <v>31.56</v>
       </c>
       <c r="L52" t="n">
         <v>31.68</v>
       </c>
       <c r="M52" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="N52" t="n">
-        <v>31.92</v>
+        <v>31.88</v>
       </c>
       <c r="O52" t="n">
-        <v>32.27</v>
+        <v>32.02</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4904,85 +4895,83 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.62</v>
+        <v>31.68</v>
       </c>
       <c r="C53" t="n">
-        <v>31.69</v>
+        <v>31.94</v>
       </c>
       <c r="D53" t="n">
-        <v>31.42</v>
+        <v>31.61</v>
       </c>
       <c r="E53" t="n">
-        <v>31.63</v>
+        <v>31.76</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0043</v>
       </c>
       <c r="H53" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="I53" t="n">
-        <v>31.37</v>
+        <v>31.14</v>
       </c>
       <c r="J53" t="n">
-        <v>31.44</v>
+        <v>31.39</v>
       </c>
       <c r="K53" t="n">
-        <v>31.56</v>
+        <v>31.49</v>
       </c>
       <c r="L53" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M53" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="N53" t="n">
-        <v>31.88</v>
+        <v>31.94</v>
       </c>
       <c r="O53" t="n">
-        <v>32.02</v>
+        <v>31.97</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4990,64 +4979,60 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="C54" t="n">
-        <v>31.94</v>
+        <v>31.86</v>
       </c>
       <c r="D54" t="n">
-        <v>31.61</v>
+        <v>31.6</v>
       </c>
       <c r="E54" t="n">
-        <v>31.76</v>
+        <v>31.71</v>
       </c>
       <c r="F54" t="n">
-        <v>0.14</v>
+        <v>-0.05</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0016</v>
       </c>
       <c r="H54" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="I54" t="n">
-        <v>31.14</v>
+        <v>31.29</v>
       </c>
       <c r="J54" t="n">
-        <v>31.39</v>
+        <v>31.44</v>
       </c>
       <c r="K54" t="n">
-        <v>31.49</v>
+        <v>31.6</v>
       </c>
       <c r="L54" t="n">
-        <v>31.59</v>
+        <v>31.77</v>
       </c>
       <c r="M54" t="n">
-        <v>31.77</v>
+        <v>31.93</v>
       </c>
       <c r="N54" t="n">
-        <v>31.94</v>
+        <v>32.08</v>
       </c>
       <c r="O54" t="n">
-        <v>31.97</v>
+        <v>32.26</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5055,18 +5040,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5074,60 +5059,64 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="C55" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="D55" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E55" t="n">
         <v>31.81</v>
       </c>
-      <c r="C55" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="D55" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E55" t="n">
-        <v>31.71</v>
-      </c>
       <c r="F55" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0029</v>
       </c>
       <c r="H55" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I55" t="n">
-        <v>31.29</v>
+        <v>31.33</v>
       </c>
       <c r="J55" t="n">
         <v>31.44</v>
       </c>
       <c r="K55" t="n">
-        <v>31.6</v>
+        <v>31.58</v>
       </c>
       <c r="L55" t="n">
-        <v>31.77</v>
+        <v>31.72</v>
       </c>
       <c r="M55" t="n">
-        <v>31.93</v>
+        <v>31.85</v>
       </c>
       <c r="N55" t="n">
-        <v>32.08</v>
+        <v>31.97</v>
       </c>
       <c r="O55" t="n">
-        <v>32.26</v>
+        <v>32.13</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5135,83 +5124,81 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.78</v>
+        <v>31.83</v>
       </c>
       <c r="C56" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="D56" t="n">
-        <v>31.73</v>
+        <v>31.7</v>
       </c>
       <c r="E56" t="n">
-        <v>31.81</v>
+        <v>31.95</v>
       </c>
       <c r="F56" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0044</v>
       </c>
       <c r="H56" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="I56" t="n">
-        <v>31.33</v>
+        <v>31.38</v>
       </c>
       <c r="J56" t="n">
-        <v>31.44</v>
+        <v>31.42</v>
       </c>
       <c r="K56" t="n">
-        <v>31.58</v>
+        <v>31.63</v>
       </c>
       <c r="L56" t="n">
-        <v>31.72</v>
+        <v>31.85</v>
       </c>
       <c r="M56" t="n">
-        <v>31.85</v>
+        <v>31.98</v>
       </c>
       <c r="N56" t="n">
-        <v>31.97</v>
+        <v>32.1</v>
       </c>
       <c r="O56" t="n">
-        <v>32.13</v>
+        <v>32.42</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5222,7 +5209,7 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5232,68 +5219,70 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="C57" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="D57" t="n">
         <v>31.83</v>
       </c>
-      <c r="C57" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="D57" t="n">
-        <v>31.7</v>
-      </c>
       <c r="E57" t="n">
-        <v>31.95</v>
+        <v>32.44</v>
       </c>
       <c r="F57" t="n">
-        <v>0.14</v>
+        <v>0.49</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0154</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I57" t="n">
-        <v>31.38</v>
+        <v>31.4</v>
       </c>
       <c r="J57" t="n">
-        <v>31.42</v>
+        <v>31.69</v>
       </c>
       <c r="K57" t="n">
-        <v>31.63</v>
+        <v>31.8</v>
       </c>
       <c r="L57" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="M57" t="n">
-        <v>31.98</v>
+        <v>32.1</v>
       </c>
       <c r="N57" t="n">
-        <v>32.1</v>
+        <v>32.29</v>
       </c>
       <c r="O57" t="n">
-        <v>32.42</v>
+        <v>32.31</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5304,83 +5293,85 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.92</v>
+        <v>32.43</v>
       </c>
       <c r="C58" t="n">
-        <v>32.53</v>
+        <v>32.44</v>
       </c>
       <c r="D58" t="n">
-        <v>31.83</v>
+        <v>32.38</v>
       </c>
       <c r="E58" t="n">
-        <v>32.44</v>
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>0.49</v>
+        <v/>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0154</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>0.7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>31.4</v>
+        <v>31.13</v>
       </c>
       <c r="J58" t="n">
-        <v>31.69</v>
+        <v>31.87</v>
       </c>
       <c r="K58" t="n">
-        <v>31.8</v>
+        <v>32.09</v>
       </c>
       <c r="L58" t="n">
-        <v>31.9</v>
+        <v>32.31</v>
       </c>
       <c r="M58" t="n">
-        <v>32.1</v>
+        <v>32.79</v>
       </c>
       <c r="N58" t="n">
-        <v>32.29</v>
+        <v>33.27</v>
       </c>
       <c r="O58" t="n">
-        <v>32.31</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+        <v>33.23</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5388,32 +5379,30 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>0.44</v>
       </c>
       <c r="I2" t="n">
-        <v>29.56</v>
+        <v>29.62</v>
       </c>
       <c r="J2" t="n">
-        <v>29.71</v>
+        <v>29.79</v>
       </c>
       <c r="K2" t="n">
-        <v>29.92</v>
+        <v>29.95</v>
       </c>
       <c r="L2" t="n">
-        <v>30.12</v>
+        <v>30.11</v>
       </c>
       <c r="M2" t="n">
-        <v>30.3</v>
+        <v>30.27</v>
       </c>
       <c r="N2" t="n">
-        <v>30.48</v>
+        <v>30.44</v>
       </c>
       <c r="O2" t="n">
-        <v>30.71</v>
+        <v>30.59</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -706,8 +703,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5327,25 +5326,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>32.43</v>
+        <v>32.39</v>
       </c>
       <c r="C58" t="n">
-        <v>32.44</v>
+        <v>32.54</v>
       </c>
       <c r="D58" t="n">
         <v>32.38</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>32.39</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-0.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0016</v>
       </c>
       <c r="H58" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="I58" t="n">
         <v>31.13</v>
@@ -5368,10 +5367,8 @@
       <c r="O58" t="n">
         <v>33.23</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5379,9 +5376,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -5329,22 +5329,22 @@
         <v>32.39</v>
       </c>
       <c r="C58" t="n">
-        <v>32.54</v>
+        <v>32.7</v>
       </c>
       <c r="D58" t="n">
         <v>32.38</v>
       </c>
       <c r="E58" t="n">
-        <v>32.39</v>
+        <v>32.48</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0013</v>
       </c>
       <c r="H58" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="I58" t="n">
         <v>31.13</v>
@@ -5395,11 +5395,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.44</v>
       </c>
       <c r="I2" t="n">
-        <v>29.62</v>
+        <v>29.82</v>
       </c>
       <c r="J2" t="n">
-        <v>29.79</v>
+        <v>29.87</v>
       </c>
       <c r="K2" t="n">
-        <v>29.95</v>
+        <v>30</v>
       </c>
       <c r="L2" t="n">
-        <v>30.11</v>
+        <v>30.13</v>
       </c>
       <c r="M2" t="n">
-        <v>30.27</v>
+        <v>30.22</v>
       </c>
       <c r="N2" t="n">
-        <v>30.44</v>
+        <v>30.31</v>
       </c>
       <c r="O2" t="n">
-        <v>30.59</v>
+        <v>30.49</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5332,19 +5332,19 @@
         <v>32.7</v>
       </c>
       <c r="D58" t="n">
-        <v>32.38</v>
+        <v>32.35</v>
       </c>
       <c r="E58" t="n">
-        <v>32.48</v>
+        <v>32.58</v>
       </c>
       <c r="F58" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0043</v>
       </c>
       <c r="H58" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="I58" t="n">
         <v>31.13</v>
@@ -5378,11 +5378,13 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.44</v>
       </c>
       <c r="I2" t="n">
-        <v>29.82</v>
+        <v>29.89</v>
       </c>
       <c r="J2" t="n">
-        <v>29.87</v>
+        <v>29.89</v>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>30.02</v>
       </c>
       <c r="L2" t="n">
-        <v>30.13</v>
+        <v>30.14</v>
       </c>
       <c r="M2" t="n">
-        <v>30.22</v>
+        <v>30.2</v>
       </c>
       <c r="N2" t="n">
-        <v>30.31</v>
+        <v>30.27</v>
       </c>
       <c r="O2" t="n">
-        <v>30.49</v>
+        <v>30.45</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5335,13 +5335,13 @@
         <v>32.35</v>
       </c>
       <c r="E58" t="n">
-        <v>32.58</v>
+        <v>32.37</v>
       </c>
       <c r="F58" t="n">
-        <v>0.14</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0022</v>
       </c>
       <c r="H58" t="n">
         <v>0.36</v>
@@ -5378,13 +5378,11 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5397,7 +5395,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="K2" t="n">
         <v>30.22</v>
       </c>
-      <c r="C2" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I2" t="n">
-        <v>29.89</v>
-      </c>
-      <c r="J2" t="n">
-        <v>29.89</v>
-      </c>
-      <c r="K2" t="n">
-        <v>30.02</v>
-      </c>
       <c r="L2" t="n">
-        <v>30.14</v>
+        <v>30.41</v>
       </c>
       <c r="M2" t="n">
-        <v>30.2</v>
+        <v>30.66</v>
       </c>
       <c r="N2" t="n">
-        <v>30.27</v>
+        <v>30.92</v>
       </c>
       <c r="O2" t="n">
-        <v>30.45</v>
+        <v>31.03</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,78 +690,76 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.44</v>
+        <v>30.42</v>
       </c>
       <c r="C3" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I3" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="K3" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="L3" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="M3" t="n">
         <v>30.53</v>
       </c>
-      <c r="D3" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="E3" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>-0.0003</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>29.71</v>
-      </c>
-      <c r="J3" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="K3" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="L3" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="M3" t="n">
-        <v>30.66</v>
-      </c>
       <c r="N3" t="n">
-        <v>30.92</v>
+        <v>30.63</v>
       </c>
       <c r="O3" t="n">
-        <v>31.03</v>
+        <v>30.73</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,22 +767,30 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -793,57 +799,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.42</v>
+        <v>30.67</v>
       </c>
       <c r="C4" t="n">
-        <v>30.71</v>
+        <v>30.8</v>
       </c>
       <c r="D4" t="n">
-        <v>30.24</v>
+        <v>30.48</v>
       </c>
       <c r="E4" t="n">
-        <v>30.71</v>
+        <v>30.62</v>
       </c>
       <c r="F4" t="n">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.0027</v>
       </c>
       <c r="H4" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="I4" t="n">
-        <v>30.14</v>
+        <v>29.78</v>
       </c>
       <c r="J4" t="n">
-        <v>30.24</v>
+        <v>30.36</v>
       </c>
       <c r="K4" t="n">
-        <v>30.34</v>
+        <v>30.47</v>
       </c>
       <c r="L4" t="n">
-        <v>30.43</v>
+        <v>30.59</v>
       </c>
       <c r="M4" t="n">
-        <v>30.53</v>
+        <v>30.94</v>
       </c>
       <c r="N4" t="n">
-        <v>30.63</v>
+        <v>31.28</v>
       </c>
       <c r="O4" t="n">
-        <v>30.73</v>
+        <v>31.17</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,30 +857,22 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -890,50 +888,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="C5" t="n">
-        <v>30.8</v>
+        <v>30.85</v>
       </c>
       <c r="D5" t="n">
-        <v>30.48</v>
+        <v>30.53</v>
       </c>
       <c r="E5" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.08</v>
+        <v>0.21</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0069</v>
       </c>
       <c r="H5" t="n">
         <v>0.32</v>
       </c>
       <c r="I5" t="n">
-        <v>29.78</v>
+        <v>30.16</v>
       </c>
       <c r="J5" t="n">
-        <v>30.36</v>
+        <v>30.29</v>
       </c>
       <c r="K5" t="n">
-        <v>30.47</v>
+        <v>30.46</v>
       </c>
       <c r="L5" t="n">
-        <v>30.59</v>
+        <v>30.63</v>
       </c>
       <c r="M5" t="n">
-        <v>30.94</v>
+        <v>30.78</v>
       </c>
       <c r="N5" t="n">
-        <v>31.28</v>
+        <v>30.93</v>
       </c>
       <c r="O5" t="n">
-        <v>31.17</v>
+        <v>31.12</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -946,11 +944,13 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -963,78 +963,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.62</v>
+        <v>30.83</v>
       </c>
       <c r="C6" t="n">
-        <v>30.85</v>
+        <v>30.83</v>
       </c>
       <c r="D6" t="n">
-        <v>30.53</v>
+        <v>30.52</v>
       </c>
       <c r="E6" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="F6" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0069</v>
+        <v>-0.0017</v>
       </c>
       <c r="H6" t="n">
         <v>0.32</v>
       </c>
       <c r="I6" t="n">
-        <v>30.16</v>
+        <v>30.2</v>
       </c>
       <c r="J6" t="n">
-        <v>30.29</v>
+        <v>30.58</v>
       </c>
       <c r="K6" t="n">
-        <v>30.46</v>
+        <v>30.67</v>
       </c>
       <c r="L6" t="n">
-        <v>30.63</v>
+        <v>30.76</v>
       </c>
       <c r="M6" t="n">
-        <v>30.78</v>
+        <v>31</v>
       </c>
       <c r="N6" t="n">
-        <v>30.93</v>
+        <v>31.23</v>
       </c>
       <c r="O6" t="n">
-        <v>31.12</v>
+        <v>31.18</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1047,76 +1045,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="C7" t="n">
-        <v>30.83</v>
+        <v>31.01</v>
       </c>
       <c r="D7" t="n">
-        <v>30.52</v>
+        <v>30.76</v>
       </c>
       <c r="E7" t="n">
-        <v>30.78</v>
+        <v>30.97</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.05</v>
+        <v>0.19</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.006</v>
       </c>
       <c r="H7" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="I7" t="n">
         <v>30.2</v>
       </c>
       <c r="J7" t="n">
-        <v>30.58</v>
+        <v>30.52</v>
       </c>
       <c r="K7" t="n">
-        <v>30.67</v>
+        <v>30.62</v>
       </c>
       <c r="L7" t="n">
-        <v>30.76</v>
+        <v>30.73</v>
       </c>
       <c r="M7" t="n">
-        <v>31</v>
+        <v>30.94</v>
       </c>
       <c r="N7" t="n">
-        <v>31.23</v>
+        <v>31.15</v>
       </c>
       <c r="O7" t="n">
-        <v>31.18</v>
+        <v>31.15</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1129,77 +1129,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.78</v>
+        <v>30.96</v>
       </c>
       <c r="C8" t="n">
-        <v>31.01</v>
+        <v>31.18</v>
       </c>
       <c r="D8" t="n">
-        <v>30.76</v>
+        <v>30.36</v>
       </c>
       <c r="E8" t="n">
-        <v>30.97</v>
+        <v>30.55</v>
       </c>
       <c r="F8" t="n">
-        <v>0.19</v>
+        <v>-0.41</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.0133</v>
       </c>
       <c r="H8" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="I8" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="J8" t="n">
-        <v>30.52</v>
+        <v>30.75</v>
       </c>
       <c r="K8" t="n">
-        <v>30.62</v>
+        <v>30.84</v>
       </c>
       <c r="L8" t="n">
-        <v>30.73</v>
+        <v>30.93</v>
       </c>
       <c r="M8" t="n">
-        <v>30.94</v>
+        <v>31.09</v>
       </c>
       <c r="N8" t="n">
-        <v>31.15</v>
+        <v>31.26</v>
       </c>
       <c r="O8" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>31.26</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1208,174 +1210,170 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.96</v>
+        <v>30.62</v>
       </c>
       <c r="C9" t="n">
-        <v>31.18</v>
+        <v>31.44</v>
       </c>
       <c r="D9" t="n">
-        <v>30.36</v>
+        <v>30.62</v>
       </c>
       <c r="E9" t="n">
-        <v>30.55</v>
+        <v>31.34</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.41</v>
+        <v>0.78</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0257</v>
       </c>
       <c r="H9" t="n">
         <v>0.82</v>
       </c>
       <c r="I9" t="n">
-        <v>30.5</v>
+        <v>29.54</v>
       </c>
       <c r="J9" t="n">
-        <v>30.75</v>
+        <v>29.63</v>
       </c>
       <c r="K9" t="n">
-        <v>30.84</v>
+        <v>30.15</v>
       </c>
       <c r="L9" t="n">
-        <v>30.93</v>
+        <v>30.66</v>
       </c>
       <c r="M9" t="n">
-        <v>31.09</v>
+        <v>30.96</v>
       </c>
       <c r="N9" t="n">
-        <v>31.26</v>
+        <v>31.27</v>
       </c>
       <c r="O9" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.62</v>
+        <v>31.34</v>
       </c>
       <c r="C10" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="D10" t="n">
-        <v>30.62</v>
+        <v>30.65</v>
       </c>
       <c r="E10" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="F10" t="n">
-        <v>0.78</v>
+        <v>0.04</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0012</v>
       </c>
       <c r="H10" t="n">
         <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>29.54</v>
+        <v>29.81</v>
       </c>
       <c r="J10" t="n">
-        <v>29.63</v>
+        <v>30.67</v>
       </c>
       <c r="K10" t="n">
-        <v>30.15</v>
+        <v>30.93</v>
       </c>
       <c r="L10" t="n">
-        <v>30.66</v>
+        <v>31.19</v>
       </c>
       <c r="M10" t="n">
-        <v>30.96</v>
+        <v>31.75</v>
       </c>
       <c r="N10" t="n">
-        <v>31.27</v>
+        <v>32.31</v>
       </c>
       <c r="O10" t="n">
-        <v>32</v>
+        <v>32.26</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1390,63 +1388,59 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="C11" t="n">
-        <v>31.47</v>
+        <v>31.46</v>
       </c>
       <c r="D11" t="n">
-        <v>30.65</v>
+        <v>31.17</v>
       </c>
       <c r="E11" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0033</v>
       </c>
       <c r="H11" t="n">
-        <v>0.82</v>
+        <v>0.29</v>
       </c>
       <c r="I11" t="n">
-        <v>29.81</v>
+        <v>29.83</v>
       </c>
       <c r="J11" t="n">
-        <v>30.67</v>
+        <v>30.71</v>
       </c>
       <c r="K11" t="n">
-        <v>30.93</v>
+        <v>30.97</v>
       </c>
       <c r="L11" t="n">
-        <v>31.19</v>
+        <v>31.22</v>
       </c>
       <c r="M11" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="N11" t="n">
-        <v>32.31</v>
+        <v>32.36</v>
       </c>
       <c r="O11" t="n">
-        <v>32.26</v>
+        <v>32.3</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
@@ -1467,55 +1461,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31.38</v>
+        <v>31.27</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46</v>
+        <v>31.32</v>
       </c>
       <c r="D12" t="n">
-        <v>31.17</v>
+        <v>31.08</v>
       </c>
       <c r="E12" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0015</v>
       </c>
       <c r="H12" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="I12" t="n">
-        <v>29.83</v>
+        <v>30.88</v>
       </c>
       <c r="J12" t="n">
-        <v>30.71</v>
+        <v>30.96</v>
       </c>
       <c r="K12" t="n">
-        <v>30.97</v>
+        <v>31.13</v>
       </c>
       <c r="L12" t="n">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="M12" t="n">
-        <v>31.79</v>
+        <v>31.42</v>
       </c>
       <c r="N12" t="n">
-        <v>32.36</v>
+        <v>31.54</v>
       </c>
       <c r="O12" t="n">
-        <v>32.3</v>
+        <v>31.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1523,8 +1521,10 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
@@ -1554,50 +1554,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="C13" t="n">
-        <v>31.32</v>
+        <v>31.63</v>
       </c>
       <c r="D13" t="n">
-        <v>31.08</v>
+        <v>31.24</v>
       </c>
       <c r="E13" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0059</v>
       </c>
       <c r="H13" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="I13" t="n">
-        <v>30.88</v>
+        <v>30.83</v>
       </c>
       <c r="J13" t="n">
-        <v>30.96</v>
+        <v>31.14</v>
       </c>
       <c r="K13" t="n">
-        <v>31.13</v>
+        <v>31.2</v>
       </c>
       <c r="L13" t="n">
-        <v>31.3</v>
+        <v>31.26</v>
       </c>
       <c r="M13" t="n">
-        <v>31.42</v>
+        <v>31.44</v>
       </c>
       <c r="N13" t="n">
-        <v>31.54</v>
+        <v>31.62</v>
       </c>
       <c r="O13" t="n">
-        <v>31.75</v>
+        <v>31.56</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1605,83 +1605,83 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.32</v>
+        <v>31.5</v>
       </c>
       <c r="C14" t="n">
-        <v>31.63</v>
+        <v>31.57</v>
       </c>
       <c r="D14" t="n">
-        <v>31.24</v>
+        <v>31.37</v>
       </c>
       <c r="E14" t="n">
-        <v>31.5</v>
+        <v>31.38</v>
       </c>
       <c r="F14" t="n">
-        <v>0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0039</v>
       </c>
       <c r="H14" t="n">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>30.83</v>
+        <v>30.86</v>
       </c>
       <c r="J14" t="n">
-        <v>31.14</v>
+        <v>31.15</v>
       </c>
       <c r="K14" t="n">
-        <v>31.2</v>
+        <v>31.31</v>
       </c>
       <c r="L14" t="n">
-        <v>31.26</v>
+        <v>31.47</v>
       </c>
       <c r="M14" t="n">
-        <v>31.44</v>
+        <v>31.7</v>
       </c>
       <c r="N14" t="n">
-        <v>31.62</v>
+        <v>31.92</v>
       </c>
       <c r="O14" t="n">
-        <v>31.56</v>
+        <v>32.01</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,83 +1689,83 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31.5</v>
+        <v>31.39</v>
       </c>
       <c r="C15" t="n">
-        <v>31.57</v>
+        <v>31.46</v>
       </c>
       <c r="D15" t="n">
-        <v>31.37</v>
+        <v>31.25</v>
       </c>
       <c r="E15" t="n">
-        <v>31.38</v>
+        <v>31.36</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0007</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I15" t="n">
-        <v>30.86</v>
+        <v>31.16</v>
       </c>
       <c r="J15" t="n">
-        <v>31.15</v>
+        <v>31.13</v>
       </c>
       <c r="K15" t="n">
-        <v>31.31</v>
+        <v>31.28</v>
       </c>
       <c r="L15" t="n">
-        <v>31.47</v>
+        <v>31.42</v>
       </c>
       <c r="M15" t="n">
-        <v>31.7</v>
+        <v>31.48</v>
       </c>
       <c r="N15" t="n">
-        <v>31.92</v>
+        <v>31.54</v>
       </c>
       <c r="O15" t="n">
-        <v>32.01</v>
+        <v>31.78</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1799,57 +1799,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31.39</v>
+        <v>31.38</v>
       </c>
       <c r="C16" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="E16" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I16" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="L16" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="M16" t="n">
         <v>31.46</v>
       </c>
-      <c r="D16" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="E16" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>-0.0007</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I16" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="J16" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="K16" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="L16" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="M16" t="n">
-        <v>31.48</v>
-      </c>
       <c r="N16" t="n">
-        <v>31.54</v>
+        <v>31.57</v>
       </c>
       <c r="O16" t="n">
-        <v>31.78</v>
+        <v>31.68</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1857,83 +1857,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.38</v>
+        <v>31.6</v>
       </c>
       <c r="C17" t="n">
-        <v>31.68</v>
+        <v>31.74</v>
       </c>
       <c r="D17" t="n">
-        <v>31.35</v>
+        <v>31.51</v>
       </c>
       <c r="E17" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="F17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H17" t="n">
         <v>0.23</v>
       </c>
-      <c r="G17" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.33</v>
-      </c>
       <c r="I17" t="n">
-        <v>31.04</v>
+        <v>31.02</v>
       </c>
       <c r="J17" t="n">
-        <v>31.15</v>
+        <v>31.31</v>
       </c>
       <c r="K17" t="n">
-        <v>31.25</v>
+        <v>31.43</v>
       </c>
       <c r="L17" t="n">
-        <v>31.36</v>
+        <v>31.55</v>
       </c>
       <c r="M17" t="n">
-        <v>31.46</v>
+        <v>31.76</v>
       </c>
       <c r="N17" t="n">
-        <v>31.57</v>
+        <v>31.96</v>
       </c>
       <c r="O17" t="n">
-        <v>31.68</v>
+        <v>32</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1946,23 +1946,17 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1974,63 +1968,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.6</v>
+        <v>31.61</v>
       </c>
       <c r="C18" t="n">
-        <v>31.74</v>
+        <v>31.68</v>
       </c>
       <c r="D18" t="n">
-        <v>31.51</v>
+        <v>31.37</v>
       </c>
       <c r="E18" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0005</v>
+        <v>-0.0075</v>
       </c>
       <c r="H18" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="I18" t="n">
-        <v>31.02</v>
+        <v>31.27</v>
       </c>
       <c r="J18" t="n">
-        <v>31.31</v>
+        <v>31.37</v>
       </c>
       <c r="K18" t="n">
-        <v>31.43</v>
+        <v>31.49</v>
       </c>
       <c r="L18" t="n">
-        <v>31.55</v>
+        <v>31.62</v>
       </c>
       <c r="M18" t="n">
-        <v>31.76</v>
+        <v>31.73</v>
       </c>
       <c r="N18" t="n">
-        <v>31.96</v>
+        <v>31.83</v>
       </c>
       <c r="O18" t="n">
-        <v>32</v>
+        <v>31.98</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2047,80 +2045,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="C19" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="D19" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="E19" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I19" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="J19" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="K19" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="L19" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M19" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N19" t="n">
         <v>31.61</v>
       </c>
-      <c r="C19" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="D19" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="E19" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I19" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="J19" t="n">
-        <v>31.37</v>
-      </c>
-      <c r="K19" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="L19" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="M19" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="N19" t="n">
-        <v>31.83</v>
-      </c>
       <c r="O19" t="n">
-        <v>31.98</v>
+        <v>32</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2131,57 +2135,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31.38</v>
+        <v>31.61</v>
       </c>
       <c r="C20" t="n">
-        <v>31.58</v>
+        <v>31.71</v>
       </c>
       <c r="D20" t="n">
-        <v>31.12</v>
+        <v>31.49</v>
       </c>
       <c r="E20" t="n">
         <v>31.58</v>
       </c>
       <c r="F20" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0003</v>
       </c>
       <c r="H20" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="I20" t="n">
-        <v>31.06</v>
+        <v>30.65</v>
       </c>
       <c r="J20" t="n">
-        <v>30.98</v>
+        <v>31.23</v>
       </c>
       <c r="K20" t="n">
-        <v>31.21</v>
+        <v>31.35</v>
       </c>
       <c r="L20" t="n">
-        <v>31.45</v>
+        <v>31.47</v>
       </c>
       <c r="M20" t="n">
-        <v>31.53</v>
+        <v>31.82</v>
       </c>
       <c r="N20" t="n">
-        <v>31.61</v>
+        <v>32.16</v>
       </c>
       <c r="O20" t="n">
-        <v>32</v>
+        <v>32.05</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2189,25 +2193,19 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2219,80 +2217,90 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>31.61</v>
       </c>
       <c r="C21" t="n">
-        <v>31.71</v>
+        <v>32.77</v>
       </c>
       <c r="D21" t="n">
-        <v>31.49</v>
+        <v>31.32</v>
       </c>
       <c r="E21" t="n">
-        <v>31.58</v>
+        <v>31.37</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0065</v>
       </c>
       <c r="H21" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="I21" t="n">
-        <v>30.65</v>
+        <v>31.27</v>
       </c>
       <c r="J21" t="n">
-        <v>31.23</v>
+        <v>31.34</v>
       </c>
       <c r="K21" t="n">
-        <v>31.35</v>
+        <v>31.46</v>
       </c>
       <c r="L21" t="n">
-        <v>31.47</v>
+        <v>31.59</v>
       </c>
       <c r="M21" t="n">
-        <v>31.82</v>
+        <v>31.69</v>
       </c>
       <c r="N21" t="n">
-        <v>32.16</v>
+        <v>31.79</v>
       </c>
       <c r="O21" t="n">
-        <v>32.05</v>
+        <v>31.94</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2301,90 +2309,80 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="C22" t="n">
-        <v>32.77</v>
+        <v>31.65</v>
       </c>
       <c r="D22" t="n">
-        <v>31.32</v>
+        <v>31.26</v>
       </c>
       <c r="E22" t="n">
-        <v>31.37</v>
+        <v>31.51</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.21</v>
+        <v>0.14</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0045</v>
       </c>
       <c r="H22" t="n">
-        <v>1.45</v>
+        <v>0.39</v>
       </c>
       <c r="I22" t="n">
-        <v>31.27</v>
+        <v>29.88</v>
       </c>
       <c r="J22" t="n">
-        <v>31.34</v>
+        <v>29.58</v>
       </c>
       <c r="K22" t="n">
-        <v>31.46</v>
+        <v>30.65</v>
       </c>
       <c r="L22" t="n">
-        <v>31.59</v>
+        <v>31.71</v>
       </c>
       <c r="M22" t="n">
-        <v>31.69</v>
+        <v>32.09</v>
       </c>
       <c r="N22" t="n">
-        <v>31.79</v>
+        <v>32.48</v>
       </c>
       <c r="O22" t="n">
-        <v>31.94</v>
+        <v>34.22</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2400,50 +2398,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>31.37</v>
+        <v>31.47</v>
       </c>
       <c r="C23" t="n">
-        <v>31.65</v>
+        <v>31.5</v>
       </c>
       <c r="D23" t="n">
-        <v>31.26</v>
+        <v>31.18</v>
       </c>
       <c r="E23" t="n">
-        <v>31.51</v>
+        <v>31.38</v>
       </c>
       <c r="F23" t="n">
-        <v>0.14</v>
+        <v>-0.14</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0043</v>
       </c>
       <c r="H23" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="I23" t="n">
-        <v>29.88</v>
+        <v>30.87</v>
       </c>
       <c r="J23" t="n">
-        <v>29.58</v>
+        <v>31.14</v>
       </c>
       <c r="K23" t="n">
-        <v>30.65</v>
+        <v>31.31</v>
       </c>
       <c r="L23" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="M23" t="n">
         <v>31.71</v>
       </c>
-      <c r="M23" t="n">
-        <v>32.09</v>
-      </c>
       <c r="N23" t="n">
-        <v>32.48</v>
+        <v>31.93</v>
       </c>
       <c r="O23" t="n">
-        <v>34.22</v>
+        <v>32.05</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2451,12 +2449,14 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2475,57 +2475,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C24" t="n">
-        <v>31.5</v>
+        <v>31.96</v>
       </c>
       <c r="D24" t="n">
-        <v>31.18</v>
+        <v>31.39</v>
       </c>
       <c r="E24" t="n">
-        <v>31.38</v>
+        <v>31.8</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0136</v>
       </c>
       <c r="H24" t="n">
-        <v>0.32</v>
+        <v>0.57</v>
       </c>
       <c r="I24" t="n">
-        <v>30.87</v>
+        <v>30.86</v>
       </c>
       <c r="J24" t="n">
-        <v>31.14</v>
+        <v>31.08</v>
       </c>
       <c r="K24" t="n">
-        <v>31.31</v>
+        <v>31.22</v>
       </c>
       <c r="L24" t="n">
-        <v>31.48</v>
+        <v>31.36</v>
       </c>
       <c r="M24" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N24" t="n">
         <v>31.71</v>
       </c>
-      <c r="N24" t="n">
-        <v>31.93</v>
-      </c>
       <c r="O24" t="n">
-        <v>32.05</v>
+        <v>31.81</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2533,83 +2533,83 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31.44</v>
+        <v>32.03</v>
       </c>
       <c r="C25" t="n">
-        <v>31.96</v>
+        <v>32.16</v>
       </c>
       <c r="D25" t="n">
-        <v>31.39</v>
+        <v>31.53</v>
       </c>
       <c r="E25" t="n">
-        <v>31.8</v>
+        <v>32.16</v>
       </c>
       <c r="F25" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0113</v>
       </c>
       <c r="H25" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="I25" t="n">
-        <v>30.86</v>
+        <v>30.82</v>
       </c>
       <c r="J25" t="n">
-        <v>31.08</v>
+        <v>31.29</v>
       </c>
       <c r="K25" t="n">
-        <v>31.22</v>
+        <v>31.52</v>
       </c>
       <c r="L25" t="n">
-        <v>31.36</v>
+        <v>31.74</v>
       </c>
       <c r="M25" t="n">
-        <v>31.53</v>
+        <v>32.09</v>
       </c>
       <c r="N25" t="n">
-        <v>31.71</v>
+        <v>32.44</v>
       </c>
       <c r="O25" t="n">
-        <v>31.81</v>
+        <v>32.54</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2627,18 +2627,14 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2650,50 +2646,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="C26" t="n">
-        <v>32.16</v>
+        <v>32.12</v>
       </c>
       <c r="D26" t="n">
-        <v>31.53</v>
+        <v>31.8</v>
       </c>
       <c r="E26" t="n">
-        <v>32.16</v>
+        <v>32.02</v>
       </c>
       <c r="F26" t="n">
-        <v>0.36</v>
+        <v>-0.14</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0044</v>
       </c>
       <c r="H26" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="I26" t="n">
-        <v>30.82</v>
+        <v>30.91</v>
       </c>
       <c r="J26" t="n">
-        <v>31.29</v>
+        <v>31.69</v>
       </c>
       <c r="K26" t="n">
-        <v>31.52</v>
+        <v>31.85</v>
       </c>
       <c r="L26" t="n">
-        <v>31.74</v>
+        <v>32.01</v>
       </c>
       <c r="M26" t="n">
-        <v>32.09</v>
+        <v>32.48</v>
       </c>
       <c r="N26" t="n">
-        <v>32.44</v>
+        <v>32.95</v>
       </c>
       <c r="O26" t="n">
-        <v>32.54</v>
+        <v>32.79</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2701,18 +2697,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2725,55 +2721,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32.09</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>32.12</v>
+        <v>32.14</v>
       </c>
       <c r="D27" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="E27" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0002</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I27" t="n">
-        <v>30.91</v>
+        <v>31.47</v>
       </c>
       <c r="J27" t="n">
-        <v>31.69</v>
+        <v>31.73</v>
       </c>
       <c r="K27" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="L27" t="n">
-        <v>32.01</v>
+        <v>31.99</v>
       </c>
       <c r="M27" t="n">
-        <v>32.48</v>
+        <v>32.18</v>
       </c>
       <c r="N27" t="n">
-        <v>32.95</v>
+        <v>32.38</v>
       </c>
       <c r="O27" t="n">
-        <v>32.79</v>
+        <v>32.44</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2807,57 +2807,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="C28" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="D28" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="E28" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I28" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="J28" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="L28" t="n">
         <v>32</v>
       </c>
-      <c r="C28" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="D28" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="E28" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I28" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="J28" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="K28" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="L28" t="n">
-        <v>31.99</v>
-      </c>
       <c r="M28" t="n">
-        <v>32.18</v>
+        <v>32.21</v>
       </c>
       <c r="N28" t="n">
-        <v>32.38</v>
+        <v>32.43</v>
       </c>
       <c r="O28" t="n">
-        <v>32.44</v>
+        <v>32.51</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2870,13 +2870,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2898,50 +2900,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
       <c r="C29" t="n">
-        <v>32.22</v>
+        <v>32.04</v>
       </c>
       <c r="D29" t="n">
-        <v>31.84</v>
+        <v>31.68</v>
       </c>
       <c r="E29" t="n">
-        <v>31.96</v>
+        <v>31.73</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0074</v>
       </c>
       <c r="H29" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I29" t="n">
-        <v>31.42</v>
+        <v>31.47</v>
       </c>
       <c r="J29" t="n">
-        <v>31.7</v>
+        <v>31.55</v>
       </c>
       <c r="K29" t="n">
-        <v>31.85</v>
+        <v>31.78</v>
       </c>
       <c r="L29" t="n">
         <v>32</v>
       </c>
       <c r="M29" t="n">
-        <v>32.21</v>
+        <v>32.15</v>
       </c>
       <c r="N29" t="n">
-        <v>32.43</v>
+        <v>32.3</v>
       </c>
       <c r="O29" t="n">
-        <v>32.51</v>
+        <v>32.59</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2951,18 +2953,16 @@
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2977,57 +2977,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>31.96</v>
+        <v>31.77</v>
       </c>
       <c r="C30" t="n">
-        <v>32.04</v>
+        <v>31.87</v>
       </c>
       <c r="D30" t="n">
-        <v>31.68</v>
+        <v>31.37</v>
       </c>
       <c r="E30" t="n">
-        <v>31.73</v>
+        <v>31.47</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0083</v>
       </c>
       <c r="H30" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="I30" t="n">
-        <v>31.47</v>
+        <v>31.32</v>
       </c>
       <c r="J30" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K30" t="n">
         <v>31.55</v>
       </c>
-      <c r="K30" t="n">
-        <v>31.78</v>
-      </c>
       <c r="L30" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="M30" t="n">
-        <v>32.15</v>
+        <v>31.91</v>
       </c>
       <c r="N30" t="n">
-        <v>32.3</v>
+        <v>32.02</v>
       </c>
       <c r="O30" t="n">
-        <v>32.59</v>
+        <v>32.41</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3068,50 +3068,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.77</v>
+        <v>31.47</v>
       </c>
       <c r="C31" t="n">
-        <v>31.87</v>
+        <v>31.59</v>
       </c>
       <c r="D31" t="n">
-        <v>31.37</v>
+        <v>31.18</v>
       </c>
       <c r="E31" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0009</v>
       </c>
       <c r="H31" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="I31" t="n">
-        <v>31.32</v>
+        <v>30.88</v>
       </c>
       <c r="J31" t="n">
-        <v>31.3</v>
+        <v>30.89</v>
       </c>
       <c r="K31" t="n">
-        <v>31.55</v>
+        <v>31.22</v>
       </c>
       <c r="L31" t="n">
-        <v>31.8</v>
+        <v>31.54</v>
       </c>
       <c r="M31" t="n">
-        <v>31.91</v>
+        <v>31.71</v>
       </c>
       <c r="N31" t="n">
-        <v>32.02</v>
+        <v>31.88</v>
       </c>
       <c r="O31" t="n">
-        <v>32.41</v>
+        <v>32.36</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3152,50 +3152,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31.47</v>
+        <v>31.44</v>
       </c>
       <c r="C32" t="n">
-        <v>31.59</v>
+        <v>31.75</v>
       </c>
       <c r="D32" t="n">
-        <v>31.18</v>
+        <v>31.38</v>
       </c>
       <c r="E32" t="n">
-        <v>31.44</v>
+        <v>31.55</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0037</v>
       </c>
       <c r="H32" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="I32" t="n">
-        <v>30.88</v>
+        <v>30.78</v>
       </c>
       <c r="J32" t="n">
-        <v>30.89</v>
+        <v>31.05</v>
       </c>
       <c r="K32" t="n">
-        <v>31.22</v>
+        <v>31.23</v>
       </c>
       <c r="L32" t="n">
-        <v>31.54</v>
+        <v>31.41</v>
       </c>
       <c r="M32" t="n">
-        <v>31.71</v>
+        <v>31.64</v>
       </c>
       <c r="N32" t="n">
-        <v>31.88</v>
+        <v>31.87</v>
       </c>
       <c r="O32" t="n">
-        <v>32.36</v>
+        <v>32</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3203,18 +3203,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3227,59 +3227,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31.44</v>
+        <v>31.64</v>
       </c>
       <c r="C33" t="n">
-        <v>31.75</v>
+        <v>31.69</v>
       </c>
       <c r="D33" t="n">
-        <v>31.38</v>
+        <v>31.3</v>
       </c>
       <c r="E33" t="n">
-        <v>31.55</v>
+        <v>31.3</v>
       </c>
       <c r="F33" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="I33" t="n">
-        <v>30.78</v>
+        <v>31.02</v>
       </c>
       <c r="J33" t="n">
-        <v>31.05</v>
+        <v>31.18</v>
       </c>
       <c r="K33" t="n">
-        <v>31.23</v>
+        <v>31.37</v>
       </c>
       <c r="L33" t="n">
-        <v>31.41</v>
+        <v>31.56</v>
       </c>
       <c r="M33" t="n">
-        <v>31.64</v>
+        <v>31.74</v>
       </c>
       <c r="N33" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="O33" t="n">
-        <v>32</v>
+        <v>32.11</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3287,19 +3283,19 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3311,55 +3307,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.64</v>
+        <v>31.3</v>
       </c>
       <c r="C34" t="n">
-        <v>31.69</v>
+        <v>31.62</v>
       </c>
       <c r="D34" t="n">
         <v>31.3</v>
       </c>
       <c r="E34" t="n">
-        <v>31.3</v>
+        <v>31.56</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.26</v>
+        <v>0.27</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="I34" t="n">
-        <v>31.02</v>
+        <v>30.9</v>
       </c>
       <c r="J34" t="n">
-        <v>31.18</v>
+        <v>30.8</v>
       </c>
       <c r="K34" t="n">
-        <v>31.37</v>
+        <v>31.1</v>
       </c>
       <c r="L34" t="n">
-        <v>31.56</v>
+        <v>31.39</v>
       </c>
       <c r="M34" t="n">
-        <v>31.74</v>
+        <v>31.49</v>
       </c>
       <c r="N34" t="n">
-        <v>31.91</v>
+        <v>31.59</v>
       </c>
       <c r="O34" t="n">
-        <v>32.11</v>
+        <v>32.09</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3367,22 +3367,24 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3393,57 +3395,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.3</v>
+        <v>31.59</v>
       </c>
       <c r="C35" t="n">
-        <v>31.62</v>
+        <v>31.78</v>
       </c>
       <c r="D35" t="n">
-        <v>31.3</v>
+        <v>31.36</v>
       </c>
       <c r="E35" t="n">
-        <v>31.56</v>
+        <v>31.36</v>
       </c>
       <c r="F35" t="n">
-        <v>0.27</v>
+        <v>-0.21</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0065</v>
       </c>
       <c r="H35" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="I35" t="n">
-        <v>30.9</v>
+        <v>30.98</v>
       </c>
       <c r="J35" t="n">
-        <v>30.8</v>
+        <v>31.29</v>
       </c>
       <c r="K35" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="L35" t="n">
-        <v>31.39</v>
+        <v>31.51</v>
       </c>
       <c r="M35" t="n">
-        <v>31.49</v>
+        <v>31.72</v>
       </c>
       <c r="N35" t="n">
-        <v>31.59</v>
+        <v>31.93</v>
       </c>
       <c r="O35" t="n">
-        <v>32.09</v>
+        <v>31.95</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3451,12 +3453,14 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3464,10 +3468,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3486,50 +3488,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31.59</v>
+        <v>31.44</v>
       </c>
       <c r="C36" t="n">
-        <v>31.78</v>
+        <v>31.52</v>
       </c>
       <c r="D36" t="n">
-        <v>31.36</v>
+        <v>31.31</v>
       </c>
       <c r="E36" t="n">
-        <v>31.36</v>
+        <v>31.41</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0018</v>
       </c>
       <c r="H36" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="I36" t="n">
-        <v>30.98</v>
+        <v>30.94</v>
       </c>
       <c r="J36" t="n">
-        <v>31.29</v>
+        <v>30.83</v>
       </c>
       <c r="K36" t="n">
-        <v>31.4</v>
+        <v>31.15</v>
       </c>
       <c r="L36" t="n">
-        <v>31.51</v>
+        <v>31.46</v>
       </c>
       <c r="M36" t="n">
-        <v>31.72</v>
+        <v>31.57</v>
       </c>
       <c r="N36" t="n">
-        <v>31.93</v>
+        <v>31.67</v>
       </c>
       <c r="O36" t="n">
-        <v>31.95</v>
+        <v>32.2</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3537,20 +3539,16 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3565,57 +3563,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.44</v>
+        <v>31.41</v>
       </c>
       <c r="C37" t="n">
-        <v>31.52</v>
+        <v>31.6</v>
       </c>
       <c r="D37" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="E37" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I37" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J37" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="K37" t="n">
         <v>31.31</v>
       </c>
-      <c r="E37" t="n">
+      <c r="L37" t="n">
         <v>31.41</v>
       </c>
-      <c r="F37" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I37" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="J37" t="n">
-        <v>30.83</v>
-      </c>
-      <c r="K37" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="L37" t="n">
-        <v>31.46</v>
-      </c>
       <c r="M37" t="n">
-        <v>31.57</v>
+        <v>31.51</v>
       </c>
       <c r="N37" t="n">
-        <v>31.67</v>
+        <v>31.61</v>
       </c>
       <c r="O37" t="n">
-        <v>32.2</v>
+        <v>31.72</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3623,16 +3621,20 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3647,57 +3649,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.41</v>
+        <v>31.59</v>
       </c>
       <c r="C38" t="n">
-        <v>31.6</v>
+        <v>31.76</v>
       </c>
       <c r="D38" t="n">
-        <v>31.28</v>
+        <v>31.44</v>
       </c>
       <c r="E38" t="n">
         <v>31.56</v>
       </c>
       <c r="F38" t="n">
-        <v>0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0002</v>
       </c>
       <c r="H38" t="n">
         <v>0.33</v>
       </c>
       <c r="I38" t="n">
-        <v>31.11</v>
+        <v>30.95</v>
       </c>
       <c r="J38" t="n">
-        <v>31.21</v>
+        <v>31.3</v>
       </c>
       <c r="K38" t="n">
-        <v>31.31</v>
+        <v>31.4</v>
       </c>
       <c r="L38" t="n">
-        <v>31.41</v>
+        <v>31.5</v>
       </c>
       <c r="M38" t="n">
-        <v>31.51</v>
+        <v>31.73</v>
       </c>
       <c r="N38" t="n">
-        <v>31.61</v>
+        <v>31.95</v>
       </c>
       <c r="O38" t="n">
-        <v>31.72</v>
+        <v>31.93</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3705,19 +3707,17 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
@@ -3740,50 +3740,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.59</v>
+        <v>31.61</v>
       </c>
       <c r="C39" t="n">
-        <v>31.76</v>
+        <v>31.7</v>
       </c>
       <c r="D39" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="E39" t="n">
-        <v>31.56</v>
+        <v>31.65</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0028</v>
       </c>
       <c r="H39" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="I39" t="n">
-        <v>30.95</v>
+        <v>31.11</v>
       </c>
       <c r="J39" t="n">
-        <v>31.3</v>
+        <v>31.21</v>
       </c>
       <c r="K39" t="n">
-        <v>31.4</v>
+        <v>31.39</v>
       </c>
       <c r="L39" t="n">
-        <v>31.5</v>
+        <v>31.58</v>
       </c>
       <c r="M39" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="N39" t="n">
-        <v>31.95</v>
+        <v>31.86</v>
       </c>
       <c r="O39" t="n">
-        <v>31.93</v>
+        <v>32.09</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3799,10 +3799,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3824,50 +3822,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="C40" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="D40" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="E40" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I40" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="J40" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="K40" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="L40" t="n">
         <v>31.61</v>
       </c>
-      <c r="C40" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="D40" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="E40" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I40" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="J40" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="K40" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="L40" t="n">
-        <v>31.58</v>
-      </c>
       <c r="M40" t="n">
-        <v>31.72</v>
+        <v>31.76</v>
       </c>
       <c r="N40" t="n">
-        <v>31.86</v>
+        <v>31.91</v>
       </c>
       <c r="O40" t="n">
-        <v>32.09</v>
+        <v>31.93</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3880,14 +3878,18 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3897,59 +3899,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.7</v>
+        <v>31.85</v>
       </c>
       <c r="C41" t="n">
-        <v>31.91</v>
+        <v>31.96</v>
       </c>
       <c r="D41" t="n">
-        <v>31.58</v>
+        <v>31.79</v>
       </c>
       <c r="E41" t="n">
-        <v>31.84</v>
+        <v>31.9</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0016</v>
       </c>
       <c r="H41" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="I41" t="n">
-        <v>31.23</v>
+        <v>31.26</v>
       </c>
       <c r="J41" t="n">
-        <v>31.45</v>
+        <v>31.57</v>
       </c>
       <c r="K41" t="n">
-        <v>31.53</v>
+        <v>31.68</v>
       </c>
       <c r="L41" t="n">
-        <v>31.61</v>
+        <v>31.79</v>
       </c>
       <c r="M41" t="n">
-        <v>31.76</v>
+        <v>32.01</v>
       </c>
       <c r="N41" t="n">
-        <v>31.91</v>
+        <v>32.22</v>
       </c>
       <c r="O41" t="n">
-        <v>31.93</v>
+        <v>32.23</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3962,18 +3960,14 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3988,50 +3982,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.85</v>
+        <v>31.93</v>
       </c>
       <c r="C42" t="n">
-        <v>31.96</v>
+        <v>32.23</v>
       </c>
       <c r="D42" t="n">
-        <v>31.79</v>
+        <v>31.92</v>
       </c>
       <c r="E42" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0063</v>
       </c>
       <c r="H42" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="I42" t="n">
-        <v>31.26</v>
+        <v>31.62</v>
       </c>
       <c r="J42" t="n">
-        <v>31.57</v>
+        <v>31.74</v>
       </c>
       <c r="K42" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="L42" t="n">
-        <v>31.79</v>
+        <v>31.89</v>
       </c>
       <c r="M42" t="n">
-        <v>32.01</v>
+        <v>31.98</v>
       </c>
       <c r="N42" t="n">
-        <v>32.22</v>
+        <v>32.08</v>
       </c>
       <c r="O42" t="n">
-        <v>32.23</v>
+        <v>32.13</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4044,17 +4038,23 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
@@ -4066,50 +4066,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.93</v>
+        <v>32.1</v>
       </c>
       <c r="C43" t="n">
-        <v>32.23</v>
+        <v>32.42</v>
       </c>
       <c r="D43" t="n">
-        <v>31.92</v>
+        <v>32.03</v>
       </c>
       <c r="E43" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="I43" t="n">
-        <v>31.62</v>
+        <v>31.61</v>
       </c>
       <c r="J43" t="n">
-        <v>31.74</v>
+        <v>31.8</v>
       </c>
       <c r="K43" t="n">
-        <v>31.81</v>
+        <v>31.94</v>
       </c>
       <c r="L43" t="n">
-        <v>31.89</v>
+        <v>32.09</v>
       </c>
       <c r="M43" t="n">
-        <v>31.98</v>
+        <v>32.25</v>
       </c>
       <c r="N43" t="n">
-        <v>32.08</v>
+        <v>32.42</v>
       </c>
       <c r="O43" t="n">
-        <v>32.13</v>
+        <v>32.53</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4135,10 +4135,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
@@ -4150,50 +4148,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="C44" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D44" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="E44" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I44" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="J44" t="n">
         <v>32.1</v>
       </c>
-      <c r="C44" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="D44" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="E44" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I44" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="J44" t="n">
-        <v>31.8</v>
-      </c>
       <c r="K44" t="n">
-        <v>31.94</v>
+        <v>32.2</v>
       </c>
       <c r="L44" t="n">
-        <v>32.09</v>
+        <v>32.31</v>
       </c>
       <c r="M44" t="n">
-        <v>32.25</v>
+        <v>32.59</v>
       </c>
       <c r="N44" t="n">
-        <v>32.42</v>
+        <v>32.87</v>
       </c>
       <c r="O44" t="n">
-        <v>32.53</v>
+        <v>32.81</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4206,18 +4204,14 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4227,55 +4221,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32.31</v>
+        <v>32.32</v>
       </c>
       <c r="C45" t="n">
-        <v>32.49</v>
+        <v>32.55</v>
       </c>
       <c r="D45" t="n">
-        <v>32.23</v>
+        <v>32.21</v>
       </c>
       <c r="E45" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I45" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="J45" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="K45" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="L45" t="n">
         <v>32.35</v>
       </c>
-      <c r="F45" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I45" t="n">
-        <v>31.65</v>
-      </c>
-      <c r="J45" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="L45" t="n">
-        <v>32.31</v>
-      </c>
       <c r="M45" t="n">
-        <v>32.59</v>
+        <v>32.48</v>
       </c>
       <c r="N45" t="n">
-        <v>32.87</v>
+        <v>32.6</v>
       </c>
       <c r="O45" t="n">
-        <v>32.81</v>
+        <v>32.74</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4283,16 +4281,20 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4307,57 +4309,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32.32</v>
+        <v>32.29</v>
       </c>
       <c r="C46" t="n">
-        <v>32.55</v>
+        <v>32.49</v>
       </c>
       <c r="D46" t="n">
-        <v>32.21</v>
+        <v>32.12</v>
       </c>
       <c r="E46" t="n">
-        <v>32.29</v>
+        <v>32.24</v>
       </c>
       <c r="F46" t="n">
         <v>-0.06</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="H46" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I46" t="n">
-        <v>31.98</v>
+        <v>31.86</v>
       </c>
       <c r="J46" t="n">
-        <v>32.09</v>
+        <v>31.91</v>
       </c>
       <c r="K46" t="n">
-        <v>32.22</v>
+        <v>32.12</v>
       </c>
       <c r="L46" t="n">
-        <v>32.35</v>
+        <v>32.34</v>
       </c>
       <c r="M46" t="n">
-        <v>32.48</v>
+        <v>32.47</v>
       </c>
       <c r="N46" t="n">
         <v>32.6</v>
       </c>
       <c r="O46" t="n">
-        <v>32.74</v>
+        <v>32.9</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4365,21 +4367,19 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4393,57 +4393,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="C47" t="n">
         <v>32.29</v>
       </c>
-      <c r="C47" t="n">
-        <v>32.49</v>
-      </c>
       <c r="D47" t="n">
-        <v>32.12</v>
+        <v>31.92</v>
       </c>
       <c r="E47" t="n">
-        <v>32.24</v>
+        <v>32.01</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.0071</v>
       </c>
       <c r="H47" t="n">
         <v>0.37</v>
       </c>
       <c r="I47" t="n">
-        <v>31.86</v>
+        <v>31.76</v>
       </c>
       <c r="J47" t="n">
-        <v>31.91</v>
+        <v>31.83</v>
       </c>
       <c r="K47" t="n">
-        <v>32.12</v>
+        <v>32.05</v>
       </c>
       <c r="L47" t="n">
-        <v>32.34</v>
+        <v>32.27</v>
       </c>
       <c r="M47" t="n">
-        <v>32.47</v>
+        <v>32.42</v>
       </c>
       <c r="N47" t="n">
-        <v>32.6</v>
+        <v>32.57</v>
       </c>
       <c r="O47" t="n">
-        <v>32.9</v>
+        <v>32.86</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4451,18 +4451,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4484,50 +4484,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32.24</v>
+        <v>31.99</v>
       </c>
       <c r="C48" t="n">
-        <v>32.29</v>
+        <v>32.01</v>
       </c>
       <c r="D48" t="n">
-        <v>31.92</v>
+        <v>31.75</v>
       </c>
       <c r="E48" t="n">
-        <v>32.01</v>
+        <v>31.83</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0071</v>
+        <v>-0.0055</v>
       </c>
       <c r="H48" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="I48" t="n">
-        <v>31.76</v>
+        <v>31.55</v>
       </c>
       <c r="J48" t="n">
-        <v>31.83</v>
+        <v>31.59</v>
       </c>
       <c r="K48" t="n">
-        <v>32.05</v>
+        <v>31.82</v>
       </c>
       <c r="L48" t="n">
-        <v>32.27</v>
+        <v>32.06</v>
       </c>
       <c r="M48" t="n">
-        <v>32.42</v>
+        <v>32.19</v>
       </c>
       <c r="N48" t="n">
-        <v>32.57</v>
+        <v>32.33</v>
       </c>
       <c r="O48" t="n">
-        <v>32.86</v>
+        <v>32.66</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4568,60 +4568,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.99</v>
+        <v>31.82</v>
       </c>
       <c r="C49" t="n">
-        <v>32.01</v>
+        <v>31.91</v>
       </c>
       <c r="D49" t="n">
-        <v>31.75</v>
+        <v>31.55</v>
       </c>
       <c r="E49" t="n">
-        <v>31.83</v>
+        <v>31.62</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0066</v>
       </c>
       <c r="H49" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="I49" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J49" t="n">
         <v>31.55</v>
       </c>
-      <c r="J49" t="n">
-        <v>31.59</v>
-      </c>
       <c r="K49" t="n">
-        <v>31.82</v>
+        <v>31.7</v>
       </c>
       <c r="L49" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="M49" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="N49" t="n">
         <v>32.06</v>
       </c>
-      <c r="M49" t="n">
-        <v>32.19</v>
-      </c>
-      <c r="N49" t="n">
-        <v>32.33</v>
-      </c>
       <c r="O49" t="n">
-        <v>32.66</v>
+        <v>32.26</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
@@ -4652,72 +4654,70 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.82</v>
+        <v>31.63</v>
       </c>
       <c r="C50" t="n">
-        <v>31.91</v>
+        <v>31.8</v>
       </c>
       <c r="D50" t="n">
-        <v>31.55</v>
+        <v>31.58</v>
       </c>
       <c r="E50" t="n">
-        <v>31.62</v>
+        <v>31.67</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.21</v>
+        <v>0.05</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0066</v>
+        <v>0.0016</v>
       </c>
       <c r="H50" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="I50" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="J50" t="n">
-        <v>31.55</v>
+        <v>31.21</v>
       </c>
       <c r="K50" t="n">
-        <v>31.7</v>
+        <v>31.44</v>
       </c>
       <c r="L50" t="n">
-        <v>31.86</v>
+        <v>31.68</v>
       </c>
       <c r="M50" t="n">
-        <v>31.96</v>
+        <v>31.8</v>
       </c>
       <c r="N50" t="n">
-        <v>32.06</v>
+        <v>31.92</v>
       </c>
       <c r="O50" t="n">
-        <v>32.26</v>
+        <v>32.27</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4731,76 +4731,78 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="C51" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="D51" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="E51" t="n">
         <v>31.63</v>
       </c>
-      <c r="C51" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D51" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="E51" t="n">
-        <v>31.67</v>
-      </c>
       <c r="F51" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0013</v>
       </c>
       <c r="H51" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="I51" t="n">
-        <v>31.2</v>
+        <v>31.37</v>
       </c>
       <c r="J51" t="n">
-        <v>31.21</v>
+        <v>31.44</v>
       </c>
       <c r="K51" t="n">
-        <v>31.44</v>
+        <v>31.56</v>
       </c>
       <c r="L51" t="n">
         <v>31.68</v>
       </c>
       <c r="M51" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="N51" t="n">
-        <v>31.92</v>
+        <v>31.88</v>
       </c>
       <c r="O51" t="n">
-        <v>32.27</v>
+        <v>32.02</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4815,78 +4817,76 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31.62</v>
+        <v>31.68</v>
       </c>
       <c r="C52" t="n">
-        <v>31.69</v>
+        <v>31.94</v>
       </c>
       <c r="D52" t="n">
-        <v>31.42</v>
+        <v>31.61</v>
       </c>
       <c r="E52" t="n">
-        <v>31.63</v>
+        <v>31.76</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0043</v>
       </c>
       <c r="H52" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="I52" t="n">
-        <v>31.37</v>
+        <v>31.14</v>
       </c>
       <c r="J52" t="n">
-        <v>31.44</v>
+        <v>31.39</v>
       </c>
       <c r="K52" t="n">
-        <v>31.56</v>
+        <v>31.49</v>
       </c>
       <c r="L52" t="n">
-        <v>31.68</v>
+        <v>31.59</v>
       </c>
       <c r="M52" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="N52" t="n">
-        <v>31.88</v>
+        <v>31.94</v>
       </c>
       <c r="O52" t="n">
-        <v>32.02</v>
+        <v>31.97</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4899,59 +4899,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>31.68</v>
+        <v>31.81</v>
       </c>
       <c r="C53" t="n">
-        <v>31.94</v>
+        <v>31.86</v>
       </c>
       <c r="D53" t="n">
-        <v>31.61</v>
+        <v>31.6</v>
       </c>
       <c r="E53" t="n">
-        <v>31.76</v>
+        <v>31.71</v>
       </c>
       <c r="F53" t="n">
-        <v>0.14</v>
+        <v>-0.05</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0016</v>
       </c>
       <c r="H53" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="I53" t="n">
-        <v>31.14</v>
+        <v>31.29</v>
       </c>
       <c r="J53" t="n">
-        <v>31.39</v>
+        <v>31.44</v>
       </c>
       <c r="K53" t="n">
-        <v>31.49</v>
+        <v>31.6</v>
       </c>
       <c r="L53" t="n">
-        <v>31.59</v>
+        <v>31.77</v>
       </c>
       <c r="M53" t="n">
-        <v>31.77</v>
+        <v>31.93</v>
       </c>
       <c r="N53" t="n">
-        <v>31.94</v>
+        <v>32.08</v>
       </c>
       <c r="O53" t="n">
-        <v>31.97</v>
+        <v>32.26</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4959,18 +4955,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4983,55 +4979,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="C54" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="D54" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="E54" t="n">
         <v>31.81</v>
       </c>
-      <c r="C54" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="D54" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E54" t="n">
-        <v>31.71</v>
-      </c>
       <c r="F54" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0029</v>
       </c>
       <c r="H54" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="I54" t="n">
-        <v>31.29</v>
+        <v>31.33</v>
       </c>
       <c r="J54" t="n">
         <v>31.44</v>
       </c>
       <c r="K54" t="n">
-        <v>31.6</v>
+        <v>31.58</v>
       </c>
       <c r="L54" t="n">
-        <v>31.77</v>
+        <v>31.72</v>
       </c>
       <c r="M54" t="n">
-        <v>31.93</v>
+        <v>31.85</v>
       </c>
       <c r="N54" t="n">
-        <v>32.08</v>
+        <v>31.97</v>
       </c>
       <c r="O54" t="n">
-        <v>32.26</v>
+        <v>32.13</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5039,22 +5039,24 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5063,59 +5065,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.78</v>
+        <v>31.83</v>
       </c>
       <c r="C55" t="n">
-        <v>32.07</v>
+        <v>32.01</v>
       </c>
       <c r="D55" t="n">
-        <v>31.73</v>
+        <v>31.7</v>
       </c>
       <c r="E55" t="n">
-        <v>31.81</v>
+        <v>31.95</v>
       </c>
       <c r="F55" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0044</v>
       </c>
       <c r="H55" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="I55" t="n">
-        <v>31.33</v>
+        <v>31.38</v>
       </c>
       <c r="J55" t="n">
-        <v>31.44</v>
+        <v>31.42</v>
       </c>
       <c r="K55" t="n">
-        <v>31.58</v>
+        <v>31.63</v>
       </c>
       <c r="L55" t="n">
-        <v>31.72</v>
+        <v>31.85</v>
       </c>
       <c r="M55" t="n">
-        <v>31.85</v>
+        <v>31.98</v>
       </c>
       <c r="N55" t="n">
-        <v>31.97</v>
+        <v>32.1</v>
       </c>
       <c r="O55" t="n">
-        <v>32.13</v>
+        <v>32.42</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5136,10 +5134,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5149,55 +5145,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="C56" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="D56" t="n">
         <v>31.83</v>
       </c>
-      <c r="C56" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="D56" t="n">
-        <v>31.7</v>
-      </c>
       <c r="E56" t="n">
-        <v>31.95</v>
+        <v>32.44</v>
       </c>
       <c r="F56" t="n">
-        <v>0.14</v>
+        <v>0.49</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0154</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>31.38</v>
+        <v>31.4</v>
       </c>
       <c r="J56" t="n">
-        <v>31.42</v>
+        <v>31.69</v>
       </c>
       <c r="K56" t="n">
-        <v>31.63</v>
+        <v>31.8</v>
       </c>
       <c r="L56" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="M56" t="n">
-        <v>31.98</v>
+        <v>32.1</v>
       </c>
       <c r="N56" t="n">
-        <v>32.1</v>
+        <v>32.29</v>
       </c>
       <c r="O56" t="n">
-        <v>32.42</v>
+        <v>32.31</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5215,73 +5215,73 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.92</v>
+        <v>32.39</v>
       </c>
       <c r="C57" t="n">
-        <v>32.53</v>
+        <v>32.7</v>
       </c>
       <c r="D57" t="n">
-        <v>31.83</v>
+        <v>32.35</v>
       </c>
       <c r="E57" t="n">
-        <v>32.44</v>
+        <v>32.57</v>
       </c>
       <c r="F57" t="n">
-        <v>0.49</v>
+        <v>0.13</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0041</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
       <c r="I57" t="n">
-        <v>31.4</v>
+        <v>31.13</v>
       </c>
       <c r="J57" t="n">
-        <v>31.69</v>
+        <v>31.87</v>
       </c>
       <c r="K57" t="n">
-        <v>31.8</v>
+        <v>32.09</v>
       </c>
       <c r="L57" t="n">
-        <v>31.9</v>
+        <v>32.31</v>
       </c>
       <c r="M57" t="n">
-        <v>32.1</v>
+        <v>32.79</v>
       </c>
       <c r="N57" t="n">
-        <v>32.29</v>
+        <v>33.27</v>
       </c>
       <c r="O57" t="n">
-        <v>32.31</v>
+        <v>33.23</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5299,107 +5299,21 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="C58" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="D58" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="E58" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0022</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I58" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="J58" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="K58" t="n">
-        <v>32.09</v>
-      </c>
-      <c r="L58" t="n">
-        <v>32.31</v>
-      </c>
-      <c r="M58" t="n">
-        <v>32.79</v>
-      </c>
-      <c r="N58" t="n">
-        <v>33.27</v>
-      </c>
-      <c r="O58" t="n">
-        <v>33.23</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5315,6 +5315,88 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="C58" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="D58" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="E58" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I58" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="J58" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="K58" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="L58" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="M58" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="N58" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="O58" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -5325,22 +5325,22 @@
         <v>32.57</v>
       </c>
       <c r="C58" t="n">
-        <v>32.6</v>
+        <v>32.62</v>
       </c>
       <c r="D58" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="E58" t="n">
         <v>32.53</v>
       </c>
-      <c r="E58" t="n">
-        <v>32.57</v>
-      </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0</v>
+        <v>-0.0012</v>
       </c>
       <c r="H58" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="I58" t="n">
         <v>31.99</v>
@@ -5372,9 +5372,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,26 +659,26 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>29.71</v>
+        <v>29.94</v>
       </c>
       <c r="J2" t="n">
-        <v>30.04</v>
+        <v>30.12</v>
       </c>
       <c r="K2" t="n">
-        <v>30.22</v>
+        <v>30.28</v>
       </c>
       <c r="L2" t="n">
-        <v>30.41</v>
+        <v>30.44</v>
       </c>
       <c r="M2" t="n">
-        <v>30.66</v>
+        <v>30.61</v>
       </c>
       <c r="N2" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="O2" t="n">
         <v>30.92</v>
       </c>
-      <c r="O2" t="n">
-        <v>31.03</v>
-      </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
@@ -690,7 +690,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -772,7 +772,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -860,7 +860,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -942,7 +942,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1026,7 +1026,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1108,7 +1108,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1194,7 +1194,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1278,7 +1278,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1364,7 +1364,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1442,7 +1442,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1526,7 +1526,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1608,7 +1608,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1694,7 +1694,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1778,7 +1778,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1860,7 +1860,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1944,7 +1944,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2026,7 +2026,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2110,7 +2110,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2196,7 +2196,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2282,7 +2282,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2370,7 +2370,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2454,7 +2454,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2536,7 +2536,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2620,7 +2620,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2702,7 +2702,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2786,7 +2786,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2870,7 +2870,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2956,7 +2956,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3040,7 +3040,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3124,7 +3124,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3206,7 +3206,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3288,7 +3288,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3370,7 +3370,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3458,7 +3458,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3542,7 +3542,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3626,7 +3626,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3710,7 +3710,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3794,7 +3794,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3876,7 +3876,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3958,7 +3958,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4036,7 +4036,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4120,7 +4120,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4202,7 +4202,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4286,7 +4286,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4370,7 +4370,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4456,7 +4456,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4540,7 +4540,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4626,7 +4626,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4708,7 +4708,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4796,7 +4796,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4878,7 +4878,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4960,7 +4960,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5042,7 +5042,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5124,7 +5124,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5208,7 +5208,7 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5292,7 +5292,7 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5328,19 +5328,19 @@
         <v>32.62</v>
       </c>
       <c r="D58" t="n">
-        <v>32.49</v>
+        <v>32.34</v>
       </c>
       <c r="E58" t="n">
-        <v>32.53</v>
+        <v>32.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.04</v>
+        <v>-0.17</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0053</v>
       </c>
       <c r="H58" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="I58" t="n">
         <v>31.99</v>
@@ -5369,12 +5369,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5393,7 +5395,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>29.94</v>
+        <v>30.12</v>
       </c>
       <c r="J2" t="n">
-        <v>30.12</v>
+        <v>30.19</v>
       </c>
       <c r="K2" t="n">
-        <v>30.28</v>
+        <v>30.33</v>
       </c>
       <c r="L2" t="n">
-        <v>30.44</v>
+        <v>30.46</v>
       </c>
       <c r="M2" t="n">
-        <v>30.61</v>
+        <v>30.56</v>
       </c>
       <c r="N2" t="n">
-        <v>30.78</v>
+        <v>30.67</v>
       </c>
       <c r="O2" t="n">
-        <v>30.92</v>
+        <v>30.83</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -709,7 +709,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5328,19 +5328,19 @@
         <v>32.62</v>
       </c>
       <c r="D58" t="n">
-        <v>32.34</v>
+        <v>32.33</v>
       </c>
       <c r="E58" t="n">
-        <v>32.4</v>
+        <v>32.44</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.0039</v>
       </c>
       <c r="H58" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I58" t="n">
         <v>31.99</v>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>30.12</v>
+        <v>30.22</v>
       </c>
       <c r="J2" t="n">
-        <v>30.19</v>
+        <v>30.23</v>
       </c>
       <c r="K2" t="n">
-        <v>30.33</v>
+        <v>30.35</v>
       </c>
       <c r="L2" t="n">
-        <v>30.46</v>
+        <v>30.47</v>
       </c>
       <c r="M2" t="n">
-        <v>30.56</v>
+        <v>30.54</v>
       </c>
       <c r="N2" t="n">
-        <v>30.67</v>
+        <v>30.6</v>
       </c>
       <c r="O2" t="n">
-        <v>30.83</v>
+        <v>30.78</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -5325,22 +5327,22 @@
         <v>32.57</v>
       </c>
       <c r="C58" t="n">
-        <v>32.62</v>
+        <v>32.67</v>
       </c>
       <c r="D58" t="n">
-        <v>32.33</v>
+        <v>32.36</v>
       </c>
       <c r="E58" t="n">
-        <v>32.44</v>
+        <v>32.64</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0021</v>
       </c>
       <c r="H58" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="I58" t="n">
         <v>31.99</v>
@@ -5371,12 +5373,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5395,7 +5397,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/USDTWD_weekly.xlsx
+++ b/three_gate/analysis/USDTWD_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,31 +659,35 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>30.22</v>
+        <v>30.44</v>
       </c>
       <c r="J2" t="n">
-        <v>30.23</v>
+        <v>30.44</v>
       </c>
       <c r="K2" t="n">
-        <v>30.35</v>
+        <v>30.44</v>
       </c>
       <c r="L2" t="n">
-        <v>30.47</v>
+        <v>30.44</v>
       </c>
       <c r="M2" t="n">
-        <v>30.54</v>
+        <v>30.44</v>
       </c>
       <c r="N2" t="n">
-        <v>30.6</v>
+        <v>30.44</v>
       </c>
       <c r="O2" t="n">
-        <v>30.78</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>30.44</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -692,26 +696,32 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -794,7 +804,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -876,7 +886,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -960,7 +970,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1042,7 +1052,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1126,7 +1136,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1212,7 +1222,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1298,7 +1308,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1380,7 +1390,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1458,7 +1468,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1542,7 +1552,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1630,7 +1640,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1710,7 +1720,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1794,7 +1804,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1882,7 +1892,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1960,7 +1970,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2042,7 +2052,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2130,7 +2140,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2212,7 +2222,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2304,7 +2314,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2386,7 +2396,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2470,7 +2480,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2558,7 +2568,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2638,7 +2648,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2718,7 +2728,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2802,7 +2812,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2888,7 +2898,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2972,7 +2982,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3056,7 +3066,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3140,7 +3150,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3224,7 +3234,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3304,7 +3314,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3390,7 +3400,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3476,7 +3486,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3558,7 +3568,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3644,7 +3654,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3728,7 +3738,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3810,7 +3820,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3896,7 +3906,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3974,7 +3984,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4058,7 +4068,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4140,7 +4150,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4218,7 +4228,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4304,7 +4314,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4388,7 +4398,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4472,7 +4482,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4556,7 +4566,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4642,7 +4652,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4726,7 +4736,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4812,7 +4822,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4896,7 +4906,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4976,7 +4986,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5062,7 +5072,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5142,7 +5152,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5230,7 +5240,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5310,7 +5320,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5327,22 +5337,22 @@
         <v>32.57</v>
       </c>
       <c r="C58" t="n">
-        <v>32.67</v>
+        <v>32.7</v>
       </c>
       <c r="D58" t="n">
         <v>32.36</v>
       </c>
       <c r="E58" t="n">
-        <v>32.64</v>
+        <v>32.6</v>
       </c>
       <c r="F58" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="I58" t="n">
         <v>31.99</v>
@@ -5390,7 +5400,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
